--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -26501,10 +26501,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>117615181</v>
+        <v>117614921</v>
       </c>
       <c r="B207" t="n">
-        <v>78480</v>
+        <v>90499</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -26517,21 +26517,21 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -26541,13 +26541,13 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>520218</v>
+        <v>520237</v>
       </c>
       <c r="R207" t="n">
-        <v>6933644</v>
+        <v>6933645</v>
       </c>
       <c r="S207" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -26603,10 +26603,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>117614921</v>
+        <v>117615181</v>
       </c>
       <c r="B208" t="n">
-        <v>90499</v>
+        <v>78480</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -26619,21 +26619,21 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -26643,13 +26643,13 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>520237</v>
+        <v>520218</v>
       </c>
       <c r="R208" t="n">
-        <v>6933645</v>
+        <v>6933644</v>
       </c>
       <c r="S208" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -27215,10 +27215,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>117617321</v>
+        <v>117624124</v>
       </c>
       <c r="B214" t="n">
-        <v>104929</v>
+        <v>97836</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -27227,41 +27227,41 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>520138</v>
+        <v>520234</v>
       </c>
       <c r="R214" t="n">
-        <v>6933887</v>
+        <v>6933656</v>
       </c>
       <c r="S214" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -27317,10 +27317,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>117624124</v>
+        <v>117617321</v>
       </c>
       <c r="B215" t="n">
-        <v>97836</v>
+        <v>104929</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -27329,41 +27329,41 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>520234</v>
+        <v>520138</v>
       </c>
       <c r="R215" t="n">
-        <v>6933656</v>
+        <v>6933887</v>
       </c>
       <c r="S215" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -29576,10 +29576,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>117620214</v>
+        <v>117619317</v>
       </c>
       <c r="B237" t="n">
-        <v>78216</v>
+        <v>79561</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -29592,21 +29592,21 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
@@ -29616,13 +29616,13 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>519974</v>
+        <v>519864</v>
       </c>
       <c r="R237" t="n">
-        <v>6934018</v>
+        <v>6933761</v>
       </c>
       <c r="S237" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="T237" t="inlineStr">
         <is>
@@ -29678,10 +29678,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>117619600</v>
+        <v>117624141</v>
       </c>
       <c r="B238" t="n">
-        <v>78480</v>
+        <v>79561</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -29694,37 +29694,37 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>519868</v>
+        <v>520775</v>
       </c>
       <c r="R238" t="n">
-        <v>6933813</v>
+        <v>6933753</v>
       </c>
       <c r="S238" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T238" t="inlineStr">
         <is>
@@ -29780,10 +29780,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>117619317</v>
+        <v>117620214</v>
       </c>
       <c r="B239" t="n">
-        <v>79561</v>
+        <v>78216</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -29796,21 +29796,21 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -29820,13 +29820,13 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>519864</v>
+        <v>519974</v>
       </c>
       <c r="R239" t="n">
-        <v>6933761</v>
+        <v>6934018</v>
       </c>
       <c r="S239" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="T239" t="inlineStr">
         <is>
@@ -29882,10 +29882,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>117624141</v>
+        <v>117619600</v>
       </c>
       <c r="B240" t="n">
-        <v>79561</v>
+        <v>78480</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -29898,37 +29898,37 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>520775</v>
+        <v>519868</v>
       </c>
       <c r="R240" t="n">
-        <v>6933753</v>
+        <v>6933813</v>
       </c>
       <c r="S240" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T240" t="inlineStr">
         <is>
@@ -30193,10 +30193,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>117618861</v>
+        <v>117615933</v>
       </c>
       <c r="B243" t="n">
-        <v>79597</v>
+        <v>78216</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -30205,25 +30205,25 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>6464</v>
+        <v>6446</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -30233,13 +30233,13 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>520011</v>
+        <v>520184</v>
       </c>
       <c r="R243" t="n">
-        <v>6933775</v>
+        <v>6933872</v>
       </c>
       <c r="S243" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -30295,10 +30295,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>117615776</v>
+        <v>117624148</v>
       </c>
       <c r="B244" t="n">
-        <v>79098</v>
+        <v>78216</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -30311,37 +30311,37 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>520220</v>
+        <v>520400</v>
       </c>
       <c r="R244" t="n">
-        <v>6933822</v>
+        <v>6933760</v>
       </c>
       <c r="S244" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T244" t="inlineStr">
         <is>
@@ -30397,10 +30397,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>117620395</v>
+        <v>117618861</v>
       </c>
       <c r="B245" t="n">
-        <v>90499</v>
+        <v>79597</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -30409,25 +30409,25 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -30437,13 +30437,13 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>520058</v>
+        <v>520011</v>
       </c>
       <c r="R245" t="n">
-        <v>6934065</v>
+        <v>6933775</v>
       </c>
       <c r="S245" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -30499,10 +30499,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>117615933</v>
+        <v>117615776</v>
       </c>
       <c r="B246" t="n">
-        <v>78216</v>
+        <v>79098</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -30515,21 +30515,21 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -30539,13 +30539,13 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>520184</v>
+        <v>520220</v>
       </c>
       <c r="R246" t="n">
-        <v>6933872</v>
+        <v>6933822</v>
       </c>
       <c r="S246" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T246" t="inlineStr">
         <is>
@@ -30601,10 +30601,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>117624148</v>
+        <v>117620395</v>
       </c>
       <c r="B247" t="n">
-        <v>78216</v>
+        <v>90499</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -30617,37 +30617,37 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>520400</v>
+        <v>520058</v>
       </c>
       <c r="R247" t="n">
-        <v>6933760</v>
+        <v>6934065</v>
       </c>
       <c r="S247" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T247" t="inlineStr">
         <is>
@@ -31417,10 +31417,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>117624149</v>
+        <v>117617145</v>
       </c>
       <c r="B255" t="n">
-        <v>97836</v>
+        <v>56499</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -31429,41 +31429,41 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
       <c r="P255" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>520061</v>
+        <v>520159</v>
       </c>
       <c r="R255" t="n">
-        <v>6934068</v>
+        <v>6933938</v>
       </c>
       <c r="S255" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T255" t="inlineStr">
         <is>
@@ -31493,6 +31493,11 @@
       <c r="AA255" t="inlineStr">
         <is>
           <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AC255" t="inlineStr">
+        <is>
+          <t>Färsk spillning</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -31519,10 +31524,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>117617145</v>
+        <v>117615486</v>
       </c>
       <c r="B256" t="n">
-        <v>56499</v>
+        <v>97836</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -31531,25 +31536,25 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -31559,10 +31564,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>520159</v>
+        <v>520113</v>
       </c>
       <c r="R256" t="n">
-        <v>6933938</v>
+        <v>6933665</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -31595,11 +31600,6 @@
       <c r="AA256" t="inlineStr">
         <is>
           <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AC256" t="inlineStr">
-        <is>
-          <t>Färsk spillning</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -31626,7 +31626,7 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>117615486</v>
+        <v>117624149</v>
       </c>
       <c r="B257" t="n">
         <v>97836</v>
@@ -31662,17 +31662,17 @@
       <c r="I257" t="inlineStr"/>
       <c r="P257" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>520113</v>
+        <v>520061</v>
       </c>
       <c r="R257" t="n">
-        <v>6933665</v>
+        <v>6934068</v>
       </c>
       <c r="S257" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T257" t="inlineStr">
         <is>
@@ -33366,10 +33366,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>117624140</v>
+        <v>117624155</v>
       </c>
       <c r="B274" t="n">
-        <v>79561</v>
+        <v>78480</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -33382,21 +33382,21 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -33406,10 +33406,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>520519</v>
+        <v>520423</v>
       </c>
       <c r="R274" t="n">
-        <v>6933772</v>
+        <v>6933800</v>
       </c>
       <c r="S274" t="n">
         <v>25</v>
@@ -33468,7 +33468,7 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>117619522</v>
+        <v>117624140</v>
       </c>
       <c r="B275" t="n">
         <v>79561</v>
@@ -33504,17 +33504,17 @@
       <c r="I275" t="inlineStr"/>
       <c r="P275" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>519865</v>
+        <v>520519</v>
       </c>
       <c r="R275" t="n">
-        <v>6933800</v>
+        <v>6933772</v>
       </c>
       <c r="S275" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T275" t="inlineStr">
         <is>
@@ -33570,10 +33570,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>117624155</v>
+        <v>117619522</v>
       </c>
       <c r="B276" t="n">
-        <v>78480</v>
+        <v>79561</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -33586,37 +33586,37 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
       <c r="P276" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>520423</v>
+        <v>519865</v>
       </c>
       <c r="R276" t="n">
         <v>6933800</v>
       </c>
       <c r="S276" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T276" t="inlineStr">
         <is>
@@ -34396,7 +34396,7 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>117624136</v>
+        <v>117624138</v>
       </c>
       <c r="B284" t="n">
         <v>79561</v>
@@ -34436,10 +34436,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>520420</v>
+        <v>520508</v>
       </c>
       <c r="R284" t="n">
-        <v>6933788</v>
+        <v>6933774</v>
       </c>
       <c r="S284" t="n">
         <v>25</v>
@@ -34472,11 +34472,6 @@
       <c r="AA284" t="inlineStr">
         <is>
           <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AC284" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD284" t="b">
@@ -34503,7 +34498,7 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>117624138</v>
+        <v>117624136</v>
       </c>
       <c r="B285" t="n">
         <v>79561</v>
@@ -34543,10 +34538,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>520508</v>
+        <v>520420</v>
       </c>
       <c r="R285" t="n">
-        <v>6933774</v>
+        <v>6933788</v>
       </c>
       <c r="S285" t="n">
         <v>25</v>
@@ -34579,6 +34574,11 @@
       <c r="AA285" t="inlineStr">
         <is>
           <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AC285" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD285" t="b">

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -26399,10 +26399,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>117619662</v>
+        <v>117615007</v>
       </c>
       <c r="B206" t="n">
-        <v>79561</v>
+        <v>97836</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -26411,25 +26411,25 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -26439,13 +26439,13 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>519882</v>
+        <v>520238</v>
       </c>
       <c r="R206" t="n">
-        <v>6933843</v>
+        <v>6933656</v>
       </c>
       <c r="S206" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -26501,10 +26501,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>117614921</v>
+        <v>117624124</v>
       </c>
       <c r="B207" t="n">
-        <v>90499</v>
+        <v>97836</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -26513,41 +26513,41 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>520237</v>
+        <v>520234</v>
       </c>
       <c r="R207" t="n">
-        <v>6933645</v>
+        <v>6933656</v>
       </c>
       <c r="S207" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -26603,10 +26603,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>117615181</v>
+        <v>117614921</v>
       </c>
       <c r="B208" t="n">
-        <v>78480</v>
+        <v>90499</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -26619,21 +26619,21 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -26643,13 +26643,13 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>520218</v>
+        <v>520237</v>
       </c>
       <c r="R208" t="n">
-        <v>6933644</v>
+        <v>6933645</v>
       </c>
       <c r="S208" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -26705,10 +26705,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>117618578</v>
+        <v>117620347</v>
       </c>
       <c r="B209" t="n">
-        <v>79561</v>
+        <v>90782</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -26721,21 +26721,21 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -26745,13 +26745,13 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>520076</v>
+        <v>520060</v>
       </c>
       <c r="R209" t="n">
-        <v>6933805</v>
+        <v>6934064</v>
       </c>
       <c r="S209" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -26807,10 +26807,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>117615266</v>
+        <v>117624133</v>
       </c>
       <c r="B210" t="n">
-        <v>79561</v>
+        <v>90519</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -26823,37 +26823,37 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>520175</v>
+        <v>520382</v>
       </c>
       <c r="R210" t="n">
-        <v>6933657</v>
+        <v>6933719</v>
       </c>
       <c r="S210" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -26909,10 +26909,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>117624128</v>
+        <v>117619317</v>
       </c>
       <c r="B211" t="n">
-        <v>90499</v>
+        <v>79561</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -26925,37 +26925,37 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>520240</v>
+        <v>519864</v>
       </c>
       <c r="R211" t="n">
-        <v>6933649</v>
+        <v>6933761</v>
       </c>
       <c r="S211" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -27011,10 +27011,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>117624125</v>
+        <v>117624136</v>
       </c>
       <c r="B212" t="n">
-        <v>95384</v>
+        <v>79561</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -27027,21 +27027,21 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -27051,10 +27051,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>520234</v>
+        <v>520420</v>
       </c>
       <c r="R212" t="n">
-        <v>6933656</v>
+        <v>6933788</v>
       </c>
       <c r="S212" t="n">
         <v>25</v>
@@ -27087,6 +27087,11 @@
       <c r="AA212" t="inlineStr">
         <is>
           <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -27113,10 +27118,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>117620347</v>
+        <v>117614799</v>
       </c>
       <c r="B213" t="n">
-        <v>90782</v>
+        <v>57440</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -27129,37 +27134,42 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P213" t="inlineStr">
         <is>
           <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>520060</v>
+        <v>520250</v>
       </c>
       <c r="R213" t="n">
-        <v>6934064</v>
+        <v>6933680</v>
       </c>
       <c r="S213" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -27215,10 +27225,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>117624124</v>
+        <v>117618946</v>
       </c>
       <c r="B214" t="n">
-        <v>97836</v>
+        <v>79561</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -27227,41 +27237,41 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>520234</v>
+        <v>519986</v>
       </c>
       <c r="R214" t="n">
-        <v>6933656</v>
+        <v>6933778</v>
       </c>
       <c r="S214" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -27317,10 +27327,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>117617321</v>
+        <v>117619662</v>
       </c>
       <c r="B215" t="n">
-        <v>104929</v>
+        <v>79561</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -27329,25 +27339,25 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>221144</v>
+        <v>6458</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -27357,13 +27367,13 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>520138</v>
+        <v>519882</v>
       </c>
       <c r="R215" t="n">
-        <v>6933887</v>
+        <v>6933843</v>
       </c>
       <c r="S215" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -27419,10 +27429,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>117620495</v>
+        <v>117619423</v>
       </c>
       <c r="B216" t="n">
-        <v>97836</v>
+        <v>79561</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -27431,25 +27441,25 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -27459,13 +27469,13 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>520061</v>
+        <v>519861</v>
       </c>
       <c r="R216" t="n">
-        <v>6934070</v>
+        <v>6933798</v>
       </c>
       <c r="S216" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -27521,7 +27531,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>117618841</v>
+        <v>117615300</v>
       </c>
       <c r="B217" t="n">
         <v>79561</v>
@@ -27561,13 +27571,13 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>520006</v>
+        <v>520171</v>
       </c>
       <c r="R217" t="n">
-        <v>6933772</v>
+        <v>6933646</v>
       </c>
       <c r="S217" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -27623,10 +27633,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>117614566</v>
+        <v>117624138</v>
       </c>
       <c r="B218" t="n">
-        <v>90519</v>
+        <v>79561</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -27639,37 +27649,37 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>520293</v>
+        <v>520508</v>
       </c>
       <c r="R218" t="n">
-        <v>6933723</v>
+        <v>6933774</v>
       </c>
       <c r="S218" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -27699,11 +27709,6 @@
       <c r="AA218" t="inlineStr">
         <is>
           <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AC218" t="inlineStr">
-        <is>
-          <t>På gammal tall med brandljud</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -27730,10 +27735,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>117624156</v>
+        <v>117620495</v>
       </c>
       <c r="B219" t="n">
-        <v>78480</v>
+        <v>97836</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -27742,41 +27747,41 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>520571</v>
+        <v>520061</v>
       </c>
       <c r="R219" t="n">
-        <v>6933768</v>
+        <v>6934070</v>
       </c>
       <c r="S219" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -27832,10 +27837,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>117619628</v>
+        <v>117624131</v>
       </c>
       <c r="B220" t="n">
-        <v>78480</v>
+        <v>57440</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -27848,37 +27853,37 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>519878</v>
+        <v>520392</v>
       </c>
       <c r="R220" t="n">
-        <v>6933831</v>
+        <v>6933757</v>
       </c>
       <c r="S220" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -27908,6 +27913,11 @@
       <c r="AA220" t="inlineStr">
         <is>
           <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AC220" t="inlineStr">
+        <is>
+          <t>Varnande</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -27934,10 +27944,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>117619989</v>
+        <v>117620594</v>
       </c>
       <c r="B221" t="n">
-        <v>79561</v>
+        <v>95384</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -27950,21 +27960,21 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -27974,10 +27984,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>519953</v>
+        <v>520083</v>
       </c>
       <c r="R221" t="n">
-        <v>6933937</v>
+        <v>6934090</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -28036,10 +28046,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>117624129</v>
+        <v>117616097</v>
       </c>
       <c r="B222" t="n">
-        <v>90499</v>
+        <v>91288</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -28052,37 +28062,37 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>1202</v>
+        <v>2014</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>520240</v>
+        <v>520192</v>
       </c>
       <c r="R222" t="n">
-        <v>6933655</v>
+        <v>6933876</v>
       </c>
       <c r="S222" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -28138,10 +28148,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>117624132</v>
+        <v>117615776</v>
       </c>
       <c r="B223" t="n">
-        <v>90519</v>
+        <v>79098</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -28154,37 +28164,37 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>520270</v>
+        <v>520220</v>
       </c>
       <c r="R223" t="n">
-        <v>6933710</v>
+        <v>6933822</v>
       </c>
       <c r="S223" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>
@@ -28214,11 +28224,6 @@
       <c r="AA223" t="inlineStr">
         <is>
           <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AC223" t="inlineStr">
-        <is>
-          <t>På tall med brandljud</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -28245,10 +28250,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>117619582</v>
+        <v>117620214</v>
       </c>
       <c r="B224" t="n">
-        <v>97857</v>
+        <v>78216</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -28257,25 +28262,25 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>221952</v>
+        <v>6446</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -28285,13 +28290,13 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>519870</v>
+        <v>519974</v>
       </c>
       <c r="R224" t="n">
-        <v>6933797</v>
+        <v>6934018</v>
       </c>
       <c r="S224" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="T224" t="inlineStr">
         <is>
@@ -28347,10 +28352,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>117616157</v>
+        <v>117624156</v>
       </c>
       <c r="B225" t="n">
-        <v>56499</v>
+        <v>78480</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -28359,41 +28364,41 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>520184</v>
+        <v>520571</v>
       </c>
       <c r="R225" t="n">
-        <v>6933878</v>
+        <v>6933768</v>
       </c>
       <c r="S225" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T225" t="inlineStr">
         <is>
@@ -28449,10 +28454,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>117624154</v>
+        <v>117619582</v>
       </c>
       <c r="B226" t="n">
-        <v>97836</v>
+        <v>97857</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -28461,41 +28466,41 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>520817</v>
+        <v>519870</v>
       </c>
       <c r="R226" t="n">
-        <v>6933807</v>
+        <v>6933797</v>
       </c>
       <c r="S226" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T226" t="inlineStr">
         <is>
@@ -28551,10 +28556,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>117624144</v>
+        <v>117614215</v>
       </c>
       <c r="B227" t="n">
-        <v>80437</v>
+        <v>57440</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -28567,34 +28572,39 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>1049</v>
+        <v>103021</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>520777</v>
+        <v>520399</v>
       </c>
       <c r="R227" t="n">
-        <v>6933766</v>
+        <v>6933756</v>
       </c>
       <c r="S227" t="n">
         <v>25</v>
@@ -28653,10 +28663,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>117614361</v>
+        <v>117618968</v>
       </c>
       <c r="B228" t="n">
-        <v>90519</v>
+        <v>79561</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -28669,21 +28679,21 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -28693,13 +28703,13 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>520373</v>
+        <v>519980</v>
       </c>
       <c r="R228" t="n">
-        <v>6933724</v>
+        <v>6933791</v>
       </c>
       <c r="S228" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T228" t="inlineStr">
         <is>
@@ -28755,10 +28765,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>117624133</v>
+        <v>117618841</v>
       </c>
       <c r="B229" t="n">
-        <v>90519</v>
+        <v>79561</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -28771,37 +28781,37 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>520382</v>
+        <v>520006</v>
       </c>
       <c r="R229" t="n">
-        <v>6933719</v>
+        <v>6933772</v>
       </c>
       <c r="S229" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T229" t="inlineStr">
         <is>
@@ -28857,10 +28867,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>117619968</v>
+        <v>117618861</v>
       </c>
       <c r="B230" t="n">
-        <v>78480</v>
+        <v>79597</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -28869,25 +28879,25 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -28897,13 +28907,13 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>519908</v>
+        <v>520011</v>
       </c>
       <c r="R230" t="n">
-        <v>6933941</v>
+        <v>6933775</v>
       </c>
       <c r="S230" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T230" t="inlineStr">
         <is>
@@ -28933,11 +28943,6 @@
       <c r="AA230" t="inlineStr">
         <is>
           <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AC230" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -28964,10 +28969,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>117616001</v>
+        <v>117624144</v>
       </c>
       <c r="B231" t="n">
-        <v>79561</v>
+        <v>80437</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -28980,37 +28985,37 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>6458</v>
+        <v>1049</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>520195</v>
+        <v>520777</v>
       </c>
       <c r="R231" t="n">
-        <v>6933879</v>
+        <v>6933766</v>
       </c>
       <c r="S231" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T231" t="inlineStr">
         <is>
@@ -29066,10 +29071,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>117619372</v>
+        <v>117615611</v>
       </c>
       <c r="B232" t="n">
-        <v>79590</v>
+        <v>79561</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -29078,25 +29083,25 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -29106,10 +29111,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>519861</v>
+        <v>520102</v>
       </c>
       <c r="R232" t="n">
-        <v>6933763</v>
+        <v>6933712</v>
       </c>
       <c r="S232" t="n">
         <v>20</v>
@@ -29168,10 +29173,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>117619862</v>
+        <v>117616751</v>
       </c>
       <c r="B233" t="n">
-        <v>78480</v>
+        <v>97870</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -29180,25 +29185,25 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>6425</v>
+        <v>219874</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -29208,13 +29213,13 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>519899</v>
+        <v>520201</v>
       </c>
       <c r="R233" t="n">
-        <v>6933938</v>
+        <v>6933913</v>
       </c>
       <c r="S233" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -29270,10 +29275,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>117617034</v>
+        <v>117619862</v>
       </c>
       <c r="B234" t="n">
-        <v>79561</v>
+        <v>78480</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -29286,21 +29291,21 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -29310,13 +29315,13 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>520184</v>
+        <v>519899</v>
       </c>
       <c r="R234" t="n">
-        <v>6933959</v>
+        <v>6933938</v>
       </c>
       <c r="S234" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T234" t="inlineStr">
         <is>
@@ -29372,10 +29377,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>117620029</v>
+        <v>117619202</v>
       </c>
       <c r="B235" t="n">
-        <v>79561</v>
+        <v>104929</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -29384,25 +29389,25 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>6458</v>
+        <v>221144</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -29412,10 +29417,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>519945</v>
+        <v>519909</v>
       </c>
       <c r="R235" t="n">
-        <v>6933946</v>
+        <v>6933766</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -29474,10 +29479,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>117617526</v>
+        <v>117616723</v>
       </c>
       <c r="B236" t="n">
-        <v>78216</v>
+        <v>79561</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -29490,21 +29495,21 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -29514,10 +29519,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>520120</v>
+        <v>520201</v>
       </c>
       <c r="R236" t="n">
-        <v>6933834</v>
+        <v>6933904</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -29576,10 +29581,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>117619317</v>
+        <v>117617145</v>
       </c>
       <c r="B237" t="n">
-        <v>79561</v>
+        <v>56499</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -29588,25 +29593,25 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
@@ -29616,13 +29621,13 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>519864</v>
+        <v>520159</v>
       </c>
       <c r="R237" t="n">
-        <v>6933761</v>
+        <v>6933938</v>
       </c>
       <c r="S237" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T237" t="inlineStr">
         <is>
@@ -29652,6 +29657,11 @@
       <c r="AA237" t="inlineStr">
         <is>
           <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AC237" t="inlineStr">
+        <is>
+          <t>Färsk spillning</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -29678,10 +29688,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>117624141</v>
+        <v>117624158</v>
       </c>
       <c r="B238" t="n">
-        <v>79561</v>
+        <v>78480</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -29694,21 +29704,21 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -29718,10 +29728,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>520775</v>
+        <v>520835</v>
       </c>
       <c r="R238" t="n">
-        <v>6933753</v>
+        <v>6933821</v>
       </c>
       <c r="S238" t="n">
         <v>25</v>
@@ -29780,10 +29790,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>117620214</v>
+        <v>117624151</v>
       </c>
       <c r="B239" t="n">
-        <v>78216</v>
+        <v>97836</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -29792,41 +29802,41 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>519974</v>
+        <v>520138</v>
       </c>
       <c r="R239" t="n">
-        <v>6934018</v>
+        <v>6933928</v>
       </c>
       <c r="S239" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="T239" t="inlineStr">
         <is>
@@ -29882,10 +29892,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>117619600</v>
+        <v>117615266</v>
       </c>
       <c r="B240" t="n">
-        <v>78480</v>
+        <v>79561</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -29898,21 +29908,21 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -29922,13 +29932,13 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>519868</v>
+        <v>520175</v>
       </c>
       <c r="R240" t="n">
-        <v>6933813</v>
+        <v>6933657</v>
       </c>
       <c r="S240" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T240" t="inlineStr">
         <is>
@@ -29984,10 +29994,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>117614799</v>
+        <v>117624149</v>
       </c>
       <c r="B241" t="n">
-        <v>57440</v>
+        <v>97836</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -29996,43 +30006,38 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
-      <c r="M241" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P241" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>520250</v>
+        <v>520061</v>
       </c>
       <c r="R241" t="n">
-        <v>6933680</v>
+        <v>6934068</v>
       </c>
       <c r="S241" t="n">
         <v>25</v>
@@ -30091,10 +30096,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>117619891</v>
+        <v>117619968</v>
       </c>
       <c r="B242" t="n">
-        <v>78217</v>
+        <v>78480</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -30107,21 +30112,21 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -30131,10 +30136,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>519895</v>
+        <v>519908</v>
       </c>
       <c r="R242" t="n">
-        <v>6933942</v>
+        <v>6933941</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -30167,6 +30172,11 @@
       <c r="AA242" t="inlineStr">
         <is>
           <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AC242" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -30193,10 +30203,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>117615933</v>
+        <v>117619522</v>
       </c>
       <c r="B243" t="n">
-        <v>78216</v>
+        <v>79561</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -30209,21 +30219,21 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -30233,13 +30243,13 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>520184</v>
+        <v>519865</v>
       </c>
       <c r="R243" t="n">
-        <v>6933872</v>
+        <v>6933800</v>
       </c>
       <c r="S243" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -30295,10 +30305,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>117624148</v>
+        <v>117624140</v>
       </c>
       <c r="B244" t="n">
-        <v>78216</v>
+        <v>79561</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -30311,21 +30321,21 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -30335,10 +30345,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>520400</v>
+        <v>520519</v>
       </c>
       <c r="R244" t="n">
-        <v>6933760</v>
+        <v>6933772</v>
       </c>
       <c r="S244" t="n">
         <v>25</v>
@@ -30397,10 +30407,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>117618861</v>
+        <v>117617202</v>
       </c>
       <c r="B245" t="n">
-        <v>79597</v>
+        <v>97836</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -30409,25 +30419,25 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -30437,13 +30447,13 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>520011</v>
+        <v>520144</v>
       </c>
       <c r="R245" t="n">
-        <v>6933775</v>
+        <v>6933928</v>
       </c>
       <c r="S245" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -30499,10 +30509,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>117615776</v>
+        <v>117619891</v>
       </c>
       <c r="B246" t="n">
-        <v>79098</v>
+        <v>78217</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -30515,21 +30525,21 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -30539,10 +30549,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>520220</v>
+        <v>519895</v>
       </c>
       <c r="R246" t="n">
-        <v>6933822</v>
+        <v>6933942</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -30601,10 +30611,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>117620395</v>
+        <v>117615933</v>
       </c>
       <c r="B247" t="n">
-        <v>90499</v>
+        <v>78216</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -30617,21 +30627,21 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -30641,13 +30651,13 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>520058</v>
+        <v>520184</v>
       </c>
       <c r="R247" t="n">
-        <v>6934065</v>
+        <v>6933872</v>
       </c>
       <c r="S247" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T247" t="inlineStr">
         <is>
@@ -30703,7 +30713,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>117618946</v>
+        <v>117615235</v>
       </c>
       <c r="B248" t="n">
         <v>79561</v>
@@ -30743,13 +30753,13 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>519986</v>
+        <v>520172</v>
       </c>
       <c r="R248" t="n">
-        <v>6933778</v>
+        <v>6933674</v>
       </c>
       <c r="S248" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T248" t="inlineStr">
         <is>
@@ -30805,7 +30815,7 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>117617897</v>
+        <v>117624141</v>
       </c>
       <c r="B249" t="n">
         <v>79561</v>
@@ -30841,17 +30851,17 @@
       <c r="I249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>520122</v>
+        <v>520775</v>
       </c>
       <c r="R249" t="n">
-        <v>6933863</v>
+        <v>6933753</v>
       </c>
       <c r="S249" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T249" t="inlineStr">
         <is>
@@ -30907,10 +30917,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>117616723</v>
+        <v>117616157</v>
       </c>
       <c r="B250" t="n">
-        <v>79561</v>
+        <v>56499</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -30919,25 +30929,25 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -30947,13 +30957,13 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>520201</v>
+        <v>520184</v>
       </c>
       <c r="R250" t="n">
-        <v>6933904</v>
+        <v>6933878</v>
       </c>
       <c r="S250" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T250" t="inlineStr">
         <is>
@@ -31009,10 +31019,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>117614268</v>
+        <v>117615974</v>
       </c>
       <c r="B251" t="n">
-        <v>78216</v>
+        <v>56499</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -31021,25 +31031,25 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -31049,13 +31059,13 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>520362</v>
+        <v>520185</v>
       </c>
       <c r="R251" t="n">
-        <v>6933716</v>
+        <v>6933863</v>
       </c>
       <c r="S251" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T251" t="inlineStr">
         <is>
@@ -31085,6 +31095,11 @@
       <c r="AA251" t="inlineStr">
         <is>
           <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AC251" t="inlineStr">
+        <is>
+          <t>Färsk spillning</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -31111,7 +31126,7 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>117620580</v>
+        <v>117617321</v>
       </c>
       <c r="B252" t="n">
         <v>104929</v>
@@ -31151,13 +31166,13 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>520068</v>
+        <v>520138</v>
       </c>
       <c r="R252" t="n">
-        <v>6934077</v>
+        <v>6933887</v>
       </c>
       <c r="S252" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T252" t="inlineStr">
         <is>
@@ -31213,10 +31228,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>117624152</v>
+        <v>117617526</v>
       </c>
       <c r="B253" t="n">
-        <v>97836</v>
+        <v>78216</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -31225,41 +31240,41 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>520185</v>
+        <v>520120</v>
       </c>
       <c r="R253" t="n">
-        <v>6933876</v>
+        <v>6933834</v>
       </c>
       <c r="S253" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T253" t="inlineStr">
         <is>
@@ -31417,10 +31432,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>117617145</v>
+        <v>117618638</v>
       </c>
       <c r="B255" t="n">
-        <v>56499</v>
+        <v>97836</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -31429,25 +31444,25 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -31457,10 +31472,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>520159</v>
+        <v>520072</v>
       </c>
       <c r="R255" t="n">
-        <v>6933938</v>
+        <v>6933810</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -31493,11 +31508,6 @@
       <c r="AA255" t="inlineStr">
         <is>
           <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AC255" t="inlineStr">
-        <is>
-          <t>Färsk spillning</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -31524,10 +31534,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>117615486</v>
+        <v>117624126</v>
       </c>
       <c r="B256" t="n">
-        <v>97836</v>
+        <v>90499</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -31536,41 +31546,41 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
       <c r="P256" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>520113</v>
+        <v>520058</v>
       </c>
       <c r="R256" t="n">
-        <v>6933665</v>
+        <v>6934066</v>
       </c>
       <c r="S256" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T256" t="inlineStr">
         <is>
@@ -31626,10 +31636,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>117624149</v>
+        <v>117615181</v>
       </c>
       <c r="B257" t="n">
-        <v>97836</v>
+        <v>78480</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -31638,41 +31648,41 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
       <c r="P257" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>520061</v>
+        <v>520218</v>
       </c>
       <c r="R257" t="n">
-        <v>6934068</v>
+        <v>6933644</v>
       </c>
       <c r="S257" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T257" t="inlineStr">
         <is>
@@ -31728,10 +31738,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>117619423</v>
+        <v>117619600</v>
       </c>
       <c r="B258" t="n">
-        <v>79561</v>
+        <v>78480</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -31744,21 +31754,21 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -31768,13 +31778,13 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>519861</v>
+        <v>519868</v>
       </c>
       <c r="R258" t="n">
-        <v>6933798</v>
+        <v>6933813</v>
       </c>
       <c r="S258" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T258" t="inlineStr">
         <is>
@@ -31830,10 +31840,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>117624158</v>
+        <v>117624148</v>
       </c>
       <c r="B259" t="n">
-        <v>78480</v>
+        <v>78216</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -31846,21 +31856,21 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
@@ -31870,10 +31880,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>520835</v>
+        <v>520400</v>
       </c>
       <c r="R259" t="n">
-        <v>6933821</v>
+        <v>6933760</v>
       </c>
       <c r="S259" t="n">
         <v>25</v>
@@ -31932,10 +31942,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>117624159</v>
+        <v>117624125</v>
       </c>
       <c r="B260" t="n">
-        <v>90907</v>
+        <v>95384</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -31944,25 +31954,25 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>5321</v>
+        <v>53</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
@@ -31972,10 +31982,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>520522</v>
+        <v>520234</v>
       </c>
       <c r="R260" t="n">
-        <v>6933775</v>
+        <v>6933656</v>
       </c>
       <c r="S260" t="n">
         <v>25</v>
@@ -32016,7 +32026,6 @@
       <c r="AE260" t="b">
         <v>0</v>
       </c>
-      <c r="AF260" t="inlineStr"/>
       <c r="AG260" t="b">
         <v>0</v>
       </c>
@@ -32035,10 +32044,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>117619202</v>
+        <v>117619989</v>
       </c>
       <c r="B261" t="n">
-        <v>104929</v>
+        <v>79561</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -32047,25 +32056,25 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>221144</v>
+        <v>6458</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -32075,10 +32084,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>519909</v>
+        <v>519953</v>
       </c>
       <c r="R261" t="n">
-        <v>6933766</v>
+        <v>6933937</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -32137,7 +32146,7 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>117617202</v>
+        <v>117624152</v>
       </c>
       <c r="B262" t="n">
         <v>97836</v>
@@ -32173,17 +32182,17 @@
       <c r="I262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>520144</v>
+        <v>520185</v>
       </c>
       <c r="R262" t="n">
-        <v>6933928</v>
+        <v>6933876</v>
       </c>
       <c r="S262" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T262" t="inlineStr">
         <is>
@@ -32239,7 +32248,7 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>117624150</v>
+        <v>117624153</v>
       </c>
       <c r="B263" t="n">
         <v>97836</v>
@@ -32279,10 +32288,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>520069</v>
+        <v>520113</v>
       </c>
       <c r="R263" t="n">
-        <v>6933806</v>
+        <v>6933668</v>
       </c>
       <c r="S263" t="n">
         <v>25</v>
@@ -32341,10 +32350,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>117618235</v>
+        <v>117619504</v>
       </c>
       <c r="B264" t="n">
-        <v>96791</v>
+        <v>79562</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -32353,25 +32362,25 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>221945</v>
+        <v>2081</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
@@ -32381,13 +32390,13 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>520117</v>
+        <v>519854</v>
       </c>
       <c r="R264" t="n">
-        <v>6933840</v>
+        <v>6933806</v>
       </c>
       <c r="S264" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T264" t="inlineStr">
         <is>
@@ -32443,10 +32452,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>117615235</v>
+        <v>117614361</v>
       </c>
       <c r="B265" t="n">
-        <v>79561</v>
+        <v>90519</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -32459,21 +32468,21 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
@@ -32483,13 +32492,13 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>520172</v>
+        <v>520373</v>
       </c>
       <c r="R265" t="n">
-        <v>6933674</v>
+        <v>6933724</v>
       </c>
       <c r="S265" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T265" t="inlineStr">
         <is>
@@ -32545,10 +32554,10 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>117624126</v>
+        <v>117624132</v>
       </c>
       <c r="B266" t="n">
-        <v>90499</v>
+        <v>90519</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -32561,21 +32570,21 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
@@ -32585,10 +32594,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>520058</v>
+        <v>520270</v>
       </c>
       <c r="R266" t="n">
-        <v>6934066</v>
+        <v>6933710</v>
       </c>
       <c r="S266" t="n">
         <v>25</v>
@@ -32621,6 +32630,11 @@
       <c r="AA266" t="inlineStr">
         <is>
           <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AC266" t="inlineStr">
+        <is>
+          <t>På tall med brandljud</t>
         </is>
       </c>
       <c r="AD266" t="b">
@@ -32647,10 +32661,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>117614781</v>
+        <v>117619372</v>
       </c>
       <c r="B267" t="n">
-        <v>79561</v>
+        <v>79590</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -32659,25 +32673,25 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
@@ -32687,13 +32701,13 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>520247</v>
+        <v>519861</v>
       </c>
       <c r="R267" t="n">
-        <v>6933662</v>
+        <v>6933763</v>
       </c>
       <c r="S267" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T267" t="inlineStr">
         <is>
@@ -32749,10 +32763,10 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>117619504</v>
+        <v>117620580</v>
       </c>
       <c r="B268" t="n">
-        <v>79562</v>
+        <v>104929</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -32761,25 +32775,25 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>2081</v>
+        <v>221144</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
@@ -32789,13 +32803,13 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>519854</v>
+        <v>520068</v>
       </c>
       <c r="R268" t="n">
-        <v>6933806</v>
+        <v>6934077</v>
       </c>
       <c r="S268" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T268" t="inlineStr">
         <is>
@@ -32851,10 +32865,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>117624131</v>
+        <v>117616189</v>
       </c>
       <c r="B269" t="n">
-        <v>57440</v>
+        <v>78480</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -32867,37 +32881,37 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
       <c r="P269" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>520392</v>
+        <v>520186</v>
       </c>
       <c r="R269" t="n">
-        <v>6933757</v>
+        <v>6933870</v>
       </c>
       <c r="S269" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T269" t="inlineStr">
         <is>
@@ -32927,11 +32941,6 @@
       <c r="AA269" t="inlineStr">
         <is>
           <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AC269" t="inlineStr">
-        <is>
-          <t>Varnande</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -32958,10 +32967,10 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>117615056</v>
+        <v>117624155</v>
       </c>
       <c r="B270" t="n">
-        <v>95384</v>
+        <v>78480</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -32974,37 +32983,37 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
       <c r="P270" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>520233</v>
+        <v>520423</v>
       </c>
       <c r="R270" t="n">
-        <v>6933656</v>
+        <v>6933800</v>
       </c>
       <c r="S270" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T270" t="inlineStr">
         <is>
@@ -33060,10 +33069,10 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>117615007</v>
+        <v>117624128</v>
       </c>
       <c r="B271" t="n">
-        <v>97836</v>
+        <v>90499</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -33072,41 +33081,41 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
       <c r="P271" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>520238</v>
+        <v>520240</v>
       </c>
       <c r="R271" t="n">
-        <v>6933656</v>
+        <v>6933649</v>
       </c>
       <c r="S271" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T271" t="inlineStr">
         <is>
@@ -33162,10 +33171,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>117624153</v>
+        <v>117617897</v>
       </c>
       <c r="B272" t="n">
-        <v>97836</v>
+        <v>79561</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -33174,41 +33183,41 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
       <c r="P272" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>520113</v>
+        <v>520122</v>
       </c>
       <c r="R272" t="n">
-        <v>6933668</v>
+        <v>6933863</v>
       </c>
       <c r="S272" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T272" t="inlineStr">
         <is>
@@ -33264,10 +33273,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>117618638</v>
+        <v>117624143</v>
       </c>
       <c r="B273" t="n">
-        <v>97836</v>
+        <v>79561</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -33276,41 +33285,41 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
       <c r="P273" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>520072</v>
+        <v>520804</v>
       </c>
       <c r="R273" t="n">
-        <v>6933810</v>
+        <v>6933797</v>
       </c>
       <c r="S273" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T273" t="inlineStr">
         <is>
@@ -33366,10 +33375,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>117624155</v>
+        <v>117618578</v>
       </c>
       <c r="B274" t="n">
-        <v>78480</v>
+        <v>79561</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -33382,37 +33391,37 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
       <c r="P274" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>520423</v>
+        <v>520076</v>
       </c>
       <c r="R274" t="n">
-        <v>6933800</v>
+        <v>6933805</v>
       </c>
       <c r="S274" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T274" t="inlineStr">
         <is>
@@ -33468,7 +33477,7 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>117624140</v>
+        <v>117617034</v>
       </c>
       <c r="B275" t="n">
         <v>79561</v>
@@ -33504,17 +33513,17 @@
       <c r="I275" t="inlineStr"/>
       <c r="P275" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>520519</v>
+        <v>520184</v>
       </c>
       <c r="R275" t="n">
-        <v>6933772</v>
+        <v>6933959</v>
       </c>
       <c r="S275" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T275" t="inlineStr">
         <is>
@@ -33570,10 +33579,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>117619522</v>
+        <v>117624159</v>
       </c>
       <c r="B276" t="n">
-        <v>79561</v>
+        <v>90907</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -33582,41 +33591,41 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>6458</v>
+        <v>5321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rigidoporus corticola</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
       <c r="P276" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>519865</v>
+        <v>520522</v>
       </c>
       <c r="R276" t="n">
-        <v>6933800</v>
+        <v>6933775</v>
       </c>
       <c r="S276" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T276" t="inlineStr">
         <is>
@@ -33654,6 +33663,7 @@
       <c r="AE276" t="b">
         <v>0</v>
       </c>
+      <c r="AF276" t="inlineStr"/>
       <c r="AG276" t="b">
         <v>0</v>
       </c>
@@ -33672,7 +33682,7 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>117624151</v>
+        <v>117620535</v>
       </c>
       <c r="B277" t="n">
         <v>97836</v>
@@ -33708,17 +33718,17 @@
       <c r="I277" t="inlineStr"/>
       <c r="P277" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>520138</v>
+        <v>520056</v>
       </c>
       <c r="R277" t="n">
-        <v>6933928</v>
+        <v>6934071</v>
       </c>
       <c r="S277" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T277" t="inlineStr">
         <is>
@@ -33774,10 +33784,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>117616632</v>
+        <v>117615105</v>
       </c>
       <c r="B278" t="n">
-        <v>79561</v>
+        <v>57440</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -33790,37 +33800,42 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P278" t="inlineStr">
         <is>
           <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>520219</v>
+        <v>520242</v>
       </c>
       <c r="R278" t="n">
-        <v>6933885</v>
+        <v>6933642</v>
       </c>
       <c r="S278" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T278" t="inlineStr">
         <is>
@@ -33876,10 +33891,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>117615611</v>
+        <v>117624150</v>
       </c>
       <c r="B279" t="n">
-        <v>79561</v>
+        <v>97836</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -33888,41 +33903,41 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
       <c r="P279" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>520102</v>
+        <v>520069</v>
       </c>
       <c r="R279" t="n">
-        <v>6933712</v>
+        <v>6933806</v>
       </c>
       <c r="S279" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T279" t="inlineStr">
         <is>
@@ -33978,10 +33993,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>117615300</v>
+        <v>117614268</v>
       </c>
       <c r="B280" t="n">
-        <v>79561</v>
+        <v>78216</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -33994,21 +34009,21 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
@@ -34018,13 +34033,13 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>520171</v>
+        <v>520362</v>
       </c>
       <c r="R280" t="n">
-        <v>6933646</v>
+        <v>6933716</v>
       </c>
       <c r="S280" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T280" t="inlineStr">
         <is>
@@ -34080,10 +34095,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>117620923</v>
+        <v>117619065</v>
       </c>
       <c r="B281" t="n">
-        <v>90907</v>
+        <v>78480</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -34092,25 +34107,25 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>5321</v>
+        <v>6425</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
@@ -34120,10 +34135,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>520467</v>
+        <v>519960</v>
       </c>
       <c r="R281" t="n">
-        <v>6933927</v>
+        <v>6933780</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -34182,10 +34197,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>117615105</v>
+        <v>117618235</v>
       </c>
       <c r="B282" t="n">
-        <v>57440</v>
+        <v>96791</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -34194,46 +34209,41 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
-      <c r="M282" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P282" t="inlineStr">
         <is>
           <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>520242</v>
+        <v>520117</v>
       </c>
       <c r="R282" t="n">
-        <v>6933642</v>
+        <v>6933840</v>
       </c>
       <c r="S282" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T282" t="inlineStr">
         <is>
@@ -34289,10 +34299,10 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>117614215</v>
+        <v>117624129</v>
       </c>
       <c r="B283" t="n">
-        <v>57440</v>
+        <v>90499</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -34305,39 +34315,34 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I283" t="inlineStr"/>
-      <c r="M283" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P283" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>520399</v>
+        <v>520240</v>
       </c>
       <c r="R283" t="n">
-        <v>6933756</v>
+        <v>6933655</v>
       </c>
       <c r="S283" t="n">
         <v>25</v>
@@ -34396,7 +34401,7 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>117624138</v>
+        <v>117616001</v>
       </c>
       <c r="B284" t="n">
         <v>79561</v>
@@ -34432,17 +34437,17 @@
       <c r="I284" t="inlineStr"/>
       <c r="P284" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>520508</v>
+        <v>520195</v>
       </c>
       <c r="R284" t="n">
-        <v>6933774</v>
+        <v>6933879</v>
       </c>
       <c r="S284" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T284" t="inlineStr">
         <is>
@@ -34498,7 +34503,7 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>117624136</v>
+        <v>117616632</v>
       </c>
       <c r="B285" t="n">
         <v>79561</v>
@@ -34534,17 +34539,17 @@
       <c r="I285" t="inlineStr"/>
       <c r="P285" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>520420</v>
+        <v>520219</v>
       </c>
       <c r="R285" t="n">
-        <v>6933788</v>
+        <v>6933885</v>
       </c>
       <c r="S285" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T285" t="inlineStr">
         <is>
@@ -34574,11 +34579,6 @@
       <c r="AA285" t="inlineStr">
         <is>
           <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AC285" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD285" t="b">
@@ -34605,10 +34605,10 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>117618968</v>
+        <v>117620923</v>
       </c>
       <c r="B286" t="n">
-        <v>79561</v>
+        <v>90907</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
@@ -34617,25 +34617,25 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>6458</v>
+        <v>5321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rigidoporus corticola</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I286" t="inlineStr"/>
@@ -34645,13 +34645,13 @@
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>519980</v>
+        <v>520467</v>
       </c>
       <c r="R286" t="n">
-        <v>6933791</v>
+        <v>6933927</v>
       </c>
       <c r="S286" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T286" t="inlineStr">
         <is>
@@ -34707,10 +34707,10 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>117624143</v>
+        <v>117619628</v>
       </c>
       <c r="B287" t="n">
-        <v>79561</v>
+        <v>78480</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -34723,37 +34723,37 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I287" t="inlineStr"/>
       <c r="P287" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>520804</v>
+        <v>519878</v>
       </c>
       <c r="R287" t="n">
-        <v>6933797</v>
+        <v>6933831</v>
       </c>
       <c r="S287" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T287" t="inlineStr">
         <is>
@@ -34809,10 +34809,10 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>117616097</v>
+        <v>117614781</v>
       </c>
       <c r="B288" t="n">
-        <v>91288</v>
+        <v>79561</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -34825,21 +34825,21 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>2014</v>
+        <v>6458</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I288" t="inlineStr"/>
@@ -34849,13 +34849,13 @@
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>520192</v>
+        <v>520247</v>
       </c>
       <c r="R288" t="n">
-        <v>6933876</v>
+        <v>6933662</v>
       </c>
       <c r="S288" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T288" t="inlineStr">
         <is>
@@ -34911,10 +34911,10 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>117619065</v>
+        <v>117620395</v>
       </c>
       <c r="B289" t="n">
-        <v>78480</v>
+        <v>90499</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -34927,21 +34927,21 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I289" t="inlineStr"/>
@@ -34951,10 +34951,10 @@
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>519960</v>
+        <v>520058</v>
       </c>
       <c r="R289" t="n">
-        <v>6933780</v>
+        <v>6934065</v>
       </c>
       <c r="S289" t="n">
         <v>10</v>
@@ -35013,10 +35013,10 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>117615974</v>
+        <v>117624135</v>
       </c>
       <c r="B290" t="n">
-        <v>56499</v>
+        <v>90782</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
@@ -35025,41 +35025,41 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I290" t="inlineStr"/>
       <c r="P290" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>520185</v>
+        <v>520054</v>
       </c>
       <c r="R290" t="n">
-        <v>6933863</v>
+        <v>6934068</v>
       </c>
       <c r="S290" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T290" t="inlineStr">
         <is>
@@ -35089,11 +35089,6 @@
       <c r="AA290" t="inlineStr">
         <is>
           <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AC290" t="inlineStr">
-        <is>
-          <t>Färsk spillning</t>
         </is>
       </c>
       <c r="AD290" t="b">
@@ -35120,7 +35115,7 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>117616291</v>
+        <v>117624154</v>
       </c>
       <c r="B291" t="n">
         <v>97836</v>
@@ -35156,17 +35151,17 @@
       <c r="I291" t="inlineStr"/>
       <c r="P291" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>520169</v>
+        <v>520817</v>
       </c>
       <c r="R291" t="n">
-        <v>6933869</v>
+        <v>6933807</v>
       </c>
       <c r="S291" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T291" t="inlineStr">
         <is>
@@ -35222,10 +35217,10 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>117624135</v>
+        <v>117615056</v>
       </c>
       <c r="B292" t="n">
-        <v>90782</v>
+        <v>95384</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
@@ -35238,37 +35233,37 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I292" t="inlineStr"/>
       <c r="P292" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q292" t="n">
-        <v>520054</v>
+        <v>520233</v>
       </c>
       <c r="R292" t="n">
-        <v>6934068</v>
+        <v>6933656</v>
       </c>
       <c r="S292" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T292" t="inlineStr">
         <is>
@@ -35324,10 +35319,10 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>117620594</v>
+        <v>117620029</v>
       </c>
       <c r="B293" t="n">
-        <v>95384</v>
+        <v>79561</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -35340,21 +35335,21 @@
         </is>
       </c>
       <c r="E293" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I293" t="inlineStr"/>
@@ -35364,10 +35359,10 @@
         </is>
       </c>
       <c r="Q293" t="n">
-        <v>520083</v>
+        <v>519945</v>
       </c>
       <c r="R293" t="n">
-        <v>6934090</v>
+        <v>6933946</v>
       </c>
       <c r="S293" t="n">
         <v>10</v>
@@ -35426,10 +35421,10 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>117616189</v>
+        <v>117615486</v>
       </c>
       <c r="B294" t="n">
-        <v>78480</v>
+        <v>97836</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
@@ -35438,25 +35433,25 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I294" t="inlineStr"/>
@@ -35466,13 +35461,13 @@
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>520186</v>
+        <v>520113</v>
       </c>
       <c r="R294" t="n">
-        <v>6933870</v>
+        <v>6933665</v>
       </c>
       <c r="S294" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T294" t="inlineStr">
         <is>
@@ -35528,10 +35523,10 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>117624146</v>
+        <v>117616291</v>
       </c>
       <c r="B295" t="n">
-        <v>78216</v>
+        <v>97836</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
@@ -35540,41 +35535,41 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I295" t="inlineStr"/>
       <c r="P295" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>520355</v>
+        <v>520169</v>
       </c>
       <c r="R295" t="n">
-        <v>6933736</v>
+        <v>6933869</v>
       </c>
       <c r="S295" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T295" t="inlineStr">
         <is>
@@ -35630,10 +35625,10 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>117616751</v>
+        <v>117614566</v>
       </c>
       <c r="B296" t="n">
-        <v>97870</v>
+        <v>90519</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
@@ -35642,25 +35637,25 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E296" t="n">
-        <v>219874</v>
+        <v>5442</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I296" t="inlineStr"/>
@@ -35670,13 +35665,13 @@
         </is>
       </c>
       <c r="Q296" t="n">
-        <v>520201</v>
+        <v>520293</v>
       </c>
       <c r="R296" t="n">
-        <v>6933913</v>
+        <v>6933723</v>
       </c>
       <c r="S296" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T296" t="inlineStr">
         <is>
@@ -35706,6 +35701,11 @@
       <c r="AA296" t="inlineStr">
         <is>
           <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AC296" t="inlineStr">
+        <is>
+          <t>På gammal tall med brandljud</t>
         </is>
       </c>
       <c r="AD296" t="b">
@@ -35732,10 +35732,10 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>117620535</v>
+        <v>117624146</v>
       </c>
       <c r="B297" t="n">
-        <v>97836</v>
+        <v>78216</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
@@ -35744,41 +35744,41 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I297" t="inlineStr"/>
       <c r="P297" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q297" t="n">
-        <v>520056</v>
+        <v>520355</v>
       </c>
       <c r="R297" t="n">
-        <v>6934071</v>
+        <v>6933736</v>
       </c>
       <c r="S297" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T297" t="inlineStr">
         <is>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -26399,10 +26399,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>117615007</v>
+        <v>117618638</v>
       </c>
       <c r="B206" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -26439,13 +26439,13 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>520238</v>
+        <v>520072</v>
       </c>
       <c r="R206" t="n">
-        <v>6933656</v>
+        <v>6933810</v>
       </c>
       <c r="S206" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -26501,10 +26501,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>117624124</v>
+        <v>117624131</v>
       </c>
       <c r="B207" t="n">
-        <v>97836</v>
+        <v>57441</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -26513,25 +26513,25 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -26541,10 +26541,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>520234</v>
+        <v>520392</v>
       </c>
       <c r="R207" t="n">
-        <v>6933656</v>
+        <v>6933757</v>
       </c>
       <c r="S207" t="n">
         <v>25</v>
@@ -26577,6 +26577,11 @@
       <c r="AA207" t="inlineStr">
         <is>
           <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>Varnande</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -26603,10 +26608,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>117614921</v>
+        <v>117620347</v>
       </c>
       <c r="B208" t="n">
-        <v>90499</v>
+        <v>90784</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -26619,21 +26624,21 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -26643,10 +26648,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>520237</v>
+        <v>520060</v>
       </c>
       <c r="R208" t="n">
-        <v>6933645</v>
+        <v>6934064</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -26705,10 +26710,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>117620347</v>
+        <v>117615611</v>
       </c>
       <c r="B209" t="n">
-        <v>90782</v>
+        <v>79563</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -26721,21 +26726,21 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -26745,13 +26750,13 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>520060</v>
+        <v>520102</v>
       </c>
       <c r="R209" t="n">
-        <v>6934064</v>
+        <v>6933712</v>
       </c>
       <c r="S209" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -26807,10 +26812,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>117624133</v>
+        <v>117624143</v>
       </c>
       <c r="B210" t="n">
-        <v>90519</v>
+        <v>79563</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -26823,21 +26828,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -26847,10 +26852,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>520382</v>
+        <v>520804</v>
       </c>
       <c r="R210" t="n">
-        <v>6933719</v>
+        <v>6933797</v>
       </c>
       <c r="S210" t="n">
         <v>25</v>
@@ -26909,10 +26914,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>117619317</v>
+        <v>117620594</v>
       </c>
       <c r="B211" t="n">
-        <v>79561</v>
+        <v>95386</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -26925,21 +26930,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -26949,13 +26954,13 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>519864</v>
+        <v>520083</v>
       </c>
       <c r="R211" t="n">
-        <v>6933761</v>
+        <v>6934090</v>
       </c>
       <c r="S211" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -27011,10 +27016,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>117624136</v>
+        <v>117618578</v>
       </c>
       <c r="B212" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -27047,17 +27052,17 @@
       <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>520420</v>
+        <v>520076</v>
       </c>
       <c r="R212" t="n">
-        <v>6933788</v>
+        <v>6933805</v>
       </c>
       <c r="S212" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
@@ -27087,11 +27092,6 @@
       <c r="AA212" t="inlineStr">
         <is>
           <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AC212" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -27118,10 +27118,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>117614799</v>
+        <v>117615396</v>
       </c>
       <c r="B213" t="n">
-        <v>57440</v>
+        <v>78218</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -27134,42 +27134,37 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
-      <c r="M213" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P213" t="inlineStr">
         <is>
           <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>520250</v>
+        <v>520133</v>
       </c>
       <c r="R213" t="n">
-        <v>6933680</v>
+        <v>6933665</v>
       </c>
       <c r="S213" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -27225,10 +27220,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>117618946</v>
+        <v>117615056</v>
       </c>
       <c r="B214" t="n">
-        <v>79561</v>
+        <v>95386</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -27241,21 +27236,21 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -27265,10 +27260,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>519986</v>
+        <v>520233</v>
       </c>
       <c r="R214" t="n">
-        <v>6933778</v>
+        <v>6933656</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -27327,10 +27322,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>117619662</v>
+        <v>117624144</v>
       </c>
       <c r="B215" t="n">
-        <v>79561</v>
+        <v>80439</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -27343,37 +27338,37 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6458</v>
+        <v>1049</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>519882</v>
+        <v>520777</v>
       </c>
       <c r="R215" t="n">
-        <v>6933843</v>
+        <v>6933766</v>
       </c>
       <c r="S215" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -27429,10 +27424,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>117619423</v>
+        <v>117620535</v>
       </c>
       <c r="B216" t="n">
-        <v>79561</v>
+        <v>97838</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -27441,25 +27436,25 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -27469,13 +27464,13 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>519861</v>
+        <v>520056</v>
       </c>
       <c r="R216" t="n">
-        <v>6933798</v>
+        <v>6934071</v>
       </c>
       <c r="S216" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -27531,10 +27526,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>117615300</v>
+        <v>117624150</v>
       </c>
       <c r="B217" t="n">
-        <v>79561</v>
+        <v>97838</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -27543,41 +27538,41 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>520171</v>
+        <v>520069</v>
       </c>
       <c r="R217" t="n">
-        <v>6933646</v>
+        <v>6933806</v>
       </c>
       <c r="S217" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -27633,10 +27628,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>117624138</v>
+        <v>117624153</v>
       </c>
       <c r="B218" t="n">
-        <v>79561</v>
+        <v>97838</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -27645,25 +27640,25 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -27673,10 +27668,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>520508</v>
+        <v>520113</v>
       </c>
       <c r="R218" t="n">
-        <v>6933774</v>
+        <v>6933668</v>
       </c>
       <c r="S218" t="n">
         <v>25</v>
@@ -27735,10 +27730,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>117620495</v>
+        <v>117624133</v>
       </c>
       <c r="B219" t="n">
-        <v>97836</v>
+        <v>90521</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -27747,41 +27742,41 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>520061</v>
+        <v>520382</v>
       </c>
       <c r="R219" t="n">
-        <v>6934070</v>
+        <v>6933719</v>
       </c>
       <c r="S219" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -27837,10 +27832,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>117624131</v>
+        <v>117619600</v>
       </c>
       <c r="B220" t="n">
-        <v>57440</v>
+        <v>78482</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -27853,37 +27848,37 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>520392</v>
+        <v>519868</v>
       </c>
       <c r="R220" t="n">
-        <v>6933757</v>
+        <v>6933813</v>
       </c>
       <c r="S220" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -27913,11 +27908,6 @@
       <c r="AA220" t="inlineStr">
         <is>
           <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AC220" t="inlineStr">
-        <is>
-          <t>Varnande</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -27944,10 +27934,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>117620594</v>
+        <v>117619423</v>
       </c>
       <c r="B221" t="n">
-        <v>95384</v>
+        <v>79563</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -27960,21 +27950,21 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -27984,13 +27974,13 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>520083</v>
+        <v>519861</v>
       </c>
       <c r="R221" t="n">
-        <v>6934090</v>
+        <v>6933798</v>
       </c>
       <c r="S221" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -28046,10 +28036,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>117616097</v>
+        <v>117624148</v>
       </c>
       <c r="B222" t="n">
-        <v>91288</v>
+        <v>78218</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -28062,37 +28052,37 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>2014</v>
+        <v>6446</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>520192</v>
+        <v>520400</v>
       </c>
       <c r="R222" t="n">
-        <v>6933876</v>
+        <v>6933760</v>
       </c>
       <c r="S222" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -28148,10 +28138,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>117615776</v>
+        <v>117624128</v>
       </c>
       <c r="B223" t="n">
-        <v>79098</v>
+        <v>90501</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -28164,37 +28154,37 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>520220</v>
+        <v>520240</v>
       </c>
       <c r="R223" t="n">
-        <v>6933822</v>
+        <v>6933649</v>
       </c>
       <c r="S223" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>
@@ -28250,10 +28240,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>117620214</v>
+        <v>117624129</v>
       </c>
       <c r="B224" t="n">
-        <v>78216</v>
+        <v>90501</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -28266,37 +28256,37 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>519974</v>
+        <v>520240</v>
       </c>
       <c r="R224" t="n">
-        <v>6934018</v>
+        <v>6933655</v>
       </c>
       <c r="S224" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="T224" t="inlineStr">
         <is>
@@ -28352,10 +28342,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>117624156</v>
+        <v>117616189</v>
       </c>
       <c r="B225" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -28388,17 +28378,17 @@
       <c r="I225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>520571</v>
+        <v>520186</v>
       </c>
       <c r="R225" t="n">
-        <v>6933768</v>
+        <v>6933870</v>
       </c>
       <c r="S225" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T225" t="inlineStr">
         <is>
@@ -28454,10 +28444,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>117619582</v>
+        <v>117624136</v>
       </c>
       <c r="B226" t="n">
-        <v>97857</v>
+        <v>79563</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -28466,41 +28456,41 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>519870</v>
+        <v>520420</v>
       </c>
       <c r="R226" t="n">
-        <v>6933797</v>
+        <v>6933788</v>
       </c>
       <c r="S226" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T226" t="inlineStr">
         <is>
@@ -28530,6 +28520,11 @@
       <c r="AA226" t="inlineStr">
         <is>
           <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -28556,10 +28551,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>117614215</v>
+        <v>117624141</v>
       </c>
       <c r="B227" t="n">
-        <v>57440</v>
+        <v>79563</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -28572,39 +28567,34 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>520399</v>
+        <v>520775</v>
       </c>
       <c r="R227" t="n">
-        <v>6933756</v>
+        <v>6933753</v>
       </c>
       <c r="S227" t="n">
         <v>25</v>
@@ -28663,10 +28653,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>117618968</v>
+        <v>117619202</v>
       </c>
       <c r="B228" t="n">
-        <v>79561</v>
+        <v>104931</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -28675,25 +28665,25 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6458</v>
+        <v>221144</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -28703,13 +28693,13 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>519980</v>
+        <v>519909</v>
       </c>
       <c r="R228" t="n">
-        <v>6933791</v>
+        <v>6933766</v>
       </c>
       <c r="S228" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T228" t="inlineStr">
         <is>
@@ -28765,10 +28755,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>117618841</v>
+        <v>117614361</v>
       </c>
       <c r="B229" t="n">
-        <v>79561</v>
+        <v>90521</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -28781,21 +28771,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -28805,13 +28795,13 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>520006</v>
+        <v>520373</v>
       </c>
       <c r="R229" t="n">
-        <v>6933772</v>
+        <v>6933724</v>
       </c>
       <c r="S229" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T229" t="inlineStr">
         <is>
@@ -28870,7 +28860,7 @@
         <v>117618861</v>
       </c>
       <c r="B230" t="n">
-        <v>79597</v>
+        <v>79599</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -28969,10 +28959,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>117624144</v>
+        <v>117619372</v>
       </c>
       <c r="B231" t="n">
-        <v>80437</v>
+        <v>79592</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -28981,41 +28971,41 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>1049</v>
+        <v>6462</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>520777</v>
+        <v>519861</v>
       </c>
       <c r="R231" t="n">
-        <v>6933766</v>
+        <v>6933763</v>
       </c>
       <c r="S231" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T231" t="inlineStr">
         <is>
@@ -29071,10 +29061,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>117615611</v>
+        <v>117615007</v>
       </c>
       <c r="B232" t="n">
-        <v>79561</v>
+        <v>97838</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -29083,25 +29073,25 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -29111,13 +29101,13 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>520102</v>
+        <v>520238</v>
       </c>
       <c r="R232" t="n">
-        <v>6933712</v>
+        <v>6933656</v>
       </c>
       <c r="S232" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T232" t="inlineStr">
         <is>
@@ -29173,10 +29163,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>117616751</v>
+        <v>117624154</v>
       </c>
       <c r="B233" t="n">
-        <v>97870</v>
+        <v>97838</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -29185,41 +29175,41 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>520201</v>
+        <v>520817</v>
       </c>
       <c r="R233" t="n">
-        <v>6933913</v>
+        <v>6933807</v>
       </c>
       <c r="S233" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -29275,10 +29265,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>117619862</v>
+        <v>117615776</v>
       </c>
       <c r="B234" t="n">
-        <v>78480</v>
+        <v>79100</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -29291,21 +29281,21 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -29315,13 +29305,13 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>519899</v>
+        <v>520220</v>
       </c>
       <c r="R234" t="n">
-        <v>6933938</v>
+        <v>6933822</v>
       </c>
       <c r="S234" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T234" t="inlineStr">
         <is>
@@ -29377,10 +29367,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>117619202</v>
+        <v>117620214</v>
       </c>
       <c r="B235" t="n">
-        <v>104929</v>
+        <v>78218</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -29389,25 +29379,25 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>221144</v>
+        <v>6446</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -29417,13 +29407,13 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>519909</v>
+        <v>519974</v>
       </c>
       <c r="R235" t="n">
-        <v>6933766</v>
+        <v>6934018</v>
       </c>
       <c r="S235" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="T235" t="inlineStr">
         <is>
@@ -29479,10 +29469,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>117616723</v>
+        <v>117616097</v>
       </c>
       <c r="B236" t="n">
-        <v>79561</v>
+        <v>91290</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -29495,21 +29485,21 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>6458</v>
+        <v>2014</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -29519,13 +29509,13 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>520201</v>
+        <v>520192</v>
       </c>
       <c r="R236" t="n">
-        <v>6933904</v>
+        <v>6933876</v>
       </c>
       <c r="S236" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T236" t="inlineStr">
         <is>
@@ -29581,10 +29571,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>117617145</v>
+        <v>117616723</v>
       </c>
       <c r="B237" t="n">
-        <v>56499</v>
+        <v>79563</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -29593,25 +29583,25 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
@@ -29621,10 +29611,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>520159</v>
+        <v>520201</v>
       </c>
       <c r="R237" t="n">
-        <v>6933938</v>
+        <v>6933904</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -29657,11 +29647,6 @@
       <c r="AA237" t="inlineStr">
         <is>
           <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AC237" t="inlineStr">
-        <is>
-          <t>Färsk spillning</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -29688,10 +29673,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>117624158</v>
+        <v>117615266</v>
       </c>
       <c r="B238" t="n">
-        <v>78480</v>
+        <v>79563</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -29704,37 +29689,37 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>520835</v>
+        <v>520175</v>
       </c>
       <c r="R238" t="n">
-        <v>6933821</v>
+        <v>6933657</v>
       </c>
       <c r="S238" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T238" t="inlineStr">
         <is>
@@ -29793,7 +29778,7 @@
         <v>117624151</v>
       </c>
       <c r="B239" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -29892,10 +29877,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>117615266</v>
+        <v>117620395</v>
       </c>
       <c r="B240" t="n">
-        <v>79561</v>
+        <v>90501</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -29908,21 +29893,21 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -29932,13 +29917,13 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>520175</v>
+        <v>520058</v>
       </c>
       <c r="R240" t="n">
-        <v>6933657</v>
+        <v>6934065</v>
       </c>
       <c r="S240" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T240" t="inlineStr">
         <is>
@@ -29994,10 +29979,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>117624149</v>
+        <v>117624155</v>
       </c>
       <c r="B241" t="n">
-        <v>97836</v>
+        <v>78482</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -30006,25 +29991,25 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -30034,10 +30019,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>520061</v>
+        <v>520423</v>
       </c>
       <c r="R241" t="n">
-        <v>6934068</v>
+        <v>6933800</v>
       </c>
       <c r="S241" t="n">
         <v>25</v>
@@ -30096,10 +30081,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>117619968</v>
+        <v>117616157</v>
       </c>
       <c r="B242" t="n">
-        <v>78480</v>
+        <v>56500</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -30108,25 +30093,25 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -30136,13 +30121,13 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>519908</v>
+        <v>520184</v>
       </c>
       <c r="R242" t="n">
-        <v>6933941</v>
+        <v>6933878</v>
       </c>
       <c r="S242" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -30172,11 +30157,6 @@
       <c r="AA242" t="inlineStr">
         <is>
           <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AC242" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -30203,10 +30183,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>117619522</v>
+        <v>117618946</v>
       </c>
       <c r="B243" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -30243,13 +30223,13 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>519865</v>
+        <v>519986</v>
       </c>
       <c r="R243" t="n">
-        <v>6933800</v>
+        <v>6933778</v>
       </c>
       <c r="S243" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -30305,10 +30285,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>117624140</v>
+        <v>117619628</v>
       </c>
       <c r="B244" t="n">
-        <v>79561</v>
+        <v>78482</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -30321,37 +30301,37 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>520519</v>
+        <v>519878</v>
       </c>
       <c r="R244" t="n">
-        <v>6933772</v>
+        <v>6933831</v>
       </c>
       <c r="S244" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T244" t="inlineStr">
         <is>
@@ -30407,10 +30387,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>117617202</v>
+        <v>117620495</v>
       </c>
       <c r="B245" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -30447,10 +30427,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>520144</v>
+        <v>520061</v>
       </c>
       <c r="R245" t="n">
-        <v>6933928</v>
+        <v>6934070</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -30512,7 +30492,7 @@
         <v>117619891</v>
       </c>
       <c r="B246" t="n">
-        <v>78217</v>
+        <v>78219</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -30611,10 +30591,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>117615933</v>
+        <v>117624126</v>
       </c>
       <c r="B247" t="n">
-        <v>78216</v>
+        <v>90501</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -30627,37 +30607,37 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>520184</v>
+        <v>520058</v>
       </c>
       <c r="R247" t="n">
-        <v>6933872</v>
+        <v>6934066</v>
       </c>
       <c r="S247" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T247" t="inlineStr">
         <is>
@@ -30713,10 +30693,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>117615235</v>
+        <v>117617897</v>
       </c>
       <c r="B248" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -30753,13 +30733,13 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>520172</v>
+        <v>520122</v>
       </c>
       <c r="R248" t="n">
-        <v>6933674</v>
+        <v>6933863</v>
       </c>
       <c r="S248" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T248" t="inlineStr">
         <is>
@@ -30815,10 +30795,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>117624141</v>
+        <v>117618235</v>
       </c>
       <c r="B249" t="n">
-        <v>79561</v>
+        <v>96793</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -30827,41 +30807,41 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>520775</v>
+        <v>520117</v>
       </c>
       <c r="R249" t="n">
-        <v>6933753</v>
+        <v>6933840</v>
       </c>
       <c r="S249" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T249" t="inlineStr">
         <is>
@@ -30917,10 +30897,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>117616157</v>
+        <v>117615974</v>
       </c>
       <c r="B250" t="n">
-        <v>56499</v>
+        <v>56500</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -30957,13 +30937,13 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>520184</v>
+        <v>520185</v>
       </c>
       <c r="R250" t="n">
-        <v>6933878</v>
+        <v>6933863</v>
       </c>
       <c r="S250" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T250" t="inlineStr">
         <is>
@@ -30993,6 +30973,11 @@
       <c r="AA250" t="inlineStr">
         <is>
           <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>Färsk spillning</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -31019,10 +31004,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>117615974</v>
+        <v>117615300</v>
       </c>
       <c r="B251" t="n">
-        <v>56499</v>
+        <v>79563</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -31031,25 +31016,25 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -31059,13 +31044,13 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>520185</v>
+        <v>520171</v>
       </c>
       <c r="R251" t="n">
-        <v>6933863</v>
+        <v>6933646</v>
       </c>
       <c r="S251" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T251" t="inlineStr">
         <is>
@@ -31095,11 +31080,6 @@
       <c r="AA251" t="inlineStr">
         <is>
           <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AC251" t="inlineStr">
-        <is>
-          <t>Färsk spillning</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -31126,10 +31106,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>117617321</v>
+        <v>117617034</v>
       </c>
       <c r="B252" t="n">
-        <v>104929</v>
+        <v>79563</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -31138,25 +31118,25 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>221144</v>
+        <v>6458</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -31166,13 +31146,13 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>520138</v>
+        <v>520184</v>
       </c>
       <c r="R252" t="n">
-        <v>6933887</v>
+        <v>6933959</v>
       </c>
       <c r="S252" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T252" t="inlineStr">
         <is>
@@ -31228,10 +31208,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>117617526</v>
+        <v>117624156</v>
       </c>
       <c r="B253" t="n">
-        <v>78216</v>
+        <v>78482</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -31244,37 +31224,37 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>520120</v>
+        <v>520571</v>
       </c>
       <c r="R253" t="n">
-        <v>6933834</v>
+        <v>6933768</v>
       </c>
       <c r="S253" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T253" t="inlineStr">
         <is>
@@ -31330,10 +31310,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>117615396</v>
+        <v>117614799</v>
       </c>
       <c r="B254" t="n">
-        <v>78216</v>
+        <v>57441</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -31346,37 +31326,42 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P254" t="inlineStr">
         <is>
           <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>520133</v>
+        <v>520250</v>
       </c>
       <c r="R254" t="n">
-        <v>6933665</v>
+        <v>6933680</v>
       </c>
       <c r="S254" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T254" t="inlineStr">
         <is>
@@ -31432,10 +31417,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>117618638</v>
+        <v>117617321</v>
       </c>
       <c r="B255" t="n">
-        <v>97836</v>
+        <v>104931</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -31444,25 +31429,25 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -31472,13 +31457,13 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>520072</v>
+        <v>520138</v>
       </c>
       <c r="R255" t="n">
-        <v>6933810</v>
+        <v>6933887</v>
       </c>
       <c r="S255" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T255" t="inlineStr">
         <is>
@@ -31534,10 +31519,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>117624126</v>
+        <v>117624149</v>
       </c>
       <c r="B256" t="n">
-        <v>90499</v>
+        <v>97838</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -31546,25 +31531,25 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -31574,10 +31559,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>520058</v>
+        <v>520061</v>
       </c>
       <c r="R256" t="n">
-        <v>6934066</v>
+        <v>6934068</v>
       </c>
       <c r="S256" t="n">
         <v>25</v>
@@ -31636,10 +31621,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>117615181</v>
+        <v>117616001</v>
       </c>
       <c r="B257" t="n">
-        <v>78480</v>
+        <v>79563</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -31652,21 +31637,21 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -31676,10 +31661,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>520218</v>
+        <v>520195</v>
       </c>
       <c r="R257" t="n">
-        <v>6933644</v>
+        <v>6933879</v>
       </c>
       <c r="S257" t="n">
         <v>15</v>
@@ -31738,10 +31723,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>117619600</v>
+        <v>117624125</v>
       </c>
       <c r="B258" t="n">
-        <v>78480</v>
+        <v>95386</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -31754,37 +31739,37 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
       <c r="P258" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>519868</v>
+        <v>520234</v>
       </c>
       <c r="R258" t="n">
-        <v>6933813</v>
+        <v>6933656</v>
       </c>
       <c r="S258" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T258" t="inlineStr">
         <is>
@@ -31840,10 +31825,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>117624148</v>
+        <v>117618968</v>
       </c>
       <c r="B259" t="n">
-        <v>78216</v>
+        <v>79563</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -31856,37 +31841,37 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
       <c r="P259" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>520400</v>
+        <v>519980</v>
       </c>
       <c r="R259" t="n">
-        <v>6933760</v>
+        <v>6933791</v>
       </c>
       <c r="S259" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T259" t="inlineStr">
         <is>
@@ -31942,10 +31927,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>117624125</v>
+        <v>117614921</v>
       </c>
       <c r="B260" t="n">
-        <v>95384</v>
+        <v>90501</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -31958,37 +31943,37 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>520234</v>
+        <v>520237</v>
       </c>
       <c r="R260" t="n">
-        <v>6933656</v>
+        <v>6933645</v>
       </c>
       <c r="S260" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T260" t="inlineStr">
         <is>
@@ -32044,10 +32029,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>117619989</v>
+        <v>117617145</v>
       </c>
       <c r="B261" t="n">
-        <v>79561</v>
+        <v>56500</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -32056,25 +32041,25 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -32084,10 +32069,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>519953</v>
+        <v>520159</v>
       </c>
       <c r="R261" t="n">
-        <v>6933937</v>
+        <v>6933938</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -32120,6 +32105,11 @@
       <c r="AA261" t="inlineStr">
         <is>
           <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AC261" t="inlineStr">
+        <is>
+          <t>Färsk spillning</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -32146,10 +32136,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>117624152</v>
+        <v>117624140</v>
       </c>
       <c r="B262" t="n">
-        <v>97836</v>
+        <v>79563</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -32158,25 +32148,25 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -32186,10 +32176,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>520185</v>
+        <v>520519</v>
       </c>
       <c r="R262" t="n">
-        <v>6933876</v>
+        <v>6933772</v>
       </c>
       <c r="S262" t="n">
         <v>25</v>
@@ -32248,10 +32238,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>117624153</v>
+        <v>117619317</v>
       </c>
       <c r="B263" t="n">
-        <v>97836</v>
+        <v>79563</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -32260,41 +32250,41 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>520113</v>
+        <v>519864</v>
       </c>
       <c r="R263" t="n">
-        <v>6933668</v>
+        <v>6933761</v>
       </c>
       <c r="S263" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T263" t="inlineStr">
         <is>
@@ -32350,10 +32340,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>117619504</v>
+        <v>117614566</v>
       </c>
       <c r="B264" t="n">
-        <v>79562</v>
+        <v>90521</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -32366,21 +32356,21 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>2081</v>
+        <v>5442</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
@@ -32390,13 +32380,13 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>519854</v>
+        <v>520293</v>
       </c>
       <c r="R264" t="n">
-        <v>6933806</v>
+        <v>6933723</v>
       </c>
       <c r="S264" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T264" t="inlineStr">
         <is>
@@ -32426,6 +32416,11 @@
       <c r="AA264" t="inlineStr">
         <is>
           <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AC264" t="inlineStr">
+        <is>
+          <t>På gammal tall med brandljud</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -32452,10 +32447,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>117614361</v>
+        <v>117624158</v>
       </c>
       <c r="B265" t="n">
-        <v>90519</v>
+        <v>78482</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -32468,37 +32463,37 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
       <c r="P265" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>520373</v>
+        <v>520835</v>
       </c>
       <c r="R265" t="n">
-        <v>6933724</v>
+        <v>6933821</v>
       </c>
       <c r="S265" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T265" t="inlineStr">
         <is>
@@ -32554,10 +32549,10 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>117624132</v>
+        <v>117614781</v>
       </c>
       <c r="B266" t="n">
-        <v>90519</v>
+        <v>79563</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -32570,37 +32565,37 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>520270</v>
+        <v>520247</v>
       </c>
       <c r="R266" t="n">
-        <v>6933710</v>
+        <v>6933662</v>
       </c>
       <c r="S266" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T266" t="inlineStr">
         <is>
@@ -32630,11 +32625,6 @@
       <c r="AA266" t="inlineStr">
         <is>
           <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AC266" t="inlineStr">
-        <is>
-          <t>På tall med brandljud</t>
         </is>
       </c>
       <c r="AD266" t="b">
@@ -32661,10 +32651,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>117619372</v>
+        <v>117624146</v>
       </c>
       <c r="B267" t="n">
-        <v>79590</v>
+        <v>78218</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -32673,41 +32663,41 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
       <c r="P267" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>519861</v>
+        <v>520355</v>
       </c>
       <c r="R267" t="n">
-        <v>6933763</v>
+        <v>6933736</v>
       </c>
       <c r="S267" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T267" t="inlineStr">
         <is>
@@ -32763,10 +32753,10 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>117620580</v>
+        <v>117617202</v>
       </c>
       <c r="B268" t="n">
-        <v>104929</v>
+        <v>97838</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -32775,25 +32765,25 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
@@ -32803,10 +32793,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>520068</v>
+        <v>520144</v>
       </c>
       <c r="R268" t="n">
-        <v>6934077</v>
+        <v>6933928</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -32865,10 +32855,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>117616189</v>
+        <v>117616632</v>
       </c>
       <c r="B269" t="n">
-        <v>78480</v>
+        <v>79563</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -32881,21 +32871,21 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
@@ -32905,13 +32895,13 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>520186</v>
+        <v>520219</v>
       </c>
       <c r="R269" t="n">
-        <v>6933870</v>
+        <v>6933885</v>
       </c>
       <c r="S269" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T269" t="inlineStr">
         <is>
@@ -32967,10 +32957,10 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>117624155</v>
+        <v>117615181</v>
       </c>
       <c r="B270" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -33003,17 +32993,17 @@
       <c r="I270" t="inlineStr"/>
       <c r="P270" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>520423</v>
+        <v>520218</v>
       </c>
       <c r="R270" t="n">
-        <v>6933800</v>
+        <v>6933644</v>
       </c>
       <c r="S270" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T270" t="inlineStr">
         <is>
@@ -33069,10 +33059,10 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>117624128</v>
+        <v>117619065</v>
       </c>
       <c r="B271" t="n">
-        <v>90499</v>
+        <v>78482</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -33085,37 +33075,37 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
       <c r="P271" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>520240</v>
+        <v>519960</v>
       </c>
       <c r="R271" t="n">
-        <v>6933649</v>
+        <v>6933780</v>
       </c>
       <c r="S271" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T271" t="inlineStr">
         <is>
@@ -33171,10 +33161,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>117617897</v>
+        <v>117624135</v>
       </c>
       <c r="B272" t="n">
-        <v>79561</v>
+        <v>90784</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -33187,37 +33177,37 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
       <c r="P272" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>520122</v>
+        <v>520054</v>
       </c>
       <c r="R272" t="n">
-        <v>6933863</v>
+        <v>6934068</v>
       </c>
       <c r="S272" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T272" t="inlineStr">
         <is>
@@ -33273,10 +33263,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>117624143</v>
+        <v>117618841</v>
       </c>
       <c r="B273" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -33309,17 +33299,17 @@
       <c r="I273" t="inlineStr"/>
       <c r="P273" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>520804</v>
+        <v>520006</v>
       </c>
       <c r="R273" t="n">
-        <v>6933797</v>
+        <v>6933772</v>
       </c>
       <c r="S273" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T273" t="inlineStr">
         <is>
@@ -33375,10 +33365,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>117618578</v>
+        <v>117616751</v>
       </c>
       <c r="B274" t="n">
-        <v>79561</v>
+        <v>97872</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -33387,25 +33377,25 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -33415,10 +33405,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>520076</v>
+        <v>520201</v>
       </c>
       <c r="R274" t="n">
-        <v>6933805</v>
+        <v>6933913</v>
       </c>
       <c r="S274" t="n">
         <v>15</v>
@@ -33477,10 +33467,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>117617034</v>
+        <v>117615486</v>
       </c>
       <c r="B275" t="n">
-        <v>79561</v>
+        <v>97838</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -33489,25 +33479,25 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
@@ -33517,10 +33507,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>520184</v>
+        <v>520113</v>
       </c>
       <c r="R275" t="n">
-        <v>6933959</v>
+        <v>6933665</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -33579,10 +33569,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>117624159</v>
+        <v>117620923</v>
       </c>
       <c r="B276" t="n">
-        <v>90907</v>
+        <v>90909</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -33615,17 +33605,17 @@
       <c r="I276" t="inlineStr"/>
       <c r="P276" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>520522</v>
+        <v>520467</v>
       </c>
       <c r="R276" t="n">
-        <v>6933775</v>
+        <v>6933927</v>
       </c>
       <c r="S276" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T276" t="inlineStr">
         <is>
@@ -33663,7 +33653,6 @@
       <c r="AE276" t="b">
         <v>0</v>
       </c>
-      <c r="AF276" t="inlineStr"/>
       <c r="AG276" t="b">
         <v>0</v>
       </c>
@@ -33682,10 +33671,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>117620535</v>
+        <v>117614215</v>
       </c>
       <c r="B277" t="n">
-        <v>97836</v>
+        <v>57441</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -33694,41 +33683,46 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P277" t="inlineStr">
         <is>
           <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>520056</v>
+        <v>520399</v>
       </c>
       <c r="R277" t="n">
-        <v>6934071</v>
+        <v>6933756</v>
       </c>
       <c r="S277" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T277" t="inlineStr">
         <is>
@@ -33784,10 +33778,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>117615105</v>
+        <v>117620580</v>
       </c>
       <c r="B278" t="n">
-        <v>57440</v>
+        <v>104931</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -33796,46 +33790,41 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
-      <c r="M278" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P278" t="inlineStr">
         <is>
           <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>520242</v>
+        <v>520068</v>
       </c>
       <c r="R278" t="n">
-        <v>6933642</v>
+        <v>6934077</v>
       </c>
       <c r="S278" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T278" t="inlineStr">
         <is>
@@ -33891,10 +33880,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>117624150</v>
+        <v>117615105</v>
       </c>
       <c r="B279" t="n">
-        <v>97836</v>
+        <v>57441</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -33903,38 +33892,43 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P279" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>520069</v>
+        <v>520242</v>
       </c>
       <c r="R279" t="n">
-        <v>6933806</v>
+        <v>6933642</v>
       </c>
       <c r="S279" t="n">
         <v>25</v>
@@ -33996,7 +33990,7 @@
         <v>117614268</v>
       </c>
       <c r="B280" t="n">
-        <v>78216</v>
+        <v>78218</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -34095,10 +34089,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>117619065</v>
+        <v>117624132</v>
       </c>
       <c r="B281" t="n">
-        <v>78480</v>
+        <v>90521</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -34111,37 +34105,37 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
       <c r="P281" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>519960</v>
+        <v>520270</v>
       </c>
       <c r="R281" t="n">
-        <v>6933780</v>
+        <v>6933710</v>
       </c>
       <c r="S281" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T281" t="inlineStr">
         <is>
@@ -34171,6 +34165,11 @@
       <c r="AA281" t="inlineStr">
         <is>
           <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AC281" t="inlineStr">
+        <is>
+          <t>På tall med brandljud</t>
         </is>
       </c>
       <c r="AD281" t="b">
@@ -34197,10 +34196,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>117618235</v>
+        <v>117624159</v>
       </c>
       <c r="B282" t="n">
-        <v>96791</v>
+        <v>90909</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -34213,37 +34212,37 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>221945</v>
+        <v>5321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rigidoporus corticola</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
       <c r="P282" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>520117</v>
+        <v>520522</v>
       </c>
       <c r="R282" t="n">
-        <v>6933840</v>
+        <v>6933775</v>
       </c>
       <c r="S282" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T282" t="inlineStr">
         <is>
@@ -34281,6 +34280,7 @@
       <c r="AE282" t="b">
         <v>0</v>
       </c>
+      <c r="AF282" t="inlineStr"/>
       <c r="AG282" t="b">
         <v>0</v>
       </c>
@@ -34299,10 +34299,10 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>117624129</v>
+        <v>117619968</v>
       </c>
       <c r="B283" t="n">
-        <v>90499</v>
+        <v>78482</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -34315,37 +34315,37 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I283" t="inlineStr"/>
       <c r="P283" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>520240</v>
+        <v>519908</v>
       </c>
       <c r="R283" t="n">
-        <v>6933655</v>
+        <v>6933941</v>
       </c>
       <c r="S283" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T283" t="inlineStr">
         <is>
@@ -34375,6 +34375,11 @@
       <c r="AA283" t="inlineStr">
         <is>
           <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AC283" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD283" t="b">
@@ -34401,10 +34406,10 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>117616001</v>
+        <v>117619582</v>
       </c>
       <c r="B284" t="n">
-        <v>79561</v>
+        <v>97859</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -34413,25 +34418,25 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
@@ -34441,13 +34446,13 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>520195</v>
+        <v>519870</v>
       </c>
       <c r="R284" t="n">
-        <v>6933879</v>
+        <v>6933797</v>
       </c>
       <c r="S284" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T284" t="inlineStr">
         <is>
@@ -34503,10 +34508,10 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>117616632</v>
+        <v>117619662</v>
       </c>
       <c r="B285" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -34543,13 +34548,13 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>520219</v>
+        <v>519882</v>
       </c>
       <c r="R285" t="n">
-        <v>6933885</v>
+        <v>6933843</v>
       </c>
       <c r="S285" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T285" t="inlineStr">
         <is>
@@ -34605,10 +34610,10 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>117620923</v>
+        <v>117620029</v>
       </c>
       <c r="B286" t="n">
-        <v>90907</v>
+        <v>79563</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
@@ -34617,25 +34622,25 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>5321</v>
+        <v>6458</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I286" t="inlineStr"/>
@@ -34645,10 +34650,10 @@
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>520467</v>
+        <v>519945</v>
       </c>
       <c r="R286" t="n">
-        <v>6933927</v>
+        <v>6933946</v>
       </c>
       <c r="S286" t="n">
         <v>10</v>
@@ -34707,10 +34712,10 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>117619628</v>
+        <v>117619989</v>
       </c>
       <c r="B287" t="n">
-        <v>78480</v>
+        <v>79563</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -34723,21 +34728,21 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I287" t="inlineStr"/>
@@ -34747,13 +34752,13 @@
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>519878</v>
+        <v>519953</v>
       </c>
       <c r="R287" t="n">
-        <v>6933831</v>
+        <v>6933937</v>
       </c>
       <c r="S287" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T287" t="inlineStr">
         <is>
@@ -34809,10 +34814,10 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>117614781</v>
+        <v>117619504</v>
       </c>
       <c r="B288" t="n">
-        <v>79561</v>
+        <v>79564</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -34825,21 +34830,21 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I288" t="inlineStr"/>
@@ -34849,13 +34854,13 @@
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>520247</v>
+        <v>519854</v>
       </c>
       <c r="R288" t="n">
-        <v>6933662</v>
+        <v>6933806</v>
       </c>
       <c r="S288" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T288" t="inlineStr">
         <is>
@@ -34911,10 +34916,10 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>117620395</v>
+        <v>117619862</v>
       </c>
       <c r="B289" t="n">
-        <v>90499</v>
+        <v>78482</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -34927,21 +34932,21 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I289" t="inlineStr"/>
@@ -34951,13 +34956,13 @@
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>520058</v>
+        <v>519899</v>
       </c>
       <c r="R289" t="n">
-        <v>6934065</v>
+        <v>6933938</v>
       </c>
       <c r="S289" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T289" t="inlineStr">
         <is>
@@ -35013,10 +35018,10 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>117624135</v>
+        <v>117617526</v>
       </c>
       <c r="B290" t="n">
-        <v>90782</v>
+        <v>78218</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
@@ -35029,37 +35034,37 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I290" t="inlineStr"/>
       <c r="P290" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>520054</v>
+        <v>520120</v>
       </c>
       <c r="R290" t="n">
-        <v>6934068</v>
+        <v>6933834</v>
       </c>
       <c r="S290" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T290" t="inlineStr">
         <is>
@@ -35115,10 +35120,10 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>117624154</v>
+        <v>117624124</v>
       </c>
       <c r="B291" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
@@ -35155,10 +35160,10 @@
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>520817</v>
+        <v>520234</v>
       </c>
       <c r="R291" t="n">
-        <v>6933807</v>
+        <v>6933656</v>
       </c>
       <c r="S291" t="n">
         <v>25</v>
@@ -35217,10 +35222,10 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>117615056</v>
+        <v>117615235</v>
       </c>
       <c r="B292" t="n">
-        <v>95384</v>
+        <v>79563</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
@@ -35233,21 +35238,21 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I292" t="inlineStr"/>
@@ -35257,13 +35262,13 @@
         </is>
       </c>
       <c r="Q292" t="n">
-        <v>520233</v>
+        <v>520172</v>
       </c>
       <c r="R292" t="n">
-        <v>6933656</v>
+        <v>6933674</v>
       </c>
       <c r="S292" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T292" t="inlineStr">
         <is>
@@ -35319,10 +35324,10 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>117620029</v>
+        <v>117624138</v>
       </c>
       <c r="B293" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -35355,17 +35360,17 @@
       <c r="I293" t="inlineStr"/>
       <c r="P293" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q293" t="n">
-        <v>519945</v>
+        <v>520508</v>
       </c>
       <c r="R293" t="n">
-        <v>6933946</v>
+        <v>6933774</v>
       </c>
       <c r="S293" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T293" t="inlineStr">
         <is>
@@ -35421,10 +35426,10 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>117615486</v>
+        <v>117615933</v>
       </c>
       <c r="B294" t="n">
-        <v>97836</v>
+        <v>78218</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
@@ -35433,25 +35438,25 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I294" t="inlineStr"/>
@@ -35461,13 +35466,13 @@
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>520113</v>
+        <v>520184</v>
       </c>
       <c r="R294" t="n">
-        <v>6933665</v>
+        <v>6933872</v>
       </c>
       <c r="S294" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T294" t="inlineStr">
         <is>
@@ -35523,10 +35528,10 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>117616291</v>
+        <v>117619522</v>
       </c>
       <c r="B295" t="n">
-        <v>97836</v>
+        <v>79563</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
@@ -35535,25 +35540,25 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I295" t="inlineStr"/>
@@ -35563,13 +35568,13 @@
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>520169</v>
+        <v>519865</v>
       </c>
       <c r="R295" t="n">
-        <v>6933869</v>
+        <v>6933800</v>
       </c>
       <c r="S295" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T295" t="inlineStr">
         <is>
@@ -35625,10 +35630,10 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>117614566</v>
+        <v>117616291</v>
       </c>
       <c r="B296" t="n">
-        <v>90519</v>
+        <v>97838</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
@@ -35637,25 +35642,25 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E296" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I296" t="inlineStr"/>
@@ -35665,13 +35670,13 @@
         </is>
       </c>
       <c r="Q296" t="n">
-        <v>520293</v>
+        <v>520169</v>
       </c>
       <c r="R296" t="n">
-        <v>6933723</v>
+        <v>6933869</v>
       </c>
       <c r="S296" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T296" t="inlineStr">
         <is>
@@ -35701,11 +35706,6 @@
       <c r="AA296" t="inlineStr">
         <is>
           <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AC296" t="inlineStr">
-        <is>
-          <t>På gammal tall med brandljud</t>
         </is>
       </c>
       <c r="AD296" t="b">
@@ -35732,10 +35732,10 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>117624146</v>
+        <v>117624152</v>
       </c>
       <c r="B297" t="n">
-        <v>78216</v>
+        <v>97838</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
@@ -35744,25 +35744,25 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I297" t="inlineStr"/>
@@ -35772,10 +35772,10 @@
         </is>
       </c>
       <c r="Q297" t="n">
-        <v>520355</v>
+        <v>520185</v>
       </c>
       <c r="R297" t="n">
-        <v>6933736</v>
+        <v>6933876</v>
       </c>
       <c r="S297" t="n">
         <v>25</v>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -26399,10 +26399,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>117618638</v>
+        <v>117620347</v>
       </c>
       <c r="B206" t="n">
-        <v>97838</v>
+        <v>90784</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -26411,25 +26411,25 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -26439,10 +26439,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>520072</v>
+        <v>520060</v>
       </c>
       <c r="R206" t="n">
-        <v>6933810</v>
+        <v>6934064</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -26501,10 +26501,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>117624131</v>
+        <v>117624143</v>
       </c>
       <c r="B207" t="n">
-        <v>57441</v>
+        <v>79563</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -26517,21 +26517,21 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -26541,10 +26541,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>520392</v>
+        <v>520804</v>
       </c>
       <c r="R207" t="n">
-        <v>6933757</v>
+        <v>6933797</v>
       </c>
       <c r="S207" t="n">
         <v>25</v>
@@ -26577,11 +26577,6 @@
       <c r="AA207" t="inlineStr">
         <is>
           <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AC207" t="inlineStr">
-        <is>
-          <t>Varnande</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -26608,10 +26603,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>117620347</v>
+        <v>117618638</v>
       </c>
       <c r="B208" t="n">
-        <v>90784</v>
+        <v>97838</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -26620,25 +26615,25 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -26648,10 +26643,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>520060</v>
+        <v>520072</v>
       </c>
       <c r="R208" t="n">
-        <v>6934064</v>
+        <v>6933810</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -26812,10 +26807,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>117624143</v>
+        <v>117624131</v>
       </c>
       <c r="B210" t="n">
-        <v>79563</v>
+        <v>57441</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -26828,21 +26823,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -26852,10 +26847,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>520804</v>
+        <v>520392</v>
       </c>
       <c r="R210" t="n">
-        <v>6933797</v>
+        <v>6933757</v>
       </c>
       <c r="S210" t="n">
         <v>25</v>
@@ -26888,6 +26883,11 @@
       <c r="AA210" t="inlineStr">
         <is>
           <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>Varnande</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -26914,10 +26914,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>117620594</v>
+        <v>117620535</v>
       </c>
       <c r="B211" t="n">
-        <v>95386</v>
+        <v>97838</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -26926,25 +26926,25 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -26954,10 +26954,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>520083</v>
+        <v>520056</v>
       </c>
       <c r="R211" t="n">
-        <v>6934090</v>
+        <v>6934071</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -27322,10 +27322,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>117624144</v>
+        <v>117620594</v>
       </c>
       <c r="B215" t="n">
-        <v>80439</v>
+        <v>95386</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -27338,37 +27338,37 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>1049</v>
+        <v>53</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>520777</v>
+        <v>520083</v>
       </c>
       <c r="R215" t="n">
-        <v>6933766</v>
+        <v>6934090</v>
       </c>
       <c r="S215" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -27424,10 +27424,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>117620535</v>
+        <v>117624144</v>
       </c>
       <c r="B216" t="n">
-        <v>97838</v>
+        <v>80439</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -27436,41 +27436,41 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>520056</v>
+        <v>520777</v>
       </c>
       <c r="R216" t="n">
-        <v>6934071</v>
+        <v>6933766</v>
       </c>
       <c r="S216" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -28342,10 +28342,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>117616189</v>
+        <v>117624141</v>
       </c>
       <c r="B225" t="n">
-        <v>78482</v>
+        <v>79563</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -28358,37 +28358,37 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>520186</v>
+        <v>520775</v>
       </c>
       <c r="R225" t="n">
-        <v>6933870</v>
+        <v>6933753</v>
       </c>
       <c r="S225" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T225" t="inlineStr">
         <is>
@@ -28444,10 +28444,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>117624136</v>
+        <v>117616189</v>
       </c>
       <c r="B226" t="n">
-        <v>79563</v>
+        <v>78482</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -28460,37 +28460,37 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>520420</v>
+        <v>520186</v>
       </c>
       <c r="R226" t="n">
-        <v>6933788</v>
+        <v>6933870</v>
       </c>
       <c r="S226" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T226" t="inlineStr">
         <is>
@@ -28520,11 +28520,6 @@
       <c r="AA226" t="inlineStr">
         <is>
           <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AC226" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -28551,7 +28546,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>117624141</v>
+        <v>117624136</v>
       </c>
       <c r="B227" t="n">
         <v>79563</v>
@@ -28591,10 +28586,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>520775</v>
+        <v>520420</v>
       </c>
       <c r="R227" t="n">
-        <v>6933753</v>
+        <v>6933788</v>
       </c>
       <c r="S227" t="n">
         <v>25</v>
@@ -28627,6 +28622,11 @@
       <c r="AA227" t="inlineStr">
         <is>
           <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AC227" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -30897,10 +30897,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>117615974</v>
+        <v>117615300</v>
       </c>
       <c r="B250" t="n">
-        <v>56500</v>
+        <v>79563</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -30909,25 +30909,25 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -30937,13 +30937,13 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>520185</v>
+        <v>520171</v>
       </c>
       <c r="R250" t="n">
-        <v>6933863</v>
+        <v>6933646</v>
       </c>
       <c r="S250" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T250" t="inlineStr">
         <is>
@@ -30973,11 +30973,6 @@
       <c r="AA250" t="inlineStr">
         <is>
           <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AC250" t="inlineStr">
-        <is>
-          <t>Färsk spillning</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -31004,7 +30999,7 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>117615300</v>
+        <v>117617034</v>
       </c>
       <c r="B251" t="n">
         <v>79563</v>
@@ -31044,13 +31039,13 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>520171</v>
+        <v>520184</v>
       </c>
       <c r="R251" t="n">
-        <v>6933646</v>
+        <v>6933959</v>
       </c>
       <c r="S251" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T251" t="inlineStr">
         <is>
@@ -31106,10 +31101,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>117617034</v>
+        <v>117624156</v>
       </c>
       <c r="B252" t="n">
-        <v>79563</v>
+        <v>78482</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -31122,37 +31117,37 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
       <c r="P252" t="inlineStr">
         <is>
-          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>520184</v>
+        <v>520571</v>
       </c>
       <c r="R252" t="n">
-        <v>6933959</v>
+        <v>6933768</v>
       </c>
       <c r="S252" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T252" t="inlineStr">
         <is>
@@ -31208,10 +31203,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>117624156</v>
+        <v>117615974</v>
       </c>
       <c r="B253" t="n">
-        <v>78482</v>
+        <v>56500</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -31220,41 +31215,41 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget (Grinsjöberget), Mpd</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>520571</v>
+        <v>520185</v>
       </c>
       <c r="R253" t="n">
-        <v>6933768</v>
+        <v>6933863</v>
       </c>
       <c r="S253" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T253" t="inlineStr">
         <is>
@@ -31284,6 +31279,11 @@
       <c r="AA253" t="inlineStr">
         <is>
           <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AC253" t="inlineStr">
+        <is>
+          <t>Färsk spillning</t>
         </is>
       </c>
       <c r="AD253" t="b">

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY297"/>
+  <dimension ref="A1:AY300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35832,6 +35832,316 @@
       </c>
       <c r="AY297" t="inlineStr"/>
     </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>120593385</v>
+      </c>
+      <c r="B298" t="n">
+        <v>78279</v>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E298" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr"/>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>Snöberg N, Mpd</t>
+        </is>
+      </c>
+      <c r="Q298" t="n">
+        <v>520822</v>
+      </c>
+      <c r="R298" t="n">
+        <v>6933973</v>
+      </c>
+      <c r="S298" t="n">
+        <v>10</v>
+      </c>
+      <c r="T298" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U298" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V298" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W298" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y298" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA298" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD298" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE298" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG298" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT298" t="inlineStr"/>
+      <c r="AW298" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX298" t="inlineStr">
+        <is>
+          <t>Johannes Esberg</t>
+        </is>
+      </c>
+      <c r="AY298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>120593206</v>
+      </c>
+      <c r="B299" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E299" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr"/>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>Snöberg N, Mpd</t>
+        </is>
+      </c>
+      <c r="Q299" t="n">
+        <v>521003</v>
+      </c>
+      <c r="R299" t="n">
+        <v>6933490</v>
+      </c>
+      <c r="S299" t="n">
+        <v>10</v>
+      </c>
+      <c r="T299" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U299" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V299" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W299" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y299" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA299" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD299" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE299" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG299" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT299" t="inlineStr"/>
+      <c r="AW299" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX299" t="inlineStr">
+        <is>
+          <t>Johannes Esberg</t>
+        </is>
+      </c>
+      <c r="AY299" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>120593384</v>
+      </c>
+      <c r="B300" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E300" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P300" t="inlineStr">
+        <is>
+          <t>Snöberg N, Mpd</t>
+        </is>
+      </c>
+      <c r="Q300" t="n">
+        <v>520842</v>
+      </c>
+      <c r="R300" t="n">
+        <v>6933947</v>
+      </c>
+      <c r="S300" t="n">
+        <v>10</v>
+      </c>
+      <c r="T300" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U300" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V300" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W300" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y300" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA300" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD300" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE300" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG300" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT300" t="inlineStr"/>
+      <c r="AW300" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX300" t="inlineStr">
+        <is>
+          <t>Johannes Esberg</t>
+        </is>
+      </c>
+      <c r="AY300" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -36144,10 +36144,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>122277223</v>
+        <v>122277219</v>
       </c>
       <c r="B301" t="n">
-        <v>56576</v>
+        <v>90797</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -36160,46 +36160,37 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I301" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M301" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr"/>
       <c r="P301" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>520088</v>
+        <v>519857</v>
       </c>
       <c r="R301" t="n">
-        <v>6933802</v>
+        <v>6933857</v>
       </c>
       <c r="S301" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T301" t="inlineStr">
         <is>
@@ -36255,10 +36246,10 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>122277252</v>
+        <v>122277221</v>
       </c>
       <c r="B302" t="n">
-        <v>79263</v>
+        <v>98175</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -36267,25 +36258,25 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I302" t="inlineStr"/>
@@ -36295,10 +36286,10 @@
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>520742</v>
+        <v>519944</v>
       </c>
       <c r="R302" t="n">
-        <v>6933667</v>
+        <v>6934006</v>
       </c>
       <c r="S302" t="n">
         <v>10</v>
@@ -36357,10 +36348,10 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>122277244</v>
+        <v>122277223</v>
       </c>
       <c r="B303" t="n">
-        <v>78679</v>
+        <v>56576</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -36373,37 +36364,46 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>185</v>
+        <v>102612</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I303" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P303" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>520589</v>
+        <v>520088</v>
       </c>
       <c r="R303" t="n">
-        <v>6933704</v>
+        <v>6933802</v>
       </c>
       <c r="S303" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T303" t="inlineStr">
         <is>
@@ -36459,10 +36459,10 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>122277225</v>
+        <v>122277240</v>
       </c>
       <c r="B304" t="n">
-        <v>98175</v>
+        <v>56576</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -36471,41 +36471,50 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I304" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P304" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>520115</v>
+        <v>520322</v>
       </c>
       <c r="R304" t="n">
-        <v>6933705</v>
+        <v>6933606</v>
       </c>
       <c r="S304" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T304" t="inlineStr">
         <is>
@@ -36561,10 +36570,10 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>122277254</v>
+        <v>122277249</v>
       </c>
       <c r="B305" t="n">
-        <v>79726</v>
+        <v>57744</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -36573,41 +36582,50 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I305" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P305" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>520941</v>
+        <v>520694</v>
       </c>
       <c r="R305" t="n">
-        <v>6933486</v>
+        <v>6933625</v>
       </c>
       <c r="S305" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T305" t="inlineStr">
         <is>
@@ -36663,10 +36681,10 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>122277249</v>
+        <v>122277227</v>
       </c>
       <c r="B306" t="n">
-        <v>57744</v>
+        <v>98175</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -36675,50 +36693,41 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I306" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M306" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr"/>
       <c r="P306" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>520694</v>
+        <v>520109</v>
       </c>
       <c r="R306" t="n">
-        <v>6933625</v>
+        <v>6933653</v>
       </c>
       <c r="S306" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T306" t="inlineStr">
         <is>
@@ -36774,10 +36783,10 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>122277238</v>
+        <v>122277244</v>
       </c>
       <c r="B307" t="n">
-        <v>79727</v>
+        <v>78679</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -36790,21 +36799,21 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I307" t="inlineStr"/>
@@ -36814,10 +36823,10 @@
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>520316</v>
+        <v>520589</v>
       </c>
       <c r="R307" t="n">
-        <v>6933594</v>
+        <v>6933704</v>
       </c>
       <c r="S307" t="n">
         <v>10</v>
@@ -36876,10 +36885,10 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>122277230</v>
+        <v>122277238</v>
       </c>
       <c r="B308" t="n">
-        <v>57527</v>
+        <v>79727</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -36892,46 +36901,37 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I308" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M308" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr"/>
       <c r="P308" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>519846</v>
+        <v>520316</v>
       </c>
       <c r="R308" t="n">
-        <v>6933784</v>
+        <v>6933594</v>
       </c>
       <c r="S308" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T308" t="inlineStr">
         <is>
@@ -36987,10 +36987,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>122277227</v>
+        <v>122277246</v>
       </c>
       <c r="B309" t="n">
-        <v>98175</v>
+        <v>78645</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -36999,25 +36999,25 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I309" t="inlineStr"/>
@@ -37027,10 +37027,10 @@
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>520109</v>
+        <v>520527</v>
       </c>
       <c r="R309" t="n">
-        <v>6933653</v>
+        <v>6933702</v>
       </c>
       <c r="S309" t="n">
         <v>10</v>
@@ -37089,10 +37089,10 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>122277246</v>
+        <v>122277230</v>
       </c>
       <c r="B310" t="n">
-        <v>78645</v>
+        <v>57527</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -37105,37 +37105,46 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I310" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P310" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>520527</v>
+        <v>519846</v>
       </c>
       <c r="R310" t="n">
-        <v>6933702</v>
+        <v>6933784</v>
       </c>
       <c r="S310" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T310" t="inlineStr">
         <is>
@@ -37191,10 +37200,10 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>122277240</v>
+        <v>122277225</v>
       </c>
       <c r="B311" t="n">
-        <v>56576</v>
+        <v>98175</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -37203,50 +37212,41 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I311" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M311" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr"/>
       <c r="P311" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>520322</v>
+        <v>520115</v>
       </c>
       <c r="R311" t="n">
-        <v>6933606</v>
+        <v>6933705</v>
       </c>
       <c r="S311" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T311" t="inlineStr">
         <is>
@@ -37302,10 +37302,10 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>122277219</v>
+        <v>122277254</v>
       </c>
       <c r="B312" t="n">
-        <v>90797</v>
+        <v>79726</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -37318,21 +37318,21 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I312" t="inlineStr"/>
@@ -37342,10 +37342,10 @@
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>519857</v>
+        <v>520941</v>
       </c>
       <c r="R312" t="n">
-        <v>6933857</v>
+        <v>6933486</v>
       </c>
       <c r="S312" t="n">
         <v>10</v>
@@ -37404,10 +37404,10 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>122277242</v>
+        <v>122277234</v>
       </c>
       <c r="B313" t="n">
-        <v>79726</v>
+        <v>98175</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -37416,25 +37416,25 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E313" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I313" t="inlineStr"/>
@@ -37444,10 +37444,10 @@
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>520443</v>
+        <v>520330</v>
       </c>
       <c r="R313" t="n">
-        <v>6933656</v>
+        <v>6933624</v>
       </c>
       <c r="S313" t="n">
         <v>10</v>
@@ -37506,10 +37506,10 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>122277234</v>
+        <v>122277242</v>
       </c>
       <c r="B314" t="n">
-        <v>98175</v>
+        <v>79726</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -37518,25 +37518,25 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I314" t="inlineStr"/>
@@ -37546,10 +37546,10 @@
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>520330</v>
+        <v>520443</v>
       </c>
       <c r="R314" t="n">
-        <v>6933624</v>
+        <v>6933656</v>
       </c>
       <c r="S314" t="n">
         <v>10</v>
@@ -37608,10 +37608,10 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>122277221</v>
+        <v>122277252</v>
       </c>
       <c r="B315" t="n">
-        <v>98175</v>
+        <v>79263</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -37620,25 +37620,25 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I315" t="inlineStr"/>
@@ -37648,10 +37648,10 @@
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>519944</v>
+        <v>520742</v>
       </c>
       <c r="R315" t="n">
-        <v>6934006</v>
+        <v>6933667</v>
       </c>
       <c r="S315" t="n">
         <v>10</v>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -36144,10 +36144,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>122277219</v>
+        <v>122277234</v>
       </c>
       <c r="B301" t="n">
-        <v>90797</v>
+        <v>98185</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -36156,25 +36156,25 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I301" t="inlineStr"/>
@@ -36184,10 +36184,10 @@
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>519857</v>
+        <v>520330</v>
       </c>
       <c r="R301" t="n">
-        <v>6933857</v>
+        <v>6933624</v>
       </c>
       <c r="S301" t="n">
         <v>10</v>
@@ -36246,10 +36246,10 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>122277221</v>
+        <v>122277240</v>
       </c>
       <c r="B302" t="n">
-        <v>98175</v>
+        <v>56576</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -36258,41 +36258,50 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I302" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P302" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>519944</v>
+        <v>520322</v>
       </c>
       <c r="R302" t="n">
-        <v>6934006</v>
+        <v>6933606</v>
       </c>
       <c r="S302" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T302" t="inlineStr">
         <is>
@@ -36348,10 +36357,10 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>122277223</v>
+        <v>122277227</v>
       </c>
       <c r="B303" t="n">
-        <v>56576</v>
+        <v>98185</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -36360,50 +36369,41 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I303" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M303" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr"/>
       <c r="P303" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>520088</v>
+        <v>520109</v>
       </c>
       <c r="R303" t="n">
-        <v>6933802</v>
+        <v>6933653</v>
       </c>
       <c r="S303" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T303" t="inlineStr">
         <is>
@@ -36459,10 +36459,10 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>122277240</v>
+        <v>122277219</v>
       </c>
       <c r="B304" t="n">
-        <v>56576</v>
+        <v>90807</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -36475,46 +36475,37 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I304" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M304" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr"/>
       <c r="P304" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>520322</v>
+        <v>519857</v>
       </c>
       <c r="R304" t="n">
-        <v>6933606</v>
+        <v>6933857</v>
       </c>
       <c r="S304" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T304" t="inlineStr">
         <is>
@@ -36570,10 +36561,10 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>122277249</v>
+        <v>122277252</v>
       </c>
       <c r="B305" t="n">
-        <v>57744</v>
+        <v>79264</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -36582,50 +36573,41 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I305" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M305" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr"/>
       <c r="P305" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>520694</v>
+        <v>520742</v>
       </c>
       <c r="R305" t="n">
-        <v>6933625</v>
+        <v>6933667</v>
       </c>
       <c r="S305" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T305" t="inlineStr">
         <is>
@@ -36681,10 +36663,10 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>122277227</v>
+        <v>122277254</v>
       </c>
       <c r="B306" t="n">
-        <v>98175</v>
+        <v>79727</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -36693,25 +36675,25 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I306" t="inlineStr"/>
@@ -36721,10 +36703,10 @@
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>520109</v>
+        <v>520941</v>
       </c>
       <c r="R306" t="n">
-        <v>6933653</v>
+        <v>6933486</v>
       </c>
       <c r="S306" t="n">
         <v>10</v>
@@ -36783,10 +36765,10 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>122277244</v>
+        <v>122277246</v>
       </c>
       <c r="B307" t="n">
-        <v>78679</v>
+        <v>78646</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -36799,21 +36781,21 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I307" t="inlineStr"/>
@@ -36823,10 +36805,10 @@
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>520589</v>
+        <v>520527</v>
       </c>
       <c r="R307" t="n">
-        <v>6933704</v>
+        <v>6933702</v>
       </c>
       <c r="S307" t="n">
         <v>10</v>
@@ -36885,10 +36867,10 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>122277238</v>
+        <v>122277223</v>
       </c>
       <c r="B308" t="n">
-        <v>79727</v>
+        <v>56576</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -36901,37 +36883,46 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>2081</v>
+        <v>102612</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I308" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P308" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>520316</v>
+        <v>520088</v>
       </c>
       <c r="R308" t="n">
-        <v>6933594</v>
+        <v>6933802</v>
       </c>
       <c r="S308" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T308" t="inlineStr">
         <is>
@@ -36987,10 +36978,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>122277246</v>
+        <v>122277225</v>
       </c>
       <c r="B309" t="n">
-        <v>78645</v>
+        <v>98185</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -36999,25 +36990,25 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I309" t="inlineStr"/>
@@ -37027,10 +37018,10 @@
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>520527</v>
+        <v>520115</v>
       </c>
       <c r="R309" t="n">
-        <v>6933702</v>
+        <v>6933705</v>
       </c>
       <c r="S309" t="n">
         <v>10</v>
@@ -37089,10 +37080,10 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>122277230</v>
+        <v>122277238</v>
       </c>
       <c r="B310" t="n">
-        <v>57527</v>
+        <v>79728</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -37105,46 +37096,37 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I310" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M310" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr"/>
       <c r="P310" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>519846</v>
+        <v>520316</v>
       </c>
       <c r="R310" t="n">
-        <v>6933784</v>
+        <v>6933594</v>
       </c>
       <c r="S310" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T310" t="inlineStr">
         <is>
@@ -37200,10 +37182,10 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>122277225</v>
+        <v>122277242</v>
       </c>
       <c r="B311" t="n">
-        <v>98175</v>
+        <v>79727</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -37212,25 +37194,25 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I311" t="inlineStr"/>
@@ -37240,10 +37222,10 @@
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>520115</v>
+        <v>520443</v>
       </c>
       <c r="R311" t="n">
-        <v>6933705</v>
+        <v>6933656</v>
       </c>
       <c r="S311" t="n">
         <v>10</v>
@@ -37302,10 +37284,10 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>122277254</v>
+        <v>122277230</v>
       </c>
       <c r="B312" t="n">
-        <v>79726</v>
+        <v>57527</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -37318,37 +37300,46 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I312" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P312" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>520941</v>
+        <v>519846</v>
       </c>
       <c r="R312" t="n">
-        <v>6933486</v>
+        <v>6933784</v>
       </c>
       <c r="S312" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T312" t="inlineStr">
         <is>
@@ -37404,10 +37395,10 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>122277234</v>
+        <v>122277249</v>
       </c>
       <c r="B313" t="n">
-        <v>98175</v>
+        <v>57744</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -37416,41 +37407,50 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E313" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I313" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P313" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>520330</v>
+        <v>520694</v>
       </c>
       <c r="R313" t="n">
-        <v>6933624</v>
+        <v>6933625</v>
       </c>
       <c r="S313" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T313" t="inlineStr">
         <is>
@@ -37506,10 +37506,10 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>122277242</v>
+        <v>122277221</v>
       </c>
       <c r="B314" t="n">
-        <v>79726</v>
+        <v>98185</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -37518,25 +37518,25 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I314" t="inlineStr"/>
@@ -37546,10 +37546,10 @@
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>520443</v>
+        <v>519944</v>
       </c>
       <c r="R314" t="n">
-        <v>6933656</v>
+        <v>6934006</v>
       </c>
       <c r="S314" t="n">
         <v>10</v>
@@ -37608,10 +37608,10 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>122277252</v>
+        <v>122277244</v>
       </c>
       <c r="B315" t="n">
-        <v>79263</v>
+        <v>78680</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -37624,21 +37624,21 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I315" t="inlineStr"/>
@@ -37648,10 +37648,10 @@
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>520742</v>
+        <v>520589</v>
       </c>
       <c r="R315" t="n">
-        <v>6933667</v>
+        <v>6933704</v>
       </c>
       <c r="S315" t="n">
         <v>10</v>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -36144,10 +36144,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>122277234</v>
+        <v>122277223</v>
       </c>
       <c r="B301" t="n">
-        <v>98185</v>
+        <v>56576</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -36156,41 +36156,50 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I301" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P301" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>520330</v>
+        <v>520088</v>
       </c>
       <c r="R301" t="n">
-        <v>6933624</v>
+        <v>6933802</v>
       </c>
       <c r="S301" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T301" t="inlineStr">
         <is>
@@ -36246,10 +36255,10 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>122277240</v>
+        <v>122277244</v>
       </c>
       <c r="B302" t="n">
-        <v>56576</v>
+        <v>78680</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -36262,46 +36271,37 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>102612</v>
+        <v>185</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I302" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M302" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr"/>
       <c r="P302" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>520322</v>
+        <v>520589</v>
       </c>
       <c r="R302" t="n">
-        <v>6933606</v>
+        <v>6933704</v>
       </c>
       <c r="S302" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T302" t="inlineStr">
         <is>
@@ -36357,7 +36357,7 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>122277227</v>
+        <v>122277225</v>
       </c>
       <c r="B303" t="n">
         <v>98185</v>
@@ -36397,10 +36397,10 @@
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>520109</v>
+        <v>520115</v>
       </c>
       <c r="R303" t="n">
-        <v>6933653</v>
+        <v>6933705</v>
       </c>
       <c r="S303" t="n">
         <v>10</v>
@@ -36459,10 +36459,10 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>122277219</v>
+        <v>122277238</v>
       </c>
       <c r="B304" t="n">
-        <v>90807</v>
+        <v>79728</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -36475,21 +36475,21 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I304" t="inlineStr"/>
@@ -36499,10 +36499,10 @@
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>519857</v>
+        <v>520316</v>
       </c>
       <c r="R304" t="n">
-        <v>6933857</v>
+        <v>6933594</v>
       </c>
       <c r="S304" t="n">
         <v>10</v>
@@ -36561,10 +36561,10 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>122277252</v>
+        <v>122277221</v>
       </c>
       <c r="B305" t="n">
-        <v>79264</v>
+        <v>98185</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -36573,25 +36573,25 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I305" t="inlineStr"/>
@@ -36601,10 +36601,10 @@
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>520742</v>
+        <v>519944</v>
       </c>
       <c r="R305" t="n">
-        <v>6933667</v>
+        <v>6934006</v>
       </c>
       <c r="S305" t="n">
         <v>10</v>
@@ -36663,10 +36663,10 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>122277254</v>
+        <v>122277230</v>
       </c>
       <c r="B306" t="n">
-        <v>79727</v>
+        <v>57527</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -36679,37 +36679,46 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I306" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P306" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>520941</v>
+        <v>519846</v>
       </c>
       <c r="R306" t="n">
-        <v>6933486</v>
+        <v>6933784</v>
       </c>
       <c r="S306" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T306" t="inlineStr">
         <is>
@@ -36765,10 +36774,10 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>122277246</v>
+        <v>122277234</v>
       </c>
       <c r="B307" t="n">
-        <v>78646</v>
+        <v>98185</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -36777,25 +36786,25 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I307" t="inlineStr"/>
@@ -36805,10 +36814,10 @@
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>520527</v>
+        <v>520330</v>
       </c>
       <c r="R307" t="n">
-        <v>6933702</v>
+        <v>6933624</v>
       </c>
       <c r="S307" t="n">
         <v>10</v>
@@ -36867,10 +36876,10 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>122277223</v>
+        <v>122277252</v>
       </c>
       <c r="B308" t="n">
-        <v>56576</v>
+        <v>79264</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -36883,46 +36892,37 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>102612</v>
+        <v>6453</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I308" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M308" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr"/>
       <c r="P308" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>520088</v>
+        <v>520742</v>
       </c>
       <c r="R308" t="n">
-        <v>6933802</v>
+        <v>6933667</v>
       </c>
       <c r="S308" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T308" t="inlineStr">
         <is>
@@ -36978,10 +36978,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>122277225</v>
+        <v>122277249</v>
       </c>
       <c r="B309" t="n">
-        <v>98185</v>
+        <v>57744</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -36990,41 +36990,50 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I309" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P309" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>520115</v>
+        <v>520694</v>
       </c>
       <c r="R309" t="n">
-        <v>6933705</v>
+        <v>6933625</v>
       </c>
       <c r="S309" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T309" t="inlineStr">
         <is>
@@ -37080,10 +37089,10 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>122277238</v>
+        <v>122277227</v>
       </c>
       <c r="B310" t="n">
-        <v>79728</v>
+        <v>98185</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -37092,25 +37101,25 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I310" t="inlineStr"/>
@@ -37120,10 +37129,10 @@
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>520316</v>
+        <v>520109</v>
       </c>
       <c r="R310" t="n">
-        <v>6933594</v>
+        <v>6933653</v>
       </c>
       <c r="S310" t="n">
         <v>10</v>
@@ -37182,10 +37191,10 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>122277242</v>
+        <v>122277219</v>
       </c>
       <c r="B311" t="n">
-        <v>79727</v>
+        <v>90807</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -37198,21 +37207,21 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I311" t="inlineStr"/>
@@ -37222,10 +37231,10 @@
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>520443</v>
+        <v>519857</v>
       </c>
       <c r="R311" t="n">
-        <v>6933656</v>
+        <v>6933857</v>
       </c>
       <c r="S311" t="n">
         <v>10</v>
@@ -37284,10 +37293,10 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>122277230</v>
+        <v>122277246</v>
       </c>
       <c r="B312" t="n">
-        <v>57527</v>
+        <v>78646</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -37300,46 +37309,37 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I312" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M312" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr"/>
       <c r="P312" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>519846</v>
+        <v>520527</v>
       </c>
       <c r="R312" t="n">
-        <v>6933784</v>
+        <v>6933702</v>
       </c>
       <c r="S312" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T312" t="inlineStr">
         <is>
@@ -37395,10 +37395,10 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>122277249</v>
+        <v>122277242</v>
       </c>
       <c r="B313" t="n">
-        <v>57744</v>
+        <v>79727</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -37407,50 +37407,41 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E313" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I313" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M313" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr"/>
       <c r="P313" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>520694</v>
+        <v>520443</v>
       </c>
       <c r="R313" t="n">
-        <v>6933625</v>
+        <v>6933656</v>
       </c>
       <c r="S313" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T313" t="inlineStr">
         <is>
@@ -37506,10 +37497,10 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>122277221</v>
+        <v>122277254</v>
       </c>
       <c r="B314" t="n">
-        <v>98185</v>
+        <v>79727</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -37518,25 +37509,25 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I314" t="inlineStr"/>
@@ -37546,10 +37537,10 @@
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>519944</v>
+        <v>520941</v>
       </c>
       <c r="R314" t="n">
-        <v>6934006</v>
+        <v>6933486</v>
       </c>
       <c r="S314" t="n">
         <v>10</v>
@@ -37608,10 +37599,10 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>122277244</v>
+        <v>122277240</v>
       </c>
       <c r="B315" t="n">
-        <v>78680</v>
+        <v>56576</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -37624,37 +37615,46 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>185</v>
+        <v>102612</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I315" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P315" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>520589</v>
+        <v>520322</v>
       </c>
       <c r="R315" t="n">
-        <v>6933704</v>
+        <v>6933606</v>
       </c>
       <c r="S315" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T315" t="inlineStr">
         <is>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -36144,10 +36144,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>122277223</v>
+        <v>122277249</v>
       </c>
       <c r="B301" t="n">
-        <v>56576</v>
+        <v>57749</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -36156,20 +36156,20 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>102612</v>
+        <v>103015</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -36184,7 +36184,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P301" t="inlineStr">
@@ -36193,10 +36193,10 @@
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>520088</v>
+        <v>520694</v>
       </c>
       <c r="R301" t="n">
-        <v>6933802</v>
+        <v>6933625</v>
       </c>
       <c r="S301" t="n">
         <v>25</v>
@@ -36255,10 +36255,10 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>122277244</v>
+        <v>122277254</v>
       </c>
       <c r="B302" t="n">
-        <v>78680</v>
+        <v>79732</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -36271,21 +36271,21 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I302" t="inlineStr"/>
@@ -36295,10 +36295,10 @@
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>520589</v>
+        <v>520941</v>
       </c>
       <c r="R302" t="n">
-        <v>6933704</v>
+        <v>6933486</v>
       </c>
       <c r="S302" t="n">
         <v>10</v>
@@ -36357,10 +36357,10 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>122277225</v>
+        <v>122277221</v>
       </c>
       <c r="B303" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -36397,10 +36397,10 @@
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>520115</v>
+        <v>519944</v>
       </c>
       <c r="R303" t="n">
-        <v>6933705</v>
+        <v>6934006</v>
       </c>
       <c r="S303" t="n">
         <v>10</v>
@@ -36462,7 +36462,7 @@
         <v>122277238</v>
       </c>
       <c r="B304" t="n">
-        <v>79728</v>
+        <v>79733</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -36561,10 +36561,10 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>122277221</v>
+        <v>122277230</v>
       </c>
       <c r="B305" t="n">
-        <v>98185</v>
+        <v>57532</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -36573,41 +36573,50 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I305" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P305" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>519944</v>
+        <v>519846</v>
       </c>
       <c r="R305" t="n">
-        <v>6934006</v>
+        <v>6933784</v>
       </c>
       <c r="S305" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T305" t="inlineStr">
         <is>
@@ -36663,10 +36672,10 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>122277230</v>
+        <v>122277242</v>
       </c>
       <c r="B306" t="n">
-        <v>57527</v>
+        <v>79732</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -36679,46 +36688,37 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I306" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M306" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr"/>
       <c r="P306" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>519846</v>
+        <v>520443</v>
       </c>
       <c r="R306" t="n">
-        <v>6933784</v>
+        <v>6933656</v>
       </c>
       <c r="S306" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T306" t="inlineStr">
         <is>
@@ -36774,10 +36774,10 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>122277234</v>
+        <v>122277227</v>
       </c>
       <c r="B307" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -36814,10 +36814,10 @@
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>520330</v>
+        <v>520109</v>
       </c>
       <c r="R307" t="n">
-        <v>6933624</v>
+        <v>6933653</v>
       </c>
       <c r="S307" t="n">
         <v>10</v>
@@ -36876,10 +36876,10 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>122277252</v>
+        <v>122277246</v>
       </c>
       <c r="B308" t="n">
-        <v>79264</v>
+        <v>78651</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -36892,21 +36892,21 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I308" t="inlineStr"/>
@@ -36916,10 +36916,10 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>520742</v>
+        <v>520527</v>
       </c>
       <c r="R308" t="n">
-        <v>6933667</v>
+        <v>6933702</v>
       </c>
       <c r="S308" t="n">
         <v>10</v>
@@ -36978,10 +36978,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>122277249</v>
+        <v>122277244</v>
       </c>
       <c r="B309" t="n">
-        <v>57744</v>
+        <v>78685</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -36990,50 +36990,41 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>103015</v>
+        <v>185</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I309" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M309" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr"/>
       <c r="P309" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>520694</v>
+        <v>520589</v>
       </c>
       <c r="R309" t="n">
-        <v>6933625</v>
+        <v>6933704</v>
       </c>
       <c r="S309" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T309" t="inlineStr">
         <is>
@@ -37089,10 +37080,10 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>122277227</v>
+        <v>122277234</v>
       </c>
       <c r="B310" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -37129,10 +37120,10 @@
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>520109</v>
+        <v>520330</v>
       </c>
       <c r="R310" t="n">
-        <v>6933653</v>
+        <v>6933624</v>
       </c>
       <c r="S310" t="n">
         <v>10</v>
@@ -37194,7 +37185,7 @@
         <v>122277219</v>
       </c>
       <c r="B311" t="n">
-        <v>90807</v>
+        <v>90819</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -37293,10 +37284,10 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>122277246</v>
+        <v>122277223</v>
       </c>
       <c r="B312" t="n">
-        <v>78646</v>
+        <v>56581</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -37309,37 +37300,46 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I312" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P312" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>520527</v>
+        <v>520088</v>
       </c>
       <c r="R312" t="n">
-        <v>6933702</v>
+        <v>6933802</v>
       </c>
       <c r="S312" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T312" t="inlineStr">
         <is>
@@ -37395,10 +37395,10 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>122277242</v>
+        <v>122277252</v>
       </c>
       <c r="B313" t="n">
-        <v>79727</v>
+        <v>79269</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -37411,21 +37411,21 @@
         </is>
       </c>
       <c r="E313" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I313" t="inlineStr"/>
@@ -37435,10 +37435,10 @@
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>520443</v>
+        <v>520742</v>
       </c>
       <c r="R313" t="n">
-        <v>6933656</v>
+        <v>6933667</v>
       </c>
       <c r="S313" t="n">
         <v>10</v>
@@ -37497,10 +37497,10 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>122277254</v>
+        <v>122277240</v>
       </c>
       <c r="B314" t="n">
-        <v>79727</v>
+        <v>56581</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -37513,37 +37513,46 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I314" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P314" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>520941</v>
+        <v>520322</v>
       </c>
       <c r="R314" t="n">
-        <v>6933486</v>
+        <v>6933606</v>
       </c>
       <c r="S314" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T314" t="inlineStr">
         <is>
@@ -37599,10 +37608,10 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>122277240</v>
+        <v>122277225</v>
       </c>
       <c r="B315" t="n">
-        <v>56576</v>
+        <v>98197</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -37611,50 +37620,41 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I315" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M315" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr"/>
       <c r="P315" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>520322</v>
+        <v>520115</v>
       </c>
       <c r="R315" t="n">
-        <v>6933606</v>
+        <v>6933705</v>
       </c>
       <c r="S315" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T315" t="inlineStr">
         <is>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -36144,10 +36144,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>122277249</v>
+        <v>122277219</v>
       </c>
       <c r="B301" t="n">
-        <v>57749</v>
+        <v>90826</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -36156,50 +36156,41 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I301" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M301" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr"/>
       <c r="P301" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>520694</v>
+        <v>519857</v>
       </c>
       <c r="R301" t="n">
-        <v>6933625</v>
+        <v>6933857</v>
       </c>
       <c r="S301" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T301" t="inlineStr">
         <is>
@@ -36255,10 +36246,10 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>122277254</v>
+        <v>122277246</v>
       </c>
       <c r="B302" t="n">
-        <v>79732</v>
+        <v>78651</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -36271,21 +36262,21 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I302" t="inlineStr"/>
@@ -36295,10 +36286,10 @@
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>520941</v>
+        <v>520527</v>
       </c>
       <c r="R302" t="n">
-        <v>6933486</v>
+        <v>6933702</v>
       </c>
       <c r="S302" t="n">
         <v>10</v>
@@ -36357,10 +36348,10 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>122277221</v>
+        <v>122277225</v>
       </c>
       <c r="B303" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -36397,10 +36388,10 @@
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>519944</v>
+        <v>520115</v>
       </c>
       <c r="R303" t="n">
-        <v>6934006</v>
+        <v>6933705</v>
       </c>
       <c r="S303" t="n">
         <v>10</v>
@@ -36561,10 +36552,10 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>122277230</v>
+        <v>122277254</v>
       </c>
       <c r="B305" t="n">
-        <v>57532</v>
+        <v>79732</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -36577,46 +36568,37 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I305" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M305" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr"/>
       <c r="P305" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>519846</v>
+        <v>520941</v>
       </c>
       <c r="R305" t="n">
-        <v>6933784</v>
+        <v>6933486</v>
       </c>
       <c r="S305" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T305" t="inlineStr">
         <is>
@@ -36672,10 +36654,10 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>122277242</v>
+        <v>122277234</v>
       </c>
       <c r="B306" t="n">
-        <v>79732</v>
+        <v>98202</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -36684,25 +36666,25 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I306" t="inlineStr"/>
@@ -36712,10 +36694,10 @@
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>520443</v>
+        <v>520330</v>
       </c>
       <c r="R306" t="n">
-        <v>6933656</v>
+        <v>6933624</v>
       </c>
       <c r="S306" t="n">
         <v>10</v>
@@ -36774,10 +36756,10 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>122277227</v>
+        <v>122277223</v>
       </c>
       <c r="B307" t="n">
-        <v>98197</v>
+        <v>56581</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -36786,41 +36768,50 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I307" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P307" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>520109</v>
+        <v>520088</v>
       </c>
       <c r="R307" t="n">
-        <v>6933653</v>
+        <v>6933802</v>
       </c>
       <c r="S307" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T307" t="inlineStr">
         <is>
@@ -36876,10 +36867,10 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>122277246</v>
+        <v>122277221</v>
       </c>
       <c r="B308" t="n">
-        <v>78651</v>
+        <v>98202</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -36888,25 +36879,25 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I308" t="inlineStr"/>
@@ -36916,10 +36907,10 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>520527</v>
+        <v>519944</v>
       </c>
       <c r="R308" t="n">
-        <v>6933702</v>
+        <v>6934006</v>
       </c>
       <c r="S308" t="n">
         <v>10</v>
@@ -36978,10 +36969,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>122277244</v>
+        <v>122277240</v>
       </c>
       <c r="B309" t="n">
-        <v>78685</v>
+        <v>56581</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -36994,37 +36985,46 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>185</v>
+        <v>102612</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I309" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P309" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>520589</v>
+        <v>520322</v>
       </c>
       <c r="R309" t="n">
-        <v>6933704</v>
+        <v>6933606</v>
       </c>
       <c r="S309" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T309" t="inlineStr">
         <is>
@@ -37080,10 +37080,10 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>122277234</v>
+        <v>122277227</v>
       </c>
       <c r="B310" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -37120,10 +37120,10 @@
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>520330</v>
+        <v>520109</v>
       </c>
       <c r="R310" t="n">
-        <v>6933624</v>
+        <v>6933653</v>
       </c>
       <c r="S310" t="n">
         <v>10</v>
@@ -37182,10 +37182,10 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>122277219</v>
+        <v>122277230</v>
       </c>
       <c r="B311" t="n">
-        <v>90819</v>
+        <v>57532</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -37198,37 +37198,46 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I311" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P311" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>519857</v>
+        <v>519846</v>
       </c>
       <c r="R311" t="n">
-        <v>6933857</v>
+        <v>6933784</v>
       </c>
       <c r="S311" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T311" t="inlineStr">
         <is>
@@ -37284,10 +37293,10 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>122277223</v>
+        <v>122277252</v>
       </c>
       <c r="B312" t="n">
-        <v>56581</v>
+        <v>79269</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -37300,46 +37309,37 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>102612</v>
+        <v>6453</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I312" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M312" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr"/>
       <c r="P312" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>520088</v>
+        <v>520742</v>
       </c>
       <c r="R312" t="n">
-        <v>6933802</v>
+        <v>6933667</v>
       </c>
       <c r="S312" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T312" t="inlineStr">
         <is>
@@ -37395,10 +37395,10 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>122277252</v>
+        <v>122277249</v>
       </c>
       <c r="B313" t="n">
-        <v>79269</v>
+        <v>57749</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -37407,41 +37407,50 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E313" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I313" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P313" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>520742</v>
+        <v>520694</v>
       </c>
       <c r="R313" t="n">
-        <v>6933667</v>
+        <v>6933625</v>
       </c>
       <c r="S313" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T313" t="inlineStr">
         <is>
@@ -37497,10 +37506,10 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>122277240</v>
+        <v>122277244</v>
       </c>
       <c r="B314" t="n">
-        <v>56581</v>
+        <v>78685</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -37513,46 +37522,37 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>102612</v>
+        <v>185</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I314" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M314" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr"/>
       <c r="P314" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>520322</v>
+        <v>520589</v>
       </c>
       <c r="R314" t="n">
-        <v>6933606</v>
+        <v>6933704</v>
       </c>
       <c r="S314" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T314" t="inlineStr">
         <is>
@@ -37608,10 +37608,10 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>122277225</v>
+        <v>122277242</v>
       </c>
       <c r="B315" t="n">
-        <v>98197</v>
+        <v>79732</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -37620,25 +37620,25 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I315" t="inlineStr"/>
@@ -37648,10 +37648,10 @@
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>520115</v>
+        <v>520443</v>
       </c>
       <c r="R315" t="n">
-        <v>6933705</v>
+        <v>6933656</v>
       </c>
       <c r="S315" t="n">
         <v>10</v>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -36144,10 +36144,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>122277219</v>
+        <v>122277225</v>
       </c>
       <c r="B301" t="n">
-        <v>90826</v>
+        <v>98202</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -36156,25 +36156,25 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I301" t="inlineStr"/>
@@ -36184,10 +36184,10 @@
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>519857</v>
+        <v>520115</v>
       </c>
       <c r="R301" t="n">
-        <v>6933857</v>
+        <v>6933705</v>
       </c>
       <c r="S301" t="n">
         <v>10</v>
@@ -36246,10 +36246,10 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>122277246</v>
+        <v>122277219</v>
       </c>
       <c r="B302" t="n">
-        <v>78651</v>
+        <v>90826</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -36262,21 +36262,21 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I302" t="inlineStr"/>
@@ -36286,10 +36286,10 @@
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>520527</v>
+        <v>519857</v>
       </c>
       <c r="R302" t="n">
-        <v>6933702</v>
+        <v>6933857</v>
       </c>
       <c r="S302" t="n">
         <v>10</v>
@@ -36348,10 +36348,10 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>122277225</v>
+        <v>122277246</v>
       </c>
       <c r="B303" t="n">
-        <v>98202</v>
+        <v>78651</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -36360,25 +36360,25 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I303" t="inlineStr"/>
@@ -36388,10 +36388,10 @@
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>520115</v>
+        <v>520527</v>
       </c>
       <c r="R303" t="n">
-        <v>6933705</v>
+        <v>6933702</v>
       </c>
       <c r="S303" t="n">
         <v>10</v>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -36144,10 +36144,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>122277225</v>
+        <v>122277219</v>
       </c>
       <c r="B301" t="n">
-        <v>98202</v>
+        <v>90826</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -36156,25 +36156,25 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I301" t="inlineStr"/>
@@ -36184,10 +36184,10 @@
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>520115</v>
+        <v>519857</v>
       </c>
       <c r="R301" t="n">
-        <v>6933705</v>
+        <v>6933857</v>
       </c>
       <c r="S301" t="n">
         <v>10</v>
@@ -36246,10 +36246,10 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>122277219</v>
+        <v>122277246</v>
       </c>
       <c r="B302" t="n">
-        <v>90826</v>
+        <v>78651</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -36262,21 +36262,21 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I302" t="inlineStr"/>
@@ -36286,10 +36286,10 @@
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>519857</v>
+        <v>520527</v>
       </c>
       <c r="R302" t="n">
-        <v>6933857</v>
+        <v>6933702</v>
       </c>
       <c r="S302" t="n">
         <v>10</v>
@@ -36348,10 +36348,10 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>122277246</v>
+        <v>122277225</v>
       </c>
       <c r="B303" t="n">
-        <v>78651</v>
+        <v>98202</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -36360,25 +36360,25 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I303" t="inlineStr"/>
@@ -36388,10 +36388,10 @@
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>520527</v>
+        <v>520115</v>
       </c>
       <c r="R303" t="n">
-        <v>6933702</v>
+        <v>6933705</v>
       </c>
       <c r="S303" t="n">
         <v>10</v>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -36144,10 +36144,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>122277219</v>
+        <v>122277240</v>
       </c>
       <c r="B301" t="n">
-        <v>90826</v>
+        <v>56581</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -36160,37 +36160,41 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F301" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>102612</v>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I301" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P301" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>519857</v>
+        <v>520322</v>
       </c>
       <c r="R301" t="n">
-        <v>6933857</v>
+        <v>6933606</v>
       </c>
       <c r="S301" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T301" t="inlineStr">
         <is>
@@ -36246,10 +36250,10 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>122277246</v>
+        <v>122277219</v>
       </c>
       <c r="B302" t="n">
-        <v>78651</v>
+        <v>90831</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -36262,21 +36266,16 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F302" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>5432</v>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I302" t="inlineStr"/>
@@ -36286,10 +36285,10 @@
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>520527</v>
+        <v>519857</v>
       </c>
       <c r="R302" t="n">
-        <v>6933702</v>
+        <v>6933857</v>
       </c>
       <c r="S302" t="n">
         <v>10</v>
@@ -36351,7 +36350,7 @@
         <v>122277225</v>
       </c>
       <c r="B303" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -36365,11 +36364,6 @@
       </c>
       <c r="E303" t="n">
         <v>220787</v>
-      </c>
-      <c r="F303" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
@@ -36450,10 +36444,10 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>122277238</v>
+        <v>122277234</v>
       </c>
       <c r="B304" t="n">
-        <v>79733</v>
+        <v>98211</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -36462,25 +36456,20 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F304" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I304" t="inlineStr"/>
@@ -36490,10 +36479,10 @@
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>520316</v>
+        <v>520330</v>
       </c>
       <c r="R304" t="n">
-        <v>6933594</v>
+        <v>6933624</v>
       </c>
       <c r="S304" t="n">
         <v>10</v>
@@ -36555,7 +36544,7 @@
         <v>122277254</v>
       </c>
       <c r="B305" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -36569,11 +36558,6 @@
       </c>
       <c r="E305" t="n">
         <v>6458</v>
-      </c>
-      <c r="F305" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
@@ -36654,10 +36638,10 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>122277234</v>
+        <v>122277249</v>
       </c>
       <c r="B306" t="n">
-        <v>98202</v>
+        <v>57749</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -36666,41 +36650,45 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F306" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>103015</v>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I306" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P306" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>520330</v>
+        <v>520694</v>
       </c>
       <c r="R306" t="n">
-        <v>6933624</v>
+        <v>6933625</v>
       </c>
       <c r="S306" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T306" t="inlineStr">
         <is>
@@ -36756,10 +36744,10 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>122277223</v>
+        <v>122277244</v>
       </c>
       <c r="B307" t="n">
-        <v>56581</v>
+        <v>78686</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -36772,46 +36760,32 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>102612</v>
-      </c>
-      <c r="F307" t="inlineStr">
-        <is>
-          <t>Järpe</t>
-        </is>
+        <v>185</v>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I307" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M307" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr"/>
       <c r="P307" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>520088</v>
+        <v>520589</v>
       </c>
       <c r="R307" t="n">
-        <v>6933802</v>
+        <v>6933704</v>
       </c>
       <c r="S307" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T307" t="inlineStr">
         <is>
@@ -36867,10 +36841,10 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>122277221</v>
+        <v>122277252</v>
       </c>
       <c r="B308" t="n">
-        <v>98202</v>
+        <v>79270</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -36879,25 +36853,20 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F308" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6453</v>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I308" t="inlineStr"/>
@@ -36907,10 +36876,10 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>519944</v>
+        <v>520742</v>
       </c>
       <c r="R308" t="n">
-        <v>6934006</v>
+        <v>6933667</v>
       </c>
       <c r="S308" t="n">
         <v>10</v>
@@ -36969,10 +36938,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>122277240</v>
+        <v>122277242</v>
       </c>
       <c r="B309" t="n">
-        <v>56581</v>
+        <v>79733</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -36985,46 +36954,32 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>102612</v>
-      </c>
-      <c r="F309" t="inlineStr">
-        <is>
-          <t>Järpe</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I309" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M309" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr"/>
       <c r="P309" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>520322</v>
+        <v>520443</v>
       </c>
       <c r="R309" t="n">
-        <v>6933606</v>
+        <v>6933656</v>
       </c>
       <c r="S309" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T309" t="inlineStr">
         <is>
@@ -37080,10 +37035,10 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>122277227</v>
+        <v>122277238</v>
       </c>
       <c r="B310" t="n">
-        <v>98202</v>
+        <v>79734</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -37092,25 +37047,20 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F310" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>2081</v>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I310" t="inlineStr"/>
@@ -37120,10 +37070,10 @@
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>520109</v>
+        <v>520316</v>
       </c>
       <c r="R310" t="n">
-        <v>6933653</v>
+        <v>6933594</v>
       </c>
       <c r="S310" t="n">
         <v>10</v>
@@ -37182,10 +37132,10 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>122277230</v>
+        <v>122277221</v>
       </c>
       <c r="B311" t="n">
-        <v>57532</v>
+        <v>98211</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -37194,50 +37144,36 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F311" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I311" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M311" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr"/>
       <c r="P311" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>519846</v>
+        <v>519944</v>
       </c>
       <c r="R311" t="n">
-        <v>6933784</v>
+        <v>6934006</v>
       </c>
       <c r="S311" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T311" t="inlineStr">
         <is>
@@ -37293,10 +37229,10 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>122277252</v>
+        <v>122277246</v>
       </c>
       <c r="B312" t="n">
-        <v>79269</v>
+        <v>78652</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -37309,21 +37245,16 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F312" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I312" t="inlineStr"/>
@@ -37333,10 +37264,10 @@
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>520742</v>
+        <v>520527</v>
       </c>
       <c r="R312" t="n">
-        <v>6933667</v>
+        <v>6933702</v>
       </c>
       <c r="S312" t="n">
         <v>10</v>
@@ -37395,10 +37326,10 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>122277249</v>
+        <v>122277223</v>
       </c>
       <c r="B313" t="n">
-        <v>57749</v>
+        <v>56581</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -37407,20 +37338,15 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E313" t="n">
-        <v>103015</v>
-      </c>
-      <c r="F313" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
+        <v>102612</v>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -37435,7 +37361,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P313" t="inlineStr">
@@ -37444,10 +37370,10 @@
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>520694</v>
+        <v>520088</v>
       </c>
       <c r="R313" t="n">
-        <v>6933625</v>
+        <v>6933802</v>
       </c>
       <c r="S313" t="n">
         <v>25</v>
@@ -37506,10 +37432,10 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>122277244</v>
+        <v>122277230</v>
       </c>
       <c r="B314" t="n">
-        <v>78685</v>
+        <v>57532</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -37522,37 +37448,41 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>185</v>
-      </c>
-      <c r="F314" t="inlineStr">
-        <is>
-          <t>Violettgrå tagellav</t>
-        </is>
+        <v>103021</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I314" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P314" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>520589</v>
+        <v>519846</v>
       </c>
       <c r="R314" t="n">
-        <v>6933704</v>
+        <v>6933784</v>
       </c>
       <c r="S314" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T314" t="inlineStr">
         <is>
@@ -37608,10 +37538,10 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>122277242</v>
+        <v>122277227</v>
       </c>
       <c r="B315" t="n">
-        <v>79732</v>
+        <v>98211</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -37620,25 +37550,20 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F315" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I315" t="inlineStr"/>
@@ -37648,10 +37573,10 @@
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>520443</v>
+        <v>520109</v>
       </c>
       <c r="R315" t="n">
-        <v>6933656</v>
+        <v>6933653</v>
       </c>
       <c r="S315" t="n">
         <v>10</v>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -36444,10 +36444,10 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>122277234</v>
+        <v>122277254</v>
       </c>
       <c r="B304" t="n">
-        <v>98211</v>
+        <v>79733</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -36456,20 +36456,20 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I304" t="inlineStr"/>
@@ -36479,10 +36479,10 @@
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>520330</v>
+        <v>520941</v>
       </c>
       <c r="R304" t="n">
-        <v>6933624</v>
+        <v>6933486</v>
       </c>
       <c r="S304" t="n">
         <v>10</v>
@@ -36541,10 +36541,10 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>122277254</v>
+        <v>122277234</v>
       </c>
       <c r="B305" t="n">
-        <v>79733</v>
+        <v>98211</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -36553,20 +36553,20 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I305" t="inlineStr"/>
@@ -36576,10 +36576,10 @@
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>520941</v>
+        <v>520330</v>
       </c>
       <c r="R305" t="n">
-        <v>6933486</v>
+        <v>6933624</v>
       </c>
       <c r="S305" t="n">
         <v>10</v>
@@ -37432,10 +37432,10 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>122277230</v>
+        <v>122277227</v>
       </c>
       <c r="B314" t="n">
-        <v>57532</v>
+        <v>98211</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -37444,45 +37444,36 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I314" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M314" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr"/>
       <c r="P314" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>519846</v>
+        <v>520109</v>
       </c>
       <c r="R314" t="n">
-        <v>6933784</v>
+        <v>6933653</v>
       </c>
       <c r="S314" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T314" t="inlineStr">
         <is>
@@ -37538,10 +37529,10 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>122277227</v>
+        <v>122277230</v>
       </c>
       <c r="B315" t="n">
-        <v>98211</v>
+        <v>57532</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -37550,36 +37541,45 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I315" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P315" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>520109</v>
+        <v>519846</v>
       </c>
       <c r="R315" t="n">
-        <v>6933653</v>
+        <v>6933784</v>
       </c>
       <c r="S315" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T315" t="inlineStr">
         <is>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -37432,10 +37432,10 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>122277227</v>
+        <v>122277230</v>
       </c>
       <c r="B314" t="n">
-        <v>98211</v>
+        <v>57532</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -37444,36 +37444,45 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I314" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P314" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>520109</v>
+        <v>519846</v>
       </c>
       <c r="R314" t="n">
-        <v>6933653</v>
+        <v>6933784</v>
       </c>
       <c r="S314" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T314" t="inlineStr">
         <is>
@@ -37529,10 +37538,10 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>122277230</v>
+        <v>122277227</v>
       </c>
       <c r="B315" t="n">
-        <v>57532</v>
+        <v>98211</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -37541,45 +37550,36 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I315" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M315" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr"/>
       <c r="P315" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>519846</v>
+        <v>520109</v>
       </c>
       <c r="R315" t="n">
-        <v>6933784</v>
+        <v>6933653</v>
       </c>
       <c r="S315" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T315" t="inlineStr">
         <is>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -36144,10 +36144,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>122277240</v>
+        <v>122277242</v>
       </c>
       <c r="B301" t="n">
-        <v>56581</v>
+        <v>79737</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -36160,41 +36160,37 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>102612</v>
+        <v>6458</v>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I301" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M301" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr"/>
       <c r="P301" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>520322</v>
+        <v>520443</v>
       </c>
       <c r="R301" t="n">
-        <v>6933606</v>
+        <v>6933656</v>
       </c>
       <c r="S301" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T301" t="inlineStr">
         <is>
@@ -36250,10 +36246,10 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>122277219</v>
+        <v>122277238</v>
       </c>
       <c r="B302" t="n">
-        <v>90831</v>
+        <v>79738</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -36266,16 +36262,21 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>5432</v>
+        <v>2081</v>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I302" t="inlineStr"/>
@@ -36285,10 +36286,10 @@
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>519857</v>
+        <v>520316</v>
       </c>
       <c r="R302" t="n">
-        <v>6933857</v>
+        <v>6933594</v>
       </c>
       <c r="S302" t="n">
         <v>10</v>
@@ -36347,10 +36348,10 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>122277225</v>
+        <v>122277223</v>
       </c>
       <c r="B303" t="n">
-        <v>98211</v>
+        <v>56585</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -36359,36 +36360,50 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>220787</v>
+        <v>102612</v>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I303" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P303" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>520115</v>
+        <v>520088</v>
       </c>
       <c r="R303" t="n">
-        <v>6933705</v>
+        <v>6933802</v>
       </c>
       <c r="S303" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T303" t="inlineStr">
         <is>
@@ -36444,10 +36459,10 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>122277254</v>
+        <v>122277252</v>
       </c>
       <c r="B304" t="n">
-        <v>79733</v>
+        <v>79274</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -36460,16 +36475,21 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>6458</v>
+        <v>6453</v>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I304" t="inlineStr"/>
@@ -36479,10 +36499,10 @@
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>520941</v>
+        <v>520742</v>
       </c>
       <c r="R304" t="n">
-        <v>6933486</v>
+        <v>6933667</v>
       </c>
       <c r="S304" t="n">
         <v>10</v>
@@ -36541,10 +36561,10 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>122277234</v>
+        <v>122277254</v>
       </c>
       <c r="B305" t="n">
-        <v>98211</v>
+        <v>79737</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -36553,20 +36573,25 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>220787</v>
+        <v>6458</v>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I305" t="inlineStr"/>
@@ -36576,10 +36601,10 @@
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>520330</v>
+        <v>520941</v>
       </c>
       <c r="R305" t="n">
-        <v>6933624</v>
+        <v>6933486</v>
       </c>
       <c r="S305" t="n">
         <v>10</v>
@@ -36638,10 +36663,10 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>122277249</v>
+        <v>122277240</v>
       </c>
       <c r="B306" t="n">
-        <v>57749</v>
+        <v>56585</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -36650,15 +36675,20 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>103015</v>
+        <v>102612</v>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -36668,12 +36698,12 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P306" t="inlineStr">
@@ -36682,10 +36712,10 @@
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>520694</v>
+        <v>520322</v>
       </c>
       <c r="R306" t="n">
-        <v>6933625</v>
+        <v>6933606</v>
       </c>
       <c r="S306" t="n">
         <v>25</v>
@@ -36744,10 +36774,10 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>122277244</v>
+        <v>122277230</v>
       </c>
       <c r="B307" t="n">
-        <v>78686</v>
+        <v>57536</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -36760,32 +36790,46 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>185</v>
+        <v>103021</v>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I307" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P307" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>520589</v>
+        <v>519846</v>
       </c>
       <c r="R307" t="n">
-        <v>6933704</v>
+        <v>6933784</v>
       </c>
       <c r="S307" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T307" t="inlineStr">
         <is>
@@ -36841,10 +36885,10 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>122277252</v>
+        <v>122277244</v>
       </c>
       <c r="B308" t="n">
-        <v>79270</v>
+        <v>78690</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -36857,16 +36901,21 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>6453</v>
+        <v>185</v>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I308" t="inlineStr"/>
@@ -36876,10 +36925,10 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>520742</v>
+        <v>520589</v>
       </c>
       <c r="R308" t="n">
-        <v>6933667</v>
+        <v>6933704</v>
       </c>
       <c r="S308" t="n">
         <v>10</v>
@@ -36938,10 +36987,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>122277242</v>
+        <v>122277234</v>
       </c>
       <c r="B309" t="n">
-        <v>79733</v>
+        <v>98224</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -36950,20 +36999,25 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>6458</v>
+        <v>220787</v>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I309" t="inlineStr"/>
@@ -36973,10 +37027,10 @@
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>520443</v>
+        <v>520330</v>
       </c>
       <c r="R309" t="n">
-        <v>6933656</v>
+        <v>6933624</v>
       </c>
       <c r="S309" t="n">
         <v>10</v>
@@ -37035,10 +37089,10 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>122277238</v>
+        <v>122277219</v>
       </c>
       <c r="B310" t="n">
-        <v>79734</v>
+        <v>90844</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -37051,16 +37105,21 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>2081</v>
+        <v>5432</v>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I310" t="inlineStr"/>
@@ -37070,10 +37129,10 @@
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>520316</v>
+        <v>519857</v>
       </c>
       <c r="R310" t="n">
-        <v>6933594</v>
+        <v>6933857</v>
       </c>
       <c r="S310" t="n">
         <v>10</v>
@@ -37132,10 +37191,10 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>122277221</v>
+        <v>122277249</v>
       </c>
       <c r="B311" t="n">
-        <v>98211</v>
+        <v>57753</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -37144,36 +37203,50 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>220787</v>
+        <v>103015</v>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I311" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P311" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>519944</v>
+        <v>520694</v>
       </c>
       <c r="R311" t="n">
-        <v>6934006</v>
+        <v>6933625</v>
       </c>
       <c r="S311" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T311" t="inlineStr">
         <is>
@@ -37229,10 +37302,10 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>122277246</v>
+        <v>122277221</v>
       </c>
       <c r="B312" t="n">
-        <v>78652</v>
+        <v>98224</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -37241,20 +37314,25 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E312" t="n">
-        <v>6425</v>
+        <v>220787</v>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I312" t="inlineStr"/>
@@ -37264,10 +37342,10 @@
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>520527</v>
+        <v>519944</v>
       </c>
       <c r="R312" t="n">
-        <v>6933702</v>
+        <v>6934006</v>
       </c>
       <c r="S312" t="n">
         <v>10</v>
@@ -37326,10 +37404,10 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>122277223</v>
+        <v>122277246</v>
       </c>
       <c r="B313" t="n">
-        <v>56581</v>
+        <v>78656</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -37342,41 +37420,37 @@
         </is>
       </c>
       <c r="E313" t="n">
-        <v>102612</v>
+        <v>6425</v>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I313" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M313" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr"/>
       <c r="P313" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>520088</v>
+        <v>520527</v>
       </c>
       <c r="R313" t="n">
-        <v>6933802</v>
+        <v>6933702</v>
       </c>
       <c r="S313" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T313" t="inlineStr">
         <is>
@@ -37432,10 +37506,10 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>122277230</v>
+        <v>122277225</v>
       </c>
       <c r="B314" t="n">
-        <v>57532</v>
+        <v>98224</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -37444,45 +37518,41 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>103021</v>
+        <v>220787</v>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I314" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M314" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr"/>
       <c r="P314" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>519846</v>
+        <v>520115</v>
       </c>
       <c r="R314" t="n">
-        <v>6933784</v>
+        <v>6933705</v>
       </c>
       <c r="S314" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T314" t="inlineStr">
         <is>
@@ -37541,7 +37611,7 @@
         <v>122277227</v>
       </c>
       <c r="B315" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -37555,6 +37625,11 @@
       </c>
       <c r="E315" t="n">
         <v>220787</v>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -36144,10 +36144,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>122277242</v>
+        <v>122277238</v>
       </c>
       <c r="B301" t="n">
-        <v>79737</v>
+        <v>79738</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -36160,21 +36160,21 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I301" t="inlineStr"/>
@@ -36184,10 +36184,10 @@
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>520443</v>
+        <v>520316</v>
       </c>
       <c r="R301" t="n">
-        <v>6933656</v>
+        <v>6933594</v>
       </c>
       <c r="S301" t="n">
         <v>10</v>
@@ -36246,10 +36246,10 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>122277238</v>
+        <v>122277244</v>
       </c>
       <c r="B302" t="n">
-        <v>79738</v>
+        <v>78690</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -36262,21 +36262,21 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I302" t="inlineStr"/>
@@ -36286,10 +36286,10 @@
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>520316</v>
+        <v>520589</v>
       </c>
       <c r="R302" t="n">
-        <v>6933594</v>
+        <v>6933704</v>
       </c>
       <c r="S302" t="n">
         <v>10</v>
@@ -36348,10 +36348,10 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>122277223</v>
+        <v>122277227</v>
       </c>
       <c r="B303" t="n">
-        <v>56585</v>
+        <v>98237</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -36360,50 +36360,41 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I303" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M303" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr"/>
       <c r="P303" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>520088</v>
+        <v>520109</v>
       </c>
       <c r="R303" t="n">
-        <v>6933802</v>
+        <v>6933653</v>
       </c>
       <c r="S303" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T303" t="inlineStr">
         <is>
@@ -36459,10 +36450,10 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>122277252</v>
+        <v>122277219</v>
       </c>
       <c r="B304" t="n">
-        <v>79274</v>
+        <v>90857</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -36475,21 +36466,21 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I304" t="inlineStr"/>
@@ -36499,10 +36490,10 @@
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>520742</v>
+        <v>519857</v>
       </c>
       <c r="R304" t="n">
-        <v>6933667</v>
+        <v>6933857</v>
       </c>
       <c r="S304" t="n">
         <v>10</v>
@@ -36561,7 +36552,7 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>122277254</v>
+        <v>122277242</v>
       </c>
       <c r="B305" t="n">
         <v>79737</v>
@@ -36601,10 +36592,10 @@
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>520941</v>
+        <v>520443</v>
       </c>
       <c r="R305" t="n">
-        <v>6933486</v>
+        <v>6933656</v>
       </c>
       <c r="S305" t="n">
         <v>10</v>
@@ -36663,10 +36654,10 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>122277240</v>
+        <v>122277230</v>
       </c>
       <c r="B306" t="n">
-        <v>56585</v>
+        <v>57536</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -36679,26 +36670,26 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
@@ -36712,10 +36703,10 @@
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>520322</v>
+        <v>519846</v>
       </c>
       <c r="R306" t="n">
-        <v>6933606</v>
+        <v>6933784</v>
       </c>
       <c r="S306" t="n">
         <v>25</v>
@@ -36774,10 +36765,10 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>122277230</v>
+        <v>122277254</v>
       </c>
       <c r="B307" t="n">
-        <v>57536</v>
+        <v>79737</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -36790,46 +36781,37 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I307" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M307" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr"/>
       <c r="P307" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>519846</v>
+        <v>520941</v>
       </c>
       <c r="R307" t="n">
-        <v>6933784</v>
+        <v>6933486</v>
       </c>
       <c r="S307" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T307" t="inlineStr">
         <is>
@@ -36885,10 +36867,10 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>122277244</v>
+        <v>122277252</v>
       </c>
       <c r="B308" t="n">
-        <v>78690</v>
+        <v>79274</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -36901,21 +36883,21 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I308" t="inlineStr"/>
@@ -36925,10 +36907,10 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>520589</v>
+        <v>520742</v>
       </c>
       <c r="R308" t="n">
-        <v>6933704</v>
+        <v>6933667</v>
       </c>
       <c r="S308" t="n">
         <v>10</v>
@@ -36987,10 +36969,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>122277234</v>
+        <v>122277249</v>
       </c>
       <c r="B309" t="n">
-        <v>98224</v>
+        <v>57753</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -36999,41 +36981,50 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I309" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P309" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>520330</v>
+        <v>520694</v>
       </c>
       <c r="R309" t="n">
-        <v>6933624</v>
+        <v>6933625</v>
       </c>
       <c r="S309" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T309" t="inlineStr">
         <is>
@@ -37089,10 +37080,10 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>122277219</v>
+        <v>122277234</v>
       </c>
       <c r="B310" t="n">
-        <v>90844</v>
+        <v>98237</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -37101,25 +37092,25 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I310" t="inlineStr"/>
@@ -37129,10 +37120,10 @@
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>519857</v>
+        <v>520330</v>
       </c>
       <c r="R310" t="n">
-        <v>6933857</v>
+        <v>6933624</v>
       </c>
       <c r="S310" t="n">
         <v>10</v>
@@ -37191,10 +37182,10 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>122277249</v>
+        <v>122277221</v>
       </c>
       <c r="B311" t="n">
-        <v>57753</v>
+        <v>98237</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -37203,50 +37194,41 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I311" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M311" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr"/>
       <c r="P311" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>520694</v>
+        <v>519944</v>
       </c>
       <c r="R311" t="n">
-        <v>6933625</v>
+        <v>6934006</v>
       </c>
       <c r="S311" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T311" t="inlineStr">
         <is>
@@ -37302,10 +37284,10 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>122277221</v>
+        <v>122277223</v>
       </c>
       <c r="B312" t="n">
-        <v>98224</v>
+        <v>56585</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -37314,41 +37296,50 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E312" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I312" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P312" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>519944</v>
+        <v>520088</v>
       </c>
       <c r="R312" t="n">
-        <v>6934006</v>
+        <v>6933802</v>
       </c>
       <c r="S312" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T312" t="inlineStr">
         <is>
@@ -37404,10 +37395,10 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>122277246</v>
+        <v>122277240</v>
       </c>
       <c r="B313" t="n">
-        <v>78656</v>
+        <v>56585</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -37420,37 +37411,46 @@
         </is>
       </c>
       <c r="E313" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I313" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P313" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>520527</v>
+        <v>520322</v>
       </c>
       <c r="R313" t="n">
-        <v>6933702</v>
+        <v>6933606</v>
       </c>
       <c r="S313" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T313" t="inlineStr">
         <is>
@@ -37509,7 +37509,7 @@
         <v>122277225</v>
       </c>
       <c r="B314" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -37608,10 +37608,10 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>122277227</v>
+        <v>122277246</v>
       </c>
       <c r="B315" t="n">
-        <v>98224</v>
+        <v>78656</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -37620,25 +37620,25 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I315" t="inlineStr"/>
@@ -37648,10 +37648,10 @@
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>520109</v>
+        <v>520527</v>
       </c>
       <c r="R315" t="n">
-        <v>6933653</v>
+        <v>6933702</v>
       </c>
       <c r="S315" t="n">
         <v>10</v>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -36144,10 +36144,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>122277238</v>
+        <v>122277242</v>
       </c>
       <c r="B301" t="n">
-        <v>79738</v>
+        <v>79737</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -36160,21 +36160,21 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I301" t="inlineStr"/>
@@ -36184,10 +36184,10 @@
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>520316</v>
+        <v>520443</v>
       </c>
       <c r="R301" t="n">
-        <v>6933594</v>
+        <v>6933656</v>
       </c>
       <c r="S301" t="n">
         <v>10</v>
@@ -36348,10 +36348,10 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>122277227</v>
+        <v>122277249</v>
       </c>
       <c r="B303" t="n">
-        <v>98237</v>
+        <v>57753</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -36360,41 +36360,50 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I303" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P303" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>520109</v>
+        <v>520694</v>
       </c>
       <c r="R303" t="n">
-        <v>6933653</v>
+        <v>6933625</v>
       </c>
       <c r="S303" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T303" t="inlineStr">
         <is>
@@ -36552,10 +36561,10 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>122277242</v>
+        <v>122277240</v>
       </c>
       <c r="B305" t="n">
-        <v>79737</v>
+        <v>56585</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -36568,37 +36577,46 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I305" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P305" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>520443</v>
+        <v>520322</v>
       </c>
       <c r="R305" t="n">
-        <v>6933656</v>
+        <v>6933606</v>
       </c>
       <c r="S305" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T305" t="inlineStr">
         <is>
@@ -36654,10 +36672,10 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>122277230</v>
+        <v>122277223</v>
       </c>
       <c r="B306" t="n">
-        <v>57536</v>
+        <v>56585</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -36670,21 +36688,21 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -36703,10 +36721,10 @@
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>519846</v>
+        <v>520088</v>
       </c>
       <c r="R306" t="n">
-        <v>6933784</v>
+        <v>6933802</v>
       </c>
       <c r="S306" t="n">
         <v>25</v>
@@ -36765,10 +36783,10 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>122277254</v>
+        <v>122277230</v>
       </c>
       <c r="B307" t="n">
-        <v>79737</v>
+        <v>57536</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -36781,37 +36799,46 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I307" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P307" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>520941</v>
+        <v>519846</v>
       </c>
       <c r="R307" t="n">
-        <v>6933486</v>
+        <v>6933784</v>
       </c>
       <c r="S307" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T307" t="inlineStr">
         <is>
@@ -36867,10 +36894,10 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>122277252</v>
+        <v>122277238</v>
       </c>
       <c r="B308" t="n">
-        <v>79274</v>
+        <v>79738</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -36883,21 +36910,21 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>6453</v>
+        <v>2081</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I308" t="inlineStr"/>
@@ -36907,10 +36934,10 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>520742</v>
+        <v>520316</v>
       </c>
       <c r="R308" t="n">
-        <v>6933667</v>
+        <v>6933594</v>
       </c>
       <c r="S308" t="n">
         <v>10</v>
@@ -36969,10 +36996,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>122277249</v>
+        <v>122277252</v>
       </c>
       <c r="B309" t="n">
-        <v>57753</v>
+        <v>79274</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -36981,50 +37008,41 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I309" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M309" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr"/>
       <c r="P309" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>520694</v>
+        <v>520742</v>
       </c>
       <c r="R309" t="n">
-        <v>6933625</v>
+        <v>6933667</v>
       </c>
       <c r="S309" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T309" t="inlineStr">
         <is>
@@ -37080,10 +37098,10 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>122277234</v>
+        <v>122277254</v>
       </c>
       <c r="B310" t="n">
-        <v>98237</v>
+        <v>79737</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -37092,25 +37110,25 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I310" t="inlineStr"/>
@@ -37120,10 +37138,10 @@
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>520330</v>
+        <v>520941</v>
       </c>
       <c r="R310" t="n">
-        <v>6933624</v>
+        <v>6933486</v>
       </c>
       <c r="S310" t="n">
         <v>10</v>
@@ -37182,7 +37200,7 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>122277221</v>
+        <v>122277225</v>
       </c>
       <c r="B311" t="n">
         <v>98237</v>
@@ -37222,10 +37240,10 @@
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>519944</v>
+        <v>520115</v>
       </c>
       <c r="R311" t="n">
-        <v>6934006</v>
+        <v>6933705</v>
       </c>
       <c r="S311" t="n">
         <v>10</v>
@@ -37284,10 +37302,10 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>122277223</v>
+        <v>122277221</v>
       </c>
       <c r="B312" t="n">
-        <v>56585</v>
+        <v>98237</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -37296,50 +37314,41 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E312" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I312" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M312" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr"/>
       <c r="P312" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>520088</v>
+        <v>519944</v>
       </c>
       <c r="R312" t="n">
-        <v>6933802</v>
+        <v>6934006</v>
       </c>
       <c r="S312" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T312" t="inlineStr">
         <is>
@@ -37395,10 +37404,10 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>122277240</v>
+        <v>122277246</v>
       </c>
       <c r="B313" t="n">
-        <v>56585</v>
+        <v>78656</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -37411,46 +37420,37 @@
         </is>
       </c>
       <c r="E313" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I313" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M313" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr"/>
       <c r="P313" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>520322</v>
+        <v>520527</v>
       </c>
       <c r="R313" t="n">
-        <v>6933606</v>
+        <v>6933702</v>
       </c>
       <c r="S313" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T313" t="inlineStr">
         <is>
@@ -37506,7 +37506,7 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>122277225</v>
+        <v>122277234</v>
       </c>
       <c r="B314" t="n">
         <v>98237</v>
@@ -37546,10 +37546,10 @@
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>520115</v>
+        <v>520330</v>
       </c>
       <c r="R314" t="n">
-        <v>6933705</v>
+        <v>6933624</v>
       </c>
       <c r="S314" t="n">
         <v>10</v>
@@ -37608,10 +37608,10 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>122277246</v>
+        <v>122277227</v>
       </c>
       <c r="B315" t="n">
-        <v>78656</v>
+        <v>98237</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -37620,25 +37620,25 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I315" t="inlineStr"/>
@@ -37648,10 +37648,10 @@
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>520527</v>
+        <v>520109</v>
       </c>
       <c r="R315" t="n">
-        <v>6933702</v>
+        <v>6933653</v>
       </c>
       <c r="S315" t="n">
         <v>10</v>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -36144,10 +36144,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>122277242</v>
+        <v>122277225</v>
       </c>
       <c r="B301" t="n">
-        <v>79737</v>
+        <v>98240</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -36156,25 +36156,25 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I301" t="inlineStr"/>
@@ -36184,10 +36184,10 @@
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>520443</v>
+        <v>520115</v>
       </c>
       <c r="R301" t="n">
-        <v>6933656</v>
+        <v>6933705</v>
       </c>
       <c r="S301" t="n">
         <v>10</v>
@@ -36246,10 +36246,10 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>122277244</v>
+        <v>122277234</v>
       </c>
       <c r="B302" t="n">
-        <v>78690</v>
+        <v>98240</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -36258,25 +36258,25 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I302" t="inlineStr"/>
@@ -36286,10 +36286,10 @@
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>520589</v>
+        <v>520330</v>
       </c>
       <c r="R302" t="n">
-        <v>6933704</v>
+        <v>6933624</v>
       </c>
       <c r="S302" t="n">
         <v>10</v>
@@ -36348,10 +36348,10 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>122277249</v>
+        <v>122277219</v>
       </c>
       <c r="B303" t="n">
-        <v>57753</v>
+        <v>90851</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -36360,50 +36360,41 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I303" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M303" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr"/>
       <c r="P303" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>520694</v>
+        <v>519857</v>
       </c>
       <c r="R303" t="n">
-        <v>6933625</v>
+        <v>6933857</v>
       </c>
       <c r="S303" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T303" t="inlineStr">
         <is>
@@ -36459,10 +36450,10 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>122277219</v>
+        <v>122277244</v>
       </c>
       <c r="B304" t="n">
-        <v>90857</v>
+        <v>78690</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -36475,21 +36466,21 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>5432</v>
+        <v>185</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I304" t="inlineStr"/>
@@ -36499,10 +36490,10 @@
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>519857</v>
+        <v>520589</v>
       </c>
       <c r="R304" t="n">
-        <v>6933857</v>
+        <v>6933704</v>
       </c>
       <c r="S304" t="n">
         <v>10</v>
@@ -36561,10 +36552,10 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>122277240</v>
+        <v>122277221</v>
       </c>
       <c r="B305" t="n">
-        <v>56585</v>
+        <v>98240</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -36573,50 +36564,41 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I305" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M305" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr"/>
       <c r="P305" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>520322</v>
+        <v>519944</v>
       </c>
       <c r="R305" t="n">
-        <v>6933606</v>
+        <v>6934006</v>
       </c>
       <c r="S305" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T305" t="inlineStr">
         <is>
@@ -36672,10 +36654,10 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>122277223</v>
+        <v>122277242</v>
       </c>
       <c r="B306" t="n">
-        <v>56585</v>
+        <v>79737</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -36688,46 +36670,37 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I306" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M306" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr"/>
       <c r="P306" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>520088</v>
+        <v>520443</v>
       </c>
       <c r="R306" t="n">
-        <v>6933802</v>
+        <v>6933656</v>
       </c>
       <c r="S306" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T306" t="inlineStr">
         <is>
@@ -36783,10 +36756,10 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>122277230</v>
+        <v>122277249</v>
       </c>
       <c r="B307" t="n">
-        <v>57536</v>
+        <v>57753</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -36795,25 +36768,25 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -36823,7 +36796,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P307" t="inlineStr">
@@ -36832,10 +36805,10 @@
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>519846</v>
+        <v>520694</v>
       </c>
       <c r="R307" t="n">
-        <v>6933784</v>
+        <v>6933625</v>
       </c>
       <c r="S307" t="n">
         <v>25</v>
@@ -36894,10 +36867,10 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>122277238</v>
+        <v>122277254</v>
       </c>
       <c r="B308" t="n">
-        <v>79738</v>
+        <v>79737</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -36910,21 +36883,21 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I308" t="inlineStr"/>
@@ -36934,10 +36907,10 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>520316</v>
+        <v>520941</v>
       </c>
       <c r="R308" t="n">
-        <v>6933594</v>
+        <v>6933486</v>
       </c>
       <c r="S308" t="n">
         <v>10</v>
@@ -36996,10 +36969,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>122277252</v>
+        <v>122277227</v>
       </c>
       <c r="B309" t="n">
-        <v>79274</v>
+        <v>98240</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -37008,25 +36981,25 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I309" t="inlineStr"/>
@@ -37036,10 +37009,10 @@
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>520742</v>
+        <v>520109</v>
       </c>
       <c r="R309" t="n">
-        <v>6933667</v>
+        <v>6933653</v>
       </c>
       <c r="S309" t="n">
         <v>10</v>
@@ -37098,10 +37071,10 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>122277254</v>
+        <v>122277240</v>
       </c>
       <c r="B310" t="n">
-        <v>79737</v>
+        <v>56585</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -37114,37 +37087,46 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I310" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P310" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>520941</v>
+        <v>520322</v>
       </c>
       <c r="R310" t="n">
-        <v>6933486</v>
+        <v>6933606</v>
       </c>
       <c r="S310" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T310" t="inlineStr">
         <is>
@@ -37200,10 +37182,10 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>122277225</v>
+        <v>122277238</v>
       </c>
       <c r="B311" t="n">
-        <v>98237</v>
+        <v>79738</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -37212,25 +37194,25 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I311" t="inlineStr"/>
@@ -37240,10 +37222,10 @@
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>520115</v>
+        <v>520316</v>
       </c>
       <c r="R311" t="n">
-        <v>6933705</v>
+        <v>6933594</v>
       </c>
       <c r="S311" t="n">
         <v>10</v>
@@ -37302,10 +37284,10 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>122277221</v>
+        <v>122277223</v>
       </c>
       <c r="B312" t="n">
-        <v>98237</v>
+        <v>56585</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -37314,41 +37296,50 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E312" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I312" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P312" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>519944</v>
+        <v>520088</v>
       </c>
       <c r="R312" t="n">
-        <v>6934006</v>
+        <v>6933802</v>
       </c>
       <c r="S312" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T312" t="inlineStr">
         <is>
@@ -37404,10 +37395,10 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>122277246</v>
+        <v>122277252</v>
       </c>
       <c r="B313" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -37420,21 +37411,21 @@
         </is>
       </c>
       <c r="E313" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I313" t="inlineStr"/>
@@ -37444,10 +37435,10 @@
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>520527</v>
+        <v>520742</v>
       </c>
       <c r="R313" t="n">
-        <v>6933702</v>
+        <v>6933667</v>
       </c>
       <c r="S313" t="n">
         <v>10</v>
@@ -37506,10 +37497,10 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>122277234</v>
+        <v>122277246</v>
       </c>
       <c r="B314" t="n">
-        <v>98237</v>
+        <v>78656</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -37518,25 +37509,25 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I314" t="inlineStr"/>
@@ -37546,10 +37537,10 @@
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>520330</v>
+        <v>520527</v>
       </c>
       <c r="R314" t="n">
-        <v>6933624</v>
+        <v>6933702</v>
       </c>
       <c r="S314" t="n">
         <v>10</v>
@@ -37608,10 +37599,10 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>122277227</v>
+        <v>122277230</v>
       </c>
       <c r="B315" t="n">
-        <v>98237</v>
+        <v>57536</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -37620,41 +37611,50 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I315" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P315" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>520109</v>
+        <v>519846</v>
       </c>
       <c r="R315" t="n">
-        <v>6933653</v>
+        <v>6933784</v>
       </c>
       <c r="S315" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T315" t="inlineStr">
         <is>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -36144,10 +36144,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>122277225</v>
+        <v>122277244</v>
       </c>
       <c r="B301" t="n">
-        <v>98240</v>
+        <v>78690</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -36156,25 +36156,25 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I301" t="inlineStr"/>
@@ -36184,10 +36184,10 @@
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>520115</v>
+        <v>520589</v>
       </c>
       <c r="R301" t="n">
-        <v>6933705</v>
+        <v>6933704</v>
       </c>
       <c r="S301" t="n">
         <v>10</v>
@@ -36246,10 +36246,10 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>122277234</v>
+        <v>122277246</v>
       </c>
       <c r="B302" t="n">
-        <v>98240</v>
+        <v>78656</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -36258,25 +36258,25 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I302" t="inlineStr"/>
@@ -36286,10 +36286,10 @@
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>520330</v>
+        <v>520527</v>
       </c>
       <c r="R302" t="n">
-        <v>6933624</v>
+        <v>6933702</v>
       </c>
       <c r="S302" t="n">
         <v>10</v>
@@ -36450,10 +36450,10 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>122277244</v>
+        <v>122277225</v>
       </c>
       <c r="B304" t="n">
-        <v>78690</v>
+        <v>98240</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -36462,25 +36462,25 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I304" t="inlineStr"/>
@@ -36490,10 +36490,10 @@
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>520589</v>
+        <v>520115</v>
       </c>
       <c r="R304" t="n">
-        <v>6933704</v>
+        <v>6933705</v>
       </c>
       <c r="S304" t="n">
         <v>10</v>
@@ -36654,10 +36654,10 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>122277242</v>
+        <v>122277252</v>
       </c>
       <c r="B306" t="n">
-        <v>79737</v>
+        <v>79274</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -36670,21 +36670,21 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I306" t="inlineStr"/>
@@ -36694,10 +36694,10 @@
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>520443</v>
+        <v>520742</v>
       </c>
       <c r="R306" t="n">
-        <v>6933656</v>
+        <v>6933667</v>
       </c>
       <c r="S306" t="n">
         <v>10</v>
@@ -36756,10 +36756,10 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>122277249</v>
+        <v>122277227</v>
       </c>
       <c r="B307" t="n">
-        <v>57753</v>
+        <v>98240</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -36768,50 +36768,41 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I307" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M307" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr"/>
       <c r="P307" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>520694</v>
+        <v>520109</v>
       </c>
       <c r="R307" t="n">
-        <v>6933625</v>
+        <v>6933653</v>
       </c>
       <c r="S307" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T307" t="inlineStr">
         <is>
@@ -36867,10 +36858,10 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>122277254</v>
+        <v>122277234</v>
       </c>
       <c r="B308" t="n">
-        <v>79737</v>
+        <v>98240</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -36879,25 +36870,25 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I308" t="inlineStr"/>
@@ -36907,10 +36898,10 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>520941</v>
+        <v>520330</v>
       </c>
       <c r="R308" t="n">
-        <v>6933486</v>
+        <v>6933624</v>
       </c>
       <c r="S308" t="n">
         <v>10</v>
@@ -36969,10 +36960,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>122277227</v>
+        <v>122277223</v>
       </c>
       <c r="B309" t="n">
-        <v>98240</v>
+        <v>56585</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -36981,41 +36972,50 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I309" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P309" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>520109</v>
+        <v>520088</v>
       </c>
       <c r="R309" t="n">
-        <v>6933653</v>
+        <v>6933802</v>
       </c>
       <c r="S309" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T309" t="inlineStr">
         <is>
@@ -37071,10 +37071,10 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>122277240</v>
+        <v>122277242</v>
       </c>
       <c r="B310" t="n">
-        <v>56585</v>
+        <v>79737</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -37087,46 +37087,37 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I310" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M310" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr"/>
       <c r="P310" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>520322</v>
+        <v>520443</v>
       </c>
       <c r="R310" t="n">
-        <v>6933606</v>
+        <v>6933656</v>
       </c>
       <c r="S310" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T310" t="inlineStr">
         <is>
@@ -37284,10 +37275,10 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>122277223</v>
+        <v>122277230</v>
       </c>
       <c r="B312" t="n">
-        <v>56585</v>
+        <v>57536</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -37300,21 +37291,21 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -37333,10 +37324,10 @@
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>520088</v>
+        <v>519846</v>
       </c>
       <c r="R312" t="n">
-        <v>6933802</v>
+        <v>6933784</v>
       </c>
       <c r="S312" t="n">
         <v>25</v>
@@ -37395,10 +37386,10 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>122277252</v>
+        <v>122277240</v>
       </c>
       <c r="B313" t="n">
-        <v>79274</v>
+        <v>56585</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -37411,37 +37402,46 @@
         </is>
       </c>
       <c r="E313" t="n">
-        <v>6453</v>
+        <v>102612</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I313" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P313" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>520742</v>
+        <v>520322</v>
       </c>
       <c r="R313" t="n">
-        <v>6933667</v>
+        <v>6933606</v>
       </c>
       <c r="S313" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T313" t="inlineStr">
         <is>
@@ -37497,10 +37497,10 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>122277246</v>
+        <v>122277254</v>
       </c>
       <c r="B314" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -37513,21 +37513,21 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I314" t="inlineStr"/>
@@ -37537,10 +37537,10 @@
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>520527</v>
+        <v>520941</v>
       </c>
       <c r="R314" t="n">
-        <v>6933702</v>
+        <v>6933486</v>
       </c>
       <c r="S314" t="n">
         <v>10</v>
@@ -37599,10 +37599,10 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>122277230</v>
+        <v>122277249</v>
       </c>
       <c r="B315" t="n">
-        <v>57536</v>
+        <v>57753</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -37611,25 +37611,25 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -37639,7 +37639,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P315" t="inlineStr">
@@ -37648,10 +37648,10 @@
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>519846</v>
+        <v>520694</v>
       </c>
       <c r="R315" t="n">
-        <v>6933784</v>
+        <v>6933625</v>
       </c>
       <c r="S315" t="n">
         <v>25</v>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -36144,10 +36144,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>122277244</v>
+        <v>122277249</v>
       </c>
       <c r="B301" t="n">
-        <v>78690</v>
+        <v>57754</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -36156,41 +36156,50 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>185</v>
+        <v>103015</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I301" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P301" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>520589</v>
+        <v>520694</v>
       </c>
       <c r="R301" t="n">
-        <v>6933704</v>
+        <v>6933625</v>
       </c>
       <c r="S301" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T301" t="inlineStr">
         <is>
@@ -36246,10 +36255,10 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>122277246</v>
+        <v>122277223</v>
       </c>
       <c r="B302" t="n">
-        <v>78656</v>
+        <v>56586</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -36262,37 +36271,46 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I302" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P302" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>520527</v>
+        <v>520088</v>
       </c>
       <c r="R302" t="n">
-        <v>6933702</v>
+        <v>6933802</v>
       </c>
       <c r="S302" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T302" t="inlineStr">
         <is>
@@ -36348,10 +36366,10 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>122277219</v>
+        <v>122277252</v>
       </c>
       <c r="B303" t="n">
-        <v>90851</v>
+        <v>79275</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -36364,21 +36382,21 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I303" t="inlineStr"/>
@@ -36388,10 +36406,10 @@
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>519857</v>
+        <v>520742</v>
       </c>
       <c r="R303" t="n">
-        <v>6933857</v>
+        <v>6933667</v>
       </c>
       <c r="S303" t="n">
         <v>10</v>
@@ -36450,10 +36468,10 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>122277225</v>
+        <v>122277242</v>
       </c>
       <c r="B304" t="n">
-        <v>98240</v>
+        <v>79738</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -36462,25 +36480,25 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I304" t="inlineStr"/>
@@ -36490,10 +36508,10 @@
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>520115</v>
+        <v>520443</v>
       </c>
       <c r="R304" t="n">
-        <v>6933705</v>
+        <v>6933656</v>
       </c>
       <c r="S304" t="n">
         <v>10</v>
@@ -36552,10 +36570,10 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>122277221</v>
+        <v>122277234</v>
       </c>
       <c r="B305" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -36592,10 +36610,10 @@
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>519944</v>
+        <v>520330</v>
       </c>
       <c r="R305" t="n">
-        <v>6934006</v>
+        <v>6933624</v>
       </c>
       <c r="S305" t="n">
         <v>10</v>
@@ -36654,10 +36672,10 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>122277252</v>
+        <v>122277227</v>
       </c>
       <c r="B306" t="n">
-        <v>79274</v>
+        <v>98241</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -36666,25 +36684,25 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I306" t="inlineStr"/>
@@ -36694,10 +36712,10 @@
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>520742</v>
+        <v>520109</v>
       </c>
       <c r="R306" t="n">
-        <v>6933667</v>
+        <v>6933653</v>
       </c>
       <c r="S306" t="n">
         <v>10</v>
@@ -36756,10 +36774,10 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>122277227</v>
+        <v>122277238</v>
       </c>
       <c r="B307" t="n">
-        <v>98240</v>
+        <v>79739</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -36768,25 +36786,25 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I307" t="inlineStr"/>
@@ -36796,10 +36814,10 @@
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>520109</v>
+        <v>520316</v>
       </c>
       <c r="R307" t="n">
-        <v>6933653</v>
+        <v>6933594</v>
       </c>
       <c r="S307" t="n">
         <v>10</v>
@@ -36858,10 +36876,10 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>122277234</v>
+        <v>122277225</v>
       </c>
       <c r="B308" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -36898,10 +36916,10 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>520330</v>
+        <v>520115</v>
       </c>
       <c r="R308" t="n">
-        <v>6933624</v>
+        <v>6933705</v>
       </c>
       <c r="S308" t="n">
         <v>10</v>
@@ -36960,10 +36978,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>122277223</v>
+        <v>122277221</v>
       </c>
       <c r="B309" t="n">
-        <v>56585</v>
+        <v>98241</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -36972,50 +36990,41 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I309" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M309" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr"/>
       <c r="P309" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>520088</v>
+        <v>519944</v>
       </c>
       <c r="R309" t="n">
-        <v>6933802</v>
+        <v>6934006</v>
       </c>
       <c r="S309" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T309" t="inlineStr">
         <is>
@@ -37071,10 +37080,10 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>122277242</v>
+        <v>122277219</v>
       </c>
       <c r="B310" t="n">
-        <v>79737</v>
+        <v>90852</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -37087,21 +37096,21 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I310" t="inlineStr"/>
@@ -37111,10 +37120,10 @@
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>520443</v>
+        <v>519857</v>
       </c>
       <c r="R310" t="n">
-        <v>6933656</v>
+        <v>6933857</v>
       </c>
       <c r="S310" t="n">
         <v>10</v>
@@ -37173,10 +37182,10 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>122277238</v>
+        <v>122277246</v>
       </c>
       <c r="B311" t="n">
-        <v>79738</v>
+        <v>78657</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -37189,21 +37198,21 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I311" t="inlineStr"/>
@@ -37213,10 +37222,10 @@
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>520316</v>
+        <v>520527</v>
       </c>
       <c r="R311" t="n">
-        <v>6933594</v>
+        <v>6933702</v>
       </c>
       <c r="S311" t="n">
         <v>10</v>
@@ -37275,10 +37284,10 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>122277230</v>
+        <v>122277244</v>
       </c>
       <c r="B312" t="n">
-        <v>57536</v>
+        <v>78691</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -37291,46 +37300,37 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I312" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M312" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr"/>
       <c r="P312" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>519846</v>
+        <v>520589</v>
       </c>
       <c r="R312" t="n">
-        <v>6933784</v>
+        <v>6933704</v>
       </c>
       <c r="S312" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T312" t="inlineStr">
         <is>
@@ -37386,10 +37386,10 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>122277240</v>
+        <v>122277230</v>
       </c>
       <c r="B313" t="n">
-        <v>56585</v>
+        <v>57537</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -37402,26 +37402,26 @@
         </is>
       </c>
       <c r="E313" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
@@ -37435,10 +37435,10 @@
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>520322</v>
+        <v>519846</v>
       </c>
       <c r="R313" t="n">
-        <v>6933606</v>
+        <v>6933784</v>
       </c>
       <c r="S313" t="n">
         <v>25</v>
@@ -37497,10 +37497,10 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>122277254</v>
+        <v>122277240</v>
       </c>
       <c r="B314" t="n">
-        <v>79737</v>
+        <v>56586</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -37513,37 +37513,46 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I314" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P314" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>520941</v>
+        <v>520322</v>
       </c>
       <c r="R314" t="n">
-        <v>6933486</v>
+        <v>6933606</v>
       </c>
       <c r="S314" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T314" t="inlineStr">
         <is>
@@ -37599,10 +37608,10 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>122277249</v>
+        <v>122277254</v>
       </c>
       <c r="B315" t="n">
-        <v>57753</v>
+        <v>79738</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -37611,50 +37620,41 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I315" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M315" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr"/>
       <c r="P315" t="inlineStr">
         <is>
           <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>520694</v>
+        <v>520941</v>
       </c>
       <c r="R315" t="n">
-        <v>6933625</v>
+        <v>6933486</v>
       </c>
       <c r="S315" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T315" t="inlineStr">
         <is>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY315"/>
+  <dimension ref="A1:AY363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37708,6 +37708,4993 @@
       </c>
       <c r="AY315" t="inlineStr"/>
     </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>125660766</v>
+      </c>
+      <c r="B316" t="n">
+        <v>79565</v>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E316" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr"/>
+      <c r="P316" t="inlineStr">
+        <is>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q316" t="n">
+        <v>520729</v>
+      </c>
+      <c r="R316" t="n">
+        <v>6933543</v>
+      </c>
+      <c r="S316" t="n">
+        <v>20</v>
+      </c>
+      <c r="T316" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U316" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V316" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W316" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y316" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA316" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD316" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE316" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG316" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT316" t="inlineStr"/>
+      <c r="AW316" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX316" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY316" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>125662951</v>
+      </c>
+      <c r="B317" t="n">
+        <v>80028</v>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E317" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr"/>
+      <c r="P317" t="inlineStr">
+        <is>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q317" t="n">
+        <v>520358</v>
+      </c>
+      <c r="R317" t="n">
+        <v>6933631</v>
+      </c>
+      <c r="S317" t="n">
+        <v>20</v>
+      </c>
+      <c r="T317" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U317" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V317" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W317" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y317" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA317" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC317" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
+        </is>
+      </c>
+      <c r="AD317" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE317" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG317" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT317" t="inlineStr"/>
+      <c r="AW317" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX317" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY317" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>125661236</v>
+      </c>
+      <c r="B318" t="n">
+        <v>43932</v>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E318" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr"/>
+      <c r="P318" t="inlineStr">
+        <is>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q318" t="n">
+        <v>520684</v>
+      </c>
+      <c r="R318" t="n">
+        <v>6933537</v>
+      </c>
+      <c r="S318" t="n">
+        <v>20</v>
+      </c>
+      <c r="T318" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U318" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V318" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W318" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y318" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA318" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC318" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
+        </is>
+      </c>
+      <c r="AD318" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE318" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG318" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT318" t="inlineStr"/>
+      <c r="AW318" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX318" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY318" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>125671157</v>
+      </c>
+      <c r="B319" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E319" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr"/>
+      <c r="J319" t="inlineStr"/>
+      <c r="K319" t="inlineStr"/>
+      <c r="L319" t="inlineStr"/>
+      <c r="N319" t="inlineStr"/>
+      <c r="P319" t="inlineStr">
+        <is>
+          <t>Grinsjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q319" t="n">
+        <v>520540</v>
+      </c>
+      <c r="R319" t="n">
+        <v>6934055</v>
+      </c>
+      <c r="S319" t="n">
+        <v>10</v>
+      </c>
+      <c r="T319" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U319" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V319" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W319" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y319" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA319" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD319" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE319" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF319" t="inlineStr"/>
+      <c r="AG319" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT319" t="inlineStr"/>
+      <c r="AW319" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX319" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY319" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>125670912</v>
+      </c>
+      <c r="B320" t="n">
+        <v>80028</v>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E320" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr"/>
+      <c r="P320" t="inlineStr">
+        <is>
+          <t>Grinsjöberg, Mpd</t>
+        </is>
+      </c>
+      <c r="Q320" t="n">
+        <v>520757</v>
+      </c>
+      <c r="R320" t="n">
+        <v>6934013</v>
+      </c>
+      <c r="S320" t="n">
+        <v>25</v>
+      </c>
+      <c r="T320" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U320" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V320" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W320" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y320" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA320" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD320" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE320" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG320" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT320" t="inlineStr"/>
+      <c r="AW320" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX320" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY320" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>125670901</v>
+      </c>
+      <c r="B321" t="n">
+        <v>91166</v>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E321" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr"/>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>Grinsjöberg, Mpd</t>
+        </is>
+      </c>
+      <c r="Q321" t="n">
+        <v>520257</v>
+      </c>
+      <c r="R321" t="n">
+        <v>6933643</v>
+      </c>
+      <c r="S321" t="n">
+        <v>25</v>
+      </c>
+      <c r="T321" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U321" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V321" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W321" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y321" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA321" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD321" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE321" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG321" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT321" t="inlineStr"/>
+      <c r="AW321" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX321" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY321" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>125670920</v>
+      </c>
+      <c r="B322" t="n">
+        <v>105293</v>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E322" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr"/>
+      <c r="P322" t="inlineStr">
+        <is>
+          <t>Grinsjöberg, Mpd</t>
+        </is>
+      </c>
+      <c r="Q322" t="n">
+        <v>520141</v>
+      </c>
+      <c r="R322" t="n">
+        <v>6933910</v>
+      </c>
+      <c r="S322" t="n">
+        <v>25</v>
+      </c>
+      <c r="T322" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U322" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V322" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W322" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y322" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA322" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD322" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE322" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG322" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT322" t="inlineStr"/>
+      <c r="AW322" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX322" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY322" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>125670906</v>
+      </c>
+      <c r="B323" t="n">
+        <v>79932</v>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E323" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr"/>
+      <c r="P323" t="inlineStr">
+        <is>
+          <t>Grinsjöberg, Mpd</t>
+        </is>
+      </c>
+      <c r="Q323" t="n">
+        <v>521033</v>
+      </c>
+      <c r="R323" t="n">
+        <v>6933394</v>
+      </c>
+      <c r="S323" t="n">
+        <v>25</v>
+      </c>
+      <c r="T323" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U323" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V323" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W323" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y323" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA323" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD323" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE323" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG323" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT323" t="inlineStr"/>
+      <c r="AW323" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX323" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY323" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>125663708</v>
+      </c>
+      <c r="B324" t="n">
+        <v>56836</v>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E324" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="P324" t="inlineStr">
+        <is>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q324" t="n">
+        <v>520185</v>
+      </c>
+      <c r="R324" t="n">
+        <v>6933721</v>
+      </c>
+      <c r="S324" t="n">
+        <v>25</v>
+      </c>
+      <c r="T324" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U324" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V324" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W324" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y324" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA324" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD324" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE324" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG324" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT324" t="inlineStr"/>
+      <c r="AW324" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX324" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY324" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>125670921</v>
+      </c>
+      <c r="B325" t="n">
+        <v>92448</v>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E325" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr"/>
+      <c r="P325" t="inlineStr">
+        <is>
+          <t>Grinsjöberg, Mpd</t>
+        </is>
+      </c>
+      <c r="Q325" t="n">
+        <v>520731</v>
+      </c>
+      <c r="R325" t="n">
+        <v>6934038</v>
+      </c>
+      <c r="S325" t="n">
+        <v>25</v>
+      </c>
+      <c r="T325" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U325" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V325" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W325" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y325" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA325" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD325" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE325" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG325" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT325" t="inlineStr"/>
+      <c r="AW325" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX325" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY325" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>125671098</v>
+      </c>
+      <c r="B326" t="n">
+        <v>80028</v>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E326" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr"/>
+      <c r="J326" t="inlineStr"/>
+      <c r="K326" t="inlineStr"/>
+      <c r="N326" t="inlineStr"/>
+      <c r="P326" t="inlineStr">
+        <is>
+          <t>Grinsjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q326" t="n">
+        <v>520578</v>
+      </c>
+      <c r="R326" t="n">
+        <v>6934069</v>
+      </c>
+      <c r="S326" t="n">
+        <v>10</v>
+      </c>
+      <c r="T326" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U326" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V326" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W326" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y326" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA326" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD326" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE326" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF326" t="inlineStr"/>
+      <c r="AG326" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT326" t="inlineStr"/>
+      <c r="AW326" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX326" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY326" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>125659241</v>
+      </c>
+      <c r="B327" t="n">
+        <v>79565</v>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E327" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr"/>
+      <c r="P327" t="inlineStr">
+        <is>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q327" t="n">
+        <v>520844</v>
+      </c>
+      <c r="R327" t="n">
+        <v>6933514</v>
+      </c>
+      <c r="S327" t="n">
+        <v>20</v>
+      </c>
+      <c r="T327" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U327" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V327" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W327" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y327" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA327" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD327" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE327" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG327" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT327" t="inlineStr"/>
+      <c r="AW327" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX327" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY327" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>125670923</v>
+      </c>
+      <c r="B328" t="n">
+        <v>92448</v>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E328" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr"/>
+      <c r="P328" t="inlineStr">
+        <is>
+          <t>Grinsjöberg, Mpd</t>
+        </is>
+      </c>
+      <c r="Q328" t="n">
+        <v>520634</v>
+      </c>
+      <c r="R328" t="n">
+        <v>6934079</v>
+      </c>
+      <c r="S328" t="n">
+        <v>25</v>
+      </c>
+      <c r="T328" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U328" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V328" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W328" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y328" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA328" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD328" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE328" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG328" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT328" t="inlineStr"/>
+      <c r="AW328" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX328" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY328" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>125670917</v>
+      </c>
+      <c r="B329" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E329" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr"/>
+      <c r="P329" t="inlineStr">
+        <is>
+          <t>Grinsjöberg, Mpd</t>
+        </is>
+      </c>
+      <c r="Q329" t="n">
+        <v>520786</v>
+      </c>
+      <c r="R329" t="n">
+        <v>6933914</v>
+      </c>
+      <c r="S329" t="n">
+        <v>25</v>
+      </c>
+      <c r="T329" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U329" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V329" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W329" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y329" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA329" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD329" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE329" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG329" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT329" t="inlineStr"/>
+      <c r="AW329" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX329" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY329" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>125671498</v>
+      </c>
+      <c r="B330" t="n">
+        <v>80028</v>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E330" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr"/>
+      <c r="J330" t="inlineStr"/>
+      <c r="K330" t="inlineStr"/>
+      <c r="N330" t="inlineStr"/>
+      <c r="P330" t="inlineStr">
+        <is>
+          <t>Grinsjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q330" t="n">
+        <v>520385</v>
+      </c>
+      <c r="R330" t="n">
+        <v>6933569</v>
+      </c>
+      <c r="S330" t="n">
+        <v>25</v>
+      </c>
+      <c r="T330" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U330" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V330" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W330" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y330" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA330" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD330" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE330" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF330" t="inlineStr"/>
+      <c r="AG330" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT330" t="inlineStr"/>
+      <c r="AW330" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX330" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY330" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>125659251</v>
+      </c>
+      <c r="B331" t="n">
+        <v>78683</v>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E331" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr"/>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q331" t="n">
+        <v>520823</v>
+      </c>
+      <c r="R331" t="n">
+        <v>6933519</v>
+      </c>
+      <c r="S331" t="n">
+        <v>20</v>
+      </c>
+      <c r="T331" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U331" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V331" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W331" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y331" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA331" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD331" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE331" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG331" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT331" t="inlineStr"/>
+      <c r="AW331" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX331" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY331" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>125661442</v>
+      </c>
+      <c r="B332" t="n">
+        <v>78592</v>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E332" t="n">
+        <v>353</v>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr"/>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q332" t="n">
+        <v>520629</v>
+      </c>
+      <c r="R332" t="n">
+        <v>6933514</v>
+      </c>
+      <c r="S332" t="n">
+        <v>20</v>
+      </c>
+      <c r="T332" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U332" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V332" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W332" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y332" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA332" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD332" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE332" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG332" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT332" t="inlineStr"/>
+      <c r="AW332" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX332" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY332" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>125671278</v>
+      </c>
+      <c r="B333" t="n">
+        <v>80028</v>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E333" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr"/>
+      <c r="J333" t="inlineStr"/>
+      <c r="K333" t="inlineStr"/>
+      <c r="N333" t="inlineStr"/>
+      <c r="P333" t="inlineStr">
+        <is>
+          <t>Grinsjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q333" t="n">
+        <v>520511</v>
+      </c>
+      <c r="R333" t="n">
+        <v>6934025</v>
+      </c>
+      <c r="S333" t="n">
+        <v>10</v>
+      </c>
+      <c r="T333" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U333" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V333" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W333" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y333" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA333" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD333" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE333" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF333" t="inlineStr"/>
+      <c r="AG333" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT333" t="inlineStr"/>
+      <c r="AW333" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX333" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY333" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>125659270</v>
+      </c>
+      <c r="B334" t="n">
+        <v>92448</v>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E334" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr"/>
+      <c r="P334" t="inlineStr">
+        <is>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q334" t="n">
+        <v>520846</v>
+      </c>
+      <c r="R334" t="n">
+        <v>6933515</v>
+      </c>
+      <c r="S334" t="n">
+        <v>20</v>
+      </c>
+      <c r="T334" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U334" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V334" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W334" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y334" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA334" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD334" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE334" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG334" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT334" t="inlineStr"/>
+      <c r="AW334" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX334" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY334" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>125670910</v>
+      </c>
+      <c r="B335" t="n">
+        <v>80028</v>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E335" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr"/>
+      <c r="P335" t="inlineStr">
+        <is>
+          <t>Grinsjöberg, Mpd</t>
+        </is>
+      </c>
+      <c r="Q335" t="n">
+        <v>520830</v>
+      </c>
+      <c r="R335" t="n">
+        <v>6933884</v>
+      </c>
+      <c r="S335" t="n">
+        <v>25</v>
+      </c>
+      <c r="T335" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U335" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V335" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W335" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y335" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA335" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD335" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE335" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG335" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT335" t="inlineStr"/>
+      <c r="AW335" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX335" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY335" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>125671054</v>
+      </c>
+      <c r="B336" t="n">
+        <v>80028</v>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E336" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr"/>
+      <c r="J336" t="inlineStr"/>
+      <c r="K336" t="inlineStr"/>
+      <c r="N336" t="inlineStr"/>
+      <c r="P336" t="inlineStr">
+        <is>
+          <t>Grinsjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q336" t="n">
+        <v>520612</v>
+      </c>
+      <c r="R336" t="n">
+        <v>6934046</v>
+      </c>
+      <c r="S336" t="n">
+        <v>10</v>
+      </c>
+      <c r="T336" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U336" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V336" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W336" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y336" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA336" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD336" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE336" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF336" t="inlineStr"/>
+      <c r="AG336" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT336" t="inlineStr"/>
+      <c r="AW336" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX336" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY336" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>125670908</v>
+      </c>
+      <c r="B337" t="n">
+        <v>80028</v>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E337" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr"/>
+      <c r="P337" t="inlineStr">
+        <is>
+          <t>Grinsjöberg, Mpd</t>
+        </is>
+      </c>
+      <c r="Q337" t="n">
+        <v>520754</v>
+      </c>
+      <c r="R337" t="n">
+        <v>6933960</v>
+      </c>
+      <c r="S337" t="n">
+        <v>25</v>
+      </c>
+      <c r="T337" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U337" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V337" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W337" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y337" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA337" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC337" t="inlineStr">
+        <is>
+          <t>På björk</t>
+        </is>
+      </c>
+      <c r="AD337" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE337" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG337" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT337" t="inlineStr"/>
+      <c r="AW337" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX337" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY337" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>125670907</v>
+      </c>
+      <c r="B338" t="n">
+        <v>78684</v>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E338" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr"/>
+      <c r="P338" t="inlineStr">
+        <is>
+          <t>Grinsjöberg, Mpd</t>
+        </is>
+      </c>
+      <c r="Q338" t="n">
+        <v>520460</v>
+      </c>
+      <c r="R338" t="n">
+        <v>6933565</v>
+      </c>
+      <c r="S338" t="n">
+        <v>25</v>
+      </c>
+      <c r="T338" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U338" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V338" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W338" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y338" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA338" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD338" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE338" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG338" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT338" t="inlineStr"/>
+      <c r="AW338" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX338" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY338" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>125671391</v>
+      </c>
+      <c r="B339" t="n">
+        <v>57793</v>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E339" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr"/>
+      <c r="K339" t="inlineStr"/>
+      <c r="L339" t="inlineStr"/>
+      <c r="M339" t="inlineStr"/>
+      <c r="N339" t="inlineStr"/>
+      <c r="P339" t="inlineStr">
+        <is>
+          <t>Grinsjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q339" t="n">
+        <v>520408</v>
+      </c>
+      <c r="R339" t="n">
+        <v>6934036</v>
+      </c>
+      <c r="S339" t="n">
+        <v>25</v>
+      </c>
+      <c r="T339" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U339" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V339" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W339" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y339" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA339" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD339" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE339" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG339" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT339" t="inlineStr"/>
+      <c r="AW339" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX339" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY339" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>125660155</v>
+      </c>
+      <c r="B340" t="n">
+        <v>78684</v>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E340" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr"/>
+      <c r="P340" t="inlineStr">
+        <is>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q340" t="n">
+        <v>520786</v>
+      </c>
+      <c r="R340" t="n">
+        <v>6933540</v>
+      </c>
+      <c r="S340" t="n">
+        <v>20</v>
+      </c>
+      <c r="T340" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U340" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V340" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W340" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y340" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA340" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD340" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE340" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG340" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT340" t="inlineStr"/>
+      <c r="AW340" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX340" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY340" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>125661738</v>
+      </c>
+      <c r="B341" t="n">
+        <v>92448</v>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E341" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr"/>
+      <c r="P341" t="inlineStr">
+        <is>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q341" t="n">
+        <v>520605</v>
+      </c>
+      <c r="R341" t="n">
+        <v>6933517</v>
+      </c>
+      <c r="S341" t="n">
+        <v>20</v>
+      </c>
+      <c r="T341" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U341" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V341" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W341" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y341" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA341" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD341" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE341" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG341" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT341" t="inlineStr"/>
+      <c r="AW341" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX341" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY341" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>125670904</v>
+      </c>
+      <c r="B342" t="n">
+        <v>56836</v>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E342" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr"/>
+      <c r="P342" t="inlineStr">
+        <is>
+          <t>Grinsjöberg, Mpd</t>
+        </is>
+      </c>
+      <c r="Q342" t="n">
+        <v>520208</v>
+      </c>
+      <c r="R342" t="n">
+        <v>6933929</v>
+      </c>
+      <c r="S342" t="n">
+        <v>25</v>
+      </c>
+      <c r="T342" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U342" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V342" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W342" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y342" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA342" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD342" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE342" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG342" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT342" t="inlineStr"/>
+      <c r="AW342" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX342" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY342" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>125670903</v>
+      </c>
+      <c r="B343" t="n">
+        <v>56836</v>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E343" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr"/>
+      <c r="P343" t="inlineStr">
+        <is>
+          <t>Grinsjöberg, Mpd</t>
+        </is>
+      </c>
+      <c r="Q343" t="n">
+        <v>520731</v>
+      </c>
+      <c r="R343" t="n">
+        <v>6934042</v>
+      </c>
+      <c r="S343" t="n">
+        <v>25</v>
+      </c>
+      <c r="T343" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U343" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V343" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W343" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y343" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA343" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC343" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD343" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE343" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG343" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT343" t="inlineStr"/>
+      <c r="AW343" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX343" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY343" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>125671342</v>
+      </c>
+      <c r="B344" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E344" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr"/>
+      <c r="J344" t="inlineStr"/>
+      <c r="K344" t="inlineStr"/>
+      <c r="L344" t="inlineStr"/>
+      <c r="N344" t="inlineStr"/>
+      <c r="P344" t="inlineStr">
+        <is>
+          <t>Grinsjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q344" t="n">
+        <v>520463</v>
+      </c>
+      <c r="R344" t="n">
+        <v>6934009</v>
+      </c>
+      <c r="S344" t="n">
+        <v>10</v>
+      </c>
+      <c r="T344" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U344" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V344" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W344" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y344" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA344" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD344" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE344" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF344" t="inlineStr"/>
+      <c r="AG344" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT344" t="inlineStr"/>
+      <c r="AW344" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX344" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY344" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>125671021</v>
+      </c>
+      <c r="B345" t="n">
+        <v>57632</v>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E345" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr"/>
+      <c r="K345" t="inlineStr"/>
+      <c r="L345" t="inlineStr"/>
+      <c r="M345" t="inlineStr"/>
+      <c r="N345" t="inlineStr"/>
+      <c r="P345" t="inlineStr">
+        <is>
+          <t>Grinsjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q345" t="n">
+        <v>520607</v>
+      </c>
+      <c r="R345" t="n">
+        <v>6934048</v>
+      </c>
+      <c r="S345" t="n">
+        <v>10</v>
+      </c>
+      <c r="T345" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U345" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V345" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W345" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y345" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA345" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC345" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
+      <c r="AD345" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE345" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG345" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT345" t="inlineStr"/>
+      <c r="AW345" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX345" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY345" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>125661898</v>
+      </c>
+      <c r="B346" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E346" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr"/>
+      <c r="P346" t="inlineStr">
+        <is>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q346" t="n">
+        <v>520558</v>
+      </c>
+      <c r="R346" t="n">
+        <v>6933556</v>
+      </c>
+      <c r="S346" t="n">
+        <v>15</v>
+      </c>
+      <c r="T346" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U346" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V346" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W346" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y346" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA346" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD346" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE346" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG346" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT346" t="inlineStr"/>
+      <c r="AW346" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX346" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY346" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>125662204</v>
+      </c>
+      <c r="B347" t="n">
+        <v>91326</v>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E347" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr"/>
+      <c r="P347" t="inlineStr">
+        <is>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q347" t="n">
+        <v>520425</v>
+      </c>
+      <c r="R347" t="n">
+        <v>6933544</v>
+      </c>
+      <c r="S347" t="n">
+        <v>20</v>
+      </c>
+      <c r="T347" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U347" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V347" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W347" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y347" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA347" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD347" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE347" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG347" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT347" t="inlineStr"/>
+      <c r="AW347" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX347" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY347" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>125670905</v>
+      </c>
+      <c r="B348" t="n">
+        <v>80029</v>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E348" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr"/>
+      <c r="P348" t="inlineStr">
+        <is>
+          <t>Grinsjöberg, Mpd</t>
+        </is>
+      </c>
+      <c r="Q348" t="n">
+        <v>520801</v>
+      </c>
+      <c r="R348" t="n">
+        <v>6933448</v>
+      </c>
+      <c r="S348" t="n">
+        <v>25</v>
+      </c>
+      <c r="T348" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U348" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V348" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W348" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y348" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA348" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD348" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE348" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG348" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT348" t="inlineStr"/>
+      <c r="AW348" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX348" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY348" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>125671230</v>
+      </c>
+      <c r="B349" t="n">
+        <v>98290</v>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E349" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr"/>
+      <c r="J349" t="inlineStr"/>
+      <c r="K349" t="inlineStr"/>
+      <c r="L349" t="inlineStr"/>
+      <c r="N349" t="inlineStr"/>
+      <c r="P349" t="inlineStr">
+        <is>
+          <t>Grinsjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q349" t="n">
+        <v>520549</v>
+      </c>
+      <c r="R349" t="n">
+        <v>6934058</v>
+      </c>
+      <c r="S349" t="n">
+        <v>10</v>
+      </c>
+      <c r="T349" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U349" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V349" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W349" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y349" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA349" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD349" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE349" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF349" t="inlineStr"/>
+      <c r="AG349" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT349" t="inlineStr"/>
+      <c r="AW349" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX349" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY349" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>125671307</v>
+      </c>
+      <c r="B350" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E350" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr"/>
+      <c r="J350" t="inlineStr"/>
+      <c r="K350" t="inlineStr"/>
+      <c r="L350" t="inlineStr"/>
+      <c r="N350" t="inlineStr"/>
+      <c r="P350" t="inlineStr">
+        <is>
+          <t>Grinsjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q350" t="n">
+        <v>520477</v>
+      </c>
+      <c r="R350" t="n">
+        <v>6934031</v>
+      </c>
+      <c r="S350" t="n">
+        <v>10</v>
+      </c>
+      <c r="T350" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U350" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V350" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W350" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y350" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA350" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD350" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE350" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF350" t="inlineStr"/>
+      <c r="AG350" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT350" t="inlineStr"/>
+      <c r="AW350" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX350" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY350" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>125670909</v>
+      </c>
+      <c r="B351" t="n">
+        <v>80028</v>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E351" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr"/>
+      <c r="P351" t="inlineStr">
+        <is>
+          <t>Grinsjöberg, Mpd</t>
+        </is>
+      </c>
+      <c r="Q351" t="n">
+        <v>520754</v>
+      </c>
+      <c r="R351" t="n">
+        <v>6934006</v>
+      </c>
+      <c r="S351" t="n">
+        <v>25</v>
+      </c>
+      <c r="T351" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U351" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V351" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W351" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y351" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA351" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC351" t="inlineStr">
+        <is>
+          <t>På björk</t>
+        </is>
+      </c>
+      <c r="AD351" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE351" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG351" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT351" t="inlineStr"/>
+      <c r="AW351" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX351" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY351" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>125670922</v>
+      </c>
+      <c r="B352" t="n">
+        <v>92448</v>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E352" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr"/>
+      <c r="P352" t="inlineStr">
+        <is>
+          <t>Grinsjöberg, Mpd</t>
+        </is>
+      </c>
+      <c r="Q352" t="n">
+        <v>520637</v>
+      </c>
+      <c r="R352" t="n">
+        <v>6934037</v>
+      </c>
+      <c r="S352" t="n">
+        <v>25</v>
+      </c>
+      <c r="T352" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U352" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V352" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W352" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y352" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA352" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD352" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE352" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG352" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT352" t="inlineStr"/>
+      <c r="AW352" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX352" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY352" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>125670913</v>
+      </c>
+      <c r="B353" t="n">
+        <v>80028</v>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E353" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr"/>
+      <c r="P353" t="inlineStr">
+        <is>
+          <t>Grinsjöberg, Mpd</t>
+        </is>
+      </c>
+      <c r="Q353" t="n">
+        <v>520620</v>
+      </c>
+      <c r="R353" t="n">
+        <v>6934070</v>
+      </c>
+      <c r="S353" t="n">
+        <v>25</v>
+      </c>
+      <c r="T353" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U353" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V353" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W353" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y353" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA353" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD353" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE353" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG353" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT353" t="inlineStr"/>
+      <c r="AW353" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX353" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY353" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>125670916</v>
+      </c>
+      <c r="B354" t="n">
+        <v>80028</v>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E354" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr"/>
+      <c r="P354" t="inlineStr">
+        <is>
+          <t>Grinsjöberg, Mpd</t>
+        </is>
+      </c>
+      <c r="Q354" t="n">
+        <v>520803</v>
+      </c>
+      <c r="R354" t="n">
+        <v>6933448</v>
+      </c>
+      <c r="S354" t="n">
+        <v>25</v>
+      </c>
+      <c r="T354" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U354" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V354" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W354" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y354" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA354" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD354" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE354" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG354" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT354" t="inlineStr"/>
+      <c r="AW354" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX354" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY354" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>125661680</v>
+      </c>
+      <c r="B355" t="n">
+        <v>79565</v>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E355" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr"/>
+      <c r="P355" t="inlineStr">
+        <is>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q355" t="n">
+        <v>520639</v>
+      </c>
+      <c r="R355" t="n">
+        <v>6933509</v>
+      </c>
+      <c r="S355" t="n">
+        <v>20</v>
+      </c>
+      <c r="T355" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U355" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V355" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W355" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y355" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA355" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD355" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE355" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG355" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT355" t="inlineStr"/>
+      <c r="AW355" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX355" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY355" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>125671469</v>
+      </c>
+      <c r="B356" t="n">
+        <v>80028</v>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E356" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr"/>
+      <c r="J356" t="inlineStr"/>
+      <c r="K356" t="inlineStr"/>
+      <c r="N356" t="inlineStr"/>
+      <c r="P356" t="inlineStr">
+        <is>
+          <t>Grinsjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q356" t="n">
+        <v>520296</v>
+      </c>
+      <c r="R356" t="n">
+        <v>6933639</v>
+      </c>
+      <c r="S356" t="n">
+        <v>25</v>
+      </c>
+      <c r="T356" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U356" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V356" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W356" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y356" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA356" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD356" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE356" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF356" t="inlineStr"/>
+      <c r="AG356" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT356" t="inlineStr"/>
+      <c r="AW356" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX356" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY356" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>125670919</v>
+      </c>
+      <c r="B357" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E357" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr"/>
+      <c r="P357" t="inlineStr">
+        <is>
+          <t>Grinsjöberg, Mpd</t>
+        </is>
+      </c>
+      <c r="Q357" t="n">
+        <v>520223</v>
+      </c>
+      <c r="R357" t="n">
+        <v>6933684</v>
+      </c>
+      <c r="S357" t="n">
+        <v>25</v>
+      </c>
+      <c r="T357" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U357" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V357" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W357" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y357" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA357" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD357" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE357" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG357" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT357" t="inlineStr"/>
+      <c r="AW357" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX357" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY357" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>125670918</v>
+      </c>
+      <c r="B358" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E358" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr"/>
+      <c r="P358" t="inlineStr">
+        <is>
+          <t>Grinsjöberg, Mpd</t>
+        </is>
+      </c>
+      <c r="Q358" t="n">
+        <v>520172</v>
+      </c>
+      <c r="R358" t="n">
+        <v>6933875</v>
+      </c>
+      <c r="S358" t="n">
+        <v>25</v>
+      </c>
+      <c r="T358" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U358" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V358" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W358" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y358" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA358" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD358" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE358" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG358" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT358" t="inlineStr"/>
+      <c r="AW358" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX358" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY358" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>125670924</v>
+      </c>
+      <c r="B359" t="n">
+        <v>92448</v>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E359" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr"/>
+      <c r="P359" t="inlineStr">
+        <is>
+          <t>Grinsjöberg, Mpd</t>
+        </is>
+      </c>
+      <c r="Q359" t="n">
+        <v>520194</v>
+      </c>
+      <c r="R359" t="n">
+        <v>6933813</v>
+      </c>
+      <c r="S359" t="n">
+        <v>25</v>
+      </c>
+      <c r="T359" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U359" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V359" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W359" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y359" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA359" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD359" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE359" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG359" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT359" t="inlineStr"/>
+      <c r="AW359" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX359" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY359" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>125670914</v>
+      </c>
+      <c r="B360" t="n">
+        <v>80028</v>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E360" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr"/>
+      <c r="P360" t="inlineStr">
+        <is>
+          <t>Grinsjöberg, Mpd</t>
+        </is>
+      </c>
+      <c r="Q360" t="n">
+        <v>520224</v>
+      </c>
+      <c r="R360" t="n">
+        <v>6933690</v>
+      </c>
+      <c r="S360" t="n">
+        <v>25</v>
+      </c>
+      <c r="T360" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U360" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V360" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W360" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y360" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA360" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD360" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE360" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG360" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT360" t="inlineStr"/>
+      <c r="AW360" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX360" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY360" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>125671434</v>
+      </c>
+      <c r="B361" t="n">
+        <v>80028</v>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E361" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr"/>
+      <c r="J361" t="inlineStr"/>
+      <c r="K361" t="inlineStr"/>
+      <c r="N361" t="inlineStr"/>
+      <c r="P361" t="inlineStr">
+        <is>
+          <t>Grinsjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q361" t="n">
+        <v>520364</v>
+      </c>
+      <c r="R361" t="n">
+        <v>6934008</v>
+      </c>
+      <c r="S361" t="n">
+        <v>10</v>
+      </c>
+      <c r="T361" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U361" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V361" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W361" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y361" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA361" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD361" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE361" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF361" t="inlineStr"/>
+      <c r="AG361" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT361" t="inlineStr"/>
+      <c r="AW361" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX361" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY361" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>125663906</v>
+      </c>
+      <c r="B362" t="n">
+        <v>80028</v>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E362" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr"/>
+      <c r="P362" t="inlineStr">
+        <is>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q362" t="n">
+        <v>520184</v>
+      </c>
+      <c r="R362" t="n">
+        <v>6933765</v>
+      </c>
+      <c r="S362" t="n">
+        <v>20</v>
+      </c>
+      <c r="T362" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U362" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V362" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W362" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y362" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA362" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD362" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE362" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG362" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT362" t="inlineStr"/>
+      <c r="AW362" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX362" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY362" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>125660786</v>
+      </c>
+      <c r="B363" t="n">
+        <v>78683</v>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E363" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr"/>
+      <c r="P363" t="inlineStr">
+        <is>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q363" t="n">
+        <v>520731</v>
+      </c>
+      <c r="R363" t="n">
+        <v>6933528</v>
+      </c>
+      <c r="S363" t="n">
+        <v>20</v>
+      </c>
+      <c r="T363" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U363" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V363" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W363" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y363" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA363" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD363" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE363" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG363" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT363" t="inlineStr"/>
+      <c r="AW363" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX363" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY363" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -38860,10 +38860,10 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>125659241</v>
+        <v>125670923</v>
       </c>
       <c r="B327" t="n">
-        <v>79565</v>
+        <v>92448</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
@@ -38872,41 +38872,41 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I327" t="inlineStr"/>
       <c r="P327" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q327" t="n">
-        <v>520844</v>
+        <v>520634</v>
       </c>
       <c r="R327" t="n">
-        <v>6933514</v>
+        <v>6934079</v>
       </c>
       <c r="S327" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T327" t="inlineStr">
         <is>
@@ -38962,10 +38962,10 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>125670923</v>
+        <v>125670917</v>
       </c>
       <c r="B328" t="n">
-        <v>92448</v>
+        <v>98269</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
@@ -38974,25 +38974,25 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I328" t="inlineStr"/>
@@ -39002,10 +39002,10 @@
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>520634</v>
+        <v>520786</v>
       </c>
       <c r="R328" t="n">
-        <v>6934079</v>
+        <v>6933914</v>
       </c>
       <c r="S328" t="n">
         <v>25</v>
@@ -39064,10 +39064,10 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>125670917</v>
+        <v>125659241</v>
       </c>
       <c r="B329" t="n">
-        <v>98269</v>
+        <v>79565</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
@@ -39076,41 +39076,41 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I329" t="inlineStr"/>
       <c r="P329" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q329" t="n">
-        <v>520786</v>
+        <v>520844</v>
       </c>
       <c r="R329" t="n">
-        <v>6933914</v>
+        <v>6933514</v>
       </c>
       <c r="S329" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T329" t="inlineStr">
         <is>
@@ -40838,10 +40838,10 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>125661898</v>
+        <v>125670905</v>
       </c>
       <c r="B346" t="n">
-        <v>98269</v>
+        <v>80029</v>
       </c>
       <c r="C346" t="inlineStr">
         <is>
@@ -40850,41 +40850,41 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E346" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I346" t="inlineStr"/>
       <c r="P346" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q346" t="n">
-        <v>520558</v>
+        <v>520801</v>
       </c>
       <c r="R346" t="n">
-        <v>6933556</v>
+        <v>6933448</v>
       </c>
       <c r="S346" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T346" t="inlineStr">
         <is>
@@ -40940,10 +40940,10 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>125662204</v>
+        <v>125671230</v>
       </c>
       <c r="B347" t="n">
-        <v>91326</v>
+        <v>98290</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>
@@ -40952,41 +40952,45 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E347" t="n">
-        <v>1503</v>
+        <v>221952</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I347" t="inlineStr"/>
+      <c r="J347" t="inlineStr"/>
+      <c r="K347" t="inlineStr"/>
+      <c r="L347" t="inlineStr"/>
+      <c r="N347" t="inlineStr"/>
       <c r="P347" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q347" t="n">
-        <v>520425</v>
+        <v>520549</v>
       </c>
       <c r="R347" t="n">
-        <v>6933544</v>
+        <v>6934058</v>
       </c>
       <c r="S347" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T347" t="inlineStr">
         <is>
@@ -41024,6 +41028,7 @@
       <c r="AE347" t="b">
         <v>0</v>
       </c>
+      <c r="AF347" t="inlineStr"/>
       <c r="AG347" t="b">
         <v>0</v>
       </c>
@@ -41042,10 +41047,10 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>125670905</v>
+        <v>125661898</v>
       </c>
       <c r="B348" t="n">
-        <v>80029</v>
+        <v>98269</v>
       </c>
       <c r="C348" t="inlineStr">
         <is>
@@ -41054,41 +41059,41 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E348" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I348" t="inlineStr"/>
       <c r="P348" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q348" t="n">
-        <v>520801</v>
+        <v>520558</v>
       </c>
       <c r="R348" t="n">
-        <v>6933448</v>
+        <v>6933556</v>
       </c>
       <c r="S348" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T348" t="inlineStr">
         <is>
@@ -41144,10 +41149,10 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>125671230</v>
+        <v>125662204</v>
       </c>
       <c r="B349" t="n">
-        <v>98290</v>
+        <v>91326</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>
@@ -41156,45 +41161,41 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E349" t="n">
-        <v>221952</v>
+        <v>1503</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I349" t="inlineStr"/>
-      <c r="J349" t="inlineStr"/>
-      <c r="K349" t="inlineStr"/>
-      <c r="L349" t="inlineStr"/>
-      <c r="N349" t="inlineStr"/>
       <c r="P349" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q349" t="n">
-        <v>520549</v>
+        <v>520425</v>
       </c>
       <c r="R349" t="n">
-        <v>6934058</v>
+        <v>6933544</v>
       </c>
       <c r="S349" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T349" t="inlineStr">
         <is>
@@ -41232,7 +41233,6 @@
       <c r="AE349" t="b">
         <v>0</v>
       </c>
-      <c r="AF349" t="inlineStr"/>
       <c r="AG349" t="b">
         <v>0</v>
       </c>
@@ -42183,10 +42183,10 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>125670924</v>
+        <v>125663906</v>
       </c>
       <c r="B359" t="n">
-        <v>92448</v>
+        <v>80028</v>
       </c>
       <c r="C359" t="inlineStr">
         <is>
@@ -42195,41 +42195,41 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E359" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I359" t="inlineStr"/>
       <c r="P359" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q359" t="n">
-        <v>520194</v>
+        <v>520184</v>
       </c>
       <c r="R359" t="n">
-        <v>6933813</v>
+        <v>6933765</v>
       </c>
       <c r="S359" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T359" t="inlineStr">
         <is>
@@ -42285,10 +42285,10 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>125670914</v>
+        <v>125670924</v>
       </c>
       <c r="B360" t="n">
-        <v>80028</v>
+        <v>92448</v>
       </c>
       <c r="C360" t="inlineStr">
         <is>
@@ -42297,25 +42297,25 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E360" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I360" t="inlineStr"/>
@@ -42325,10 +42325,10 @@
         </is>
       </c>
       <c r="Q360" t="n">
-        <v>520224</v>
+        <v>520194</v>
       </c>
       <c r="R360" t="n">
-        <v>6933690</v>
+        <v>6933813</v>
       </c>
       <c r="S360" t="n">
         <v>25</v>
@@ -42387,7 +42387,7 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>125671434</v>
+        <v>125670914</v>
       </c>
       <c r="B361" t="n">
         <v>80028</v>
@@ -42421,22 +42421,19 @@
         </is>
       </c>
       <c r="I361" t="inlineStr"/>
-      <c r="J361" t="inlineStr"/>
-      <c r="K361" t="inlineStr"/>
-      <c r="N361" t="inlineStr"/>
       <c r="P361" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q361" t="n">
-        <v>520364</v>
+        <v>520224</v>
       </c>
       <c r="R361" t="n">
-        <v>6934008</v>
+        <v>6933690</v>
       </c>
       <c r="S361" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T361" t="inlineStr">
         <is>
@@ -42474,7 +42471,6 @@
       <c r="AE361" t="b">
         <v>0</v>
       </c>
-      <c r="AF361" t="inlineStr"/>
       <c r="AG361" t="b">
         <v>0</v>
       </c>
@@ -42493,7 +42489,7 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>125663906</v>
+        <v>125671434</v>
       </c>
       <c r="B362" t="n">
         <v>80028</v>
@@ -42527,19 +42523,22 @@
         </is>
       </c>
       <c r="I362" t="inlineStr"/>
+      <c r="J362" t="inlineStr"/>
+      <c r="K362" t="inlineStr"/>
+      <c r="N362" t="inlineStr"/>
       <c r="P362" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q362" t="n">
-        <v>520184</v>
+        <v>520364</v>
       </c>
       <c r="R362" t="n">
-        <v>6933765</v>
+        <v>6934008</v>
       </c>
       <c r="S362" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T362" t="inlineStr">
         <is>
@@ -42577,6 +42576,7 @@
       <c r="AE362" t="b">
         <v>0</v>
       </c>
+      <c r="AF362" t="inlineStr"/>
       <c r="AG362" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -37710,53 +37710,48 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>125660766</v>
+        <v>125670918</v>
       </c>
       <c r="B316" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E316" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I316" t="inlineStr"/>
       <c r="P316" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q316" t="n">
-        <v>520729</v>
+        <v>520172</v>
       </c>
       <c r="R316" t="n">
-        <v>6933543</v>
+        <v>6933875</v>
       </c>
       <c r="S316" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T316" t="inlineStr">
         <is>
@@ -37815,12 +37810,7 @@
         <v>125662951</v>
       </c>
       <c r="B317" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -37919,15 +37909,10 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>125661236</v>
+        <v>125670904</v>
       </c>
       <c r="B318" t="n">
-        <v>43932</v>
-      </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -37935,37 +37920,37 @@
         </is>
       </c>
       <c r="E318" t="n">
-        <v>101735</v>
+        <v>100138</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I318" t="inlineStr"/>
       <c r="P318" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q318" t="n">
-        <v>520684</v>
+        <v>520208</v>
       </c>
       <c r="R318" t="n">
-        <v>6933537</v>
+        <v>6933929</v>
       </c>
       <c r="S318" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T318" t="inlineStr">
         <is>
@@ -37995,11 +37980,6 @@
       <c r="AA318" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC318" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD318" t="b">
@@ -38026,57 +38006,48 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>125671157</v>
+        <v>125670912</v>
       </c>
       <c r="B319" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E319" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I319" t="inlineStr"/>
-      <c r="J319" t="inlineStr"/>
-      <c r="K319" t="inlineStr"/>
-      <c r="L319" t="inlineStr"/>
-      <c r="N319" t="inlineStr"/>
       <c r="P319" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>520540</v>
+        <v>520757</v>
       </c>
       <c r="R319" t="n">
-        <v>6934055</v>
+        <v>6934013</v>
       </c>
       <c r="S319" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T319" t="inlineStr">
         <is>
@@ -38114,7 +38085,6 @@
       <c r="AE319" t="b">
         <v>0</v>
       </c>
-      <c r="AF319" t="inlineStr"/>
       <c r="AG319" t="b">
         <v>0</v>
       </c>
@@ -38133,15 +38103,10 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>125670912</v>
+        <v>125671391</v>
       </c>
       <c r="B320" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57811</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -38149,34 +38114,38 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I320" t="inlineStr"/>
+      <c r="K320" t="inlineStr"/>
+      <c r="L320" t="inlineStr"/>
+      <c r="M320" t="inlineStr"/>
+      <c r="N320" t="inlineStr"/>
       <c r="P320" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>520757</v>
+        <v>520408</v>
       </c>
       <c r="R320" t="n">
-        <v>6934013</v>
+        <v>6934036</v>
       </c>
       <c r="S320" t="n">
         <v>25</v>
@@ -38235,15 +38204,10 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>125670901</v>
+        <v>125660766</v>
       </c>
       <c r="B321" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79585</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -38251,37 +38215,37 @@
         </is>
       </c>
       <c r="E321" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I321" t="inlineStr"/>
       <c r="P321" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>520257</v>
+        <v>520729</v>
       </c>
       <c r="R321" t="n">
-        <v>6933643</v>
+        <v>6933543</v>
       </c>
       <c r="S321" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T321" t="inlineStr">
         <is>
@@ -38337,53 +38301,52 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>125670920</v>
+        <v>125671307</v>
       </c>
       <c r="B322" t="n">
-        <v>105293</v>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I322" t="inlineStr"/>
+      <c r="J322" t="inlineStr"/>
+      <c r="K322" t="inlineStr"/>
+      <c r="L322" t="inlineStr"/>
+      <c r="N322" t="inlineStr"/>
       <c r="P322" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>520141</v>
+        <v>520477</v>
       </c>
       <c r="R322" t="n">
-        <v>6933910</v>
+        <v>6934031</v>
       </c>
       <c r="S322" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T322" t="inlineStr">
         <is>
@@ -38421,6 +38384,7 @@
       <c r="AE322" t="b">
         <v>0</v>
       </c>
+      <c r="AF322" t="inlineStr"/>
       <c r="AG322" t="b">
         <v>0</v>
       </c>
@@ -38439,15 +38403,10 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>125670906</v>
+        <v>125661236</v>
       </c>
       <c r="B323" t="n">
-        <v>79932</v>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43933</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -38455,37 +38414,37 @@
         </is>
       </c>
       <c r="E323" t="n">
-        <v>6456</v>
+        <v>101735</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I323" t="inlineStr"/>
       <c r="P323" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>521033</v>
+        <v>520684</v>
       </c>
       <c r="R323" t="n">
-        <v>6933394</v>
+        <v>6933537</v>
       </c>
       <c r="S323" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T323" t="inlineStr">
         <is>
@@ -38515,6 +38474,11 @@
       <c r="AA323" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC323" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD323" t="b">
@@ -38541,62 +38505,48 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>125663708</v>
+        <v>125661898</v>
       </c>
       <c r="B324" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I324" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L324" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr"/>
       <c r="P324" t="inlineStr">
         <is>
           <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>520185</v>
+        <v>520558</v>
       </c>
       <c r="R324" t="n">
-        <v>6933721</v>
+        <v>6933556</v>
       </c>
       <c r="S324" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T324" t="inlineStr">
         <is>
@@ -38652,37 +38602,32 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>125670921</v>
+        <v>125670919</v>
       </c>
       <c r="B325" t="n">
-        <v>92448</v>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E325" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I325" t="inlineStr"/>
@@ -38692,10 +38637,10 @@
         </is>
       </c>
       <c r="Q325" t="n">
-        <v>520731</v>
+        <v>520223</v>
       </c>
       <c r="R325" t="n">
-        <v>6934038</v>
+        <v>6933684</v>
       </c>
       <c r="S325" t="n">
         <v>25</v>
@@ -38754,56 +38699,48 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>125671098</v>
+        <v>125670924</v>
       </c>
       <c r="B326" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92502</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E326" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I326" t="inlineStr"/>
-      <c r="J326" t="inlineStr"/>
-      <c r="K326" t="inlineStr"/>
-      <c r="N326" t="inlineStr"/>
       <c r="P326" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q326" t="n">
-        <v>520578</v>
+        <v>520194</v>
       </c>
       <c r="R326" t="n">
-        <v>6934069</v>
+        <v>6933813</v>
       </c>
       <c r="S326" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T326" t="inlineStr">
         <is>
@@ -38841,7 +38778,6 @@
       <c r="AE326" t="b">
         <v>0</v>
       </c>
-      <c r="AF326" t="inlineStr"/>
       <c r="AG326" t="b">
         <v>0</v>
       </c>
@@ -38860,15 +38796,10 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>125670923</v>
+        <v>125670906</v>
       </c>
       <c r="B327" t="n">
-        <v>92448</v>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79974</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -38876,21 +38807,21 @@
         </is>
       </c>
       <c r="E327" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I327" t="inlineStr"/>
@@ -38900,10 +38831,10 @@
         </is>
       </c>
       <c r="Q327" t="n">
-        <v>520634</v>
+        <v>521033</v>
       </c>
       <c r="R327" t="n">
-        <v>6934079</v>
+        <v>6933394</v>
       </c>
       <c r="S327" t="n">
         <v>25</v>
@@ -38962,53 +38893,48 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>125670917</v>
+        <v>125663906</v>
       </c>
       <c r="B328" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I328" t="inlineStr"/>
       <c r="P328" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>520786</v>
+        <v>520184</v>
       </c>
       <c r="R328" t="n">
-        <v>6933914</v>
+        <v>6933765</v>
       </c>
       <c r="S328" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T328" t="inlineStr">
         <is>
@@ -39064,15 +38990,10 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>125659241</v>
+        <v>125670908</v>
       </c>
       <c r="B329" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -39080,37 +39001,37 @@
         </is>
       </c>
       <c r="E329" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I329" t="inlineStr"/>
       <c r="P329" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q329" t="n">
-        <v>520844</v>
+        <v>520754</v>
       </c>
       <c r="R329" t="n">
-        <v>6933514</v>
+        <v>6933960</v>
       </c>
       <c r="S329" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T329" t="inlineStr">
         <is>
@@ -39140,6 +39061,11 @@
       <c r="AA329" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC329" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD329" t="b">
@@ -39166,53 +39092,45 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>125671498</v>
+        <v>125670922</v>
       </c>
       <c r="B330" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92502</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I330" t="inlineStr"/>
-      <c r="J330" t="inlineStr"/>
-      <c r="K330" t="inlineStr"/>
-      <c r="N330" t="inlineStr"/>
       <c r="P330" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>520385</v>
+        <v>520637</v>
       </c>
       <c r="R330" t="n">
-        <v>6933569</v>
+        <v>6934037</v>
       </c>
       <c r="S330" t="n">
         <v>25</v>
@@ -39253,7 +39171,6 @@
       <c r="AE330" t="b">
         <v>0</v>
       </c>
-      <c r="AF330" t="inlineStr"/>
       <c r="AG330" t="b">
         <v>0</v>
       </c>
@@ -39272,37 +39189,32 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>125659251</v>
+        <v>125661738</v>
       </c>
       <c r="B331" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92502</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I331" t="inlineStr"/>
@@ -39312,10 +39224,10 @@
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>520823</v>
+        <v>520605</v>
       </c>
       <c r="R331" t="n">
-        <v>6933519</v>
+        <v>6933517</v>
       </c>
       <c r="S331" t="n">
         <v>20</v>
@@ -39374,15 +39286,10 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>125661442</v>
+        <v>125671054</v>
       </c>
       <c r="B332" t="n">
-        <v>78592</v>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -39390,37 +39297,40 @@
         </is>
       </c>
       <c r="E332" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I332" t="inlineStr"/>
+      <c r="J332" t="inlineStr"/>
+      <c r="K332" t="inlineStr"/>
+      <c r="N332" t="inlineStr"/>
       <c r="P332" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>520629</v>
+        <v>520612</v>
       </c>
       <c r="R332" t="n">
-        <v>6933514</v>
+        <v>6934046</v>
       </c>
       <c r="S332" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T332" t="inlineStr">
         <is>
@@ -39458,6 +39368,7 @@
       <c r="AE332" t="b">
         <v>0</v>
       </c>
+      <c r="AF332" t="inlineStr"/>
       <c r="AG332" t="b">
         <v>0</v>
       </c>
@@ -39476,15 +39387,10 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>125671278</v>
+        <v>125670914</v>
       </c>
       <c r="B333" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -39510,22 +39416,19 @@
         </is>
       </c>
       <c r="I333" t="inlineStr"/>
-      <c r="J333" t="inlineStr"/>
-      <c r="K333" t="inlineStr"/>
-      <c r="N333" t="inlineStr"/>
       <c r="P333" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>520511</v>
+        <v>520224</v>
       </c>
       <c r="R333" t="n">
-        <v>6934025</v>
+        <v>6933690</v>
       </c>
       <c r="S333" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T333" t="inlineStr">
         <is>
@@ -39563,7 +39466,6 @@
       <c r="AE333" t="b">
         <v>0</v>
       </c>
-      <c r="AF333" t="inlineStr"/>
       <c r="AG333" t="b">
         <v>0</v>
       </c>
@@ -39582,53 +39484,48 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>125659270</v>
+        <v>125670907</v>
       </c>
       <c r="B334" t="n">
-        <v>92448</v>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78726</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E334" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I334" t="inlineStr"/>
       <c r="P334" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q334" t="n">
-        <v>520846</v>
+        <v>520460</v>
       </c>
       <c r="R334" t="n">
-        <v>6933515</v>
+        <v>6933565</v>
       </c>
       <c r="S334" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T334" t="inlineStr">
         <is>
@@ -39684,37 +39581,32 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>125670910</v>
+        <v>125670921</v>
       </c>
       <c r="B335" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92502</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E335" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I335" t="inlineStr"/>
@@ -39724,10 +39616,10 @@
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>520830</v>
+        <v>520731</v>
       </c>
       <c r="R335" t="n">
-        <v>6933884</v>
+        <v>6934038</v>
       </c>
       <c r="S335" t="n">
         <v>25</v>
@@ -39786,56 +39678,48 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>125671054</v>
+        <v>125670903</v>
       </c>
       <c r="B336" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E336" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I336" t="inlineStr"/>
-      <c r="J336" t="inlineStr"/>
-      <c r="K336" t="inlineStr"/>
-      <c r="N336" t="inlineStr"/>
       <c r="P336" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>520612</v>
+        <v>520731</v>
       </c>
       <c r="R336" t="n">
-        <v>6934046</v>
+        <v>6934042</v>
       </c>
       <c r="S336" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T336" t="inlineStr">
         <is>
@@ -39867,13 +39751,17 @@
           <t>2025-06-03</t>
         </is>
       </c>
+      <c r="AC336" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD336" t="b">
         <v>0</v>
       </c>
       <c r="AE336" t="b">
         <v>0</v>
       </c>
-      <c r="AF336" t="inlineStr"/>
       <c r="AG336" t="b">
         <v>0</v>
       </c>
@@ -39892,15 +39780,10 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>125670908</v>
+        <v>125671021</v>
       </c>
       <c r="B337" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -39908,37 +39791,41 @@
         </is>
       </c>
       <c r="E337" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I337" t="inlineStr"/>
+      <c r="K337" t="inlineStr"/>
+      <c r="L337" t="inlineStr"/>
+      <c r="M337" t="inlineStr"/>
+      <c r="N337" t="inlineStr"/>
       <c r="P337" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>520754</v>
+        <v>520607</v>
       </c>
       <c r="R337" t="n">
-        <v>6933960</v>
+        <v>6934048</v>
       </c>
       <c r="S337" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T337" t="inlineStr">
         <is>
@@ -39972,7 +39859,7 @@
       </c>
       <c r="AC337" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD337" t="b">
@@ -39999,15 +39886,10 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>125670907</v>
+        <v>125670916</v>
       </c>
       <c r="B338" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -40015,21 +39897,21 @@
         </is>
       </c>
       <c r="E338" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I338" t="inlineStr"/>
@@ -40039,10 +39921,10 @@
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>520460</v>
+        <v>520803</v>
       </c>
       <c r="R338" t="n">
-        <v>6933565</v>
+        <v>6933448</v>
       </c>
       <c r="S338" t="n">
         <v>25</v>
@@ -40101,15 +39983,10 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>125671391</v>
+        <v>125670909</v>
       </c>
       <c r="B339" t="n">
-        <v>57793</v>
-      </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -40117,38 +39994,34 @@
         </is>
       </c>
       <c r="E339" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I339" t="inlineStr"/>
-      <c r="K339" t="inlineStr"/>
-      <c r="L339" t="inlineStr"/>
-      <c r="M339" t="inlineStr"/>
-      <c r="N339" t="inlineStr"/>
       <c r="P339" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>520408</v>
+        <v>520754</v>
       </c>
       <c r="R339" t="n">
-        <v>6934036</v>
+        <v>6934006</v>
       </c>
       <c r="S339" t="n">
         <v>25</v>
@@ -40181,6 +40054,11 @@
       <c r="AA339" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC339" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD339" t="b">
@@ -40207,15 +40085,10 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>125660155</v>
+        <v>125661442</v>
       </c>
       <c r="B340" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78634</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -40223,21 +40096,21 @@
         </is>
       </c>
       <c r="E340" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I340" t="inlineStr"/>
@@ -40247,10 +40120,10 @@
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>520786</v>
+        <v>520629</v>
       </c>
       <c r="R340" t="n">
-        <v>6933540</v>
+        <v>6933514</v>
       </c>
       <c r="S340" t="n">
         <v>20</v>
@@ -40309,15 +40182,10 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>125661738</v>
+        <v>125659270</v>
       </c>
       <c r="B341" t="n">
-        <v>92448</v>
-      </c>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92502</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -40349,10 +40217,10 @@
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>520605</v>
+        <v>520846</v>
       </c>
       <c r="R341" t="n">
-        <v>6933517</v>
+        <v>6933515</v>
       </c>
       <c r="S341" t="n">
         <v>20</v>
@@ -40411,50 +40279,48 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>125670904</v>
+        <v>125671469</v>
       </c>
       <c r="B342" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C342" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E342" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I342" t="inlineStr"/>
+      <c r="J342" t="inlineStr"/>
+      <c r="K342" t="inlineStr"/>
+      <c r="N342" t="inlineStr"/>
       <c r="P342" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>520208</v>
+        <v>520296</v>
       </c>
       <c r="R342" t="n">
-        <v>6933929</v>
+        <v>6933639</v>
       </c>
       <c r="S342" t="n">
         <v>25</v>
@@ -40495,6 +40361,7 @@
       <c r="AE342" t="b">
         <v>0</v>
       </c>
+      <c r="AF342" t="inlineStr"/>
       <c r="AG342" t="b">
         <v>0</v>
       </c>
@@ -40513,53 +40380,48 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>125670903</v>
+        <v>125660155</v>
       </c>
       <c r="B343" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C343" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78726</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E343" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I343" t="inlineStr"/>
       <c r="P343" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>520731</v>
+        <v>520786</v>
       </c>
       <c r="R343" t="n">
-        <v>6934042</v>
+        <v>6933540</v>
       </c>
       <c r="S343" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T343" t="inlineStr">
         <is>
@@ -40589,11 +40451,6 @@
       <c r="AA343" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC343" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD343" t="b">
@@ -40620,57 +40477,48 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>125671342</v>
+        <v>125670923</v>
       </c>
       <c r="B344" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92502</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E344" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I344" t="inlineStr"/>
-      <c r="J344" t="inlineStr"/>
-      <c r="K344" t="inlineStr"/>
-      <c r="L344" t="inlineStr"/>
-      <c r="N344" t="inlineStr"/>
       <c r="P344" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q344" t="n">
-        <v>520463</v>
+        <v>520634</v>
       </c>
       <c r="R344" t="n">
-        <v>6934009</v>
+        <v>6934079</v>
       </c>
       <c r="S344" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T344" t="inlineStr">
         <is>
@@ -40708,7 +40556,6 @@
       <c r="AE344" t="b">
         <v>0</v>
       </c>
-      <c r="AF344" t="inlineStr"/>
       <c r="AG344" t="b">
         <v>0</v>
       </c>
@@ -40727,15 +40574,10 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>125671021</v>
+        <v>125670905</v>
       </c>
       <c r="B345" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C345" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80071</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -40743,41 +40585,37 @@
         </is>
       </c>
       <c r="E345" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I345" t="inlineStr"/>
-      <c r="K345" t="inlineStr"/>
-      <c r="L345" t="inlineStr"/>
-      <c r="M345" t="inlineStr"/>
-      <c r="N345" t="inlineStr"/>
       <c r="P345" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q345" t="n">
-        <v>520607</v>
+        <v>520801</v>
       </c>
       <c r="R345" t="n">
-        <v>6934048</v>
+        <v>6933448</v>
       </c>
       <c r="S345" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T345" t="inlineStr">
         <is>
@@ -40807,11 +40645,6 @@
       <c r="AA345" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC345" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD345" t="b">
@@ -40838,53 +40671,48 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>125670905</v>
+        <v>125662204</v>
       </c>
       <c r="B346" t="n">
-        <v>80029</v>
-      </c>
-      <c r="C346" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91380</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E346" t="n">
-        <v>2081</v>
+        <v>1503</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I346" t="inlineStr"/>
       <c r="P346" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q346" t="n">
-        <v>520801</v>
+        <v>520425</v>
       </c>
       <c r="R346" t="n">
-        <v>6933448</v>
+        <v>6933544</v>
       </c>
       <c r="S346" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T346" t="inlineStr">
         <is>
@@ -40940,57 +40768,48 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>125671230</v>
+        <v>125659251</v>
       </c>
       <c r="B347" t="n">
-        <v>98290</v>
-      </c>
-      <c r="C347" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78725</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E347" t="n">
-        <v>221952</v>
+        <v>6446</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I347" t="inlineStr"/>
-      <c r="J347" t="inlineStr"/>
-      <c r="K347" t="inlineStr"/>
-      <c r="L347" t="inlineStr"/>
-      <c r="N347" t="inlineStr"/>
       <c r="P347" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q347" t="n">
-        <v>520549</v>
+        <v>520823</v>
       </c>
       <c r="R347" t="n">
-        <v>6934058</v>
+        <v>6933519</v>
       </c>
       <c r="S347" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T347" t="inlineStr">
         <is>
@@ -41028,7 +40847,6 @@
       <c r="AE347" t="b">
         <v>0</v>
       </c>
-      <c r="AF347" t="inlineStr"/>
       <c r="AG347" t="b">
         <v>0</v>
       </c>
@@ -41047,53 +40865,48 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>125661898</v>
+        <v>125670910</v>
       </c>
       <c r="B348" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C348" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E348" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I348" t="inlineStr"/>
       <c r="P348" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q348" t="n">
-        <v>520558</v>
+        <v>520830</v>
       </c>
       <c r="R348" t="n">
-        <v>6933556</v>
+        <v>6933884</v>
       </c>
       <c r="S348" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T348" t="inlineStr">
         <is>
@@ -41149,15 +40962,10 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>125662204</v>
+        <v>125671342</v>
       </c>
       <c r="B349" t="n">
-        <v>91326</v>
-      </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -41165,37 +40973,41 @@
         </is>
       </c>
       <c r="E349" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I349" t="inlineStr"/>
+      <c r="J349" t="inlineStr"/>
+      <c r="K349" t="inlineStr"/>
+      <c r="L349" t="inlineStr"/>
+      <c r="N349" t="inlineStr"/>
       <c r="P349" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q349" t="n">
-        <v>520425</v>
+        <v>520463</v>
       </c>
       <c r="R349" t="n">
-        <v>6933544</v>
+        <v>6934009</v>
       </c>
       <c r="S349" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T349" t="inlineStr">
         <is>
@@ -41233,6 +41045,7 @@
       <c r="AE349" t="b">
         <v>0</v>
       </c>
+      <c r="AF349" t="inlineStr"/>
       <c r="AG349" t="b">
         <v>0</v>
       </c>
@@ -41251,15 +41064,10 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>125671307</v>
+        <v>125670917</v>
       </c>
       <c r="B350" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C350" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -41285,23 +41093,19 @@
         </is>
       </c>
       <c r="I350" t="inlineStr"/>
-      <c r="J350" t="inlineStr"/>
-      <c r="K350" t="inlineStr"/>
-      <c r="L350" t="inlineStr"/>
-      <c r="N350" t="inlineStr"/>
       <c r="P350" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q350" t="n">
-        <v>520477</v>
+        <v>520786</v>
       </c>
       <c r="R350" t="n">
-        <v>6934031</v>
+        <v>6933914</v>
       </c>
       <c r="S350" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T350" t="inlineStr">
         <is>
@@ -41339,7 +41143,6 @@
       <c r="AE350" t="b">
         <v>0</v>
       </c>
-      <c r="AF350" t="inlineStr"/>
       <c r="AG350" t="b">
         <v>0</v>
       </c>
@@ -41358,50 +41161,54 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>125670909</v>
+        <v>125663708</v>
       </c>
       <c r="B351" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C351" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E351" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I351" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P351" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q351" t="n">
-        <v>520754</v>
+        <v>520185</v>
       </c>
       <c r="R351" t="n">
-        <v>6934006</v>
+        <v>6933721</v>
       </c>
       <c r="S351" t="n">
         <v>25</v>
@@ -41434,11 +41241,6 @@
       <c r="AA351" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC351" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD351" t="b">
@@ -41465,37 +41267,32 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>125670922</v>
+        <v>125670901</v>
       </c>
       <c r="B352" t="n">
-        <v>92448</v>
-      </c>
-      <c r="C352" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E352" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I352" t="inlineStr"/>
@@ -41505,10 +41302,10 @@
         </is>
       </c>
       <c r="Q352" t="n">
-        <v>520637</v>
+        <v>520257</v>
       </c>
       <c r="R352" t="n">
-        <v>6934037</v>
+        <v>6933643</v>
       </c>
       <c r="S352" t="n">
         <v>25</v>
@@ -41567,15 +41364,10 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>125670913</v>
+        <v>125671498</v>
       </c>
       <c r="B353" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C353" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -41601,16 +41393,19 @@
         </is>
       </c>
       <c r="I353" t="inlineStr"/>
+      <c r="J353" t="inlineStr"/>
+      <c r="K353" t="inlineStr"/>
+      <c r="N353" t="inlineStr"/>
       <c r="P353" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q353" t="n">
-        <v>520620</v>
+        <v>520385</v>
       </c>
       <c r="R353" t="n">
-        <v>6934070</v>
+        <v>6933569</v>
       </c>
       <c r="S353" t="n">
         <v>25</v>
@@ -41651,6 +41446,7 @@
       <c r="AE353" t="b">
         <v>0</v>
       </c>
+      <c r="AF353" t="inlineStr"/>
       <c r="AG353" t="b">
         <v>0</v>
       </c>
@@ -41669,15 +41465,10 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>125670916</v>
+        <v>125671434</v>
       </c>
       <c r="B354" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C354" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -41703,19 +41494,22 @@
         </is>
       </c>
       <c r="I354" t="inlineStr"/>
+      <c r="J354" t="inlineStr"/>
+      <c r="K354" t="inlineStr"/>
+      <c r="N354" t="inlineStr"/>
       <c r="P354" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q354" t="n">
-        <v>520803</v>
+        <v>520364</v>
       </c>
       <c r="R354" t="n">
-        <v>6933448</v>
+        <v>6934008</v>
       </c>
       <c r="S354" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T354" t="inlineStr">
         <is>
@@ -41753,6 +41547,7 @@
       <c r="AE354" t="b">
         <v>0</v>
       </c>
+      <c r="AF354" t="inlineStr"/>
       <c r="AG354" t="b">
         <v>0</v>
       </c>
@@ -41774,12 +41569,7 @@
         <v>125661680</v>
       </c>
       <c r="B355" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C355" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79585</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -41873,42 +41663,38 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>125671469</v>
+        <v>125671230</v>
       </c>
       <c r="B356" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C356" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98345</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E356" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I356" t="inlineStr"/>
       <c r="J356" t="inlineStr"/>
       <c r="K356" t="inlineStr"/>
+      <c r="L356" t="inlineStr"/>
       <c r="N356" t="inlineStr"/>
       <c r="P356" t="inlineStr">
         <is>
@@ -41916,13 +41702,13 @@
         </is>
       </c>
       <c r="Q356" t="n">
-        <v>520296</v>
+        <v>520549</v>
       </c>
       <c r="R356" t="n">
-        <v>6933639</v>
+        <v>6934058</v>
       </c>
       <c r="S356" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T356" t="inlineStr">
         <is>
@@ -41979,53 +41765,48 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>125670919</v>
+        <v>125659241</v>
       </c>
       <c r="B357" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C357" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79585</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E357" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I357" t="inlineStr"/>
       <c r="P357" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q357" t="n">
-        <v>520223</v>
+        <v>520844</v>
       </c>
       <c r="R357" t="n">
-        <v>6933684</v>
+        <v>6933514</v>
       </c>
       <c r="S357" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T357" t="inlineStr">
         <is>
@@ -42081,37 +41862,32 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>125670918</v>
+        <v>125670913</v>
       </c>
       <c r="B358" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C358" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E358" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I358" t="inlineStr"/>
@@ -42121,10 +41897,10 @@
         </is>
       </c>
       <c r="Q358" t="n">
-        <v>520172</v>
+        <v>520620</v>
       </c>
       <c r="R358" t="n">
-        <v>6933875</v>
+        <v>6934070</v>
       </c>
       <c r="S358" t="n">
         <v>25</v>
@@ -42183,15 +41959,10 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>125663906</v>
+        <v>125671278</v>
       </c>
       <c r="B359" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C359" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -42217,19 +41988,22 @@
         </is>
       </c>
       <c r="I359" t="inlineStr"/>
+      <c r="J359" t="inlineStr"/>
+      <c r="K359" t="inlineStr"/>
+      <c r="N359" t="inlineStr"/>
       <c r="P359" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q359" t="n">
-        <v>520184</v>
+        <v>520511</v>
       </c>
       <c r="R359" t="n">
-        <v>6933765</v>
+        <v>6934025</v>
       </c>
       <c r="S359" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T359" t="inlineStr">
         <is>
@@ -42267,6 +42041,7 @@
       <c r="AE359" t="b">
         <v>0</v>
       </c>
+      <c r="AF359" t="inlineStr"/>
       <c r="AG359" t="b">
         <v>0</v>
       </c>
@@ -42285,53 +42060,51 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>125670924</v>
+        <v>125671098</v>
       </c>
       <c r="B360" t="n">
-        <v>92448</v>
-      </c>
-      <c r="C360" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E360" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I360" t="inlineStr"/>
+      <c r="J360" t="inlineStr"/>
+      <c r="K360" t="inlineStr"/>
+      <c r="N360" t="inlineStr"/>
       <c r="P360" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q360" t="n">
-        <v>520194</v>
+        <v>520578</v>
       </c>
       <c r="R360" t="n">
-        <v>6933813</v>
+        <v>6934069</v>
       </c>
       <c r="S360" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T360" t="inlineStr">
         <is>
@@ -42369,6 +42142,7 @@
       <c r="AE360" t="b">
         <v>0</v>
       </c>
+      <c r="AF360" t="inlineStr"/>
       <c r="AG360" t="b">
         <v>0</v>
       </c>
@@ -42387,15 +42161,10 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>125670914</v>
+        <v>125660786</v>
       </c>
       <c r="B361" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C361" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78725</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -42403,37 +42172,37 @@
         </is>
       </c>
       <c r="E361" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I361" t="inlineStr"/>
       <c r="P361" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q361" t="n">
-        <v>520224</v>
+        <v>520731</v>
       </c>
       <c r="R361" t="n">
-        <v>6933690</v>
+        <v>6933528</v>
       </c>
       <c r="S361" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T361" t="inlineStr">
         <is>
@@ -42489,42 +42258,38 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>125671434</v>
+        <v>125671157</v>
       </c>
       <c r="B362" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C362" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E362" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I362" t="inlineStr"/>
       <c r="J362" t="inlineStr"/>
       <c r="K362" t="inlineStr"/>
+      <c r="L362" t="inlineStr"/>
       <c r="N362" t="inlineStr"/>
       <c r="P362" t="inlineStr">
         <is>
@@ -42532,10 +42297,10 @@
         </is>
       </c>
       <c r="Q362" t="n">
-        <v>520364</v>
+        <v>520540</v>
       </c>
       <c r="R362" t="n">
-        <v>6934008</v>
+        <v>6934055</v>
       </c>
       <c r="S362" t="n">
         <v>10</v>
@@ -42595,53 +42360,48 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>125660786</v>
+        <v>125670920</v>
       </c>
       <c r="B363" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C363" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105348</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E363" t="n">
-        <v>6446</v>
+        <v>221144</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I363" t="inlineStr"/>
       <c r="P363" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q363" t="n">
-        <v>520731</v>
+        <v>520141</v>
       </c>
       <c r="R363" t="n">
-        <v>6933528</v>
+        <v>6933910</v>
       </c>
       <c r="S363" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T363" t="inlineStr">
         <is>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -39581,32 +39581,32 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>125670921</v>
+        <v>125670916</v>
       </c>
       <c r="B335" t="n">
-        <v>92502</v>
+        <v>80070</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E335" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I335" t="inlineStr"/>
@@ -39616,10 +39616,10 @@
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>520731</v>
+        <v>520803</v>
       </c>
       <c r="R335" t="n">
-        <v>6934038</v>
+        <v>6933448</v>
       </c>
       <c r="S335" t="n">
         <v>25</v>
@@ -39678,32 +39678,32 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>125670903</v>
+        <v>125670909</v>
       </c>
       <c r="B336" t="n">
-        <v>56843</v>
+        <v>80070</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E336" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I336" t="inlineStr"/>
@@ -39713,10 +39713,10 @@
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>520731</v>
+        <v>520754</v>
       </c>
       <c r="R336" t="n">
-        <v>6934042</v>
+        <v>6934006</v>
       </c>
       <c r="S336" t="n">
         <v>25</v>
@@ -39753,7 +39753,7 @@
       </c>
       <c r="AC336" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD336" t="b">
@@ -39780,52 +39780,48 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>125671021</v>
+        <v>125670921</v>
       </c>
       <c r="B337" t="n">
-        <v>57648</v>
+        <v>92502</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E337" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I337" t="inlineStr"/>
-      <c r="K337" t="inlineStr"/>
-      <c r="L337" t="inlineStr"/>
-      <c r="M337" t="inlineStr"/>
-      <c r="N337" t="inlineStr"/>
       <c r="P337" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>520607</v>
+        <v>520731</v>
       </c>
       <c r="R337" t="n">
-        <v>6934048</v>
+        <v>6934038</v>
       </c>
       <c r="S337" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T337" t="inlineStr">
         <is>
@@ -39855,11 +39851,6 @@
       <c r="AA337" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC337" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD337" t="b">
@@ -39886,32 +39877,32 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>125670916</v>
+        <v>125670903</v>
       </c>
       <c r="B338" t="n">
-        <v>80070</v>
+        <v>56843</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E338" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I338" t="inlineStr"/>
@@ -39921,10 +39912,10 @@
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>520803</v>
+        <v>520731</v>
       </c>
       <c r="R338" t="n">
-        <v>6933448</v>
+        <v>6934042</v>
       </c>
       <c r="S338" t="n">
         <v>25</v>
@@ -39957,6 +39948,11 @@
       <c r="AA338" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC338" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD338" t="b">
@@ -39983,10 +39979,10 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>125670909</v>
+        <v>125671021</v>
       </c>
       <c r="B339" t="n">
-        <v>80070</v>
+        <v>57648</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -39994,37 +39990,41 @@
         </is>
       </c>
       <c r="E339" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I339" t="inlineStr"/>
+      <c r="K339" t="inlineStr"/>
+      <c r="L339" t="inlineStr"/>
+      <c r="M339" t="inlineStr"/>
+      <c r="N339" t="inlineStr"/>
       <c r="P339" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>520754</v>
+        <v>520607</v>
       </c>
       <c r="R339" t="n">
-        <v>6934006</v>
+        <v>6934048</v>
       </c>
       <c r="S339" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T339" t="inlineStr">
         <is>
@@ -40058,7 +40058,7 @@
       </c>
       <c r="AC339" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD339" t="b">

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -37713,7 +37713,7 @@
         <v>125670918</v>
       </c>
       <c r="B316" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -38006,10 +38006,10 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>125670912</v>
+        <v>125671391</v>
       </c>
       <c r="B319" t="n">
-        <v>80070</v>
+        <v>57811</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -38017,34 +38017,38 @@
         </is>
       </c>
       <c r="E319" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I319" t="inlineStr"/>
+      <c r="K319" t="inlineStr"/>
+      <c r="L319" t="inlineStr"/>
+      <c r="M319" t="inlineStr"/>
+      <c r="N319" t="inlineStr"/>
       <c r="P319" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>520757</v>
+        <v>520408</v>
       </c>
       <c r="R319" t="n">
-        <v>6934013</v>
+        <v>6934036</v>
       </c>
       <c r="S319" t="n">
         <v>25</v>
@@ -38103,10 +38107,10 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>125671391</v>
+        <v>125670912</v>
       </c>
       <c r="B320" t="n">
-        <v>57811</v>
+        <v>80070</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -38114,38 +38118,34 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I320" t="inlineStr"/>
-      <c r="K320" t="inlineStr"/>
-      <c r="L320" t="inlineStr"/>
-      <c r="M320" t="inlineStr"/>
-      <c r="N320" t="inlineStr"/>
       <c r="P320" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>520408</v>
+        <v>520757</v>
       </c>
       <c r="R320" t="n">
-        <v>6934036</v>
+        <v>6934013</v>
       </c>
       <c r="S320" t="n">
         <v>25</v>
@@ -38204,32 +38204,32 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>125660766</v>
+        <v>125661236</v>
       </c>
       <c r="B321" t="n">
-        <v>79585</v>
+        <v>43933</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>6453</v>
+        <v>101735</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I321" t="inlineStr"/>
@@ -38239,10 +38239,10 @@
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>520729</v>
+        <v>520684</v>
       </c>
       <c r="R321" t="n">
-        <v>6933543</v>
+        <v>6933537</v>
       </c>
       <c r="S321" t="n">
         <v>20</v>
@@ -38275,6 +38275,11 @@
       <c r="AA321" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC321" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD321" t="b">
@@ -38304,7 +38309,7 @@
         <v>125671307</v>
       </c>
       <c r="B322" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -38403,32 +38408,32 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>125661236</v>
+        <v>125660766</v>
       </c>
       <c r="B323" t="n">
-        <v>43933</v>
+        <v>79585</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>101735</v>
+        <v>6453</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I323" t="inlineStr"/>
@@ -38438,10 +38443,10 @@
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>520684</v>
+        <v>520729</v>
       </c>
       <c r="R323" t="n">
-        <v>6933537</v>
+        <v>6933543</v>
       </c>
       <c r="S323" t="n">
         <v>20</v>
@@ -38474,11 +38479,6 @@
       <c r="AA323" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC323" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD323" t="b">
@@ -38508,7 +38508,7 @@
         <v>125661898</v>
       </c>
       <c r="B324" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -38605,7 +38605,7 @@
         <v>125670919</v>
       </c>
       <c r="B325" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -38699,10 +38699,10 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>125670924</v>
+        <v>125670906</v>
       </c>
       <c r="B326" t="n">
-        <v>92502</v>
+        <v>79974</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -38710,21 +38710,21 @@
         </is>
       </c>
       <c r="E326" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I326" t="inlineStr"/>
@@ -38734,10 +38734,10 @@
         </is>
       </c>
       <c r="Q326" t="n">
-        <v>520194</v>
+        <v>521033</v>
       </c>
       <c r="R326" t="n">
-        <v>6933813</v>
+        <v>6933394</v>
       </c>
       <c r="S326" t="n">
         <v>25</v>
@@ -38796,48 +38796,48 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>125670906</v>
+        <v>125663906</v>
       </c>
       <c r="B327" t="n">
-        <v>79974</v>
+        <v>80070</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I327" t="inlineStr"/>
       <c r="P327" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q327" t="n">
-        <v>521033</v>
+        <v>520184</v>
       </c>
       <c r="R327" t="n">
-        <v>6933394</v>
+        <v>6933765</v>
       </c>
       <c r="S327" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T327" t="inlineStr">
         <is>
@@ -38893,48 +38893,48 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>125663906</v>
+        <v>125670924</v>
       </c>
       <c r="B328" t="n">
-        <v>80070</v>
+        <v>92509</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I328" t="inlineStr"/>
       <c r="P328" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>520184</v>
+        <v>520194</v>
       </c>
       <c r="R328" t="n">
-        <v>6933765</v>
+        <v>6933813</v>
       </c>
       <c r="S328" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T328" t="inlineStr">
         <is>
@@ -39092,32 +39092,32 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>125670922</v>
+        <v>125670914</v>
       </c>
       <c r="B330" t="n">
-        <v>92502</v>
+        <v>80070</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I330" t="inlineStr"/>
@@ -39127,10 +39127,10 @@
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>520637</v>
+        <v>520224</v>
       </c>
       <c r="R330" t="n">
-        <v>6934037</v>
+        <v>6933690</v>
       </c>
       <c r="S330" t="n">
         <v>25</v>
@@ -39189,10 +39189,10 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>125661738</v>
+        <v>125670922</v>
       </c>
       <c r="B331" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -39220,17 +39220,17 @@
       <c r="I331" t="inlineStr"/>
       <c r="P331" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>520605</v>
+        <v>520637</v>
       </c>
       <c r="R331" t="n">
-        <v>6933517</v>
+        <v>6934037</v>
       </c>
       <c r="S331" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T331" t="inlineStr">
         <is>
@@ -39387,48 +39387,48 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>125670914</v>
+        <v>125661738</v>
       </c>
       <c r="B333" t="n">
-        <v>80070</v>
+        <v>92509</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E333" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I333" t="inlineStr"/>
       <c r="P333" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>520224</v>
+        <v>520605</v>
       </c>
       <c r="R333" t="n">
-        <v>6933690</v>
+        <v>6933517</v>
       </c>
       <c r="S333" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T333" t="inlineStr">
         <is>
@@ -39581,7 +39581,7 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>125670916</v>
+        <v>125670909</v>
       </c>
       <c r="B335" t="n">
         <v>80070</v>
@@ -39616,10 +39616,10 @@
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>520803</v>
+        <v>520754</v>
       </c>
       <c r="R335" t="n">
-        <v>6933448</v>
+        <v>6934006</v>
       </c>
       <c r="S335" t="n">
         <v>25</v>
@@ -39652,6 +39652,11 @@
       <c r="AA335" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC335" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD335" t="b">
@@ -39678,7 +39683,7 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>125670909</v>
+        <v>125670916</v>
       </c>
       <c r="B336" t="n">
         <v>80070</v>
@@ -39713,10 +39718,10 @@
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>520754</v>
+        <v>520803</v>
       </c>
       <c r="R336" t="n">
-        <v>6934006</v>
+        <v>6933448</v>
       </c>
       <c r="S336" t="n">
         <v>25</v>
@@ -39749,11 +39754,6 @@
       <c r="AA336" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC336" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD336" t="b">
@@ -39783,7 +39783,7 @@
         <v>125670921</v>
       </c>
       <c r="B337" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -39877,48 +39877,52 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>125670903</v>
+        <v>125671021</v>
       </c>
       <c r="B338" t="n">
-        <v>56843</v>
+        <v>57648</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E338" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I338" t="inlineStr"/>
+      <c r="K338" t="inlineStr"/>
+      <c r="L338" t="inlineStr"/>
+      <c r="M338" t="inlineStr"/>
+      <c r="N338" t="inlineStr"/>
       <c r="P338" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>520731</v>
+        <v>520607</v>
       </c>
       <c r="R338" t="n">
-        <v>6934042</v>
+        <v>6934048</v>
       </c>
       <c r="S338" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T338" t="inlineStr">
         <is>
@@ -39952,7 +39956,7 @@
       </c>
       <c r="AC338" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD338" t="b">
@@ -39979,52 +39983,48 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>125671021</v>
+        <v>125670903</v>
       </c>
       <c r="B339" t="n">
-        <v>57648</v>
+        <v>56843</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E339" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I339" t="inlineStr"/>
-      <c r="K339" t="inlineStr"/>
-      <c r="L339" t="inlineStr"/>
-      <c r="M339" t="inlineStr"/>
-      <c r="N339" t="inlineStr"/>
       <c r="P339" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>520607</v>
+        <v>520731</v>
       </c>
       <c r="R339" t="n">
-        <v>6934048</v>
+        <v>6934042</v>
       </c>
       <c r="S339" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T339" t="inlineStr">
         <is>
@@ -40058,7 +40058,7 @@
       </c>
       <c r="AC339" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD339" t="b">
@@ -40085,10 +40085,10 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>125661442</v>
+        <v>125660155</v>
       </c>
       <c r="B340" t="n">
-        <v>78634</v>
+        <v>78726</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -40096,21 +40096,21 @@
         </is>
       </c>
       <c r="E340" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I340" t="inlineStr"/>
@@ -40120,10 +40120,10 @@
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>520629</v>
+        <v>520786</v>
       </c>
       <c r="R340" t="n">
-        <v>6933514</v>
+        <v>6933540</v>
       </c>
       <c r="S340" t="n">
         <v>20</v>
@@ -40182,32 +40182,32 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>125659270</v>
+        <v>125661442</v>
       </c>
       <c r="B341" t="n">
-        <v>92502</v>
+        <v>78634</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E341" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I341" t="inlineStr"/>
@@ -40217,10 +40217,10 @@
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>520846</v>
+        <v>520629</v>
       </c>
       <c r="R341" t="n">
-        <v>6933515</v>
+        <v>6933514</v>
       </c>
       <c r="S341" t="n">
         <v>20</v>
@@ -40380,32 +40380,32 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>125660155</v>
+        <v>125659270</v>
       </c>
       <c r="B343" t="n">
-        <v>78726</v>
+        <v>92509</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E343" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I343" t="inlineStr"/>
@@ -40415,10 +40415,10 @@
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>520786</v>
+        <v>520846</v>
       </c>
       <c r="R343" t="n">
-        <v>6933540</v>
+        <v>6933515</v>
       </c>
       <c r="S343" t="n">
         <v>20</v>
@@ -40480,7 +40480,7 @@
         <v>125670923</v>
       </c>
       <c r="B344" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -40574,10 +40574,10 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>125670905</v>
+        <v>125659251</v>
       </c>
       <c r="B345" t="n">
-        <v>80071</v>
+        <v>78725</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -40585,37 +40585,37 @@
         </is>
       </c>
       <c r="E345" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I345" t="inlineStr"/>
       <c r="P345" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q345" t="n">
-        <v>520801</v>
+        <v>520823</v>
       </c>
       <c r="R345" t="n">
-        <v>6933448</v>
+        <v>6933519</v>
       </c>
       <c r="S345" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T345" t="inlineStr">
         <is>
@@ -40671,48 +40671,48 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>125662204</v>
+        <v>125670910</v>
       </c>
       <c r="B346" t="n">
-        <v>91380</v>
+        <v>80070</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E346" t="n">
-        <v>1503</v>
+        <v>6458</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I346" t="inlineStr"/>
       <c r="P346" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q346" t="n">
-        <v>520425</v>
+        <v>520830</v>
       </c>
       <c r="R346" t="n">
-        <v>6933544</v>
+        <v>6933884</v>
       </c>
       <c r="S346" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T346" t="inlineStr">
         <is>
@@ -40768,10 +40768,10 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>125659251</v>
+        <v>125670905</v>
       </c>
       <c r="B347" t="n">
-        <v>78725</v>
+        <v>80071</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -40779,37 +40779,37 @@
         </is>
       </c>
       <c r="E347" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I347" t="inlineStr"/>
       <c r="P347" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q347" t="n">
-        <v>520823</v>
+        <v>520801</v>
       </c>
       <c r="R347" t="n">
-        <v>6933519</v>
+        <v>6933448</v>
       </c>
       <c r="S347" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T347" t="inlineStr">
         <is>
@@ -40865,48 +40865,48 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>125670910</v>
+        <v>125662204</v>
       </c>
       <c r="B348" t="n">
-        <v>80070</v>
+        <v>91387</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E348" t="n">
-        <v>6458</v>
+        <v>1503</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I348" t="inlineStr"/>
       <c r="P348" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q348" t="n">
-        <v>520830</v>
+        <v>520425</v>
       </c>
       <c r="R348" t="n">
-        <v>6933884</v>
+        <v>6933544</v>
       </c>
       <c r="S348" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T348" t="inlineStr">
         <is>
@@ -40965,7 +40965,7 @@
         <v>125671342</v>
       </c>
       <c r="B349" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -41067,7 +41067,7 @@
         <v>125670917</v>
       </c>
       <c r="B350" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -41267,48 +41267,52 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>125670901</v>
+        <v>125671230</v>
       </c>
       <c r="B352" t="n">
-        <v>91220</v>
+        <v>98352</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E352" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I352" t="inlineStr"/>
+      <c r="J352" t="inlineStr"/>
+      <c r="K352" t="inlineStr"/>
+      <c r="L352" t="inlineStr"/>
+      <c r="N352" t="inlineStr"/>
       <c r="P352" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q352" t="n">
-        <v>520257</v>
+        <v>520549</v>
       </c>
       <c r="R352" t="n">
-        <v>6933643</v>
+        <v>6934058</v>
       </c>
       <c r="S352" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T352" t="inlineStr">
         <is>
@@ -41346,6 +41350,7 @@
       <c r="AE352" t="b">
         <v>0</v>
       </c>
+      <c r="AF352" t="inlineStr"/>
       <c r="AG352" t="b">
         <v>0</v>
       </c>
@@ -41364,10 +41369,10 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>125671498</v>
+        <v>125670901</v>
       </c>
       <c r="B353" t="n">
-        <v>80070</v>
+        <v>91227</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -41375,37 +41380,34 @@
         </is>
       </c>
       <c r="E353" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I353" t="inlineStr"/>
-      <c r="J353" t="inlineStr"/>
-      <c r="K353" t="inlineStr"/>
-      <c r="N353" t="inlineStr"/>
       <c r="P353" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q353" t="n">
-        <v>520385</v>
+        <v>520257</v>
       </c>
       <c r="R353" t="n">
-        <v>6933569</v>
+        <v>6933643</v>
       </c>
       <c r="S353" t="n">
         <v>25</v>
@@ -41446,7 +41448,6 @@
       <c r="AE353" t="b">
         <v>0</v>
       </c>
-      <c r="AF353" t="inlineStr"/>
       <c r="AG353" t="b">
         <v>0</v>
       </c>
@@ -41465,7 +41466,7 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>125671434</v>
+        <v>125671498</v>
       </c>
       <c r="B354" t="n">
         <v>80070</v>
@@ -41503,13 +41504,13 @@
         </is>
       </c>
       <c r="Q354" t="n">
-        <v>520364</v>
+        <v>520385</v>
       </c>
       <c r="R354" t="n">
-        <v>6934008</v>
+        <v>6933569</v>
       </c>
       <c r="S354" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T354" t="inlineStr">
         <is>
@@ -41566,10 +41567,10 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>125661680</v>
+        <v>125671434</v>
       </c>
       <c r="B355" t="n">
-        <v>79585</v>
+        <v>80070</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -41577,37 +41578,40 @@
         </is>
       </c>
       <c r="E355" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I355" t="inlineStr"/>
+      <c r="J355" t="inlineStr"/>
+      <c r="K355" t="inlineStr"/>
+      <c r="N355" t="inlineStr"/>
       <c r="P355" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q355" t="n">
-        <v>520639</v>
+        <v>520364</v>
       </c>
       <c r="R355" t="n">
-        <v>6933509</v>
+        <v>6934008</v>
       </c>
       <c r="S355" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T355" t="inlineStr">
         <is>
@@ -41645,6 +41649,7 @@
       <c r="AE355" t="b">
         <v>0</v>
       </c>
+      <c r="AF355" t="inlineStr"/>
       <c r="AG355" t="b">
         <v>0</v>
       </c>
@@ -41663,52 +41668,48 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>125671230</v>
+        <v>125661680</v>
       </c>
       <c r="B356" t="n">
-        <v>98345</v>
+        <v>79585</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E356" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I356" t="inlineStr"/>
-      <c r="J356" t="inlineStr"/>
-      <c r="K356" t="inlineStr"/>
-      <c r="L356" t="inlineStr"/>
-      <c r="N356" t="inlineStr"/>
       <c r="P356" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q356" t="n">
-        <v>520549</v>
+        <v>520639</v>
       </c>
       <c r="R356" t="n">
-        <v>6934058</v>
+        <v>6933509</v>
       </c>
       <c r="S356" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T356" t="inlineStr">
         <is>
@@ -41746,7 +41747,6 @@
       <c r="AE356" t="b">
         <v>0</v>
       </c>
-      <c r="AF356" t="inlineStr"/>
       <c r="AG356" t="b">
         <v>0</v>
       </c>
@@ -41959,37 +41959,38 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>125671278</v>
+        <v>125671157</v>
       </c>
       <c r="B359" t="n">
-        <v>80070</v>
+        <v>98331</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E359" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I359" t="inlineStr"/>
       <c r="J359" t="inlineStr"/>
       <c r="K359" t="inlineStr"/>
+      <c r="L359" t="inlineStr"/>
       <c r="N359" t="inlineStr"/>
       <c r="P359" t="inlineStr">
         <is>
@@ -41997,10 +41998,10 @@
         </is>
       </c>
       <c r="Q359" t="n">
-        <v>520511</v>
+        <v>520540</v>
       </c>
       <c r="R359" t="n">
-        <v>6934025</v>
+        <v>6934055</v>
       </c>
       <c r="S359" t="n">
         <v>10</v>
@@ -42258,38 +42259,37 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>125671157</v>
+        <v>125671278</v>
       </c>
       <c r="B362" t="n">
-        <v>98324</v>
+        <v>80070</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E362" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I362" t="inlineStr"/>
       <c r="J362" t="inlineStr"/>
       <c r="K362" t="inlineStr"/>
-      <c r="L362" t="inlineStr"/>
       <c r="N362" t="inlineStr"/>
       <c r="P362" t="inlineStr">
         <is>
@@ -42297,10 +42297,10 @@
         </is>
       </c>
       <c r="Q362" t="n">
-        <v>520540</v>
+        <v>520511</v>
       </c>
       <c r="R362" t="n">
-        <v>6934055</v>
+        <v>6934025</v>
       </c>
       <c r="S362" t="n">
         <v>10</v>
@@ -42363,7 +42363,7 @@
         <v>125670920</v>
       </c>
       <c r="B363" t="n">
-        <v>105348</v>
+        <v>105355</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -39092,32 +39092,32 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>125670914</v>
+        <v>125670922</v>
       </c>
       <c r="B330" t="n">
-        <v>80070</v>
+        <v>92509</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I330" t="inlineStr"/>
@@ -39127,10 +39127,10 @@
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>520224</v>
+        <v>520637</v>
       </c>
       <c r="R330" t="n">
-        <v>6933690</v>
+        <v>6934037</v>
       </c>
       <c r="S330" t="n">
         <v>25</v>
@@ -39189,48 +39189,51 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>125670922</v>
+        <v>125671054</v>
       </c>
       <c r="B331" t="n">
-        <v>92509</v>
+        <v>80070</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I331" t="inlineStr"/>
+      <c r="J331" t="inlineStr"/>
+      <c r="K331" t="inlineStr"/>
+      <c r="N331" t="inlineStr"/>
       <c r="P331" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>520637</v>
+        <v>520612</v>
       </c>
       <c r="R331" t="n">
-        <v>6934037</v>
+        <v>6934046</v>
       </c>
       <c r="S331" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T331" t="inlineStr">
         <is>
@@ -39268,6 +39271,7 @@
       <c r="AE331" t="b">
         <v>0</v>
       </c>
+      <c r="AF331" t="inlineStr"/>
       <c r="AG331" t="b">
         <v>0</v>
       </c>
@@ -39286,51 +39290,48 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>125671054</v>
+        <v>125661738</v>
       </c>
       <c r="B332" t="n">
-        <v>80070</v>
+        <v>92509</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I332" t="inlineStr"/>
-      <c r="J332" t="inlineStr"/>
-      <c r="K332" t="inlineStr"/>
-      <c r="N332" t="inlineStr"/>
       <c r="P332" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>520612</v>
+        <v>520605</v>
       </c>
       <c r="R332" t="n">
-        <v>6934046</v>
+        <v>6933517</v>
       </c>
       <c r="S332" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T332" t="inlineStr">
         <is>
@@ -39368,7 +39369,6 @@
       <c r="AE332" t="b">
         <v>0</v>
       </c>
-      <c r="AF332" t="inlineStr"/>
       <c r="AG332" t="b">
         <v>0</v>
       </c>
@@ -39387,48 +39387,48 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>125661738</v>
+        <v>125670914</v>
       </c>
       <c r="B333" t="n">
-        <v>92509</v>
+        <v>80070</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E333" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I333" t="inlineStr"/>
       <c r="P333" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>520605</v>
+        <v>520224</v>
       </c>
       <c r="R333" t="n">
-        <v>6933517</v>
+        <v>6933690</v>
       </c>
       <c r="S333" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T333" t="inlineStr">
         <is>
@@ -40085,10 +40085,10 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>125660155</v>
+        <v>125661442</v>
       </c>
       <c r="B340" t="n">
-        <v>78726</v>
+        <v>78634</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -40096,21 +40096,21 @@
         </is>
       </c>
       <c r="E340" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I340" t="inlineStr"/>
@@ -40120,10 +40120,10 @@
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>520786</v>
+        <v>520629</v>
       </c>
       <c r="R340" t="n">
-        <v>6933540</v>
+        <v>6933514</v>
       </c>
       <c r="S340" t="n">
         <v>20</v>
@@ -40182,10 +40182,10 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>125661442</v>
+        <v>125671469</v>
       </c>
       <c r="B341" t="n">
-        <v>78634</v>
+        <v>80070</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -40193,37 +40193,40 @@
         </is>
       </c>
       <c r="E341" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I341" t="inlineStr"/>
+      <c r="J341" t="inlineStr"/>
+      <c r="K341" t="inlineStr"/>
+      <c r="N341" t="inlineStr"/>
       <c r="P341" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>520629</v>
+        <v>520296</v>
       </c>
       <c r="R341" t="n">
-        <v>6933514</v>
+        <v>6933639</v>
       </c>
       <c r="S341" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T341" t="inlineStr">
         <is>
@@ -40261,6 +40264,7 @@
       <c r="AE341" t="b">
         <v>0</v>
       </c>
+      <c r="AF341" t="inlineStr"/>
       <c r="AG341" t="b">
         <v>0</v>
       </c>
@@ -40279,51 +40283,48 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>125671469</v>
+        <v>125659270</v>
       </c>
       <c r="B342" t="n">
-        <v>80070</v>
+        <v>92509</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E342" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I342" t="inlineStr"/>
-      <c r="J342" t="inlineStr"/>
-      <c r="K342" t="inlineStr"/>
-      <c r="N342" t="inlineStr"/>
       <c r="P342" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>520296</v>
+        <v>520846</v>
       </c>
       <c r="R342" t="n">
-        <v>6933639</v>
+        <v>6933515</v>
       </c>
       <c r="S342" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T342" t="inlineStr">
         <is>
@@ -40361,7 +40362,6 @@
       <c r="AE342" t="b">
         <v>0</v>
       </c>
-      <c r="AF342" t="inlineStr"/>
       <c r="AG342" t="b">
         <v>0</v>
       </c>
@@ -40380,32 +40380,32 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>125659270</v>
+        <v>125660155</v>
       </c>
       <c r="B343" t="n">
-        <v>92509</v>
+        <v>78726</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E343" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I343" t="inlineStr"/>
@@ -40415,10 +40415,10 @@
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>520846</v>
+        <v>520786</v>
       </c>
       <c r="R343" t="n">
-        <v>6933515</v>
+        <v>6933540</v>
       </c>
       <c r="S343" t="n">
         <v>20</v>
@@ -41959,38 +41959,37 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>125671157</v>
+        <v>125671098</v>
       </c>
       <c r="B359" t="n">
-        <v>98331</v>
+        <v>80070</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E359" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I359" t="inlineStr"/>
       <c r="J359" t="inlineStr"/>
       <c r="K359" t="inlineStr"/>
-      <c r="L359" t="inlineStr"/>
       <c r="N359" t="inlineStr"/>
       <c r="P359" t="inlineStr">
         <is>
@@ -41998,10 +41997,10 @@
         </is>
       </c>
       <c r="Q359" t="n">
-        <v>520540</v>
+        <v>520578</v>
       </c>
       <c r="R359" t="n">
-        <v>6934055</v>
+        <v>6934069</v>
       </c>
       <c r="S359" t="n">
         <v>10</v>
@@ -42061,10 +42060,10 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>125671098</v>
+        <v>125660786</v>
       </c>
       <c r="B360" t="n">
-        <v>80070</v>
+        <v>78725</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -42072,40 +42071,37 @@
         </is>
       </c>
       <c r="E360" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I360" t="inlineStr"/>
-      <c r="J360" t="inlineStr"/>
-      <c r="K360" t="inlineStr"/>
-      <c r="N360" t="inlineStr"/>
       <c r="P360" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q360" t="n">
-        <v>520578</v>
+        <v>520731</v>
       </c>
       <c r="R360" t="n">
-        <v>6934069</v>
+        <v>6933528</v>
       </c>
       <c r="S360" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T360" t="inlineStr">
         <is>
@@ -42143,7 +42139,6 @@
       <c r="AE360" t="b">
         <v>0</v>
       </c>
-      <c r="AF360" t="inlineStr"/>
       <c r="AG360" t="b">
         <v>0</v>
       </c>
@@ -42162,10 +42157,10 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>125660786</v>
+        <v>125671278</v>
       </c>
       <c r="B361" t="n">
-        <v>78725</v>
+        <v>80070</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -42173,37 +42168,40 @@
         </is>
       </c>
       <c r="E361" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I361" t="inlineStr"/>
+      <c r="J361" t="inlineStr"/>
+      <c r="K361" t="inlineStr"/>
+      <c r="N361" t="inlineStr"/>
       <c r="P361" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q361" t="n">
-        <v>520731</v>
+        <v>520511</v>
       </c>
       <c r="R361" t="n">
-        <v>6933528</v>
+        <v>6934025</v>
       </c>
       <c r="S361" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T361" t="inlineStr">
         <is>
@@ -42241,6 +42239,7 @@
       <c r="AE361" t="b">
         <v>0</v>
       </c>
+      <c r="AF361" t="inlineStr"/>
       <c r="AG361" t="b">
         <v>0</v>
       </c>
@@ -42259,37 +42258,38 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>125671278</v>
+        <v>125671157</v>
       </c>
       <c r="B362" t="n">
-        <v>80070</v>
+        <v>98331</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E362" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I362" t="inlineStr"/>
       <c r="J362" t="inlineStr"/>
       <c r="K362" t="inlineStr"/>
+      <c r="L362" t="inlineStr"/>
       <c r="N362" t="inlineStr"/>
       <c r="P362" t="inlineStr">
         <is>
@@ -42297,10 +42297,10 @@
         </is>
       </c>
       <c r="Q362" t="n">
-        <v>520511</v>
+        <v>520540</v>
       </c>
       <c r="R362" t="n">
-        <v>6934025</v>
+        <v>6934055</v>
       </c>
       <c r="S362" t="n">
         <v>10</v>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -39092,32 +39092,32 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>125670922</v>
+        <v>125670914</v>
       </c>
       <c r="B330" t="n">
-        <v>92509</v>
+        <v>80070</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I330" t="inlineStr"/>
@@ -39127,10 +39127,10 @@
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>520637</v>
+        <v>520224</v>
       </c>
       <c r="R330" t="n">
-        <v>6934037</v>
+        <v>6933690</v>
       </c>
       <c r="S330" t="n">
         <v>25</v>
@@ -39189,51 +39189,48 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>125671054</v>
+        <v>125670922</v>
       </c>
       <c r="B331" t="n">
-        <v>80070</v>
+        <v>92509</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I331" t="inlineStr"/>
-      <c r="J331" t="inlineStr"/>
-      <c r="K331" t="inlineStr"/>
-      <c r="N331" t="inlineStr"/>
       <c r="P331" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>520612</v>
+        <v>520637</v>
       </c>
       <c r="R331" t="n">
-        <v>6934046</v>
+        <v>6934037</v>
       </c>
       <c r="S331" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T331" t="inlineStr">
         <is>
@@ -39271,7 +39268,6 @@
       <c r="AE331" t="b">
         <v>0</v>
       </c>
-      <c r="AF331" t="inlineStr"/>
       <c r="AG331" t="b">
         <v>0</v>
       </c>
@@ -39290,48 +39286,51 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>125661738</v>
+        <v>125671054</v>
       </c>
       <c r="B332" t="n">
-        <v>92509</v>
+        <v>80070</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I332" t="inlineStr"/>
+      <c r="J332" t="inlineStr"/>
+      <c r="K332" t="inlineStr"/>
+      <c r="N332" t="inlineStr"/>
       <c r="P332" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>520605</v>
+        <v>520612</v>
       </c>
       <c r="R332" t="n">
-        <v>6933517</v>
+        <v>6934046</v>
       </c>
       <c r="S332" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T332" t="inlineStr">
         <is>
@@ -39369,6 +39368,7 @@
       <c r="AE332" t="b">
         <v>0</v>
       </c>
+      <c r="AF332" t="inlineStr"/>
       <c r="AG332" t="b">
         <v>0</v>
       </c>
@@ -39387,48 +39387,48 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>125670914</v>
+        <v>125661738</v>
       </c>
       <c r="B333" t="n">
-        <v>80070</v>
+        <v>92509</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E333" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I333" t="inlineStr"/>
       <c r="P333" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>520224</v>
+        <v>520605</v>
       </c>
       <c r="R333" t="n">
-        <v>6933690</v>
+        <v>6933517</v>
       </c>
       <c r="S333" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T333" t="inlineStr">
         <is>
@@ -39581,10 +39581,10 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>125670909</v>
+        <v>125671021</v>
       </c>
       <c r="B335" t="n">
-        <v>80070</v>
+        <v>57648</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -39592,37 +39592,41 @@
         </is>
       </c>
       <c r="E335" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I335" t="inlineStr"/>
+      <c r="K335" t="inlineStr"/>
+      <c r="L335" t="inlineStr"/>
+      <c r="M335" t="inlineStr"/>
+      <c r="N335" t="inlineStr"/>
       <c r="P335" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>520754</v>
+        <v>520607</v>
       </c>
       <c r="R335" t="n">
-        <v>6934006</v>
+        <v>6934048</v>
       </c>
       <c r="S335" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T335" t="inlineStr">
         <is>
@@ -39656,7 +39660,7 @@
       </c>
       <c r="AC335" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD335" t="b">
@@ -39877,10 +39881,10 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>125671021</v>
+        <v>125670909</v>
       </c>
       <c r="B338" t="n">
-        <v>57648</v>
+        <v>80070</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -39888,41 +39892,37 @@
         </is>
       </c>
       <c r="E338" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I338" t="inlineStr"/>
-      <c r="K338" t="inlineStr"/>
-      <c r="L338" t="inlineStr"/>
-      <c r="M338" t="inlineStr"/>
-      <c r="N338" t="inlineStr"/>
       <c r="P338" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>520607</v>
+        <v>520754</v>
       </c>
       <c r="R338" t="n">
-        <v>6934048</v>
+        <v>6934006</v>
       </c>
       <c r="S338" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T338" t="inlineStr">
         <is>
@@ -39956,7 +39956,7 @@
       </c>
       <c r="AC338" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD338" t="b">

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -37713,7 +37713,7 @@
         <v>125670918</v>
       </c>
       <c r="B316" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -37810,7 +37810,7 @@
         <v>125662951</v>
       </c>
       <c r="B317" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -38006,10 +38006,10 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>125671391</v>
+        <v>125670912</v>
       </c>
       <c r="B319" t="n">
-        <v>57811</v>
+        <v>80071</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -38017,38 +38017,34 @@
         </is>
       </c>
       <c r="E319" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I319" t="inlineStr"/>
-      <c r="K319" t="inlineStr"/>
-      <c r="L319" t="inlineStr"/>
-      <c r="M319" t="inlineStr"/>
-      <c r="N319" t="inlineStr"/>
       <c r="P319" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>520408</v>
+        <v>520757</v>
       </c>
       <c r="R319" t="n">
-        <v>6934036</v>
+        <v>6934013</v>
       </c>
       <c r="S319" t="n">
         <v>25</v>
@@ -38107,10 +38103,10 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>125670912</v>
+        <v>125671391</v>
       </c>
       <c r="B320" t="n">
-        <v>80070</v>
+        <v>57811</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -38118,34 +38114,38 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I320" t="inlineStr"/>
+      <c r="K320" t="inlineStr"/>
+      <c r="L320" t="inlineStr"/>
+      <c r="M320" t="inlineStr"/>
+      <c r="N320" t="inlineStr"/>
       <c r="P320" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>520757</v>
+        <v>520408</v>
       </c>
       <c r="R320" t="n">
-        <v>6934013</v>
+        <v>6934036</v>
       </c>
       <c r="S320" t="n">
         <v>25</v>
@@ -38204,48 +38204,52 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>125661236</v>
+        <v>125671307</v>
       </c>
       <c r="B321" t="n">
-        <v>43933</v>
+        <v>98334</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>101735</v>
+        <v>220787</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I321" t="inlineStr"/>
+      <c r="J321" t="inlineStr"/>
+      <c r="K321" t="inlineStr"/>
+      <c r="L321" t="inlineStr"/>
+      <c r="N321" t="inlineStr"/>
       <c r="P321" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>520684</v>
+        <v>520477</v>
       </c>
       <c r="R321" t="n">
-        <v>6933537</v>
+        <v>6934031</v>
       </c>
       <c r="S321" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T321" t="inlineStr">
         <is>
@@ -38277,17 +38281,13 @@
           <t>2025-06-03</t>
         </is>
       </c>
-      <c r="AC321" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
-        </is>
-      </c>
       <c r="AD321" t="b">
         <v>0</v>
       </c>
       <c r="AE321" t="b">
         <v>0</v>
       </c>
+      <c r="AF321" t="inlineStr"/>
       <c r="AG321" t="b">
         <v>0</v>
       </c>
@@ -38306,52 +38306,48 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>125671307</v>
+        <v>125660766</v>
       </c>
       <c r="B322" t="n">
-        <v>98331</v>
+        <v>79586</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I322" t="inlineStr"/>
-      <c r="J322" t="inlineStr"/>
-      <c r="K322" t="inlineStr"/>
-      <c r="L322" t="inlineStr"/>
-      <c r="N322" t="inlineStr"/>
       <c r="P322" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>520477</v>
+        <v>520729</v>
       </c>
       <c r="R322" t="n">
-        <v>6934031</v>
+        <v>6933543</v>
       </c>
       <c r="S322" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T322" t="inlineStr">
         <is>
@@ -38389,7 +38385,6 @@
       <c r="AE322" t="b">
         <v>0</v>
       </c>
-      <c r="AF322" t="inlineStr"/>
       <c r="AG322" t="b">
         <v>0</v>
       </c>
@@ -38408,32 +38403,32 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>125660766</v>
+        <v>125661236</v>
       </c>
       <c r="B323" t="n">
-        <v>79585</v>
+        <v>43933</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>6453</v>
+        <v>101735</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I323" t="inlineStr"/>
@@ -38443,10 +38438,10 @@
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>520729</v>
+        <v>520684</v>
       </c>
       <c r="R323" t="n">
-        <v>6933543</v>
+        <v>6933537</v>
       </c>
       <c r="S323" t="n">
         <v>20</v>
@@ -38479,6 +38474,11 @@
       <c r="AA323" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC323" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD323" t="b">
@@ -38505,48 +38505,48 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>125661898</v>
+        <v>125670924</v>
       </c>
       <c r="B324" t="n">
-        <v>98331</v>
+        <v>92518</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I324" t="inlineStr"/>
       <c r="P324" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>520558</v>
+        <v>520194</v>
       </c>
       <c r="R324" t="n">
-        <v>6933556</v>
+        <v>6933813</v>
       </c>
       <c r="S324" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T324" t="inlineStr">
         <is>
@@ -38602,32 +38602,32 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>125670919</v>
+        <v>125670906</v>
       </c>
       <c r="B325" t="n">
-        <v>98331</v>
+        <v>79975</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E325" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I325" t="inlineStr"/>
@@ -38637,10 +38637,10 @@
         </is>
       </c>
       <c r="Q325" t="n">
-        <v>520223</v>
+        <v>521033</v>
       </c>
       <c r="R325" t="n">
-        <v>6933684</v>
+        <v>6933394</v>
       </c>
       <c r="S325" t="n">
         <v>25</v>
@@ -38699,48 +38699,48 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>125670906</v>
+        <v>125663906</v>
       </c>
       <c r="B326" t="n">
-        <v>79974</v>
+        <v>80071</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E326" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I326" t="inlineStr"/>
       <c r="P326" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q326" t="n">
-        <v>521033</v>
+        <v>520184</v>
       </c>
       <c r="R326" t="n">
-        <v>6933394</v>
+        <v>6933765</v>
       </c>
       <c r="S326" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T326" t="inlineStr">
         <is>
@@ -38796,32 +38796,32 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>125663906</v>
+        <v>125661898</v>
       </c>
       <c r="B327" t="n">
-        <v>80070</v>
+        <v>98334</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I327" t="inlineStr"/>
@@ -38831,13 +38831,13 @@
         </is>
       </c>
       <c r="Q327" t="n">
-        <v>520184</v>
+        <v>520558</v>
       </c>
       <c r="R327" t="n">
-        <v>6933765</v>
+        <v>6933556</v>
       </c>
       <c r="S327" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T327" t="inlineStr">
         <is>
@@ -38893,32 +38893,32 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>125670924</v>
+        <v>125670919</v>
       </c>
       <c r="B328" t="n">
-        <v>92509</v>
+        <v>98334</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I328" t="inlineStr"/>
@@ -38928,10 +38928,10 @@
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>520194</v>
+        <v>520223</v>
       </c>
       <c r="R328" t="n">
-        <v>6933813</v>
+        <v>6933684</v>
       </c>
       <c r="S328" t="n">
         <v>25</v>
@@ -38993,7 +38993,7 @@
         <v>125670908</v>
       </c>
       <c r="B329" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -39092,32 +39092,32 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>125670914</v>
+        <v>125670922</v>
       </c>
       <c r="B330" t="n">
-        <v>80070</v>
+        <v>92518</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I330" t="inlineStr"/>
@@ -39127,10 +39127,10 @@
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>520224</v>
+        <v>520637</v>
       </c>
       <c r="R330" t="n">
-        <v>6933690</v>
+        <v>6934037</v>
       </c>
       <c r="S330" t="n">
         <v>25</v>
@@ -39189,10 +39189,10 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>125670922</v>
+        <v>125661738</v>
       </c>
       <c r="B331" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -39220,17 +39220,17 @@
       <c r="I331" t="inlineStr"/>
       <c r="P331" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>520637</v>
+        <v>520605</v>
       </c>
       <c r="R331" t="n">
-        <v>6934037</v>
+        <v>6933517</v>
       </c>
       <c r="S331" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T331" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>125671054</v>
       </c>
       <c r="B332" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -39387,48 +39387,48 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>125661738</v>
+        <v>125670914</v>
       </c>
       <c r="B333" t="n">
-        <v>92509</v>
+        <v>80071</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E333" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I333" t="inlineStr"/>
       <c r="P333" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>520605</v>
+        <v>520224</v>
       </c>
       <c r="R333" t="n">
-        <v>6933517</v>
+        <v>6933690</v>
       </c>
       <c r="S333" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T333" t="inlineStr">
         <is>
@@ -39487,7 +39487,7 @@
         <v>125670907</v>
       </c>
       <c r="B334" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -39581,52 +39581,48 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>125671021</v>
+        <v>125670921</v>
       </c>
       <c r="B335" t="n">
-        <v>57648</v>
+        <v>92518</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E335" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I335" t="inlineStr"/>
-      <c r="K335" t="inlineStr"/>
-      <c r="L335" t="inlineStr"/>
-      <c r="M335" t="inlineStr"/>
-      <c r="N335" t="inlineStr"/>
       <c r="P335" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>520607</v>
+        <v>520731</v>
       </c>
       <c r="R335" t="n">
-        <v>6934048</v>
+        <v>6934038</v>
       </c>
       <c r="S335" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T335" t="inlineStr">
         <is>
@@ -39656,11 +39652,6 @@
       <c r="AA335" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC335" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD335" t="b">
@@ -39687,10 +39678,10 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>125670916</v>
+        <v>125671021</v>
       </c>
       <c r="B336" t="n">
-        <v>80070</v>
+        <v>57648</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -39698,37 +39689,41 @@
         </is>
       </c>
       <c r="E336" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I336" t="inlineStr"/>
+      <c r="K336" t="inlineStr"/>
+      <c r="L336" t="inlineStr"/>
+      <c r="M336" t="inlineStr"/>
+      <c r="N336" t="inlineStr"/>
       <c r="P336" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>520803</v>
+        <v>520607</v>
       </c>
       <c r="R336" t="n">
-        <v>6933448</v>
+        <v>6934048</v>
       </c>
       <c r="S336" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T336" t="inlineStr">
         <is>
@@ -39758,6 +39753,11 @@
       <c r="AA336" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC336" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD336" t="b">
@@ -39784,10 +39784,10 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>125670921</v>
+        <v>125670903</v>
       </c>
       <c r="B337" t="n">
-        <v>92509</v>
+        <v>56843</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -39795,21 +39795,21 @@
         </is>
       </c>
       <c r="E337" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I337" t="inlineStr"/>
@@ -39822,7 +39822,7 @@
         <v>520731</v>
       </c>
       <c r="R337" t="n">
-        <v>6934038</v>
+        <v>6934042</v>
       </c>
       <c r="S337" t="n">
         <v>25</v>
@@ -39855,6 +39855,11 @@
       <c r="AA337" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC337" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD337" t="b">
@@ -39881,10 +39886,10 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>125670909</v>
+        <v>125670916</v>
       </c>
       <c r="B338" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -39916,10 +39921,10 @@
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>520754</v>
+        <v>520803</v>
       </c>
       <c r="R338" t="n">
-        <v>6934006</v>
+        <v>6933448</v>
       </c>
       <c r="S338" t="n">
         <v>25</v>
@@ -39952,11 +39957,6 @@
       <c r="AA338" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC338" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD338" t="b">
@@ -39983,32 +39983,32 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>125670903</v>
+        <v>125670909</v>
       </c>
       <c r="B339" t="n">
-        <v>56843</v>
+        <v>80071</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E339" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I339" t="inlineStr"/>
@@ -40018,10 +40018,10 @@
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>520731</v>
+        <v>520754</v>
       </c>
       <c r="R339" t="n">
-        <v>6934042</v>
+        <v>6934006</v>
       </c>
       <c r="S339" t="n">
         <v>25</v>
@@ -40058,7 +40058,7 @@
       </c>
       <c r="AC339" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD339" t="b">
@@ -40088,7 +40088,7 @@
         <v>125661442</v>
       </c>
       <c r="B340" t="n">
-        <v>78634</v>
+        <v>78635</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -40185,7 +40185,7 @@
         <v>125671469</v>
       </c>
       <c r="B341" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -40286,7 +40286,7 @@
         <v>125659270</v>
       </c>
       <c r="B342" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -40383,7 +40383,7 @@
         <v>125660155</v>
       </c>
       <c r="B343" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>125670923</v>
       </c>
       <c r="B344" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -40574,32 +40574,32 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>125659251</v>
+        <v>125662204</v>
       </c>
       <c r="B345" t="n">
-        <v>78725</v>
+        <v>91389</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E345" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I345" t="inlineStr"/>
@@ -40609,10 +40609,10 @@
         </is>
       </c>
       <c r="Q345" t="n">
-        <v>520823</v>
+        <v>520425</v>
       </c>
       <c r="R345" t="n">
-        <v>6933519</v>
+        <v>6933544</v>
       </c>
       <c r="S345" t="n">
         <v>20</v>
@@ -40671,10 +40671,10 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>125670910</v>
+        <v>125670905</v>
       </c>
       <c r="B346" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -40682,21 +40682,21 @@
         </is>
       </c>
       <c r="E346" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I346" t="inlineStr"/>
@@ -40706,10 +40706,10 @@
         </is>
       </c>
       <c r="Q346" t="n">
-        <v>520830</v>
+        <v>520801</v>
       </c>
       <c r="R346" t="n">
-        <v>6933884</v>
+        <v>6933448</v>
       </c>
       <c r="S346" t="n">
         <v>25</v>
@@ -40768,10 +40768,10 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>125670905</v>
+        <v>125659251</v>
       </c>
       <c r="B347" t="n">
-        <v>80071</v>
+        <v>78726</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -40779,37 +40779,37 @@
         </is>
       </c>
       <c r="E347" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I347" t="inlineStr"/>
       <c r="P347" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q347" t="n">
-        <v>520801</v>
+        <v>520823</v>
       </c>
       <c r="R347" t="n">
-        <v>6933448</v>
+        <v>6933519</v>
       </c>
       <c r="S347" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T347" t="inlineStr">
         <is>
@@ -40865,48 +40865,48 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>125662204</v>
+        <v>125670910</v>
       </c>
       <c r="B348" t="n">
-        <v>91387</v>
+        <v>80071</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E348" t="n">
-        <v>1503</v>
+        <v>6458</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I348" t="inlineStr"/>
       <c r="P348" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q348" t="n">
-        <v>520425</v>
+        <v>520830</v>
       </c>
       <c r="R348" t="n">
-        <v>6933544</v>
+        <v>6933884</v>
       </c>
       <c r="S348" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T348" t="inlineStr">
         <is>
@@ -40965,7 +40965,7 @@
         <v>125671342</v>
       </c>
       <c r="B349" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -41067,7 +41067,7 @@
         <v>125670917</v>
       </c>
       <c r="B350" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -41267,52 +41267,48 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>125671230</v>
+        <v>125670901</v>
       </c>
       <c r="B352" t="n">
-        <v>98352</v>
+        <v>91228</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E352" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I352" t="inlineStr"/>
-      <c r="J352" t="inlineStr"/>
-      <c r="K352" t="inlineStr"/>
-      <c r="L352" t="inlineStr"/>
-      <c r="N352" t="inlineStr"/>
       <c r="P352" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q352" t="n">
-        <v>520549</v>
+        <v>520257</v>
       </c>
       <c r="R352" t="n">
-        <v>6934058</v>
+        <v>6933643</v>
       </c>
       <c r="S352" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T352" t="inlineStr">
         <is>
@@ -41350,7 +41346,6 @@
       <c r="AE352" t="b">
         <v>0</v>
       </c>
-      <c r="AF352" t="inlineStr"/>
       <c r="AG352" t="b">
         <v>0</v>
       </c>
@@ -41369,10 +41364,10 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>125670901</v>
+        <v>125671498</v>
       </c>
       <c r="B353" t="n">
-        <v>91227</v>
+        <v>80071</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -41380,34 +41375,37 @@
         </is>
       </c>
       <c r="E353" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I353" t="inlineStr"/>
+      <c r="J353" t="inlineStr"/>
+      <c r="K353" t="inlineStr"/>
+      <c r="N353" t="inlineStr"/>
       <c r="P353" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q353" t="n">
-        <v>520257</v>
+        <v>520385</v>
       </c>
       <c r="R353" t="n">
-        <v>6933643</v>
+        <v>6933569</v>
       </c>
       <c r="S353" t="n">
         <v>25</v>
@@ -41448,6 +41446,7 @@
       <c r="AE353" t="b">
         <v>0</v>
       </c>
+      <c r="AF353" t="inlineStr"/>
       <c r="AG353" t="b">
         <v>0</v>
       </c>
@@ -41466,10 +41465,10 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>125671498</v>
+        <v>125671434</v>
       </c>
       <c r="B354" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -41504,13 +41503,13 @@
         </is>
       </c>
       <c r="Q354" t="n">
-        <v>520385</v>
+        <v>520364</v>
       </c>
       <c r="R354" t="n">
-        <v>6933569</v>
+        <v>6934008</v>
       </c>
       <c r="S354" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T354" t="inlineStr">
         <is>
@@ -41567,10 +41566,10 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>125671434</v>
+        <v>125661680</v>
       </c>
       <c r="B355" t="n">
-        <v>80070</v>
+        <v>79586</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -41578,40 +41577,37 @@
         </is>
       </c>
       <c r="E355" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I355" t="inlineStr"/>
-      <c r="J355" t="inlineStr"/>
-      <c r="K355" t="inlineStr"/>
-      <c r="N355" t="inlineStr"/>
       <c r="P355" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q355" t="n">
-        <v>520364</v>
+        <v>520639</v>
       </c>
       <c r="R355" t="n">
-        <v>6934008</v>
+        <v>6933509</v>
       </c>
       <c r="S355" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T355" t="inlineStr">
         <is>
@@ -41649,7 +41645,6 @@
       <c r="AE355" t="b">
         <v>0</v>
       </c>
-      <c r="AF355" t="inlineStr"/>
       <c r="AG355" t="b">
         <v>0</v>
       </c>
@@ -41668,48 +41663,52 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>125661680</v>
+        <v>125671230</v>
       </c>
       <c r="B356" t="n">
-        <v>79585</v>
+        <v>98355</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E356" t="n">
-        <v>6453</v>
+        <v>221952</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I356" t="inlineStr"/>
+      <c r="J356" t="inlineStr"/>
+      <c r="K356" t="inlineStr"/>
+      <c r="L356" t="inlineStr"/>
+      <c r="N356" t="inlineStr"/>
       <c r="P356" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q356" t="n">
-        <v>520639</v>
+        <v>520549</v>
       </c>
       <c r="R356" t="n">
-        <v>6933509</v>
+        <v>6934058</v>
       </c>
       <c r="S356" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T356" t="inlineStr">
         <is>
@@ -41747,6 +41746,7 @@
       <c r="AE356" t="b">
         <v>0</v>
       </c>
+      <c r="AF356" t="inlineStr"/>
       <c r="AG356" t="b">
         <v>0</v>
       </c>
@@ -41768,7 +41768,7 @@
         <v>125659241</v>
       </c>
       <c r="B357" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>125670913</v>
       </c>
       <c r="B358" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -41959,10 +41959,10 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>125671098</v>
+        <v>125671278</v>
       </c>
       <c r="B359" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -41997,10 +41997,10 @@
         </is>
       </c>
       <c r="Q359" t="n">
-        <v>520578</v>
+        <v>520511</v>
       </c>
       <c r="R359" t="n">
-        <v>6934069</v>
+        <v>6934025</v>
       </c>
       <c r="S359" t="n">
         <v>10</v>
@@ -42060,10 +42060,10 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>125660786</v>
+        <v>125671098</v>
       </c>
       <c r="B360" t="n">
-        <v>78725</v>
+        <v>80071</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -42071,37 +42071,40 @@
         </is>
       </c>
       <c r="E360" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I360" t="inlineStr"/>
+      <c r="J360" t="inlineStr"/>
+      <c r="K360" t="inlineStr"/>
+      <c r="N360" t="inlineStr"/>
       <c r="P360" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q360" t="n">
-        <v>520731</v>
+        <v>520578</v>
       </c>
       <c r="R360" t="n">
-        <v>6933528</v>
+        <v>6934069</v>
       </c>
       <c r="S360" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T360" t="inlineStr">
         <is>
@@ -42139,6 +42142,7 @@
       <c r="AE360" t="b">
         <v>0</v>
       </c>
+      <c r="AF360" t="inlineStr"/>
       <c r="AG360" t="b">
         <v>0</v>
       </c>
@@ -42157,10 +42161,10 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>125671278</v>
+        <v>125660786</v>
       </c>
       <c r="B361" t="n">
-        <v>80070</v>
+        <v>78726</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -42168,40 +42172,37 @@
         </is>
       </c>
       <c r="E361" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I361" t="inlineStr"/>
-      <c r="J361" t="inlineStr"/>
-      <c r="K361" t="inlineStr"/>
-      <c r="N361" t="inlineStr"/>
       <c r="P361" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q361" t="n">
-        <v>520511</v>
+        <v>520731</v>
       </c>
       <c r="R361" t="n">
-        <v>6934025</v>
+        <v>6933528</v>
       </c>
       <c r="S361" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T361" t="inlineStr">
         <is>
@@ -42239,7 +42240,6 @@
       <c r="AE361" t="b">
         <v>0</v>
       </c>
-      <c r="AF361" t="inlineStr"/>
       <c r="AG361" t="b">
         <v>0</v>
       </c>
@@ -42261,7 +42261,7 @@
         <v>125671157</v>
       </c>
       <c r="B362" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -42363,7 +42363,7 @@
         <v>125670920</v>
       </c>
       <c r="B363" t="n">
-        <v>105355</v>
+        <v>105358</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -40085,32 +40085,32 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>125661442</v>
+        <v>125659270</v>
       </c>
       <c r="B340" t="n">
-        <v>78635</v>
+        <v>92518</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E340" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I340" t="inlineStr"/>
@@ -40120,10 +40120,10 @@
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>520629</v>
+        <v>520846</v>
       </c>
       <c r="R340" t="n">
-        <v>6933514</v>
+        <v>6933515</v>
       </c>
       <c r="S340" t="n">
         <v>20</v>
@@ -40182,10 +40182,10 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>125671469</v>
+        <v>125661442</v>
       </c>
       <c r="B341" t="n">
-        <v>80071</v>
+        <v>78635</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -40193,40 +40193,37 @@
         </is>
       </c>
       <c r="E341" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I341" t="inlineStr"/>
-      <c r="J341" t="inlineStr"/>
-      <c r="K341" t="inlineStr"/>
-      <c r="N341" t="inlineStr"/>
       <c r="P341" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>520296</v>
+        <v>520629</v>
       </c>
       <c r="R341" t="n">
-        <v>6933639</v>
+        <v>6933514</v>
       </c>
       <c r="S341" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T341" t="inlineStr">
         <is>
@@ -40264,7 +40261,6 @@
       <c r="AE341" t="b">
         <v>0</v>
       </c>
-      <c r="AF341" t="inlineStr"/>
       <c r="AG341" t="b">
         <v>0</v>
       </c>
@@ -40283,48 +40279,51 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>125659270</v>
+        <v>125671469</v>
       </c>
       <c r="B342" t="n">
-        <v>92518</v>
+        <v>80071</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E342" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I342" t="inlineStr"/>
+      <c r="J342" t="inlineStr"/>
+      <c r="K342" t="inlineStr"/>
+      <c r="N342" t="inlineStr"/>
       <c r="P342" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>520846</v>
+        <v>520296</v>
       </c>
       <c r="R342" t="n">
-        <v>6933515</v>
+        <v>6933639</v>
       </c>
       <c r="S342" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T342" t="inlineStr">
         <is>
@@ -40362,6 +40361,7 @@
       <c r="AE342" t="b">
         <v>0</v>
       </c>
+      <c r="AF342" t="inlineStr"/>
       <c r="AG342" t="b">
         <v>0</v>
       </c>
@@ -40671,10 +40671,10 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>125670905</v>
+        <v>125659251</v>
       </c>
       <c r="B346" t="n">
-        <v>80072</v>
+        <v>78726</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -40682,37 +40682,37 @@
         </is>
       </c>
       <c r="E346" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I346" t="inlineStr"/>
       <c r="P346" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q346" t="n">
-        <v>520801</v>
+        <v>520823</v>
       </c>
       <c r="R346" t="n">
-        <v>6933448</v>
+        <v>6933519</v>
       </c>
       <c r="S346" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T346" t="inlineStr">
         <is>
@@ -40768,10 +40768,10 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>125659251</v>
+        <v>125670910</v>
       </c>
       <c r="B347" t="n">
-        <v>78726</v>
+        <v>80071</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -40779,37 +40779,37 @@
         </is>
       </c>
       <c r="E347" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I347" t="inlineStr"/>
       <c r="P347" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q347" t="n">
-        <v>520823</v>
+        <v>520830</v>
       </c>
       <c r="R347" t="n">
-        <v>6933519</v>
+        <v>6933884</v>
       </c>
       <c r="S347" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T347" t="inlineStr">
         <is>
@@ -40865,10 +40865,10 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>125670910</v>
+        <v>125670905</v>
       </c>
       <c r="B348" t="n">
-        <v>80071</v>
+        <v>80072</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -40876,21 +40876,21 @@
         </is>
       </c>
       <c r="E348" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I348" t="inlineStr"/>
@@ -40900,10 +40900,10 @@
         </is>
       </c>
       <c r="Q348" t="n">
-        <v>520830</v>
+        <v>520801</v>
       </c>
       <c r="R348" t="n">
-        <v>6933884</v>
+        <v>6933448</v>
       </c>
       <c r="S348" t="n">
         <v>25</v>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -37713,7 +37713,7 @@
         <v>125670918</v>
       </c>
       <c r="B316" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -37810,7 +37810,7 @@
         <v>125662951</v>
       </c>
       <c r="B317" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -38009,7 +38009,7 @@
         <v>125670912</v>
       </c>
       <c r="B319" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -38207,7 +38207,7 @@
         <v>125671307</v>
       </c>
       <c r="B321" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -38309,7 +38309,7 @@
         <v>125660766</v>
       </c>
       <c r="B322" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -38508,7 +38508,7 @@
         <v>125670924</v>
       </c>
       <c r="B324" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -38602,48 +38602,48 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>125670906</v>
+        <v>125661898</v>
       </c>
       <c r="B325" t="n">
-        <v>79975</v>
+        <v>98338</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E325" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I325" t="inlineStr"/>
       <c r="P325" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q325" t="n">
-        <v>521033</v>
+        <v>520558</v>
       </c>
       <c r="R325" t="n">
-        <v>6933394</v>
+        <v>6933556</v>
       </c>
       <c r="S325" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T325" t="inlineStr">
         <is>
@@ -38699,48 +38699,48 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>125663906</v>
+        <v>125670919</v>
       </c>
       <c r="B326" t="n">
-        <v>80071</v>
+        <v>98338</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E326" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I326" t="inlineStr"/>
       <c r="P326" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q326" t="n">
-        <v>520184</v>
+        <v>520223</v>
       </c>
       <c r="R326" t="n">
-        <v>6933765</v>
+        <v>6933684</v>
       </c>
       <c r="S326" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T326" t="inlineStr">
         <is>
@@ -38796,48 +38796,48 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>125661898</v>
+        <v>125670906</v>
       </c>
       <c r="B327" t="n">
-        <v>98334</v>
+        <v>79979</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I327" t="inlineStr"/>
       <c r="P327" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q327" t="n">
-        <v>520558</v>
+        <v>521033</v>
       </c>
       <c r="R327" t="n">
-        <v>6933556</v>
+        <v>6933394</v>
       </c>
       <c r="S327" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T327" t="inlineStr">
         <is>
@@ -38893,48 +38893,48 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>125670919</v>
+        <v>125663906</v>
       </c>
       <c r="B328" t="n">
-        <v>98334</v>
+        <v>80075</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I328" t="inlineStr"/>
       <c r="P328" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>520223</v>
+        <v>520184</v>
       </c>
       <c r="R328" t="n">
-        <v>6933684</v>
+        <v>6933765</v>
       </c>
       <c r="S328" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T328" t="inlineStr">
         <is>
@@ -38993,7 +38993,7 @@
         <v>125670908</v>
       </c>
       <c r="B329" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -39092,48 +39092,51 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>125670922</v>
+        <v>125671054</v>
       </c>
       <c r="B330" t="n">
-        <v>92518</v>
+        <v>80075</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I330" t="inlineStr"/>
+      <c r="J330" t="inlineStr"/>
+      <c r="K330" t="inlineStr"/>
+      <c r="N330" t="inlineStr"/>
       <c r="P330" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>520637</v>
+        <v>520612</v>
       </c>
       <c r="R330" t="n">
-        <v>6934037</v>
+        <v>6934046</v>
       </c>
       <c r="S330" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T330" t="inlineStr">
         <is>
@@ -39171,6 +39174,7 @@
       <c r="AE330" t="b">
         <v>0</v>
       </c>
+      <c r="AF330" t="inlineStr"/>
       <c r="AG330" t="b">
         <v>0</v>
       </c>
@@ -39189,48 +39193,48 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>125661738</v>
+        <v>125670914</v>
       </c>
       <c r="B331" t="n">
-        <v>92518</v>
+        <v>80075</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I331" t="inlineStr"/>
       <c r="P331" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>520605</v>
+        <v>520224</v>
       </c>
       <c r="R331" t="n">
-        <v>6933517</v>
+        <v>6933690</v>
       </c>
       <c r="S331" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T331" t="inlineStr">
         <is>
@@ -39286,51 +39290,48 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>125671054</v>
+        <v>125670922</v>
       </c>
       <c r="B332" t="n">
-        <v>80071</v>
+        <v>92522</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I332" t="inlineStr"/>
-      <c r="J332" t="inlineStr"/>
-      <c r="K332" t="inlineStr"/>
-      <c r="N332" t="inlineStr"/>
       <c r="P332" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>520612</v>
+        <v>520637</v>
       </c>
       <c r="R332" t="n">
-        <v>6934046</v>
+        <v>6934037</v>
       </c>
       <c r="S332" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T332" t="inlineStr">
         <is>
@@ -39368,7 +39369,6 @@
       <c r="AE332" t="b">
         <v>0</v>
       </c>
-      <c r="AF332" t="inlineStr"/>
       <c r="AG332" t="b">
         <v>0</v>
       </c>
@@ -39387,48 +39387,48 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>125670914</v>
+        <v>125661738</v>
       </c>
       <c r="B333" t="n">
-        <v>80071</v>
+        <v>92522</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E333" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I333" t="inlineStr"/>
       <c r="P333" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>520224</v>
+        <v>520605</v>
       </c>
       <c r="R333" t="n">
-        <v>6933690</v>
+        <v>6933517</v>
       </c>
       <c r="S333" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T333" t="inlineStr">
         <is>
@@ -39487,7 +39487,7 @@
         <v>125670907</v>
       </c>
       <c r="B334" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -39581,32 +39581,32 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>125670921</v>
+        <v>125670916</v>
       </c>
       <c r="B335" t="n">
-        <v>92518</v>
+        <v>80075</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E335" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I335" t="inlineStr"/>
@@ -39616,10 +39616,10 @@
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>520731</v>
+        <v>520803</v>
       </c>
       <c r="R335" t="n">
-        <v>6934038</v>
+        <v>6933448</v>
       </c>
       <c r="S335" t="n">
         <v>25</v>
@@ -39678,10 +39678,10 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>125671021</v>
+        <v>125670909</v>
       </c>
       <c r="B336" t="n">
-        <v>57648</v>
+        <v>80075</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -39689,41 +39689,37 @@
         </is>
       </c>
       <c r="E336" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I336" t="inlineStr"/>
-      <c r="K336" t="inlineStr"/>
-      <c r="L336" t="inlineStr"/>
-      <c r="M336" t="inlineStr"/>
-      <c r="N336" t="inlineStr"/>
       <c r="P336" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>520607</v>
+        <v>520754</v>
       </c>
       <c r="R336" t="n">
-        <v>6934048</v>
+        <v>6934006</v>
       </c>
       <c r="S336" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T336" t="inlineStr">
         <is>
@@ -39757,7 +39753,7 @@
       </c>
       <c r="AC336" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD336" t="b">
@@ -39784,48 +39780,52 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>125670903</v>
+        <v>125671021</v>
       </c>
       <c r="B337" t="n">
-        <v>56843</v>
+        <v>57648</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E337" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I337" t="inlineStr"/>
+      <c r="K337" t="inlineStr"/>
+      <c r="L337" t="inlineStr"/>
+      <c r="M337" t="inlineStr"/>
+      <c r="N337" t="inlineStr"/>
       <c r="P337" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>520731</v>
+        <v>520607</v>
       </c>
       <c r="R337" t="n">
-        <v>6934042</v>
+        <v>6934048</v>
       </c>
       <c r="S337" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T337" t="inlineStr">
         <is>
@@ -39859,7 +39859,7 @@
       </c>
       <c r="AC337" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD337" t="b">
@@ -39886,32 +39886,32 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>125670916</v>
+        <v>125670903</v>
       </c>
       <c r="B338" t="n">
-        <v>80071</v>
+        <v>56843</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E338" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I338" t="inlineStr"/>
@@ -39921,10 +39921,10 @@
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>520803</v>
+        <v>520731</v>
       </c>
       <c r="R338" t="n">
-        <v>6933448</v>
+        <v>6934042</v>
       </c>
       <c r="S338" t="n">
         <v>25</v>
@@ -39957,6 +39957,11 @@
       <c r="AA338" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC338" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD338" t="b">
@@ -39983,32 +39988,32 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>125670909</v>
+        <v>125670921</v>
       </c>
       <c r="B339" t="n">
-        <v>80071</v>
+        <v>92522</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E339" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I339" t="inlineStr"/>
@@ -40018,10 +40023,10 @@
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>520754</v>
+        <v>520731</v>
       </c>
       <c r="R339" t="n">
-        <v>6934006</v>
+        <v>6934038</v>
       </c>
       <c r="S339" t="n">
         <v>25</v>
@@ -40054,11 +40059,6 @@
       <c r="AA339" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC339" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD339" t="b">
@@ -40085,32 +40085,32 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>125659270</v>
+        <v>125661442</v>
       </c>
       <c r="B340" t="n">
-        <v>92518</v>
+        <v>78639</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E340" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I340" t="inlineStr"/>
@@ -40120,10 +40120,10 @@
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>520846</v>
+        <v>520629</v>
       </c>
       <c r="R340" t="n">
-        <v>6933515</v>
+        <v>6933514</v>
       </c>
       <c r="S340" t="n">
         <v>20</v>
@@ -40182,32 +40182,32 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>125661442</v>
+        <v>125659270</v>
       </c>
       <c r="B341" t="n">
-        <v>78635</v>
+        <v>92522</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E341" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I341" t="inlineStr"/>
@@ -40217,10 +40217,10 @@
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>520629</v>
+        <v>520846</v>
       </c>
       <c r="R341" t="n">
-        <v>6933514</v>
+        <v>6933515</v>
       </c>
       <c r="S341" t="n">
         <v>20</v>
@@ -40279,10 +40279,10 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>125671469</v>
+        <v>125660155</v>
       </c>
       <c r="B342" t="n">
-        <v>80071</v>
+        <v>78731</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -40290,40 +40290,37 @@
         </is>
       </c>
       <c r="E342" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I342" t="inlineStr"/>
-      <c r="J342" t="inlineStr"/>
-      <c r="K342" t="inlineStr"/>
-      <c r="N342" t="inlineStr"/>
       <c r="P342" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>520296</v>
+        <v>520786</v>
       </c>
       <c r="R342" t="n">
-        <v>6933639</v>
+        <v>6933540</v>
       </c>
       <c r="S342" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T342" t="inlineStr">
         <is>
@@ -40361,7 +40358,6 @@
       <c r="AE342" t="b">
         <v>0</v>
       </c>
-      <c r="AF342" t="inlineStr"/>
       <c r="AG342" t="b">
         <v>0</v>
       </c>
@@ -40380,10 +40376,10 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>125660155</v>
+        <v>125671469</v>
       </c>
       <c r="B343" t="n">
-        <v>78727</v>
+        <v>80075</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -40391,37 +40387,40 @@
         </is>
       </c>
       <c r="E343" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I343" t="inlineStr"/>
+      <c r="J343" t="inlineStr"/>
+      <c r="K343" t="inlineStr"/>
+      <c r="N343" t="inlineStr"/>
       <c r="P343" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>520786</v>
+        <v>520296</v>
       </c>
       <c r="R343" t="n">
-        <v>6933540</v>
+        <v>6933639</v>
       </c>
       <c r="S343" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T343" t="inlineStr">
         <is>
@@ -40459,6 +40458,7 @@
       <c r="AE343" t="b">
         <v>0</v>
       </c>
+      <c r="AF343" t="inlineStr"/>
       <c r="AG343" t="b">
         <v>0</v>
       </c>
@@ -40480,7 +40480,7 @@
         <v>125670923</v>
       </c>
       <c r="B344" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -40577,7 +40577,7 @@
         <v>125662204</v>
       </c>
       <c r="B345" t="n">
-        <v>91389</v>
+        <v>91393</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -40674,7 +40674,7 @@
         <v>125659251</v>
       </c>
       <c r="B346" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -40771,7 +40771,7 @@
         <v>125670910</v>
       </c>
       <c r="B347" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -40868,7 +40868,7 @@
         <v>125670905</v>
       </c>
       <c r="B348" t="n">
-        <v>80072</v>
+        <v>80076</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -40965,7 +40965,7 @@
         <v>125671342</v>
       </c>
       <c r="B349" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -41067,7 +41067,7 @@
         <v>125670917</v>
       </c>
       <c r="B350" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -41267,48 +41267,52 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>125670901</v>
+        <v>125671230</v>
       </c>
       <c r="B352" t="n">
-        <v>91228</v>
+        <v>98359</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E352" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I352" t="inlineStr"/>
+      <c r="J352" t="inlineStr"/>
+      <c r="K352" t="inlineStr"/>
+      <c r="L352" t="inlineStr"/>
+      <c r="N352" t="inlineStr"/>
       <c r="P352" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q352" t="n">
-        <v>520257</v>
+        <v>520549</v>
       </c>
       <c r="R352" t="n">
-        <v>6933643</v>
+        <v>6934058</v>
       </c>
       <c r="S352" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T352" t="inlineStr">
         <is>
@@ -41346,6 +41350,7 @@
       <c r="AE352" t="b">
         <v>0</v>
       </c>
+      <c r="AF352" t="inlineStr"/>
       <c r="AG352" t="b">
         <v>0</v>
       </c>
@@ -41364,10 +41369,10 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>125671498</v>
+        <v>125670901</v>
       </c>
       <c r="B353" t="n">
-        <v>80071</v>
+        <v>91232</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -41375,37 +41380,34 @@
         </is>
       </c>
       <c r="E353" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I353" t="inlineStr"/>
-      <c r="J353" t="inlineStr"/>
-      <c r="K353" t="inlineStr"/>
-      <c r="N353" t="inlineStr"/>
       <c r="P353" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q353" t="n">
-        <v>520385</v>
+        <v>520257</v>
       </c>
       <c r="R353" t="n">
-        <v>6933569</v>
+        <v>6933643</v>
       </c>
       <c r="S353" t="n">
         <v>25</v>
@@ -41446,7 +41448,6 @@
       <c r="AE353" t="b">
         <v>0</v>
       </c>
-      <c r="AF353" t="inlineStr"/>
       <c r="AG353" t="b">
         <v>0</v>
       </c>
@@ -41465,10 +41466,10 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>125671434</v>
+        <v>125671498</v>
       </c>
       <c r="B354" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -41503,13 +41504,13 @@
         </is>
       </c>
       <c r="Q354" t="n">
-        <v>520364</v>
+        <v>520385</v>
       </c>
       <c r="R354" t="n">
-        <v>6934008</v>
+        <v>6933569</v>
       </c>
       <c r="S354" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T354" t="inlineStr">
         <is>
@@ -41566,10 +41567,10 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>125661680</v>
+        <v>125671434</v>
       </c>
       <c r="B355" t="n">
-        <v>79586</v>
+        <v>80075</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -41577,37 +41578,40 @@
         </is>
       </c>
       <c r="E355" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I355" t="inlineStr"/>
+      <c r="J355" t="inlineStr"/>
+      <c r="K355" t="inlineStr"/>
+      <c r="N355" t="inlineStr"/>
       <c r="P355" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q355" t="n">
-        <v>520639</v>
+        <v>520364</v>
       </c>
       <c r="R355" t="n">
-        <v>6933509</v>
+        <v>6934008</v>
       </c>
       <c r="S355" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T355" t="inlineStr">
         <is>
@@ -41645,6 +41649,7 @@
       <c r="AE355" t="b">
         <v>0</v>
       </c>
+      <c r="AF355" t="inlineStr"/>
       <c r="AG355" t="b">
         <v>0</v>
       </c>
@@ -41663,52 +41668,48 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>125671230</v>
+        <v>125661680</v>
       </c>
       <c r="B356" t="n">
-        <v>98355</v>
+        <v>79590</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E356" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I356" t="inlineStr"/>
-      <c r="J356" t="inlineStr"/>
-      <c r="K356" t="inlineStr"/>
-      <c r="L356" t="inlineStr"/>
-      <c r="N356" t="inlineStr"/>
       <c r="P356" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q356" t="n">
-        <v>520549</v>
+        <v>520639</v>
       </c>
       <c r="R356" t="n">
-        <v>6934058</v>
+        <v>6933509</v>
       </c>
       <c r="S356" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T356" t="inlineStr">
         <is>
@@ -41746,7 +41747,6 @@
       <c r="AE356" t="b">
         <v>0</v>
       </c>
-      <c r="AF356" t="inlineStr"/>
       <c r="AG356" t="b">
         <v>0</v>
       </c>
@@ -41768,7 +41768,7 @@
         <v>125659241</v>
       </c>
       <c r="B357" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>125670913</v>
       </c>
       <c r="B358" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>125671278</v>
       </c>
       <c r="B359" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -42063,7 +42063,7 @@
         <v>125671098</v>
       </c>
       <c r="B360" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -42164,7 +42164,7 @@
         <v>125660786</v>
       </c>
       <c r="B361" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -42261,7 +42261,7 @@
         <v>125671157</v>
       </c>
       <c r="B362" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -42363,7 +42363,7 @@
         <v>125670920</v>
       </c>
       <c r="B363" t="n">
-        <v>105358</v>
+        <v>105362</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -39581,32 +39581,32 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>125670916</v>
+        <v>125670921</v>
       </c>
       <c r="B335" t="n">
-        <v>80075</v>
+        <v>92522</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E335" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I335" t="inlineStr"/>
@@ -39616,10 +39616,10 @@
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>520803</v>
+        <v>520731</v>
       </c>
       <c r="R335" t="n">
-        <v>6933448</v>
+        <v>6934038</v>
       </c>
       <c r="S335" t="n">
         <v>25</v>
@@ -39678,32 +39678,32 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>125670909</v>
+        <v>125670903</v>
       </c>
       <c r="B336" t="n">
-        <v>80075</v>
+        <v>56843</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E336" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I336" t="inlineStr"/>
@@ -39713,10 +39713,10 @@
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>520754</v>
+        <v>520731</v>
       </c>
       <c r="R336" t="n">
-        <v>6934006</v>
+        <v>6934042</v>
       </c>
       <c r="S336" t="n">
         <v>25</v>
@@ -39753,7 +39753,7 @@
       </c>
       <c r="AC336" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD336" t="b">
@@ -39780,10 +39780,10 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>125671021</v>
+        <v>125670916</v>
       </c>
       <c r="B337" t="n">
-        <v>57648</v>
+        <v>80075</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -39791,41 +39791,37 @@
         </is>
       </c>
       <c r="E337" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I337" t="inlineStr"/>
-      <c r="K337" t="inlineStr"/>
-      <c r="L337" t="inlineStr"/>
-      <c r="M337" t="inlineStr"/>
-      <c r="N337" t="inlineStr"/>
       <c r="P337" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>520607</v>
+        <v>520803</v>
       </c>
       <c r="R337" t="n">
-        <v>6934048</v>
+        <v>6933448</v>
       </c>
       <c r="S337" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T337" t="inlineStr">
         <is>
@@ -39855,11 +39851,6 @@
       <c r="AA337" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC337" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD337" t="b">
@@ -39886,32 +39877,32 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>125670903</v>
+        <v>125670909</v>
       </c>
       <c r="B338" t="n">
-        <v>56843</v>
+        <v>80075</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E338" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I338" t="inlineStr"/>
@@ -39921,10 +39912,10 @@
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>520731</v>
+        <v>520754</v>
       </c>
       <c r="R338" t="n">
-        <v>6934042</v>
+        <v>6934006</v>
       </c>
       <c r="S338" t="n">
         <v>25</v>
@@ -39961,7 +39952,7 @@
       </c>
       <c r="AC338" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD338" t="b">
@@ -39988,48 +39979,52 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>125670921</v>
+        <v>125671021</v>
       </c>
       <c r="B339" t="n">
-        <v>92522</v>
+        <v>57648</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E339" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I339" t="inlineStr"/>
+      <c r="K339" t="inlineStr"/>
+      <c r="L339" t="inlineStr"/>
+      <c r="M339" t="inlineStr"/>
+      <c r="N339" t="inlineStr"/>
       <c r="P339" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>520731</v>
+        <v>520607</v>
       </c>
       <c r="R339" t="n">
-        <v>6934038</v>
+        <v>6934048</v>
       </c>
       <c r="S339" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T339" t="inlineStr">
         <is>
@@ -40059,6 +40054,11 @@
       <c r="AA339" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC339" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD339" t="b">

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -37713,7 +37713,7 @@
         <v>125670918</v>
       </c>
       <c r="B316" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -37807,48 +37807,48 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>125662951</v>
+        <v>125670904</v>
       </c>
       <c r="B317" t="n">
-        <v>80075</v>
+        <v>56843</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E317" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I317" t="inlineStr"/>
       <c r="P317" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q317" t="n">
-        <v>520358</v>
+        <v>520208</v>
       </c>
       <c r="R317" t="n">
-        <v>6933631</v>
+        <v>6933929</v>
       </c>
       <c r="S317" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T317" t="inlineStr">
         <is>
@@ -37878,11 +37878,6 @@
       <c r="AA317" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC317" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD317" t="b">
@@ -37909,48 +37904,48 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>125670904</v>
+        <v>125662951</v>
       </c>
       <c r="B318" t="n">
-        <v>56843</v>
+        <v>80075</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E318" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I318" t="inlineStr"/>
       <c r="P318" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q318" t="n">
-        <v>520208</v>
+        <v>520358</v>
       </c>
       <c r="R318" t="n">
-        <v>6933929</v>
+        <v>6933631</v>
       </c>
       <c r="S318" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T318" t="inlineStr">
         <is>
@@ -37980,6 +37975,11 @@
       <c r="AA318" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC318" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD318" t="b">
@@ -38006,10 +38006,10 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>125670912</v>
+        <v>125671391</v>
       </c>
       <c r="B319" t="n">
-        <v>80075</v>
+        <v>57811</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -38017,34 +38017,38 @@
         </is>
       </c>
       <c r="E319" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I319" t="inlineStr"/>
+      <c r="K319" t="inlineStr"/>
+      <c r="L319" t="inlineStr"/>
+      <c r="M319" t="inlineStr"/>
+      <c r="N319" t="inlineStr"/>
       <c r="P319" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>520757</v>
+        <v>520408</v>
       </c>
       <c r="R319" t="n">
-        <v>6934013</v>
+        <v>6934036</v>
       </c>
       <c r="S319" t="n">
         <v>25</v>
@@ -38103,10 +38107,10 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>125671391</v>
+        <v>125670912</v>
       </c>
       <c r="B320" t="n">
-        <v>57811</v>
+        <v>80075</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -38114,38 +38118,34 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I320" t="inlineStr"/>
-      <c r="K320" t="inlineStr"/>
-      <c r="L320" t="inlineStr"/>
-      <c r="M320" t="inlineStr"/>
-      <c r="N320" t="inlineStr"/>
       <c r="P320" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>520408</v>
+        <v>520757</v>
       </c>
       <c r="R320" t="n">
-        <v>6934036</v>
+        <v>6934013</v>
       </c>
       <c r="S320" t="n">
         <v>25</v>
@@ -38204,52 +38204,48 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>125671307</v>
+        <v>125661236</v>
       </c>
       <c r="B321" t="n">
-        <v>98338</v>
+        <v>43933</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>220787</v>
+        <v>101735</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I321" t="inlineStr"/>
-      <c r="J321" t="inlineStr"/>
-      <c r="K321" t="inlineStr"/>
-      <c r="L321" t="inlineStr"/>
-      <c r="N321" t="inlineStr"/>
       <c r="P321" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>520477</v>
+        <v>520684</v>
       </c>
       <c r="R321" t="n">
-        <v>6934031</v>
+        <v>6933537</v>
       </c>
       <c r="S321" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T321" t="inlineStr">
         <is>
@@ -38281,13 +38277,17 @@
           <t>2025-06-03</t>
         </is>
       </c>
+      <c r="AC321" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
+        </is>
+      </c>
       <c r="AD321" t="b">
         <v>0</v>
       </c>
       <c r="AE321" t="b">
         <v>0</v>
       </c>
-      <c r="AF321" t="inlineStr"/>
       <c r="AG321" t="b">
         <v>0</v>
       </c>
@@ -38306,48 +38306,52 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>125660766</v>
+        <v>125671307</v>
       </c>
       <c r="B322" t="n">
-        <v>79590</v>
+        <v>98339</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I322" t="inlineStr"/>
+      <c r="J322" t="inlineStr"/>
+      <c r="K322" t="inlineStr"/>
+      <c r="L322" t="inlineStr"/>
+      <c r="N322" t="inlineStr"/>
       <c r="P322" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>520729</v>
+        <v>520477</v>
       </c>
       <c r="R322" t="n">
-        <v>6933543</v>
+        <v>6934031</v>
       </c>
       <c r="S322" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T322" t="inlineStr">
         <is>
@@ -38385,6 +38389,7 @@
       <c r="AE322" t="b">
         <v>0</v>
       </c>
+      <c r="AF322" t="inlineStr"/>
       <c r="AG322" t="b">
         <v>0</v>
       </c>
@@ -38403,32 +38408,32 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>125661236</v>
+        <v>125660766</v>
       </c>
       <c r="B323" t="n">
-        <v>43933</v>
+        <v>79590</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>101735</v>
+        <v>6453</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I323" t="inlineStr"/>
@@ -38438,10 +38443,10 @@
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>520684</v>
+        <v>520729</v>
       </c>
       <c r="R323" t="n">
-        <v>6933537</v>
+        <v>6933543</v>
       </c>
       <c r="S323" t="n">
         <v>20</v>
@@ -38474,11 +38479,6 @@
       <c r="AA323" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC323" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD323" t="b">
@@ -38505,32 +38505,32 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>125670924</v>
+        <v>125670919</v>
       </c>
       <c r="B324" t="n">
-        <v>92522</v>
+        <v>98339</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I324" t="inlineStr"/>
@@ -38540,10 +38540,10 @@
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>520194</v>
+        <v>520223</v>
       </c>
       <c r="R324" t="n">
-        <v>6933813</v>
+        <v>6933684</v>
       </c>
       <c r="S324" t="n">
         <v>25</v>
@@ -38605,7 +38605,7 @@
         <v>125661898</v>
       </c>
       <c r="B325" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -38699,48 +38699,48 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>125670919</v>
+        <v>125663906</v>
       </c>
       <c r="B326" t="n">
-        <v>98338</v>
+        <v>80075</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E326" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I326" t="inlineStr"/>
       <c r="P326" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q326" t="n">
-        <v>520223</v>
+        <v>520184</v>
       </c>
       <c r="R326" t="n">
-        <v>6933684</v>
+        <v>6933765</v>
       </c>
       <c r="S326" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T326" t="inlineStr">
         <is>
@@ -38893,48 +38893,48 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>125663906</v>
+        <v>125670924</v>
       </c>
       <c r="B328" t="n">
-        <v>80075</v>
+        <v>92522</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I328" t="inlineStr"/>
       <c r="P328" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>520184</v>
+        <v>520194</v>
       </c>
       <c r="R328" t="n">
-        <v>6933765</v>
+        <v>6933813</v>
       </c>
       <c r="S328" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T328" t="inlineStr">
         <is>
@@ -39193,32 +39193,32 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>125670914</v>
+        <v>125670922</v>
       </c>
       <c r="B331" t="n">
-        <v>80075</v>
+        <v>92522</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I331" t="inlineStr"/>
@@ -39228,10 +39228,10 @@
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>520224</v>
+        <v>520637</v>
       </c>
       <c r="R331" t="n">
-        <v>6933690</v>
+        <v>6934037</v>
       </c>
       <c r="S331" t="n">
         <v>25</v>
@@ -39290,32 +39290,32 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>125670922</v>
+        <v>125670914</v>
       </c>
       <c r="B332" t="n">
-        <v>92522</v>
+        <v>80075</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I332" t="inlineStr"/>
@@ -39325,10 +39325,10 @@
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>520637</v>
+        <v>520224</v>
       </c>
       <c r="R332" t="n">
-        <v>6934037</v>
+        <v>6933690</v>
       </c>
       <c r="S332" t="n">
         <v>25</v>
@@ -39581,48 +39581,52 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>125670921</v>
+        <v>125671021</v>
       </c>
       <c r="B335" t="n">
-        <v>92522</v>
+        <v>57648</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E335" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I335" t="inlineStr"/>
+      <c r="K335" t="inlineStr"/>
+      <c r="L335" t="inlineStr"/>
+      <c r="M335" t="inlineStr"/>
+      <c r="N335" t="inlineStr"/>
       <c r="P335" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>520731</v>
+        <v>520607</v>
       </c>
       <c r="R335" t="n">
-        <v>6934038</v>
+        <v>6934048</v>
       </c>
       <c r="S335" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T335" t="inlineStr">
         <is>
@@ -39652,6 +39656,11 @@
       <c r="AA335" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC335" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD335" t="b">
@@ -39780,32 +39789,32 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>125670916</v>
+        <v>125670921</v>
       </c>
       <c r="B337" t="n">
-        <v>80075</v>
+        <v>92522</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E337" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I337" t="inlineStr"/>
@@ -39815,10 +39824,10 @@
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>520803</v>
+        <v>520731</v>
       </c>
       <c r="R337" t="n">
-        <v>6933448</v>
+        <v>6934038</v>
       </c>
       <c r="S337" t="n">
         <v>25</v>
@@ -39979,10 +39988,10 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>125671021</v>
+        <v>125670916</v>
       </c>
       <c r="B339" t="n">
-        <v>57648</v>
+        <v>80075</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -39990,41 +39999,37 @@
         </is>
       </c>
       <c r="E339" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I339" t="inlineStr"/>
-      <c r="K339" t="inlineStr"/>
-      <c r="L339" t="inlineStr"/>
-      <c r="M339" t="inlineStr"/>
-      <c r="N339" t="inlineStr"/>
       <c r="P339" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>520607</v>
+        <v>520803</v>
       </c>
       <c r="R339" t="n">
-        <v>6934048</v>
+        <v>6933448</v>
       </c>
       <c r="S339" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T339" t="inlineStr">
         <is>
@@ -40054,11 +40059,6 @@
       <c r="AA339" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC339" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD339" t="b">
@@ -40085,32 +40085,32 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>125661442</v>
+        <v>125659270</v>
       </c>
       <c r="B340" t="n">
-        <v>78639</v>
+        <v>92522</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E340" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I340" t="inlineStr"/>
@@ -40120,10 +40120,10 @@
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>520629</v>
+        <v>520846</v>
       </c>
       <c r="R340" t="n">
-        <v>6933514</v>
+        <v>6933515</v>
       </c>
       <c r="S340" t="n">
         <v>20</v>
@@ -40182,48 +40182,51 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>125659270</v>
+        <v>125671469</v>
       </c>
       <c r="B341" t="n">
-        <v>92522</v>
+        <v>80075</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E341" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I341" t="inlineStr"/>
+      <c r="J341" t="inlineStr"/>
+      <c r="K341" t="inlineStr"/>
+      <c r="N341" t="inlineStr"/>
       <c r="P341" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>520846</v>
+        <v>520296</v>
       </c>
       <c r="R341" t="n">
-        <v>6933515</v>
+        <v>6933639</v>
       </c>
       <c r="S341" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T341" t="inlineStr">
         <is>
@@ -40261,6 +40264,7 @@
       <c r="AE341" t="b">
         <v>0</v>
       </c>
+      <c r="AF341" t="inlineStr"/>
       <c r="AG341" t="b">
         <v>0</v>
       </c>
@@ -40279,10 +40283,10 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>125660155</v>
+        <v>125661442</v>
       </c>
       <c r="B342" t="n">
-        <v>78731</v>
+        <v>78639</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -40290,21 +40294,21 @@
         </is>
       </c>
       <c r="E342" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I342" t="inlineStr"/>
@@ -40314,10 +40318,10 @@
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>520786</v>
+        <v>520629</v>
       </c>
       <c r="R342" t="n">
-        <v>6933540</v>
+        <v>6933514</v>
       </c>
       <c r="S342" t="n">
         <v>20</v>
@@ -40376,10 +40380,10 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>125671469</v>
+        <v>125660155</v>
       </c>
       <c r="B343" t="n">
-        <v>80075</v>
+        <v>78731</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -40387,40 +40391,37 @@
         </is>
       </c>
       <c r="E343" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I343" t="inlineStr"/>
-      <c r="J343" t="inlineStr"/>
-      <c r="K343" t="inlineStr"/>
-      <c r="N343" t="inlineStr"/>
       <c r="P343" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>520296</v>
+        <v>520786</v>
       </c>
       <c r="R343" t="n">
-        <v>6933639</v>
+        <v>6933540</v>
       </c>
       <c r="S343" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T343" t="inlineStr">
         <is>
@@ -40458,7 +40459,6 @@
       <c r="AE343" t="b">
         <v>0</v>
       </c>
-      <c r="AF343" t="inlineStr"/>
       <c r="AG343" t="b">
         <v>0</v>
       </c>
@@ -40574,48 +40574,48 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>125662204</v>
+        <v>125670910</v>
       </c>
       <c r="B345" t="n">
-        <v>91393</v>
+        <v>80075</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E345" t="n">
-        <v>1503</v>
+        <v>6458</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I345" t="inlineStr"/>
       <c r="P345" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q345" t="n">
-        <v>520425</v>
+        <v>520830</v>
       </c>
       <c r="R345" t="n">
-        <v>6933544</v>
+        <v>6933884</v>
       </c>
       <c r="S345" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T345" t="inlineStr">
         <is>
@@ -40768,10 +40768,10 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>125670910</v>
+        <v>125670905</v>
       </c>
       <c r="B347" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -40779,21 +40779,21 @@
         </is>
       </c>
       <c r="E347" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I347" t="inlineStr"/>
@@ -40803,10 +40803,10 @@
         </is>
       </c>
       <c r="Q347" t="n">
-        <v>520830</v>
+        <v>520801</v>
       </c>
       <c r="R347" t="n">
-        <v>6933884</v>
+        <v>6933448</v>
       </c>
       <c r="S347" t="n">
         <v>25</v>
@@ -40865,48 +40865,48 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>125670905</v>
+        <v>125662204</v>
       </c>
       <c r="B348" t="n">
-        <v>80076</v>
+        <v>91393</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E348" t="n">
-        <v>2081</v>
+        <v>1503</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I348" t="inlineStr"/>
       <c r="P348" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q348" t="n">
-        <v>520801</v>
+        <v>520425</v>
       </c>
       <c r="R348" t="n">
-        <v>6933448</v>
+        <v>6933544</v>
       </c>
       <c r="S348" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T348" t="inlineStr">
         <is>
@@ -40965,7 +40965,7 @@
         <v>125671342</v>
       </c>
       <c r="B349" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -41067,7 +41067,7 @@
         <v>125670917</v>
       </c>
       <c r="B350" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -41267,52 +41267,48 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>125671230</v>
+        <v>125670901</v>
       </c>
       <c r="B352" t="n">
-        <v>98359</v>
+        <v>91232</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E352" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I352" t="inlineStr"/>
-      <c r="J352" t="inlineStr"/>
-      <c r="K352" t="inlineStr"/>
-      <c r="L352" t="inlineStr"/>
-      <c r="N352" t="inlineStr"/>
       <c r="P352" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q352" t="n">
-        <v>520549</v>
+        <v>520257</v>
       </c>
       <c r="R352" t="n">
-        <v>6934058</v>
+        <v>6933643</v>
       </c>
       <c r="S352" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T352" t="inlineStr">
         <is>
@@ -41350,7 +41346,6 @@
       <c r="AE352" t="b">
         <v>0</v>
       </c>
-      <c r="AF352" t="inlineStr"/>
       <c r="AG352" t="b">
         <v>0</v>
       </c>
@@ -41369,10 +41364,10 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>125670901</v>
+        <v>125661680</v>
       </c>
       <c r="B353" t="n">
-        <v>91232</v>
+        <v>79590</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -41380,37 +41375,37 @@
         </is>
       </c>
       <c r="E353" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I353" t="inlineStr"/>
       <c r="P353" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q353" t="n">
-        <v>520257</v>
+        <v>520639</v>
       </c>
       <c r="R353" t="n">
-        <v>6933643</v>
+        <v>6933509</v>
       </c>
       <c r="S353" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T353" t="inlineStr">
         <is>
@@ -41668,48 +41663,52 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>125661680</v>
+        <v>125671230</v>
       </c>
       <c r="B356" t="n">
-        <v>79590</v>
+        <v>98360</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E356" t="n">
-        <v>6453</v>
+        <v>221952</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I356" t="inlineStr"/>
+      <c r="J356" t="inlineStr"/>
+      <c r="K356" t="inlineStr"/>
+      <c r="L356" t="inlineStr"/>
+      <c r="N356" t="inlineStr"/>
       <c r="P356" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q356" t="n">
-        <v>520639</v>
+        <v>520549</v>
       </c>
       <c r="R356" t="n">
-        <v>6933509</v>
+        <v>6934058</v>
       </c>
       <c r="S356" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T356" t="inlineStr">
         <is>
@@ -41747,6 +41746,7 @@
       <c r="AE356" t="b">
         <v>0</v>
       </c>
+      <c r="AF356" t="inlineStr"/>
       <c r="AG356" t="b">
         <v>0</v>
       </c>
@@ -41765,10 +41765,10 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>125659241</v>
+        <v>125670913</v>
       </c>
       <c r="B357" t="n">
-        <v>79590</v>
+        <v>80075</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -41776,37 +41776,37 @@
         </is>
       </c>
       <c r="E357" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I357" t="inlineStr"/>
       <c r="P357" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q357" t="n">
-        <v>520844</v>
+        <v>520620</v>
       </c>
       <c r="R357" t="n">
-        <v>6933514</v>
+        <v>6934070</v>
       </c>
       <c r="S357" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T357" t="inlineStr">
         <is>
@@ -41862,10 +41862,10 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>125670913</v>
+        <v>125659241</v>
       </c>
       <c r="B358" t="n">
-        <v>80075</v>
+        <v>79590</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -41873,37 +41873,37 @@
         </is>
       </c>
       <c r="E358" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I358" t="inlineStr"/>
       <c r="P358" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q358" t="n">
-        <v>520620</v>
+        <v>520844</v>
       </c>
       <c r="R358" t="n">
-        <v>6934070</v>
+        <v>6933514</v>
       </c>
       <c r="S358" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T358" t="inlineStr">
         <is>
@@ -41959,10 +41959,10 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>125671278</v>
+        <v>125660786</v>
       </c>
       <c r="B359" t="n">
-        <v>80075</v>
+        <v>78730</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -41970,40 +41970,37 @@
         </is>
       </c>
       <c r="E359" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I359" t="inlineStr"/>
-      <c r="J359" t="inlineStr"/>
-      <c r="K359" t="inlineStr"/>
-      <c r="N359" t="inlineStr"/>
       <c r="P359" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q359" t="n">
-        <v>520511</v>
+        <v>520731</v>
       </c>
       <c r="R359" t="n">
-        <v>6934025</v>
+        <v>6933528</v>
       </c>
       <c r="S359" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T359" t="inlineStr">
         <is>
@@ -42041,7 +42038,6 @@
       <c r="AE359" t="b">
         <v>0</v>
       </c>
-      <c r="AF359" t="inlineStr"/>
       <c r="AG359" t="b">
         <v>0</v>
       </c>
@@ -42060,7 +42056,7 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>125671098</v>
+        <v>125671278</v>
       </c>
       <c r="B360" t="n">
         <v>80075</v>
@@ -42098,10 +42094,10 @@
         </is>
       </c>
       <c r="Q360" t="n">
-        <v>520578</v>
+        <v>520511</v>
       </c>
       <c r="R360" t="n">
-        <v>6934069</v>
+        <v>6934025</v>
       </c>
       <c r="S360" t="n">
         <v>10</v>
@@ -42161,10 +42157,10 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>125660786</v>
+        <v>125671098</v>
       </c>
       <c r="B361" t="n">
-        <v>78730</v>
+        <v>80075</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -42172,37 +42168,40 @@
         </is>
       </c>
       <c r="E361" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I361" t="inlineStr"/>
+      <c r="J361" t="inlineStr"/>
+      <c r="K361" t="inlineStr"/>
+      <c r="N361" t="inlineStr"/>
       <c r="P361" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q361" t="n">
-        <v>520731</v>
+        <v>520578</v>
       </c>
       <c r="R361" t="n">
-        <v>6933528</v>
+        <v>6934069</v>
       </c>
       <c r="S361" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T361" t="inlineStr">
         <is>
@@ -42240,6 +42239,7 @@
       <c r="AE361" t="b">
         <v>0</v>
       </c>
+      <c r="AF361" t="inlineStr"/>
       <c r="AG361" t="b">
         <v>0</v>
       </c>
@@ -42261,7 +42261,7 @@
         <v>125671157</v>
       </c>
       <c r="B362" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -42363,7 +42363,7 @@
         <v>125670920</v>
       </c>
       <c r="B363" t="n">
-        <v>105362</v>
+        <v>105363</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -39581,52 +39581,48 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>125671021</v>
+        <v>125670921</v>
       </c>
       <c r="B335" t="n">
-        <v>57648</v>
+        <v>92522</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E335" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I335" t="inlineStr"/>
-      <c r="K335" t="inlineStr"/>
-      <c r="L335" t="inlineStr"/>
-      <c r="M335" t="inlineStr"/>
-      <c r="N335" t="inlineStr"/>
       <c r="P335" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>520607</v>
+        <v>520731</v>
       </c>
       <c r="R335" t="n">
-        <v>6934048</v>
+        <v>6934038</v>
       </c>
       <c r="S335" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T335" t="inlineStr">
         <is>
@@ -39656,11 +39652,6 @@
       <c r="AA335" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC335" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD335" t="b">
@@ -39687,32 +39678,32 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>125670903</v>
+        <v>125670909</v>
       </c>
       <c r="B336" t="n">
-        <v>56843</v>
+        <v>80075</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E336" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I336" t="inlineStr"/>
@@ -39722,10 +39713,10 @@
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>520731</v>
+        <v>520754</v>
       </c>
       <c r="R336" t="n">
-        <v>6934042</v>
+        <v>6934006</v>
       </c>
       <c r="S336" t="n">
         <v>25</v>
@@ -39762,7 +39753,7 @@
       </c>
       <c r="AC336" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD336" t="b">
@@ -39789,32 +39780,32 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>125670921</v>
+        <v>125670916</v>
       </c>
       <c r="B337" t="n">
-        <v>92522</v>
+        <v>80075</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E337" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I337" t="inlineStr"/>
@@ -39824,10 +39815,10 @@
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>520731</v>
+        <v>520803</v>
       </c>
       <c r="R337" t="n">
-        <v>6934038</v>
+        <v>6933448</v>
       </c>
       <c r="S337" t="n">
         <v>25</v>
@@ -39886,10 +39877,10 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>125670909</v>
+        <v>125671021</v>
       </c>
       <c r="B338" t="n">
-        <v>80075</v>
+        <v>57648</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -39897,37 +39888,41 @@
         </is>
       </c>
       <c r="E338" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I338" t="inlineStr"/>
+      <c r="K338" t="inlineStr"/>
+      <c r="L338" t="inlineStr"/>
+      <c r="M338" t="inlineStr"/>
+      <c r="N338" t="inlineStr"/>
       <c r="P338" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>520754</v>
+        <v>520607</v>
       </c>
       <c r="R338" t="n">
-        <v>6934006</v>
+        <v>6934048</v>
       </c>
       <c r="S338" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T338" t="inlineStr">
         <is>
@@ -39961,7 +39956,7 @@
       </c>
       <c r="AC338" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD338" t="b">
@@ -39988,32 +39983,32 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>125670916</v>
+        <v>125670903</v>
       </c>
       <c r="B339" t="n">
-        <v>80075</v>
+        <v>56843</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E339" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I339" t="inlineStr"/>
@@ -40023,10 +40018,10 @@
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>520803</v>
+        <v>520731</v>
       </c>
       <c r="R339" t="n">
-        <v>6933448</v>
+        <v>6934042</v>
       </c>
       <c r="S339" t="n">
         <v>25</v>
@@ -40059,6 +40054,11 @@
       <c r="AA339" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC339" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD339" t="b">
@@ -41267,10 +41267,10 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>125670901</v>
+        <v>125661680</v>
       </c>
       <c r="B352" t="n">
-        <v>91232</v>
+        <v>79590</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -41278,37 +41278,37 @@
         </is>
       </c>
       <c r="E352" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I352" t="inlineStr"/>
       <c r="P352" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q352" t="n">
-        <v>520257</v>
+        <v>520639</v>
       </c>
       <c r="R352" t="n">
-        <v>6933643</v>
+        <v>6933509</v>
       </c>
       <c r="S352" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T352" t="inlineStr">
         <is>
@@ -41364,10 +41364,10 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>125661680</v>
+        <v>125671498</v>
       </c>
       <c r="B353" t="n">
-        <v>79590</v>
+        <v>80075</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -41375,37 +41375,40 @@
         </is>
       </c>
       <c r="E353" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I353" t="inlineStr"/>
+      <c r="J353" t="inlineStr"/>
+      <c r="K353" t="inlineStr"/>
+      <c r="N353" t="inlineStr"/>
       <c r="P353" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q353" t="n">
-        <v>520639</v>
+        <v>520385</v>
       </c>
       <c r="R353" t="n">
-        <v>6933509</v>
+        <v>6933569</v>
       </c>
       <c r="S353" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T353" t="inlineStr">
         <is>
@@ -41443,6 +41446,7 @@
       <c r="AE353" t="b">
         <v>0</v>
       </c>
+      <c r="AF353" t="inlineStr"/>
       <c r="AG353" t="b">
         <v>0</v>
       </c>
@@ -41461,7 +41465,7 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>125671498</v>
+        <v>125671434</v>
       </c>
       <c r="B354" t="n">
         <v>80075</v>
@@ -41499,13 +41503,13 @@
         </is>
       </c>
       <c r="Q354" t="n">
-        <v>520385</v>
+        <v>520364</v>
       </c>
       <c r="R354" t="n">
-        <v>6933569</v>
+        <v>6934008</v>
       </c>
       <c r="S354" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T354" t="inlineStr">
         <is>
@@ -41562,10 +41566,10 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>125671434</v>
+        <v>125670901</v>
       </c>
       <c r="B355" t="n">
-        <v>80075</v>
+        <v>91232</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -41573,40 +41577,37 @@
         </is>
       </c>
       <c r="E355" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I355" t="inlineStr"/>
-      <c r="J355" t="inlineStr"/>
-      <c r="K355" t="inlineStr"/>
-      <c r="N355" t="inlineStr"/>
       <c r="P355" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q355" t="n">
-        <v>520364</v>
+        <v>520257</v>
       </c>
       <c r="R355" t="n">
-        <v>6934008</v>
+        <v>6933643</v>
       </c>
       <c r="S355" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T355" t="inlineStr">
         <is>
@@ -41644,7 +41645,6 @@
       <c r="AE355" t="b">
         <v>0</v>
       </c>
-      <c r="AF355" t="inlineStr"/>
       <c r="AG355" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -38204,48 +38204,52 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>125661236</v>
+        <v>125671307</v>
       </c>
       <c r="B321" t="n">
-        <v>43933</v>
+        <v>98339</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>101735</v>
+        <v>220787</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I321" t="inlineStr"/>
+      <c r="J321" t="inlineStr"/>
+      <c r="K321" t="inlineStr"/>
+      <c r="L321" t="inlineStr"/>
+      <c r="N321" t="inlineStr"/>
       <c r="P321" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>520684</v>
+        <v>520477</v>
       </c>
       <c r="R321" t="n">
-        <v>6933537</v>
+        <v>6934031</v>
       </c>
       <c r="S321" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T321" t="inlineStr">
         <is>
@@ -38277,17 +38281,13 @@
           <t>2025-06-03</t>
         </is>
       </c>
-      <c r="AC321" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
-        </is>
-      </c>
       <c r="AD321" t="b">
         <v>0</v>
       </c>
       <c r="AE321" t="b">
         <v>0</v>
       </c>
+      <c r="AF321" t="inlineStr"/>
       <c r="AG321" t="b">
         <v>0</v>
       </c>
@@ -38306,52 +38306,48 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>125671307</v>
+        <v>125660766</v>
       </c>
       <c r="B322" t="n">
-        <v>98339</v>
+        <v>79590</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I322" t="inlineStr"/>
-      <c r="J322" t="inlineStr"/>
-      <c r="K322" t="inlineStr"/>
-      <c r="L322" t="inlineStr"/>
-      <c r="N322" t="inlineStr"/>
       <c r="P322" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>520477</v>
+        <v>520729</v>
       </c>
       <c r="R322" t="n">
-        <v>6934031</v>
+        <v>6933543</v>
       </c>
       <c r="S322" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T322" t="inlineStr">
         <is>
@@ -38389,7 +38385,6 @@
       <c r="AE322" t="b">
         <v>0</v>
       </c>
-      <c r="AF322" t="inlineStr"/>
       <c r="AG322" t="b">
         <v>0</v>
       </c>
@@ -38408,32 +38403,32 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>125660766</v>
+        <v>125661236</v>
       </c>
       <c r="B323" t="n">
-        <v>79590</v>
+        <v>43933</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>6453</v>
+        <v>101735</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I323" t="inlineStr"/>
@@ -38443,10 +38438,10 @@
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>520729</v>
+        <v>520684</v>
       </c>
       <c r="R323" t="n">
-        <v>6933543</v>
+        <v>6933537</v>
       </c>
       <c r="S323" t="n">
         <v>20</v>
@@ -38479,6 +38474,11 @@
       <c r="AA323" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC323" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD323" t="b">
@@ -38505,48 +38505,48 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>125670919</v>
+        <v>125663906</v>
       </c>
       <c r="B324" t="n">
-        <v>98339</v>
+        <v>80075</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I324" t="inlineStr"/>
       <c r="P324" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>520223</v>
+        <v>520184</v>
       </c>
       <c r="R324" t="n">
-        <v>6933684</v>
+        <v>6933765</v>
       </c>
       <c r="S324" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T324" t="inlineStr">
         <is>
@@ -38602,48 +38602,48 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>125661898</v>
+        <v>125670906</v>
       </c>
       <c r="B325" t="n">
-        <v>98339</v>
+        <v>79979</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E325" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I325" t="inlineStr"/>
       <c r="P325" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q325" t="n">
-        <v>520558</v>
+        <v>521033</v>
       </c>
       <c r="R325" t="n">
-        <v>6933556</v>
+        <v>6933394</v>
       </c>
       <c r="S325" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T325" t="inlineStr">
         <is>
@@ -38699,48 +38699,48 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>125663906</v>
+        <v>125670924</v>
       </c>
       <c r="B326" t="n">
-        <v>80075</v>
+        <v>92522</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E326" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I326" t="inlineStr"/>
       <c r="P326" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q326" t="n">
-        <v>520184</v>
+        <v>520194</v>
       </c>
       <c r="R326" t="n">
-        <v>6933765</v>
+        <v>6933813</v>
       </c>
       <c r="S326" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T326" t="inlineStr">
         <is>
@@ -38796,32 +38796,32 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>125670906</v>
+        <v>125670919</v>
       </c>
       <c r="B327" t="n">
-        <v>79979</v>
+        <v>98339</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I327" t="inlineStr"/>
@@ -38831,10 +38831,10 @@
         </is>
       </c>
       <c r="Q327" t="n">
-        <v>521033</v>
+        <v>520223</v>
       </c>
       <c r="R327" t="n">
-        <v>6933394</v>
+        <v>6933684</v>
       </c>
       <c r="S327" t="n">
         <v>25</v>
@@ -38893,48 +38893,48 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>125670924</v>
+        <v>125661898</v>
       </c>
       <c r="B328" t="n">
-        <v>92522</v>
+        <v>98339</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I328" t="inlineStr"/>
       <c r="P328" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>520194</v>
+        <v>520558</v>
       </c>
       <c r="R328" t="n">
-        <v>6933813</v>
+        <v>6933556</v>
       </c>
       <c r="S328" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T328" t="inlineStr">
         <is>
@@ -41267,10 +41267,10 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>125661680</v>
+        <v>125670901</v>
       </c>
       <c r="B352" t="n">
-        <v>79590</v>
+        <v>91232</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -41278,37 +41278,37 @@
         </is>
       </c>
       <c r="E352" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I352" t="inlineStr"/>
       <c r="P352" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q352" t="n">
-        <v>520639</v>
+        <v>520257</v>
       </c>
       <c r="R352" t="n">
-        <v>6933509</v>
+        <v>6933643</v>
       </c>
       <c r="S352" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T352" t="inlineStr">
         <is>
@@ -41364,10 +41364,10 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>125671498</v>
+        <v>125661680</v>
       </c>
       <c r="B353" t="n">
-        <v>80075</v>
+        <v>79590</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -41375,40 +41375,37 @@
         </is>
       </c>
       <c r="E353" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I353" t="inlineStr"/>
-      <c r="J353" t="inlineStr"/>
-      <c r="K353" t="inlineStr"/>
-      <c r="N353" t="inlineStr"/>
       <c r="P353" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q353" t="n">
-        <v>520385</v>
+        <v>520639</v>
       </c>
       <c r="R353" t="n">
-        <v>6933569</v>
+        <v>6933509</v>
       </c>
       <c r="S353" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T353" t="inlineStr">
         <is>
@@ -41446,7 +41443,6 @@
       <c r="AE353" t="b">
         <v>0</v>
       </c>
-      <c r="AF353" t="inlineStr"/>
       <c r="AG353" t="b">
         <v>0</v>
       </c>
@@ -41465,7 +41461,7 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>125671434</v>
+        <v>125671498</v>
       </c>
       <c r="B354" t="n">
         <v>80075</v>
@@ -41503,13 +41499,13 @@
         </is>
       </c>
       <c r="Q354" t="n">
-        <v>520364</v>
+        <v>520385</v>
       </c>
       <c r="R354" t="n">
-        <v>6934008</v>
+        <v>6933569</v>
       </c>
       <c r="S354" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T354" t="inlineStr">
         <is>
@@ -41566,10 +41562,10 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>125670901</v>
+        <v>125671434</v>
       </c>
       <c r="B355" t="n">
-        <v>91232</v>
+        <v>80075</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -41577,37 +41573,40 @@
         </is>
       </c>
       <c r="E355" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I355" t="inlineStr"/>
+      <c r="J355" t="inlineStr"/>
+      <c r="K355" t="inlineStr"/>
+      <c r="N355" t="inlineStr"/>
       <c r="P355" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q355" t="n">
-        <v>520257</v>
+        <v>520364</v>
       </c>
       <c r="R355" t="n">
-        <v>6933643</v>
+        <v>6934008</v>
       </c>
       <c r="S355" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T355" t="inlineStr">
         <is>
@@ -41645,6 +41644,7 @@
       <c r="AE355" t="b">
         <v>0</v>
       </c>
+      <c r="AF355" t="inlineStr"/>
       <c r="AG355" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -37713,7 +37713,7 @@
         <v>125670918</v>
       </c>
       <c r="B316" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -37807,48 +37807,48 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>125670904</v>
+        <v>125662951</v>
       </c>
       <c r="B317" t="n">
-        <v>56843</v>
+        <v>80076</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E317" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I317" t="inlineStr"/>
       <c r="P317" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q317" t="n">
-        <v>520208</v>
+        <v>520358</v>
       </c>
       <c r="R317" t="n">
-        <v>6933929</v>
+        <v>6933631</v>
       </c>
       <c r="S317" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T317" t="inlineStr">
         <is>
@@ -37878,6 +37878,11 @@
       <c r="AA317" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC317" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD317" t="b">
@@ -37904,48 +37909,48 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>125662951</v>
+        <v>125670904</v>
       </c>
       <c r="B318" t="n">
-        <v>80075</v>
+        <v>56844</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E318" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I318" t="inlineStr"/>
       <c r="P318" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q318" t="n">
-        <v>520358</v>
+        <v>520208</v>
       </c>
       <c r="R318" t="n">
-        <v>6933631</v>
+        <v>6933929</v>
       </c>
       <c r="S318" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T318" t="inlineStr">
         <is>
@@ -37975,11 +37980,6 @@
       <c r="AA318" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC318" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD318" t="b">
@@ -38009,7 +38009,7 @@
         <v>125671391</v>
       </c>
       <c r="B319" t="n">
-        <v>57811</v>
+        <v>57812</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -38110,7 +38110,7 @@
         <v>125670912</v>
       </c>
       <c r="B320" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -38204,52 +38204,48 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>125671307</v>
+        <v>125660766</v>
       </c>
       <c r="B321" t="n">
-        <v>98339</v>
+        <v>79591</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I321" t="inlineStr"/>
-      <c r="J321" t="inlineStr"/>
-      <c r="K321" t="inlineStr"/>
-      <c r="L321" t="inlineStr"/>
-      <c r="N321" t="inlineStr"/>
       <c r="P321" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>520477</v>
+        <v>520729</v>
       </c>
       <c r="R321" t="n">
-        <v>6934031</v>
+        <v>6933543</v>
       </c>
       <c r="S321" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T321" t="inlineStr">
         <is>
@@ -38287,7 +38283,6 @@
       <c r="AE321" t="b">
         <v>0</v>
       </c>
-      <c r="AF321" t="inlineStr"/>
       <c r="AG321" t="b">
         <v>0</v>
       </c>
@@ -38306,32 +38301,32 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>125660766</v>
+        <v>125661236</v>
       </c>
       <c r="B322" t="n">
-        <v>79590</v>
+        <v>43934</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>6453</v>
+        <v>101735</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I322" t="inlineStr"/>
@@ -38341,10 +38336,10 @@
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>520729</v>
+        <v>520684</v>
       </c>
       <c r="R322" t="n">
-        <v>6933543</v>
+        <v>6933537</v>
       </c>
       <c r="S322" t="n">
         <v>20</v>
@@ -38377,6 +38372,11 @@
       <c r="AA322" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC322" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD322" t="b">
@@ -38403,48 +38403,52 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>125661236</v>
+        <v>125671307</v>
       </c>
       <c r="B323" t="n">
-        <v>43933</v>
+        <v>98341</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>101735</v>
+        <v>220787</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I323" t="inlineStr"/>
+      <c r="J323" t="inlineStr"/>
+      <c r="K323" t="inlineStr"/>
+      <c r="L323" t="inlineStr"/>
+      <c r="N323" t="inlineStr"/>
       <c r="P323" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>520684</v>
+        <v>520477</v>
       </c>
       <c r="R323" t="n">
-        <v>6933537</v>
+        <v>6934031</v>
       </c>
       <c r="S323" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T323" t="inlineStr">
         <is>
@@ -38476,17 +38480,13 @@
           <t>2025-06-03</t>
         </is>
       </c>
-      <c r="AC323" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
-        </is>
-      </c>
       <c r="AD323" t="b">
         <v>0</v>
       </c>
       <c r="AE323" t="b">
         <v>0</v>
       </c>
+      <c r="AF323" t="inlineStr"/>
       <c r="AG323" t="b">
         <v>0</v>
       </c>
@@ -38505,48 +38505,48 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>125663906</v>
+        <v>125670906</v>
       </c>
       <c r="B324" t="n">
-        <v>80075</v>
+        <v>79980</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I324" t="inlineStr"/>
       <c r="P324" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>520184</v>
+        <v>521033</v>
       </c>
       <c r="R324" t="n">
-        <v>6933765</v>
+        <v>6933394</v>
       </c>
       <c r="S324" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T324" t="inlineStr">
         <is>
@@ -38602,48 +38602,48 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>125670906</v>
+        <v>125663906</v>
       </c>
       <c r="B325" t="n">
-        <v>79979</v>
+        <v>80076</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E325" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I325" t="inlineStr"/>
       <c r="P325" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q325" t="n">
-        <v>521033</v>
+        <v>520184</v>
       </c>
       <c r="R325" t="n">
-        <v>6933394</v>
+        <v>6933765</v>
       </c>
       <c r="S325" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T325" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>125670924</v>
       </c>
       <c r="B326" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -38799,7 +38799,7 @@
         <v>125670919</v>
       </c>
       <c r="B327" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -38896,7 +38896,7 @@
         <v>125661898</v>
       </c>
       <c r="B328" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -38993,7 +38993,7 @@
         <v>125670908</v>
       </c>
       <c r="B329" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -39092,51 +39092,48 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>125671054</v>
+        <v>125670922</v>
       </c>
       <c r="B330" t="n">
-        <v>80075</v>
+        <v>92524</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I330" t="inlineStr"/>
-      <c r="J330" t="inlineStr"/>
-      <c r="K330" t="inlineStr"/>
-      <c r="N330" t="inlineStr"/>
       <c r="P330" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>520612</v>
+        <v>520637</v>
       </c>
       <c r="R330" t="n">
-        <v>6934046</v>
+        <v>6934037</v>
       </c>
       <c r="S330" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T330" t="inlineStr">
         <is>
@@ -39174,7 +39171,6 @@
       <c r="AE330" t="b">
         <v>0</v>
       </c>
-      <c r="AF330" t="inlineStr"/>
       <c r="AG330" t="b">
         <v>0</v>
       </c>
@@ -39193,10 +39189,10 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>125670922</v>
+        <v>125661738</v>
       </c>
       <c r="B331" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -39224,17 +39220,17 @@
       <c r="I331" t="inlineStr"/>
       <c r="P331" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>520637</v>
+        <v>520605</v>
       </c>
       <c r="R331" t="n">
-        <v>6934037</v>
+        <v>6933517</v>
       </c>
       <c r="S331" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T331" t="inlineStr">
         <is>
@@ -39290,10 +39286,10 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>125670914</v>
+        <v>125671054</v>
       </c>
       <c r="B332" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -39319,19 +39315,22 @@
         </is>
       </c>
       <c r="I332" t="inlineStr"/>
+      <c r="J332" t="inlineStr"/>
+      <c r="K332" t="inlineStr"/>
+      <c r="N332" t="inlineStr"/>
       <c r="P332" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>520224</v>
+        <v>520612</v>
       </c>
       <c r="R332" t="n">
-        <v>6933690</v>
+        <v>6934046</v>
       </c>
       <c r="S332" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T332" t="inlineStr">
         <is>
@@ -39369,6 +39368,7 @@
       <c r="AE332" t="b">
         <v>0</v>
       </c>
+      <c r="AF332" t="inlineStr"/>
       <c r="AG332" t="b">
         <v>0</v>
       </c>
@@ -39387,48 +39387,48 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>125661738</v>
+        <v>125670914</v>
       </c>
       <c r="B333" t="n">
-        <v>92522</v>
+        <v>80076</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E333" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I333" t="inlineStr"/>
       <c r="P333" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>520605</v>
+        <v>520224</v>
       </c>
       <c r="R333" t="n">
-        <v>6933517</v>
+        <v>6933690</v>
       </c>
       <c r="S333" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T333" t="inlineStr">
         <is>
@@ -39487,7 +39487,7 @@
         <v>125670907</v>
       </c>
       <c r="B334" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -39584,7 +39584,7 @@
         <v>125670921</v>
       </c>
       <c r="B335" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -39678,32 +39678,32 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>125670909</v>
+        <v>125670903</v>
       </c>
       <c r="B336" t="n">
-        <v>80075</v>
+        <v>56844</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E336" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I336" t="inlineStr"/>
@@ -39713,10 +39713,10 @@
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>520754</v>
+        <v>520731</v>
       </c>
       <c r="R336" t="n">
-        <v>6934006</v>
+        <v>6934042</v>
       </c>
       <c r="S336" t="n">
         <v>25</v>
@@ -39753,7 +39753,7 @@
       </c>
       <c r="AC336" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD336" t="b">
@@ -39783,7 +39783,7 @@
         <v>125670916</v>
       </c>
       <c r="B337" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -39877,10 +39877,10 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>125671021</v>
+        <v>125670909</v>
       </c>
       <c r="B338" t="n">
-        <v>57648</v>
+        <v>80076</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -39888,41 +39888,37 @@
         </is>
       </c>
       <c r="E338" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I338" t="inlineStr"/>
-      <c r="K338" t="inlineStr"/>
-      <c r="L338" t="inlineStr"/>
-      <c r="M338" t="inlineStr"/>
-      <c r="N338" t="inlineStr"/>
       <c r="P338" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>520607</v>
+        <v>520754</v>
       </c>
       <c r="R338" t="n">
-        <v>6934048</v>
+        <v>6934006</v>
       </c>
       <c r="S338" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T338" t="inlineStr">
         <is>
@@ -39956,7 +39952,7 @@
       </c>
       <c r="AC338" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD338" t="b">
@@ -39983,48 +39979,52 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>125670903</v>
+        <v>125671021</v>
       </c>
       <c r="B339" t="n">
-        <v>56843</v>
+        <v>57649</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E339" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I339" t="inlineStr"/>
+      <c r="K339" t="inlineStr"/>
+      <c r="L339" t="inlineStr"/>
+      <c r="M339" t="inlineStr"/>
+      <c r="N339" t="inlineStr"/>
       <c r="P339" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>520731</v>
+        <v>520607</v>
       </c>
       <c r="R339" t="n">
-        <v>6934042</v>
+        <v>6934048</v>
       </c>
       <c r="S339" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T339" t="inlineStr">
         <is>
@@ -40058,7 +40058,7 @@
       </c>
       <c r="AC339" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD339" t="b">
@@ -40085,32 +40085,32 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>125659270</v>
+        <v>125661442</v>
       </c>
       <c r="B340" t="n">
-        <v>92522</v>
+        <v>78640</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E340" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I340" t="inlineStr"/>
@@ -40120,10 +40120,10 @@
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>520846</v>
+        <v>520629</v>
       </c>
       <c r="R340" t="n">
-        <v>6933515</v>
+        <v>6933514</v>
       </c>
       <c r="S340" t="n">
         <v>20</v>
@@ -40185,7 +40185,7 @@
         <v>125671469</v>
       </c>
       <c r="B341" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -40283,32 +40283,32 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>125661442</v>
+        <v>125659270</v>
       </c>
       <c r="B342" t="n">
-        <v>78639</v>
+        <v>92524</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E342" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I342" t="inlineStr"/>
@@ -40318,10 +40318,10 @@
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>520629</v>
+        <v>520846</v>
       </c>
       <c r="R342" t="n">
-        <v>6933514</v>
+        <v>6933515</v>
       </c>
       <c r="S342" t="n">
         <v>20</v>
@@ -40383,7 +40383,7 @@
         <v>125660155</v>
       </c>
       <c r="B343" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>125670923</v>
       </c>
       <c r="B344" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -40577,7 +40577,7 @@
         <v>125670910</v>
       </c>
       <c r="B345" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -40674,7 +40674,7 @@
         <v>125659251</v>
       </c>
       <c r="B346" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -40771,7 +40771,7 @@
         <v>125670905</v>
       </c>
       <c r="B347" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -40868,7 +40868,7 @@
         <v>125662204</v>
       </c>
       <c r="B348" t="n">
-        <v>91393</v>
+        <v>91395</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -40965,7 +40965,7 @@
         <v>125671342</v>
       </c>
       <c r="B349" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -41067,7 +41067,7 @@
         <v>125670917</v>
       </c>
       <c r="B350" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -41164,7 +41164,7 @@
         <v>125663708</v>
       </c>
       <c r="B351" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -41270,7 +41270,7 @@
         <v>125670901</v>
       </c>
       <c r="B352" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -41364,10 +41364,10 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>125661680</v>
+        <v>125671498</v>
       </c>
       <c r="B353" t="n">
-        <v>79590</v>
+        <v>80076</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -41375,37 +41375,40 @@
         </is>
       </c>
       <c r="E353" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I353" t="inlineStr"/>
+      <c r="J353" t="inlineStr"/>
+      <c r="K353" t="inlineStr"/>
+      <c r="N353" t="inlineStr"/>
       <c r="P353" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q353" t="n">
-        <v>520639</v>
+        <v>520385</v>
       </c>
       <c r="R353" t="n">
-        <v>6933509</v>
+        <v>6933569</v>
       </c>
       <c r="S353" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T353" t="inlineStr">
         <is>
@@ -41443,6 +41446,7 @@
       <c r="AE353" t="b">
         <v>0</v>
       </c>
+      <c r="AF353" t="inlineStr"/>
       <c r="AG353" t="b">
         <v>0</v>
       </c>
@@ -41461,10 +41465,10 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>125671498</v>
+        <v>125671434</v>
       </c>
       <c r="B354" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -41499,13 +41503,13 @@
         </is>
       </c>
       <c r="Q354" t="n">
-        <v>520385</v>
+        <v>520364</v>
       </c>
       <c r="R354" t="n">
-        <v>6933569</v>
+        <v>6934008</v>
       </c>
       <c r="S354" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T354" t="inlineStr">
         <is>
@@ -41562,10 +41566,10 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>125671434</v>
+        <v>125661680</v>
       </c>
       <c r="B355" t="n">
-        <v>80075</v>
+        <v>79591</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -41573,40 +41577,37 @@
         </is>
       </c>
       <c r="E355" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I355" t="inlineStr"/>
-      <c r="J355" t="inlineStr"/>
-      <c r="K355" t="inlineStr"/>
-      <c r="N355" t="inlineStr"/>
       <c r="P355" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q355" t="n">
-        <v>520364</v>
+        <v>520639</v>
       </c>
       <c r="R355" t="n">
-        <v>6934008</v>
+        <v>6933509</v>
       </c>
       <c r="S355" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T355" t="inlineStr">
         <is>
@@ -41644,7 +41645,6 @@
       <c r="AE355" t="b">
         <v>0</v>
       </c>
-      <c r="AF355" t="inlineStr"/>
       <c r="AG355" t="b">
         <v>0</v>
       </c>
@@ -41666,7 +41666,7 @@
         <v>125671230</v>
       </c>
       <c r="B356" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -41765,10 +41765,10 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>125670913</v>
+        <v>125659241</v>
       </c>
       <c r="B357" t="n">
-        <v>80075</v>
+        <v>79591</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -41776,37 +41776,37 @@
         </is>
       </c>
       <c r="E357" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I357" t="inlineStr"/>
       <c r="P357" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q357" t="n">
-        <v>520620</v>
+        <v>520844</v>
       </c>
       <c r="R357" t="n">
-        <v>6934070</v>
+        <v>6933514</v>
       </c>
       <c r="S357" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T357" t="inlineStr">
         <is>
@@ -41862,10 +41862,10 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>125659241</v>
+        <v>125670913</v>
       </c>
       <c r="B358" t="n">
-        <v>79590</v>
+        <v>80076</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -41873,37 +41873,37 @@
         </is>
       </c>
       <c r="E358" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I358" t="inlineStr"/>
       <c r="P358" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q358" t="n">
-        <v>520844</v>
+        <v>520620</v>
       </c>
       <c r="R358" t="n">
-        <v>6933514</v>
+        <v>6934070</v>
       </c>
       <c r="S358" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T358" t="inlineStr">
         <is>
@@ -41959,10 +41959,10 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>125660786</v>
+        <v>125671278</v>
       </c>
       <c r="B359" t="n">
-        <v>78730</v>
+        <v>80076</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -41970,37 +41970,40 @@
         </is>
       </c>
       <c r="E359" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I359" t="inlineStr"/>
+      <c r="J359" t="inlineStr"/>
+      <c r="K359" t="inlineStr"/>
+      <c r="N359" t="inlineStr"/>
       <c r="P359" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q359" t="n">
-        <v>520731</v>
+        <v>520511</v>
       </c>
       <c r="R359" t="n">
-        <v>6933528</v>
+        <v>6934025</v>
       </c>
       <c r="S359" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T359" t="inlineStr">
         <is>
@@ -42038,6 +42041,7 @@
       <c r="AE359" t="b">
         <v>0</v>
       </c>
+      <c r="AF359" t="inlineStr"/>
       <c r="AG359" t="b">
         <v>0</v>
       </c>
@@ -42056,10 +42060,10 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>125671278</v>
+        <v>125671098</v>
       </c>
       <c r="B360" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -42094,10 +42098,10 @@
         </is>
       </c>
       <c r="Q360" t="n">
-        <v>520511</v>
+        <v>520578</v>
       </c>
       <c r="R360" t="n">
-        <v>6934025</v>
+        <v>6934069</v>
       </c>
       <c r="S360" t="n">
         <v>10</v>
@@ -42157,10 +42161,10 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>125671098</v>
+        <v>125660786</v>
       </c>
       <c r="B361" t="n">
-        <v>80075</v>
+        <v>78731</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -42168,40 +42172,37 @@
         </is>
       </c>
       <c r="E361" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I361" t="inlineStr"/>
-      <c r="J361" t="inlineStr"/>
-      <c r="K361" t="inlineStr"/>
-      <c r="N361" t="inlineStr"/>
       <c r="P361" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q361" t="n">
-        <v>520578</v>
+        <v>520731</v>
       </c>
       <c r="R361" t="n">
-        <v>6934069</v>
+        <v>6933528</v>
       </c>
       <c r="S361" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T361" t="inlineStr">
         <is>
@@ -42239,7 +42240,6 @@
       <c r="AE361" t="b">
         <v>0</v>
       </c>
-      <c r="AF361" t="inlineStr"/>
       <c r="AG361" t="b">
         <v>0</v>
       </c>
@@ -42261,7 +42261,7 @@
         <v>125671157</v>
       </c>
       <c r="B362" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -42363,7 +42363,7 @@
         <v>125670920</v>
       </c>
       <c r="B363" t="n">
-        <v>105363</v>
+        <v>105365</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -38006,10 +38006,10 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>125671391</v>
+        <v>125670912</v>
       </c>
       <c r="B319" t="n">
-        <v>57812</v>
+        <v>80076</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -38017,38 +38017,34 @@
         </is>
       </c>
       <c r="E319" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I319" t="inlineStr"/>
-      <c r="K319" t="inlineStr"/>
-      <c r="L319" t="inlineStr"/>
-      <c r="M319" t="inlineStr"/>
-      <c r="N319" t="inlineStr"/>
       <c r="P319" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>520408</v>
+        <v>520757</v>
       </c>
       <c r="R319" t="n">
-        <v>6934036</v>
+        <v>6934013</v>
       </c>
       <c r="S319" t="n">
         <v>25</v>
@@ -38107,10 +38103,10 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>125670912</v>
+        <v>125671391</v>
       </c>
       <c r="B320" t="n">
-        <v>80076</v>
+        <v>57812</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -38118,34 +38114,38 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I320" t="inlineStr"/>
+      <c r="K320" t="inlineStr"/>
+      <c r="L320" t="inlineStr"/>
+      <c r="M320" t="inlineStr"/>
+      <c r="N320" t="inlineStr"/>
       <c r="P320" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>520757</v>
+        <v>520408</v>
       </c>
       <c r="R320" t="n">
-        <v>6934013</v>
+        <v>6934036</v>
       </c>
       <c r="S320" t="n">
         <v>25</v>
@@ -38204,48 +38204,52 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>125660766</v>
+        <v>125671307</v>
       </c>
       <c r="B321" t="n">
-        <v>79591</v>
+        <v>98341</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I321" t="inlineStr"/>
+      <c r="J321" t="inlineStr"/>
+      <c r="K321" t="inlineStr"/>
+      <c r="L321" t="inlineStr"/>
+      <c r="N321" t="inlineStr"/>
       <c r="P321" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>520729</v>
+        <v>520477</v>
       </c>
       <c r="R321" t="n">
-        <v>6933543</v>
+        <v>6934031</v>
       </c>
       <c r="S321" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T321" t="inlineStr">
         <is>
@@ -38283,6 +38287,7 @@
       <c r="AE321" t="b">
         <v>0</v>
       </c>
+      <c r="AF321" t="inlineStr"/>
       <c r="AG321" t="b">
         <v>0</v>
       </c>
@@ -38403,52 +38408,48 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>125671307</v>
+        <v>125660766</v>
       </c>
       <c r="B323" t="n">
-        <v>98341</v>
+        <v>79591</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I323" t="inlineStr"/>
-      <c r="J323" t="inlineStr"/>
-      <c r="K323" t="inlineStr"/>
-      <c r="L323" t="inlineStr"/>
-      <c r="N323" t="inlineStr"/>
       <c r="P323" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>520477</v>
+        <v>520729</v>
       </c>
       <c r="R323" t="n">
-        <v>6934031</v>
+        <v>6933543</v>
       </c>
       <c r="S323" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T323" t="inlineStr">
         <is>
@@ -38486,7 +38487,6 @@
       <c r="AE323" t="b">
         <v>0</v>
       </c>
-      <c r="AF323" t="inlineStr"/>
       <c r="AG323" t="b">
         <v>0</v>
       </c>
@@ -39581,32 +39581,32 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>125670921</v>
+        <v>125670916</v>
       </c>
       <c r="B335" t="n">
-        <v>92524</v>
+        <v>80076</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E335" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I335" t="inlineStr"/>
@@ -39616,10 +39616,10 @@
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>520731</v>
+        <v>520803</v>
       </c>
       <c r="R335" t="n">
-        <v>6934038</v>
+        <v>6933448</v>
       </c>
       <c r="S335" t="n">
         <v>25</v>
@@ -39678,32 +39678,32 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>125670903</v>
+        <v>125670909</v>
       </c>
       <c r="B336" t="n">
-        <v>56844</v>
+        <v>80076</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E336" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I336" t="inlineStr"/>
@@ -39713,10 +39713,10 @@
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>520731</v>
+        <v>520754</v>
       </c>
       <c r="R336" t="n">
-        <v>6934042</v>
+        <v>6934006</v>
       </c>
       <c r="S336" t="n">
         <v>25</v>
@@ -39753,7 +39753,7 @@
       </c>
       <c r="AC336" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD336" t="b">
@@ -39780,32 +39780,32 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>125670916</v>
+        <v>125670921</v>
       </c>
       <c r="B337" t="n">
-        <v>80076</v>
+        <v>92524</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E337" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I337" t="inlineStr"/>
@@ -39815,10 +39815,10 @@
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>520803</v>
+        <v>520731</v>
       </c>
       <c r="R337" t="n">
-        <v>6933448</v>
+        <v>6934038</v>
       </c>
       <c r="S337" t="n">
         <v>25</v>
@@ -39877,10 +39877,10 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>125670909</v>
+        <v>125671021</v>
       </c>
       <c r="B338" t="n">
-        <v>80076</v>
+        <v>57649</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -39888,37 +39888,41 @@
         </is>
       </c>
       <c r="E338" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I338" t="inlineStr"/>
+      <c r="K338" t="inlineStr"/>
+      <c r="L338" t="inlineStr"/>
+      <c r="M338" t="inlineStr"/>
+      <c r="N338" t="inlineStr"/>
       <c r="P338" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>520754</v>
+        <v>520607</v>
       </c>
       <c r="R338" t="n">
-        <v>6934006</v>
+        <v>6934048</v>
       </c>
       <c r="S338" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T338" t="inlineStr">
         <is>
@@ -39952,7 +39956,7 @@
       </c>
       <c r="AC338" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD338" t="b">
@@ -39979,52 +39983,48 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>125671021</v>
+        <v>125670903</v>
       </c>
       <c r="B339" t="n">
-        <v>57649</v>
+        <v>56844</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E339" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I339" t="inlineStr"/>
-      <c r="K339" t="inlineStr"/>
-      <c r="L339" t="inlineStr"/>
-      <c r="M339" t="inlineStr"/>
-      <c r="N339" t="inlineStr"/>
       <c r="P339" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>520607</v>
+        <v>520731</v>
       </c>
       <c r="R339" t="n">
-        <v>6934048</v>
+        <v>6934042</v>
       </c>
       <c r="S339" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T339" t="inlineStr">
         <is>
@@ -40058,7 +40058,7 @@
       </c>
       <c r="AC339" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD339" t="b">
@@ -40182,10 +40182,10 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>125671469</v>
+        <v>125660155</v>
       </c>
       <c r="B341" t="n">
-        <v>80076</v>
+        <v>78732</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -40193,40 +40193,37 @@
         </is>
       </c>
       <c r="E341" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I341" t="inlineStr"/>
-      <c r="J341" t="inlineStr"/>
-      <c r="K341" t="inlineStr"/>
-      <c r="N341" t="inlineStr"/>
       <c r="P341" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>520296</v>
+        <v>520786</v>
       </c>
       <c r="R341" t="n">
-        <v>6933639</v>
+        <v>6933540</v>
       </c>
       <c r="S341" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T341" t="inlineStr">
         <is>
@@ -40264,7 +40261,6 @@
       <c r="AE341" t="b">
         <v>0</v>
       </c>
-      <c r="AF341" t="inlineStr"/>
       <c r="AG341" t="b">
         <v>0</v>
       </c>
@@ -40283,48 +40279,51 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>125659270</v>
+        <v>125671469</v>
       </c>
       <c r="B342" t="n">
-        <v>92524</v>
+        <v>80076</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E342" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I342" t="inlineStr"/>
+      <c r="J342" t="inlineStr"/>
+      <c r="K342" t="inlineStr"/>
+      <c r="N342" t="inlineStr"/>
       <c r="P342" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>520846</v>
+        <v>520296</v>
       </c>
       <c r="R342" t="n">
-        <v>6933515</v>
+        <v>6933639</v>
       </c>
       <c r="S342" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T342" t="inlineStr">
         <is>
@@ -40362,6 +40361,7 @@
       <c r="AE342" t="b">
         <v>0</v>
       </c>
+      <c r="AF342" t="inlineStr"/>
       <c r="AG342" t="b">
         <v>0</v>
       </c>
@@ -40380,32 +40380,32 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>125660155</v>
+        <v>125659270</v>
       </c>
       <c r="B343" t="n">
-        <v>78732</v>
+        <v>92524</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E343" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I343" t="inlineStr"/>
@@ -40415,10 +40415,10 @@
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>520786</v>
+        <v>520846</v>
       </c>
       <c r="R343" t="n">
-        <v>6933540</v>
+        <v>6933515</v>
       </c>
       <c r="S343" t="n">
         <v>20</v>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -37713,7 +37713,7 @@
         <v>125670918</v>
       </c>
       <c r="B316" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -38204,52 +38204,48 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>125671307</v>
+        <v>125661236</v>
       </c>
       <c r="B321" t="n">
-        <v>98341</v>
+        <v>43934</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>220787</v>
+        <v>101735</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I321" t="inlineStr"/>
-      <c r="J321" t="inlineStr"/>
-      <c r="K321" t="inlineStr"/>
-      <c r="L321" t="inlineStr"/>
-      <c r="N321" t="inlineStr"/>
       <c r="P321" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>520477</v>
+        <v>520684</v>
       </c>
       <c r="R321" t="n">
-        <v>6934031</v>
+        <v>6933537</v>
       </c>
       <c r="S321" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T321" t="inlineStr">
         <is>
@@ -38281,13 +38277,17 @@
           <t>2025-06-03</t>
         </is>
       </c>
+      <c r="AC321" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
+        </is>
+      </c>
       <c r="AD321" t="b">
         <v>0</v>
       </c>
       <c r="AE321" t="b">
         <v>0</v>
       </c>
-      <c r="AF321" t="inlineStr"/>
       <c r="AG321" t="b">
         <v>0</v>
       </c>
@@ -38306,48 +38306,52 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>125661236</v>
+        <v>125671307</v>
       </c>
       <c r="B322" t="n">
-        <v>43934</v>
+        <v>98343</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>101735</v>
+        <v>220787</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I322" t="inlineStr"/>
+      <c r="J322" t="inlineStr"/>
+      <c r="K322" t="inlineStr"/>
+      <c r="L322" t="inlineStr"/>
+      <c r="N322" t="inlineStr"/>
       <c r="P322" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>520684</v>
+        <v>520477</v>
       </c>
       <c r="R322" t="n">
-        <v>6933537</v>
+        <v>6934031</v>
       </c>
       <c r="S322" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T322" t="inlineStr">
         <is>
@@ -38379,17 +38383,13 @@
           <t>2025-06-03</t>
         </is>
       </c>
-      <c r="AC322" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
-        </is>
-      </c>
       <c r="AD322" t="b">
         <v>0</v>
       </c>
       <c r="AE322" t="b">
         <v>0</v>
       </c>
+      <c r="AF322" t="inlineStr"/>
       <c r="AG322" t="b">
         <v>0</v>
       </c>
@@ -38505,48 +38505,48 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>125670906</v>
+        <v>125661898</v>
       </c>
       <c r="B324" t="n">
-        <v>79980</v>
+        <v>98343</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I324" t="inlineStr"/>
       <c r="P324" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>521033</v>
+        <v>520558</v>
       </c>
       <c r="R324" t="n">
-        <v>6933394</v>
+        <v>6933556</v>
       </c>
       <c r="S324" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T324" t="inlineStr">
         <is>
@@ -38602,48 +38602,48 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>125663906</v>
+        <v>125670919</v>
       </c>
       <c r="B325" t="n">
-        <v>80076</v>
+        <v>98343</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E325" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I325" t="inlineStr"/>
       <c r="P325" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q325" t="n">
-        <v>520184</v>
+        <v>520223</v>
       </c>
       <c r="R325" t="n">
-        <v>6933765</v>
+        <v>6933684</v>
       </c>
       <c r="S325" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T325" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>125670924</v>
       </c>
       <c r="B326" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -38796,32 +38796,32 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>125670919</v>
+        <v>125670906</v>
       </c>
       <c r="B327" t="n">
-        <v>98341</v>
+        <v>79980</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I327" t="inlineStr"/>
@@ -38831,10 +38831,10 @@
         </is>
       </c>
       <c r="Q327" t="n">
-        <v>520223</v>
+        <v>521033</v>
       </c>
       <c r="R327" t="n">
-        <v>6933684</v>
+        <v>6933394</v>
       </c>
       <c r="S327" t="n">
         <v>25</v>
@@ -38893,32 +38893,32 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>125661898</v>
+        <v>125663906</v>
       </c>
       <c r="B328" t="n">
-        <v>98341</v>
+        <v>80076</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I328" t="inlineStr"/>
@@ -38928,13 +38928,13 @@
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>520558</v>
+        <v>520184</v>
       </c>
       <c r="R328" t="n">
-        <v>6933556</v>
+        <v>6933765</v>
       </c>
       <c r="S328" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T328" t="inlineStr">
         <is>
@@ -39092,48 +39092,51 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>125670922</v>
+        <v>125671054</v>
       </c>
       <c r="B330" t="n">
-        <v>92524</v>
+        <v>80076</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I330" t="inlineStr"/>
+      <c r="J330" t="inlineStr"/>
+      <c r="K330" t="inlineStr"/>
+      <c r="N330" t="inlineStr"/>
       <c r="P330" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>520637</v>
+        <v>520612</v>
       </c>
       <c r="R330" t="n">
-        <v>6934037</v>
+        <v>6934046</v>
       </c>
       <c r="S330" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T330" t="inlineStr">
         <is>
@@ -39171,6 +39174,7 @@
       <c r="AE330" t="b">
         <v>0</v>
       </c>
+      <c r="AF330" t="inlineStr"/>
       <c r="AG330" t="b">
         <v>0</v>
       </c>
@@ -39189,48 +39193,48 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>125661738</v>
+        <v>125670914</v>
       </c>
       <c r="B331" t="n">
-        <v>92524</v>
+        <v>80076</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I331" t="inlineStr"/>
       <c r="P331" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>520605</v>
+        <v>520224</v>
       </c>
       <c r="R331" t="n">
-        <v>6933517</v>
+        <v>6933690</v>
       </c>
       <c r="S331" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T331" t="inlineStr">
         <is>
@@ -39286,51 +39290,48 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>125671054</v>
+        <v>125670922</v>
       </c>
       <c r="B332" t="n">
-        <v>80076</v>
+        <v>92526</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I332" t="inlineStr"/>
-      <c r="J332" t="inlineStr"/>
-      <c r="K332" t="inlineStr"/>
-      <c r="N332" t="inlineStr"/>
       <c r="P332" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>520612</v>
+        <v>520637</v>
       </c>
       <c r="R332" t="n">
-        <v>6934046</v>
+        <v>6934037</v>
       </c>
       <c r="S332" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T332" t="inlineStr">
         <is>
@@ -39368,7 +39369,6 @@
       <c r="AE332" t="b">
         <v>0</v>
       </c>
-      <c r="AF332" t="inlineStr"/>
       <c r="AG332" t="b">
         <v>0</v>
       </c>
@@ -39387,48 +39387,48 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>125670914</v>
+        <v>125661738</v>
       </c>
       <c r="B333" t="n">
-        <v>80076</v>
+        <v>92526</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E333" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I333" t="inlineStr"/>
       <c r="P333" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>520224</v>
+        <v>520605</v>
       </c>
       <c r="R333" t="n">
-        <v>6933690</v>
+        <v>6933517</v>
       </c>
       <c r="S333" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T333" t="inlineStr">
         <is>
@@ -39581,32 +39581,32 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>125670916</v>
+        <v>125670903</v>
       </c>
       <c r="B335" t="n">
-        <v>80076</v>
+        <v>56844</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E335" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I335" t="inlineStr"/>
@@ -39616,10 +39616,10 @@
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>520803</v>
+        <v>520731</v>
       </c>
       <c r="R335" t="n">
-        <v>6933448</v>
+        <v>6934042</v>
       </c>
       <c r="S335" t="n">
         <v>25</v>
@@ -39652,6 +39652,11 @@
       <c r="AA335" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC335" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD335" t="b">
@@ -39678,7 +39683,7 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>125670909</v>
+        <v>125670916</v>
       </c>
       <c r="B336" t="n">
         <v>80076</v>
@@ -39713,10 +39718,10 @@
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>520754</v>
+        <v>520803</v>
       </c>
       <c r="R336" t="n">
-        <v>6934006</v>
+        <v>6933448</v>
       </c>
       <c r="S336" t="n">
         <v>25</v>
@@ -39749,11 +39754,6 @@
       <c r="AA336" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC336" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD336" t="b">
@@ -39780,32 +39780,32 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>125670921</v>
+        <v>125670909</v>
       </c>
       <c r="B337" t="n">
-        <v>92524</v>
+        <v>80076</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E337" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I337" t="inlineStr"/>
@@ -39815,10 +39815,10 @@
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>520731</v>
+        <v>520754</v>
       </c>
       <c r="R337" t="n">
-        <v>6934038</v>
+        <v>6934006</v>
       </c>
       <c r="S337" t="n">
         <v>25</v>
@@ -39851,6 +39851,11 @@
       <c r="AA337" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC337" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD337" t="b">
@@ -39983,10 +39988,10 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>125670903</v>
+        <v>125670921</v>
       </c>
       <c r="B339" t="n">
-        <v>56844</v>
+        <v>92526</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -39994,21 +39999,21 @@
         </is>
       </c>
       <c r="E339" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I339" t="inlineStr"/>
@@ -40021,7 +40026,7 @@
         <v>520731</v>
       </c>
       <c r="R339" t="n">
-        <v>6934042</v>
+        <v>6934038</v>
       </c>
       <c r="S339" t="n">
         <v>25</v>
@@ -40054,11 +40059,6 @@
       <c r="AA339" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC339" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD339" t="b">
@@ -40085,10 +40085,10 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>125661442</v>
+        <v>125671469</v>
       </c>
       <c r="B340" t="n">
-        <v>78640</v>
+        <v>80076</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -40096,37 +40096,40 @@
         </is>
       </c>
       <c r="E340" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I340" t="inlineStr"/>
+      <c r="J340" t="inlineStr"/>
+      <c r="K340" t="inlineStr"/>
+      <c r="N340" t="inlineStr"/>
       <c r="P340" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>520629</v>
+        <v>520296</v>
       </c>
       <c r="R340" t="n">
-        <v>6933514</v>
+        <v>6933639</v>
       </c>
       <c r="S340" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T340" t="inlineStr">
         <is>
@@ -40164,6 +40167,7 @@
       <c r="AE340" t="b">
         <v>0</v>
       </c>
+      <c r="AF340" t="inlineStr"/>
       <c r="AG340" t="b">
         <v>0</v>
       </c>
@@ -40279,10 +40283,10 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>125671469</v>
+        <v>125661442</v>
       </c>
       <c r="B342" t="n">
-        <v>80076</v>
+        <v>78640</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -40290,40 +40294,37 @@
         </is>
       </c>
       <c r="E342" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I342" t="inlineStr"/>
-      <c r="J342" t="inlineStr"/>
-      <c r="K342" t="inlineStr"/>
-      <c r="N342" t="inlineStr"/>
       <c r="P342" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>520296</v>
+        <v>520629</v>
       </c>
       <c r="R342" t="n">
-        <v>6933639</v>
+        <v>6933514</v>
       </c>
       <c r="S342" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T342" t="inlineStr">
         <is>
@@ -40361,7 +40362,6 @@
       <c r="AE342" t="b">
         <v>0</v>
       </c>
-      <c r="AF342" t="inlineStr"/>
       <c r="AG342" t="b">
         <v>0</v>
       </c>
@@ -40383,7 +40383,7 @@
         <v>125659270</v>
       </c>
       <c r="B343" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>125670923</v>
       </c>
       <c r="B344" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -40574,10 +40574,10 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>125670910</v>
+        <v>125659251</v>
       </c>
       <c r="B345" t="n">
-        <v>80076</v>
+        <v>78731</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -40585,37 +40585,37 @@
         </is>
       </c>
       <c r="E345" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I345" t="inlineStr"/>
       <c r="P345" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q345" t="n">
-        <v>520830</v>
+        <v>520823</v>
       </c>
       <c r="R345" t="n">
-        <v>6933884</v>
+        <v>6933519</v>
       </c>
       <c r="S345" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T345" t="inlineStr">
         <is>
@@ -40671,10 +40671,10 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>125659251</v>
+        <v>125670910</v>
       </c>
       <c r="B346" t="n">
-        <v>78731</v>
+        <v>80076</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -40682,37 +40682,37 @@
         </is>
       </c>
       <c r="E346" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I346" t="inlineStr"/>
       <c r="P346" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q346" t="n">
-        <v>520823</v>
+        <v>520830</v>
       </c>
       <c r="R346" t="n">
-        <v>6933519</v>
+        <v>6933884</v>
       </c>
       <c r="S346" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T346" t="inlineStr">
         <is>
@@ -40868,7 +40868,7 @@
         <v>125662204</v>
       </c>
       <c r="B348" t="n">
-        <v>91395</v>
+        <v>91397</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -40965,7 +40965,7 @@
         <v>125671342</v>
       </c>
       <c r="B349" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -41067,7 +41067,7 @@
         <v>125670917</v>
       </c>
       <c r="B350" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -41267,10 +41267,10 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>125670901</v>
+        <v>125671498</v>
       </c>
       <c r="B352" t="n">
-        <v>91234</v>
+        <v>80076</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -41278,34 +41278,37 @@
         </is>
       </c>
       <c r="E352" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I352" t="inlineStr"/>
+      <c r="J352" t="inlineStr"/>
+      <c r="K352" t="inlineStr"/>
+      <c r="N352" t="inlineStr"/>
       <c r="P352" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q352" t="n">
-        <v>520257</v>
+        <v>520385</v>
       </c>
       <c r="R352" t="n">
-        <v>6933643</v>
+        <v>6933569</v>
       </c>
       <c r="S352" t="n">
         <v>25</v>
@@ -41346,6 +41349,7 @@
       <c r="AE352" t="b">
         <v>0</v>
       </c>
+      <c r="AF352" t="inlineStr"/>
       <c r="AG352" t="b">
         <v>0</v>
       </c>
@@ -41364,7 +41368,7 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>125671498</v>
+        <v>125671434</v>
       </c>
       <c r="B353" t="n">
         <v>80076</v>
@@ -41402,13 +41406,13 @@
         </is>
       </c>
       <c r="Q353" t="n">
-        <v>520385</v>
+        <v>520364</v>
       </c>
       <c r="R353" t="n">
-        <v>6933569</v>
+        <v>6934008</v>
       </c>
       <c r="S353" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T353" t="inlineStr">
         <is>
@@ -41465,10 +41469,10 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>125671434</v>
+        <v>125661680</v>
       </c>
       <c r="B354" t="n">
-        <v>80076</v>
+        <v>79591</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -41476,40 +41480,37 @@
         </is>
       </c>
       <c r="E354" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I354" t="inlineStr"/>
-      <c r="J354" t="inlineStr"/>
-      <c r="K354" t="inlineStr"/>
-      <c r="N354" t="inlineStr"/>
       <c r="P354" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q354" t="n">
-        <v>520364</v>
+        <v>520639</v>
       </c>
       <c r="R354" t="n">
-        <v>6934008</v>
+        <v>6933509</v>
       </c>
       <c r="S354" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T354" t="inlineStr">
         <is>
@@ -41547,7 +41548,6 @@
       <c r="AE354" t="b">
         <v>0</v>
       </c>
-      <c r="AF354" t="inlineStr"/>
       <c r="AG354" t="b">
         <v>0</v>
       </c>
@@ -41566,10 +41566,10 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>125661680</v>
+        <v>125670901</v>
       </c>
       <c r="B355" t="n">
-        <v>79591</v>
+        <v>91236</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -41577,37 +41577,37 @@
         </is>
       </c>
       <c r="E355" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I355" t="inlineStr"/>
       <c r="P355" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q355" t="n">
-        <v>520639</v>
+        <v>520257</v>
       </c>
       <c r="R355" t="n">
-        <v>6933509</v>
+        <v>6933643</v>
       </c>
       <c r="S355" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T355" t="inlineStr">
         <is>
@@ -41666,7 +41666,7 @@
         <v>125671230</v>
       </c>
       <c r="B356" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -42261,7 +42261,7 @@
         <v>125671157</v>
       </c>
       <c r="B362" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -42363,7 +42363,7 @@
         <v>125670920</v>
       </c>
       <c r="B363" t="n">
-        <v>105365</v>
+        <v>105367</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -38306,52 +38306,48 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>125671307</v>
+        <v>125660766</v>
       </c>
       <c r="B322" t="n">
-        <v>98343</v>
+        <v>79591</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I322" t="inlineStr"/>
-      <c r="J322" t="inlineStr"/>
-      <c r="K322" t="inlineStr"/>
-      <c r="L322" t="inlineStr"/>
-      <c r="N322" t="inlineStr"/>
       <c r="P322" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>520477</v>
+        <v>520729</v>
       </c>
       <c r="R322" t="n">
-        <v>6934031</v>
+        <v>6933543</v>
       </c>
       <c r="S322" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T322" t="inlineStr">
         <is>
@@ -38389,7 +38385,6 @@
       <c r="AE322" t="b">
         <v>0</v>
       </c>
-      <c r="AF322" t="inlineStr"/>
       <c r="AG322" t="b">
         <v>0</v>
       </c>
@@ -38408,48 +38403,52 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>125660766</v>
+        <v>125671307</v>
       </c>
       <c r="B323" t="n">
-        <v>79591</v>
+        <v>98343</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I323" t="inlineStr"/>
+      <c r="J323" t="inlineStr"/>
+      <c r="K323" t="inlineStr"/>
+      <c r="L323" t="inlineStr"/>
+      <c r="N323" t="inlineStr"/>
       <c r="P323" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>520729</v>
+        <v>520477</v>
       </c>
       <c r="R323" t="n">
-        <v>6933543</v>
+        <v>6934031</v>
       </c>
       <c r="S323" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T323" t="inlineStr">
         <is>
@@ -38487,6 +38486,7 @@
       <c r="AE323" t="b">
         <v>0</v>
       </c>
+      <c r="AF323" t="inlineStr"/>
       <c r="AG323" t="b">
         <v>0</v>
       </c>
@@ -39092,51 +39092,48 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>125671054</v>
+        <v>125670922</v>
       </c>
       <c r="B330" t="n">
-        <v>80076</v>
+        <v>92526</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I330" t="inlineStr"/>
-      <c r="J330" t="inlineStr"/>
-      <c r="K330" t="inlineStr"/>
-      <c r="N330" t="inlineStr"/>
       <c r="P330" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>520612</v>
+        <v>520637</v>
       </c>
       <c r="R330" t="n">
-        <v>6934046</v>
+        <v>6934037</v>
       </c>
       <c r="S330" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T330" t="inlineStr">
         <is>
@@ -39174,7 +39171,6 @@
       <c r="AE330" t="b">
         <v>0</v>
       </c>
-      <c r="AF330" t="inlineStr"/>
       <c r="AG330" t="b">
         <v>0</v>
       </c>
@@ -39193,48 +39189,48 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>125670914</v>
+        <v>125661738</v>
       </c>
       <c r="B331" t="n">
-        <v>80076</v>
+        <v>92526</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I331" t="inlineStr"/>
       <c r="P331" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>520224</v>
+        <v>520605</v>
       </c>
       <c r="R331" t="n">
-        <v>6933690</v>
+        <v>6933517</v>
       </c>
       <c r="S331" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T331" t="inlineStr">
         <is>
@@ -39290,48 +39286,51 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>125670922</v>
+        <v>125671054</v>
       </c>
       <c r="B332" t="n">
-        <v>92526</v>
+        <v>80076</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I332" t="inlineStr"/>
+      <c r="J332" t="inlineStr"/>
+      <c r="K332" t="inlineStr"/>
+      <c r="N332" t="inlineStr"/>
       <c r="P332" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>520637</v>
+        <v>520612</v>
       </c>
       <c r="R332" t="n">
-        <v>6934037</v>
+        <v>6934046</v>
       </c>
       <c r="S332" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T332" t="inlineStr">
         <is>
@@ -39369,6 +39368,7 @@
       <c r="AE332" t="b">
         <v>0</v>
       </c>
+      <c r="AF332" t="inlineStr"/>
       <c r="AG332" t="b">
         <v>0</v>
       </c>
@@ -39387,48 +39387,48 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>125661738</v>
+        <v>125670914</v>
       </c>
       <c r="B333" t="n">
-        <v>92526</v>
+        <v>80076</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E333" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I333" t="inlineStr"/>
       <c r="P333" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>520605</v>
+        <v>520224</v>
       </c>
       <c r="R333" t="n">
-        <v>6933517</v>
+        <v>6933690</v>
       </c>
       <c r="S333" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T333" t="inlineStr">
         <is>
@@ -40186,10 +40186,10 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>125660155</v>
+        <v>125661442</v>
       </c>
       <c r="B341" t="n">
-        <v>78732</v>
+        <v>78640</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -40197,21 +40197,21 @@
         </is>
       </c>
       <c r="E341" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I341" t="inlineStr"/>
@@ -40221,10 +40221,10 @@
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>520786</v>
+        <v>520629</v>
       </c>
       <c r="R341" t="n">
-        <v>6933540</v>
+        <v>6933514</v>
       </c>
       <c r="S341" t="n">
         <v>20</v>
@@ -40283,32 +40283,32 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>125661442</v>
+        <v>125659270</v>
       </c>
       <c r="B342" t="n">
-        <v>78640</v>
+        <v>92526</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E342" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I342" t="inlineStr"/>
@@ -40318,10 +40318,10 @@
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>520629</v>
+        <v>520846</v>
       </c>
       <c r="R342" t="n">
-        <v>6933514</v>
+        <v>6933515</v>
       </c>
       <c r="S342" t="n">
         <v>20</v>
@@ -40380,32 +40380,32 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>125659270</v>
+        <v>125660155</v>
       </c>
       <c r="B343" t="n">
-        <v>92526</v>
+        <v>78732</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E343" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I343" t="inlineStr"/>
@@ -40415,10 +40415,10 @@
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>520846</v>
+        <v>520786</v>
       </c>
       <c r="R343" t="n">
-        <v>6933515</v>
+        <v>6933540</v>
       </c>
       <c r="S343" t="n">
         <v>20</v>
@@ -41566,48 +41566,52 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>125670901</v>
+        <v>125671230</v>
       </c>
       <c r="B355" t="n">
-        <v>91236</v>
+        <v>98364</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E355" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I355" t="inlineStr"/>
+      <c r="J355" t="inlineStr"/>
+      <c r="K355" t="inlineStr"/>
+      <c r="L355" t="inlineStr"/>
+      <c r="N355" t="inlineStr"/>
       <c r="P355" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q355" t="n">
-        <v>520257</v>
+        <v>520549</v>
       </c>
       <c r="R355" t="n">
-        <v>6933643</v>
+        <v>6934058</v>
       </c>
       <c r="S355" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T355" t="inlineStr">
         <is>
@@ -41645,6 +41649,7 @@
       <c r="AE355" t="b">
         <v>0</v>
       </c>
+      <c r="AF355" t="inlineStr"/>
       <c r="AG355" t="b">
         <v>0</v>
       </c>
@@ -41663,52 +41668,48 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>125671230</v>
+        <v>125670901</v>
       </c>
       <c r="B356" t="n">
-        <v>98364</v>
+        <v>91236</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E356" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I356" t="inlineStr"/>
-      <c r="J356" t="inlineStr"/>
-      <c r="K356" t="inlineStr"/>
-      <c r="L356" t="inlineStr"/>
-      <c r="N356" t="inlineStr"/>
       <c r="P356" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q356" t="n">
-        <v>520549</v>
+        <v>520257</v>
       </c>
       <c r="R356" t="n">
-        <v>6934058</v>
+        <v>6933643</v>
       </c>
       <c r="S356" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T356" t="inlineStr">
         <is>
@@ -41746,7 +41747,6 @@
       <c r="AE356" t="b">
         <v>0</v>
       </c>
-      <c r="AF356" t="inlineStr"/>
       <c r="AG356" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -37713,7 +37713,7 @@
         <v>125670918</v>
       </c>
       <c r="B316" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -38306,48 +38306,52 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>125660766</v>
+        <v>125671307</v>
       </c>
       <c r="B322" t="n">
-        <v>79591</v>
+        <v>98345</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I322" t="inlineStr"/>
+      <c r="J322" t="inlineStr"/>
+      <c r="K322" t="inlineStr"/>
+      <c r="L322" t="inlineStr"/>
+      <c r="N322" t="inlineStr"/>
       <c r="P322" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>520729</v>
+        <v>520477</v>
       </c>
       <c r="R322" t="n">
-        <v>6933543</v>
+        <v>6934031</v>
       </c>
       <c r="S322" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T322" t="inlineStr">
         <is>
@@ -38385,6 +38389,7 @@
       <c r="AE322" t="b">
         <v>0</v>
       </c>
+      <c r="AF322" t="inlineStr"/>
       <c r="AG322" t="b">
         <v>0</v>
       </c>
@@ -38403,52 +38408,48 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>125671307</v>
+        <v>125660766</v>
       </c>
       <c r="B323" t="n">
-        <v>98343</v>
+        <v>79591</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I323" t="inlineStr"/>
-      <c r="J323" t="inlineStr"/>
-      <c r="K323" t="inlineStr"/>
-      <c r="L323" t="inlineStr"/>
-      <c r="N323" t="inlineStr"/>
       <c r="P323" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>520477</v>
+        <v>520729</v>
       </c>
       <c r="R323" t="n">
-        <v>6934031</v>
+        <v>6933543</v>
       </c>
       <c r="S323" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T323" t="inlineStr">
         <is>
@@ -38486,7 +38487,6 @@
       <c r="AE323" t="b">
         <v>0</v>
       </c>
-      <c r="AF323" t="inlineStr"/>
       <c r="AG323" t="b">
         <v>0</v>
       </c>
@@ -38505,48 +38505,48 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>125661898</v>
+        <v>125670906</v>
       </c>
       <c r="B324" t="n">
-        <v>98343</v>
+        <v>79980</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I324" t="inlineStr"/>
       <c r="P324" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>520558</v>
+        <v>521033</v>
       </c>
       <c r="R324" t="n">
-        <v>6933556</v>
+        <v>6933394</v>
       </c>
       <c r="S324" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T324" t="inlineStr">
         <is>
@@ -38602,48 +38602,48 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>125670919</v>
+        <v>125663906</v>
       </c>
       <c r="B325" t="n">
-        <v>98343</v>
+        <v>80076</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E325" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I325" t="inlineStr"/>
       <c r="P325" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q325" t="n">
-        <v>520223</v>
+        <v>520184</v>
       </c>
       <c r="R325" t="n">
-        <v>6933684</v>
+        <v>6933765</v>
       </c>
       <c r="S325" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T325" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>125670924</v>
       </c>
       <c r="B326" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -38796,48 +38796,48 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>125670906</v>
+        <v>125661898</v>
       </c>
       <c r="B327" t="n">
-        <v>79980</v>
+        <v>98345</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I327" t="inlineStr"/>
       <c r="P327" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q327" t="n">
-        <v>521033</v>
+        <v>520558</v>
       </c>
       <c r="R327" t="n">
-        <v>6933394</v>
+        <v>6933556</v>
       </c>
       <c r="S327" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T327" t="inlineStr">
         <is>
@@ -38893,48 +38893,48 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>125663906</v>
+        <v>125670919</v>
       </c>
       <c r="B328" t="n">
-        <v>80076</v>
+        <v>98345</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I328" t="inlineStr"/>
       <c r="P328" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>520184</v>
+        <v>520223</v>
       </c>
       <c r="R328" t="n">
-        <v>6933765</v>
+        <v>6933684</v>
       </c>
       <c r="S328" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T328" t="inlineStr">
         <is>
@@ -39092,48 +39092,51 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>125670922</v>
+        <v>125671054</v>
       </c>
       <c r="B330" t="n">
-        <v>92526</v>
+        <v>80076</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I330" t="inlineStr"/>
+      <c r="J330" t="inlineStr"/>
+      <c r="K330" t="inlineStr"/>
+      <c r="N330" t="inlineStr"/>
       <c r="P330" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>520637</v>
+        <v>520612</v>
       </c>
       <c r="R330" t="n">
-        <v>6934037</v>
+        <v>6934046</v>
       </c>
       <c r="S330" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T330" t="inlineStr">
         <is>
@@ -39171,6 +39174,7 @@
       <c r="AE330" t="b">
         <v>0</v>
       </c>
+      <c r="AF330" t="inlineStr"/>
       <c r="AG330" t="b">
         <v>0</v>
       </c>
@@ -39189,48 +39193,48 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>125661738</v>
+        <v>125670914</v>
       </c>
       <c r="B331" t="n">
-        <v>92526</v>
+        <v>80076</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I331" t="inlineStr"/>
       <c r="P331" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>520605</v>
+        <v>520224</v>
       </c>
       <c r="R331" t="n">
-        <v>6933517</v>
+        <v>6933690</v>
       </c>
       <c r="S331" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T331" t="inlineStr">
         <is>
@@ -39286,51 +39290,48 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>125671054</v>
+        <v>125670922</v>
       </c>
       <c r="B332" t="n">
-        <v>80076</v>
+        <v>92528</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I332" t="inlineStr"/>
-      <c r="J332" t="inlineStr"/>
-      <c r="K332" t="inlineStr"/>
-      <c r="N332" t="inlineStr"/>
       <c r="P332" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>520612</v>
+        <v>520637</v>
       </c>
       <c r="R332" t="n">
-        <v>6934046</v>
+        <v>6934037</v>
       </c>
       <c r="S332" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T332" t="inlineStr">
         <is>
@@ -39368,7 +39369,6 @@
       <c r="AE332" t="b">
         <v>0</v>
       </c>
-      <c r="AF332" t="inlineStr"/>
       <c r="AG332" t="b">
         <v>0</v>
       </c>
@@ -39387,48 +39387,48 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>125670914</v>
+        <v>125661738</v>
       </c>
       <c r="B333" t="n">
-        <v>80076</v>
+        <v>92528</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E333" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I333" t="inlineStr"/>
       <c r="P333" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>520224</v>
+        <v>520605</v>
       </c>
       <c r="R333" t="n">
-        <v>6933690</v>
+        <v>6933517</v>
       </c>
       <c r="S333" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T333" t="inlineStr">
         <is>
@@ -39581,48 +39581,52 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>125670903</v>
+        <v>125671021</v>
       </c>
       <c r="B335" t="n">
-        <v>56844</v>
+        <v>57649</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E335" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I335" t="inlineStr"/>
+      <c r="K335" t="inlineStr"/>
+      <c r="L335" t="inlineStr"/>
+      <c r="M335" t="inlineStr"/>
+      <c r="N335" t="inlineStr"/>
       <c r="P335" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>520731</v>
+        <v>520607</v>
       </c>
       <c r="R335" t="n">
-        <v>6934042</v>
+        <v>6934048</v>
       </c>
       <c r="S335" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T335" t="inlineStr">
         <is>
@@ -39656,7 +39660,7 @@
       </c>
       <c r="AC335" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD335" t="b">
@@ -39683,32 +39687,32 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>125670916</v>
+        <v>125670921</v>
       </c>
       <c r="B336" t="n">
-        <v>80076</v>
+        <v>92528</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E336" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I336" t="inlineStr"/>
@@ -39718,10 +39722,10 @@
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>520803</v>
+        <v>520731</v>
       </c>
       <c r="R336" t="n">
-        <v>6933448</v>
+        <v>6934038</v>
       </c>
       <c r="S336" t="n">
         <v>25</v>
@@ -39780,32 +39784,32 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>125670909</v>
+        <v>125670903</v>
       </c>
       <c r="B337" t="n">
-        <v>80076</v>
+        <v>56844</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E337" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I337" t="inlineStr"/>
@@ -39815,10 +39819,10 @@
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>520754</v>
+        <v>520731</v>
       </c>
       <c r="R337" t="n">
-        <v>6934006</v>
+        <v>6934042</v>
       </c>
       <c r="S337" t="n">
         <v>25</v>
@@ -39855,7 +39859,7 @@
       </c>
       <c r="AC337" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD337" t="b">
@@ -39882,10 +39886,10 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>125671021</v>
+        <v>125670916</v>
       </c>
       <c r="B338" t="n">
-        <v>57649</v>
+        <v>80076</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -39893,41 +39897,37 @@
         </is>
       </c>
       <c r="E338" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I338" t="inlineStr"/>
-      <c r="K338" t="inlineStr"/>
-      <c r="L338" t="inlineStr"/>
-      <c r="M338" t="inlineStr"/>
-      <c r="N338" t="inlineStr"/>
       <c r="P338" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>520607</v>
+        <v>520803</v>
       </c>
       <c r="R338" t="n">
-        <v>6934048</v>
+        <v>6933448</v>
       </c>
       <c r="S338" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T338" t="inlineStr">
         <is>
@@ -39957,11 +39957,6 @@
       <c r="AA338" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC338" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD338" t="b">
@@ -39988,32 +39983,32 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>125670921</v>
+        <v>125670909</v>
       </c>
       <c r="B339" t="n">
-        <v>92526</v>
+        <v>80076</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E339" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I339" t="inlineStr"/>
@@ -40023,10 +40018,10 @@
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>520731</v>
+        <v>520754</v>
       </c>
       <c r="R339" t="n">
-        <v>6934038</v>
+        <v>6934006</v>
       </c>
       <c r="S339" t="n">
         <v>25</v>
@@ -40059,6 +40054,11 @@
       <c r="AA339" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC339" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD339" t="b">
@@ -40085,10 +40085,10 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>125671469</v>
+        <v>125661442</v>
       </c>
       <c r="B340" t="n">
-        <v>80076</v>
+        <v>78640</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -40096,40 +40096,37 @@
         </is>
       </c>
       <c r="E340" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I340" t="inlineStr"/>
-      <c r="J340" t="inlineStr"/>
-      <c r="K340" t="inlineStr"/>
-      <c r="N340" t="inlineStr"/>
       <c r="P340" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>520296</v>
+        <v>520629</v>
       </c>
       <c r="R340" t="n">
-        <v>6933639</v>
+        <v>6933514</v>
       </c>
       <c r="S340" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T340" t="inlineStr">
         <is>
@@ -40167,7 +40164,6 @@
       <c r="AE340" t="b">
         <v>0</v>
       </c>
-      <c r="AF340" t="inlineStr"/>
       <c r="AG340" t="b">
         <v>0</v>
       </c>
@@ -40186,32 +40182,32 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>125661442</v>
+        <v>125659270</v>
       </c>
       <c r="B341" t="n">
-        <v>78640</v>
+        <v>92528</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E341" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I341" t="inlineStr"/>
@@ -40221,10 +40217,10 @@
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>520629</v>
+        <v>520846</v>
       </c>
       <c r="R341" t="n">
-        <v>6933514</v>
+        <v>6933515</v>
       </c>
       <c r="S341" t="n">
         <v>20</v>
@@ -40283,32 +40279,32 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>125659270</v>
+        <v>125660155</v>
       </c>
       <c r="B342" t="n">
-        <v>92526</v>
+        <v>78732</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E342" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I342" t="inlineStr"/>
@@ -40318,10 +40314,10 @@
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>520846</v>
+        <v>520786</v>
       </c>
       <c r="R342" t="n">
-        <v>6933515</v>
+        <v>6933540</v>
       </c>
       <c r="S342" t="n">
         <v>20</v>
@@ -40380,10 +40376,10 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>125660155</v>
+        <v>125671469</v>
       </c>
       <c r="B343" t="n">
-        <v>78732</v>
+        <v>80076</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -40391,37 +40387,40 @@
         </is>
       </c>
       <c r="E343" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I343" t="inlineStr"/>
+      <c r="J343" t="inlineStr"/>
+      <c r="K343" t="inlineStr"/>
+      <c r="N343" t="inlineStr"/>
       <c r="P343" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>520786</v>
+        <v>520296</v>
       </c>
       <c r="R343" t="n">
-        <v>6933540</v>
+        <v>6933639</v>
       </c>
       <c r="S343" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T343" t="inlineStr">
         <is>
@@ -40459,6 +40458,7 @@
       <c r="AE343" t="b">
         <v>0</v>
       </c>
+      <c r="AF343" t="inlineStr"/>
       <c r="AG343" t="b">
         <v>0</v>
       </c>
@@ -40480,7 +40480,7 @@
         <v>125670923</v>
       </c>
       <c r="B344" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -40574,10 +40574,10 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>125659251</v>
+        <v>125670905</v>
       </c>
       <c r="B345" t="n">
-        <v>78731</v>
+        <v>80077</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -40585,37 +40585,37 @@
         </is>
       </c>
       <c r="E345" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I345" t="inlineStr"/>
       <c r="P345" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q345" t="n">
-        <v>520823</v>
+        <v>520801</v>
       </c>
       <c r="R345" t="n">
-        <v>6933519</v>
+        <v>6933448</v>
       </c>
       <c r="S345" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T345" t="inlineStr">
         <is>
@@ -40671,48 +40671,48 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>125670910</v>
+        <v>125662204</v>
       </c>
       <c r="B346" t="n">
-        <v>80076</v>
+        <v>91399</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E346" t="n">
-        <v>6458</v>
+        <v>1503</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I346" t="inlineStr"/>
       <c r="P346" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q346" t="n">
-        <v>520830</v>
+        <v>520425</v>
       </c>
       <c r="R346" t="n">
-        <v>6933884</v>
+        <v>6933544</v>
       </c>
       <c r="S346" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T346" t="inlineStr">
         <is>
@@ -40768,10 +40768,10 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>125670905</v>
+        <v>125659251</v>
       </c>
       <c r="B347" t="n">
-        <v>80077</v>
+        <v>78731</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -40779,37 +40779,37 @@
         </is>
       </c>
       <c r="E347" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I347" t="inlineStr"/>
       <c r="P347" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q347" t="n">
-        <v>520801</v>
+        <v>520823</v>
       </c>
       <c r="R347" t="n">
-        <v>6933448</v>
+        <v>6933519</v>
       </c>
       <c r="S347" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T347" t="inlineStr">
         <is>
@@ -40865,48 +40865,48 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>125662204</v>
+        <v>125670910</v>
       </c>
       <c r="B348" t="n">
-        <v>91397</v>
+        <v>80076</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E348" t="n">
-        <v>1503</v>
+        <v>6458</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I348" t="inlineStr"/>
       <c r="P348" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q348" t="n">
-        <v>520425</v>
+        <v>520830</v>
       </c>
       <c r="R348" t="n">
-        <v>6933544</v>
+        <v>6933884</v>
       </c>
       <c r="S348" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T348" t="inlineStr">
         <is>
@@ -40965,7 +40965,7 @@
         <v>125671342</v>
       </c>
       <c r="B349" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -41067,7 +41067,7 @@
         <v>125670917</v>
       </c>
       <c r="B350" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -41267,37 +41267,38 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>125671498</v>
+        <v>125671230</v>
       </c>
       <c r="B352" t="n">
-        <v>80076</v>
+        <v>98366</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E352" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I352" t="inlineStr"/>
       <c r="J352" t="inlineStr"/>
       <c r="K352" t="inlineStr"/>
+      <c r="L352" t="inlineStr"/>
       <c r="N352" t="inlineStr"/>
       <c r="P352" t="inlineStr">
         <is>
@@ -41305,13 +41306,13 @@
         </is>
       </c>
       <c r="Q352" t="n">
-        <v>520385</v>
+        <v>520549</v>
       </c>
       <c r="R352" t="n">
-        <v>6933569</v>
+        <v>6934058</v>
       </c>
       <c r="S352" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T352" t="inlineStr">
         <is>
@@ -41368,7 +41369,7 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>125671434</v>
+        <v>125671498</v>
       </c>
       <c r="B353" t="n">
         <v>80076</v>
@@ -41406,13 +41407,13 @@
         </is>
       </c>
       <c r="Q353" t="n">
-        <v>520364</v>
+        <v>520385</v>
       </c>
       <c r="R353" t="n">
-        <v>6934008</v>
+        <v>6933569</v>
       </c>
       <c r="S353" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T353" t="inlineStr">
         <is>
@@ -41469,10 +41470,10 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>125661680</v>
+        <v>125671434</v>
       </c>
       <c r="B354" t="n">
-        <v>79591</v>
+        <v>80076</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -41480,37 +41481,40 @@
         </is>
       </c>
       <c r="E354" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I354" t="inlineStr"/>
+      <c r="J354" t="inlineStr"/>
+      <c r="K354" t="inlineStr"/>
+      <c r="N354" t="inlineStr"/>
       <c r="P354" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q354" t="n">
-        <v>520639</v>
+        <v>520364</v>
       </c>
       <c r="R354" t="n">
-        <v>6933509</v>
+        <v>6934008</v>
       </c>
       <c r="S354" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T354" t="inlineStr">
         <is>
@@ -41548,6 +41552,7 @@
       <c r="AE354" t="b">
         <v>0</v>
       </c>
+      <c r="AF354" t="inlineStr"/>
       <c r="AG354" t="b">
         <v>0</v>
       </c>
@@ -41566,52 +41571,48 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>125671230</v>
+        <v>125661680</v>
       </c>
       <c r="B355" t="n">
-        <v>98364</v>
+        <v>79591</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E355" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I355" t="inlineStr"/>
-      <c r="J355" t="inlineStr"/>
-      <c r="K355" t="inlineStr"/>
-      <c r="L355" t="inlineStr"/>
-      <c r="N355" t="inlineStr"/>
       <c r="P355" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q355" t="n">
-        <v>520549</v>
+        <v>520639</v>
       </c>
       <c r="R355" t="n">
-        <v>6934058</v>
+        <v>6933509</v>
       </c>
       <c r="S355" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T355" t="inlineStr">
         <is>
@@ -41649,7 +41650,6 @@
       <c r="AE355" t="b">
         <v>0</v>
       </c>
-      <c r="AF355" t="inlineStr"/>
       <c r="AG355" t="b">
         <v>0</v>
       </c>
@@ -41671,7 +41671,7 @@
         <v>125670901</v>
       </c>
       <c r="B356" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -41959,37 +41959,38 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>125671278</v>
+        <v>125671157</v>
       </c>
       <c r="B359" t="n">
-        <v>80076</v>
+        <v>98345</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E359" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I359" t="inlineStr"/>
       <c r="J359" t="inlineStr"/>
       <c r="K359" t="inlineStr"/>
+      <c r="L359" t="inlineStr"/>
       <c r="N359" t="inlineStr"/>
       <c r="P359" t="inlineStr">
         <is>
@@ -41997,10 +41998,10 @@
         </is>
       </c>
       <c r="Q359" t="n">
-        <v>520511</v>
+        <v>520540</v>
       </c>
       <c r="R359" t="n">
-        <v>6934025</v>
+        <v>6934055</v>
       </c>
       <c r="S359" t="n">
         <v>10</v>
@@ -42060,7 +42061,7 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>125671098</v>
+        <v>125671278</v>
       </c>
       <c r="B360" t="n">
         <v>80076</v>
@@ -42098,10 +42099,10 @@
         </is>
       </c>
       <c r="Q360" t="n">
-        <v>520578</v>
+        <v>520511</v>
       </c>
       <c r="R360" t="n">
-        <v>6934069</v>
+        <v>6934025</v>
       </c>
       <c r="S360" t="n">
         <v>10</v>
@@ -42161,10 +42162,10 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>125660786</v>
+        <v>125671098</v>
       </c>
       <c r="B361" t="n">
-        <v>78731</v>
+        <v>80076</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -42172,37 +42173,40 @@
         </is>
       </c>
       <c r="E361" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I361" t="inlineStr"/>
+      <c r="J361" t="inlineStr"/>
+      <c r="K361" t="inlineStr"/>
+      <c r="N361" t="inlineStr"/>
       <c r="P361" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q361" t="n">
-        <v>520731</v>
+        <v>520578</v>
       </c>
       <c r="R361" t="n">
-        <v>6933528</v>
+        <v>6934069</v>
       </c>
       <c r="S361" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T361" t="inlineStr">
         <is>
@@ -42240,6 +42244,7 @@
       <c r="AE361" t="b">
         <v>0</v>
       </c>
+      <c r="AF361" t="inlineStr"/>
       <c r="AG361" t="b">
         <v>0</v>
       </c>
@@ -42258,52 +42263,48 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>125671157</v>
+        <v>125660786</v>
       </c>
       <c r="B362" t="n">
-        <v>98343</v>
+        <v>78731</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E362" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I362" t="inlineStr"/>
-      <c r="J362" t="inlineStr"/>
-      <c r="K362" t="inlineStr"/>
-      <c r="L362" t="inlineStr"/>
-      <c r="N362" t="inlineStr"/>
       <c r="P362" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q362" t="n">
-        <v>520540</v>
+        <v>520731</v>
       </c>
       <c r="R362" t="n">
-        <v>6934055</v>
+        <v>6933528</v>
       </c>
       <c r="S362" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T362" t="inlineStr">
         <is>
@@ -42341,7 +42342,6 @@
       <c r="AE362" t="b">
         <v>0</v>
       </c>
-      <c r="AF362" t="inlineStr"/>
       <c r="AG362" t="b">
         <v>0</v>
       </c>
@@ -42363,7 +42363,7 @@
         <v>125670920</v>
       </c>
       <c r="B363" t="n">
-        <v>105367</v>
+        <v>105371</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -39092,51 +39092,48 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>125671054</v>
+        <v>125670922</v>
       </c>
       <c r="B330" t="n">
-        <v>80076</v>
+        <v>92528</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I330" t="inlineStr"/>
-      <c r="J330" t="inlineStr"/>
-      <c r="K330" t="inlineStr"/>
-      <c r="N330" t="inlineStr"/>
       <c r="P330" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>520612</v>
+        <v>520637</v>
       </c>
       <c r="R330" t="n">
-        <v>6934046</v>
+        <v>6934037</v>
       </c>
       <c r="S330" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T330" t="inlineStr">
         <is>
@@ -39174,7 +39171,6 @@
       <c r="AE330" t="b">
         <v>0</v>
       </c>
-      <c r="AF330" t="inlineStr"/>
       <c r="AG330" t="b">
         <v>0</v>
       </c>
@@ -39193,48 +39189,48 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>125670914</v>
+        <v>125661738</v>
       </c>
       <c r="B331" t="n">
-        <v>80076</v>
+        <v>92528</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I331" t="inlineStr"/>
       <c r="P331" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>520224</v>
+        <v>520605</v>
       </c>
       <c r="R331" t="n">
-        <v>6933690</v>
+        <v>6933517</v>
       </c>
       <c r="S331" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T331" t="inlineStr">
         <is>
@@ -39290,48 +39286,51 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>125670922</v>
+        <v>125671054</v>
       </c>
       <c r="B332" t="n">
-        <v>92528</v>
+        <v>80076</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I332" t="inlineStr"/>
+      <c r="J332" t="inlineStr"/>
+      <c r="K332" t="inlineStr"/>
+      <c r="N332" t="inlineStr"/>
       <c r="P332" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>520637</v>
+        <v>520612</v>
       </c>
       <c r="R332" t="n">
-        <v>6934037</v>
+        <v>6934046</v>
       </c>
       <c r="S332" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T332" t="inlineStr">
         <is>
@@ -39369,6 +39368,7 @@
       <c r="AE332" t="b">
         <v>0</v>
       </c>
+      <c r="AF332" t="inlineStr"/>
       <c r="AG332" t="b">
         <v>0</v>
       </c>
@@ -39387,48 +39387,48 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>125661738</v>
+        <v>125670914</v>
       </c>
       <c r="B333" t="n">
-        <v>92528</v>
+        <v>80076</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E333" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I333" t="inlineStr"/>
       <c r="P333" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>520605</v>
+        <v>520224</v>
       </c>
       <c r="R333" t="n">
-        <v>6933517</v>
+        <v>6933690</v>
       </c>
       <c r="S333" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T333" t="inlineStr">
         <is>
@@ -39581,52 +39581,48 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>125671021</v>
+        <v>125670921</v>
       </c>
       <c r="B335" t="n">
-        <v>57649</v>
+        <v>92528</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E335" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I335" t="inlineStr"/>
-      <c r="K335" t="inlineStr"/>
-      <c r="L335" t="inlineStr"/>
-      <c r="M335" t="inlineStr"/>
-      <c r="N335" t="inlineStr"/>
       <c r="P335" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>520607</v>
+        <v>520731</v>
       </c>
       <c r="R335" t="n">
-        <v>6934048</v>
+        <v>6934038</v>
       </c>
       <c r="S335" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T335" t="inlineStr">
         <is>
@@ -39656,11 +39652,6 @@
       <c r="AA335" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC335" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD335" t="b">
@@ -39687,48 +39678,52 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>125670921</v>
+        <v>125671021</v>
       </c>
       <c r="B336" t="n">
-        <v>92528</v>
+        <v>57649</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E336" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I336" t="inlineStr"/>
+      <c r="K336" t="inlineStr"/>
+      <c r="L336" t="inlineStr"/>
+      <c r="M336" t="inlineStr"/>
+      <c r="N336" t="inlineStr"/>
       <c r="P336" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>520731</v>
+        <v>520607</v>
       </c>
       <c r="R336" t="n">
-        <v>6934038</v>
+        <v>6934048</v>
       </c>
       <c r="S336" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T336" t="inlineStr">
         <is>
@@ -39758,6 +39753,11 @@
       <c r="AA336" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC336" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD336" t="b">
@@ -40279,10 +40279,10 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>125660155</v>
+        <v>125671469</v>
       </c>
       <c r="B342" t="n">
-        <v>78732</v>
+        <v>80076</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -40290,37 +40290,40 @@
         </is>
       </c>
       <c r="E342" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I342" t="inlineStr"/>
+      <c r="J342" t="inlineStr"/>
+      <c r="K342" t="inlineStr"/>
+      <c r="N342" t="inlineStr"/>
       <c r="P342" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>520786</v>
+        <v>520296</v>
       </c>
       <c r="R342" t="n">
-        <v>6933540</v>
+        <v>6933639</v>
       </c>
       <c r="S342" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T342" t="inlineStr">
         <is>
@@ -40358,6 +40361,7 @@
       <c r="AE342" t="b">
         <v>0</v>
       </c>
+      <c r="AF342" t="inlineStr"/>
       <c r="AG342" t="b">
         <v>0</v>
       </c>
@@ -40376,10 +40380,10 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>125671469</v>
+        <v>125660155</v>
       </c>
       <c r="B343" t="n">
-        <v>80076</v>
+        <v>78732</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -40387,40 +40391,37 @@
         </is>
       </c>
       <c r="E343" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I343" t="inlineStr"/>
-      <c r="J343" t="inlineStr"/>
-      <c r="K343" t="inlineStr"/>
-      <c r="N343" t="inlineStr"/>
       <c r="P343" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>520296</v>
+        <v>520786</v>
       </c>
       <c r="R343" t="n">
-        <v>6933639</v>
+        <v>6933540</v>
       </c>
       <c r="S343" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T343" t="inlineStr">
         <is>
@@ -40458,7 +40459,6 @@
       <c r="AE343" t="b">
         <v>0</v>
       </c>
-      <c r="AF343" t="inlineStr"/>
       <c r="AG343" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -37713,7 +37713,7 @@
         <v>125670918</v>
       </c>
       <c r="B316" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -37810,7 +37810,7 @@
         <v>125662951</v>
       </c>
       <c r="B317" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -37912,7 +37912,7 @@
         <v>125670904</v>
       </c>
       <c r="B318" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -38009,7 +38009,7 @@
         <v>125670912</v>
       </c>
       <c r="B319" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -38106,7 +38106,7 @@
         <v>125671391</v>
       </c>
       <c r="B320" t="n">
-        <v>57812</v>
+        <v>57816</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -38204,48 +38204,52 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>125661236</v>
+        <v>125671307</v>
       </c>
       <c r="B321" t="n">
-        <v>43934</v>
+        <v>98349</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>101735</v>
+        <v>220787</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I321" t="inlineStr"/>
+      <c r="J321" t="inlineStr"/>
+      <c r="K321" t="inlineStr"/>
+      <c r="L321" t="inlineStr"/>
+      <c r="N321" t="inlineStr"/>
       <c r="P321" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>520684</v>
+        <v>520477</v>
       </c>
       <c r="R321" t="n">
-        <v>6933537</v>
+        <v>6934031</v>
       </c>
       <c r="S321" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T321" t="inlineStr">
         <is>
@@ -38277,17 +38281,13 @@
           <t>2025-06-03</t>
         </is>
       </c>
-      <c r="AC321" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
-        </is>
-      </c>
       <c r="AD321" t="b">
         <v>0</v>
       </c>
       <c r="AE321" t="b">
         <v>0</v>
       </c>
+      <c r="AF321" t="inlineStr"/>
       <c r="AG321" t="b">
         <v>0</v>
       </c>
@@ -38306,52 +38306,48 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>125671307</v>
+        <v>125660766</v>
       </c>
       <c r="B322" t="n">
-        <v>98345</v>
+        <v>79595</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I322" t="inlineStr"/>
-      <c r="J322" t="inlineStr"/>
-      <c r="K322" t="inlineStr"/>
-      <c r="L322" t="inlineStr"/>
-      <c r="N322" t="inlineStr"/>
       <c r="P322" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>520477</v>
+        <v>520729</v>
       </c>
       <c r="R322" t="n">
-        <v>6934031</v>
+        <v>6933543</v>
       </c>
       <c r="S322" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T322" t="inlineStr">
         <is>
@@ -38389,7 +38385,6 @@
       <c r="AE322" t="b">
         <v>0</v>
       </c>
-      <c r="AF322" t="inlineStr"/>
       <c r="AG322" t="b">
         <v>0</v>
       </c>
@@ -38408,32 +38403,32 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>125660766</v>
+        <v>125661236</v>
       </c>
       <c r="B323" t="n">
-        <v>79591</v>
+        <v>43934</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>6453</v>
+        <v>101735</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I323" t="inlineStr"/>
@@ -38443,10 +38438,10 @@
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>520729</v>
+        <v>520684</v>
       </c>
       <c r="R323" t="n">
-        <v>6933543</v>
+        <v>6933537</v>
       </c>
       <c r="S323" t="n">
         <v>20</v>
@@ -38479,6 +38474,11 @@
       <c r="AA323" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC323" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD323" t="b">
@@ -38508,7 +38508,7 @@
         <v>125670906</v>
       </c>
       <c r="B324" t="n">
-        <v>79980</v>
+        <v>79984</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -38605,7 +38605,7 @@
         <v>125663906</v>
       </c>
       <c r="B325" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>125670924</v>
       </c>
       <c r="B326" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -38799,7 +38799,7 @@
         <v>125661898</v>
       </c>
       <c r="B327" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -38896,7 +38896,7 @@
         <v>125670919</v>
       </c>
       <c r="B328" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -38993,7 +38993,7 @@
         <v>125670908</v>
       </c>
       <c r="B329" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -39095,7 +39095,7 @@
         <v>125670922</v>
       </c>
       <c r="B330" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -39189,48 +39189,51 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>125661738</v>
+        <v>125671054</v>
       </c>
       <c r="B331" t="n">
-        <v>92528</v>
+        <v>80080</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I331" t="inlineStr"/>
+      <c r="J331" t="inlineStr"/>
+      <c r="K331" t="inlineStr"/>
+      <c r="N331" t="inlineStr"/>
       <c r="P331" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>520605</v>
+        <v>520612</v>
       </c>
       <c r="R331" t="n">
-        <v>6933517</v>
+        <v>6934046</v>
       </c>
       <c r="S331" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T331" t="inlineStr">
         <is>
@@ -39268,6 +39271,7 @@
       <c r="AE331" t="b">
         <v>0</v>
       </c>
+      <c r="AF331" t="inlineStr"/>
       <c r="AG331" t="b">
         <v>0</v>
       </c>
@@ -39286,51 +39290,48 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>125671054</v>
+        <v>125661738</v>
       </c>
       <c r="B332" t="n">
-        <v>80076</v>
+        <v>92532</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I332" t="inlineStr"/>
-      <c r="J332" t="inlineStr"/>
-      <c r="K332" t="inlineStr"/>
-      <c r="N332" t="inlineStr"/>
       <c r="P332" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>520612</v>
+        <v>520605</v>
       </c>
       <c r="R332" t="n">
-        <v>6934046</v>
+        <v>6933517</v>
       </c>
       <c r="S332" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T332" t="inlineStr">
         <is>
@@ -39368,7 +39369,6 @@
       <c r="AE332" t="b">
         <v>0</v>
       </c>
-      <c r="AF332" t="inlineStr"/>
       <c r="AG332" t="b">
         <v>0</v>
       </c>
@@ -39390,7 +39390,7 @@
         <v>125670914</v>
       </c>
       <c r="B333" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -39487,7 +39487,7 @@
         <v>125670907</v>
       </c>
       <c r="B334" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -39581,32 +39581,32 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>125670921</v>
+        <v>125670916</v>
       </c>
       <c r="B335" t="n">
-        <v>92528</v>
+        <v>80080</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E335" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I335" t="inlineStr"/>
@@ -39616,10 +39616,10 @@
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>520731</v>
+        <v>520803</v>
       </c>
       <c r="R335" t="n">
-        <v>6934038</v>
+        <v>6933448</v>
       </c>
       <c r="S335" t="n">
         <v>25</v>
@@ -39678,52 +39678,48 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>125671021</v>
+        <v>125670921</v>
       </c>
       <c r="B336" t="n">
-        <v>57649</v>
+        <v>92532</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E336" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I336" t="inlineStr"/>
-      <c r="K336" t="inlineStr"/>
-      <c r="L336" t="inlineStr"/>
-      <c r="M336" t="inlineStr"/>
-      <c r="N336" t="inlineStr"/>
       <c r="P336" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>520607</v>
+        <v>520731</v>
       </c>
       <c r="R336" t="n">
-        <v>6934048</v>
+        <v>6934038</v>
       </c>
       <c r="S336" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T336" t="inlineStr">
         <is>
@@ -39753,11 +39749,6 @@
       <c r="AA336" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC336" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD336" t="b">
@@ -39784,32 +39775,32 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>125670903</v>
+        <v>125670909</v>
       </c>
       <c r="B337" t="n">
-        <v>56844</v>
+        <v>80080</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E337" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I337" t="inlineStr"/>
@@ -39819,10 +39810,10 @@
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>520731</v>
+        <v>520754</v>
       </c>
       <c r="R337" t="n">
-        <v>6934042</v>
+        <v>6934006</v>
       </c>
       <c r="S337" t="n">
         <v>25</v>
@@ -39859,7 +39850,7 @@
       </c>
       <c r="AC337" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD337" t="b">
@@ -39886,32 +39877,32 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>125670916</v>
+        <v>125670903</v>
       </c>
       <c r="B338" t="n">
-        <v>80076</v>
+        <v>56848</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E338" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I338" t="inlineStr"/>
@@ -39921,10 +39912,10 @@
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>520803</v>
+        <v>520731</v>
       </c>
       <c r="R338" t="n">
-        <v>6933448</v>
+        <v>6934042</v>
       </c>
       <c r="S338" t="n">
         <v>25</v>
@@ -39957,6 +39948,11 @@
       <c r="AA338" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC338" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD338" t="b">
@@ -39983,10 +39979,10 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>125670909</v>
+        <v>125671021</v>
       </c>
       <c r="B339" t="n">
-        <v>80076</v>
+        <v>57653</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -39994,37 +39990,41 @@
         </is>
       </c>
       <c r="E339" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I339" t="inlineStr"/>
+      <c r="K339" t="inlineStr"/>
+      <c r="L339" t="inlineStr"/>
+      <c r="M339" t="inlineStr"/>
+      <c r="N339" t="inlineStr"/>
       <c r="P339" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>520754</v>
+        <v>520607</v>
       </c>
       <c r="R339" t="n">
-        <v>6934006</v>
+        <v>6934048</v>
       </c>
       <c r="S339" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T339" t="inlineStr">
         <is>
@@ -40058,7 +40058,7 @@
       </c>
       <c r="AC339" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD339" t="b">
@@ -40088,7 +40088,7 @@
         <v>125661442</v>
       </c>
       <c r="B340" t="n">
-        <v>78640</v>
+        <v>78644</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -40182,48 +40182,51 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>125659270</v>
+        <v>125671469</v>
       </c>
       <c r="B341" t="n">
-        <v>92528</v>
+        <v>80080</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E341" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I341" t="inlineStr"/>
+      <c r="J341" t="inlineStr"/>
+      <c r="K341" t="inlineStr"/>
+      <c r="N341" t="inlineStr"/>
       <c r="P341" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>520846</v>
+        <v>520296</v>
       </c>
       <c r="R341" t="n">
-        <v>6933515</v>
+        <v>6933639</v>
       </c>
       <c r="S341" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T341" t="inlineStr">
         <is>
@@ -40261,6 +40264,7 @@
       <c r="AE341" t="b">
         <v>0</v>
       </c>
+      <c r="AF341" t="inlineStr"/>
       <c r="AG341" t="b">
         <v>0</v>
       </c>
@@ -40279,51 +40283,48 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>125671469</v>
+        <v>125659270</v>
       </c>
       <c r="B342" t="n">
-        <v>80076</v>
+        <v>92532</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E342" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I342" t="inlineStr"/>
-      <c r="J342" t="inlineStr"/>
-      <c r="K342" t="inlineStr"/>
-      <c r="N342" t="inlineStr"/>
       <c r="P342" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>520296</v>
+        <v>520846</v>
       </c>
       <c r="R342" t="n">
-        <v>6933639</v>
+        <v>6933515</v>
       </c>
       <c r="S342" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T342" t="inlineStr">
         <is>
@@ -40361,7 +40362,6 @@
       <c r="AE342" t="b">
         <v>0</v>
       </c>
-      <c r="AF342" t="inlineStr"/>
       <c r="AG342" t="b">
         <v>0</v>
       </c>
@@ -40383,7 +40383,7 @@
         <v>125660155</v>
       </c>
       <c r="B343" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>125670923</v>
       </c>
       <c r="B344" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -40574,10 +40574,10 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>125670905</v>
+        <v>125659251</v>
       </c>
       <c r="B345" t="n">
-        <v>80077</v>
+        <v>78735</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -40585,37 +40585,37 @@
         </is>
       </c>
       <c r="E345" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I345" t="inlineStr"/>
       <c r="P345" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q345" t="n">
-        <v>520801</v>
+        <v>520823</v>
       </c>
       <c r="R345" t="n">
-        <v>6933448</v>
+        <v>6933519</v>
       </c>
       <c r="S345" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T345" t="inlineStr">
         <is>
@@ -40671,48 +40671,48 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>125662204</v>
+        <v>125670910</v>
       </c>
       <c r="B346" t="n">
-        <v>91399</v>
+        <v>80080</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E346" t="n">
-        <v>1503</v>
+        <v>6458</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I346" t="inlineStr"/>
       <c r="P346" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q346" t="n">
-        <v>520425</v>
+        <v>520830</v>
       </c>
       <c r="R346" t="n">
-        <v>6933544</v>
+        <v>6933884</v>
       </c>
       <c r="S346" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T346" t="inlineStr">
         <is>
@@ -40768,10 +40768,10 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>125659251</v>
+        <v>125670905</v>
       </c>
       <c r="B347" t="n">
-        <v>78731</v>
+        <v>80081</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -40779,37 +40779,37 @@
         </is>
       </c>
       <c r="E347" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I347" t="inlineStr"/>
       <c r="P347" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q347" t="n">
-        <v>520823</v>
+        <v>520801</v>
       </c>
       <c r="R347" t="n">
-        <v>6933519</v>
+        <v>6933448</v>
       </c>
       <c r="S347" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T347" t="inlineStr">
         <is>
@@ -40865,48 +40865,48 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>125670910</v>
+        <v>125662204</v>
       </c>
       <c r="B348" t="n">
-        <v>80076</v>
+        <v>91403</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E348" t="n">
-        <v>6458</v>
+        <v>1503</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I348" t="inlineStr"/>
       <c r="P348" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q348" t="n">
-        <v>520830</v>
+        <v>520425</v>
       </c>
       <c r="R348" t="n">
-        <v>6933884</v>
+        <v>6933544</v>
       </c>
       <c r="S348" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T348" t="inlineStr">
         <is>
@@ -40965,7 +40965,7 @@
         <v>125671342</v>
       </c>
       <c r="B349" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -41067,7 +41067,7 @@
         <v>125670917</v>
       </c>
       <c r="B350" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -41164,7 +41164,7 @@
         <v>125663708</v>
       </c>
       <c r="B351" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -41267,38 +41267,37 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>125671230</v>
+        <v>125671498</v>
       </c>
       <c r="B352" t="n">
-        <v>98366</v>
+        <v>80080</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E352" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I352" t="inlineStr"/>
       <c r="J352" t="inlineStr"/>
       <c r="K352" t="inlineStr"/>
-      <c r="L352" t="inlineStr"/>
       <c r="N352" t="inlineStr"/>
       <c r="P352" t="inlineStr">
         <is>
@@ -41306,13 +41305,13 @@
         </is>
       </c>
       <c r="Q352" t="n">
-        <v>520549</v>
+        <v>520385</v>
       </c>
       <c r="R352" t="n">
-        <v>6934058</v>
+        <v>6933569</v>
       </c>
       <c r="S352" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T352" t="inlineStr">
         <is>
@@ -41369,10 +41368,10 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>125671498</v>
+        <v>125671434</v>
       </c>
       <c r="B353" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -41407,13 +41406,13 @@
         </is>
       </c>
       <c r="Q353" t="n">
-        <v>520385</v>
+        <v>520364</v>
       </c>
       <c r="R353" t="n">
-        <v>6933569</v>
+        <v>6934008</v>
       </c>
       <c r="S353" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T353" t="inlineStr">
         <is>
@@ -41470,10 +41469,10 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>125671434</v>
+        <v>125661680</v>
       </c>
       <c r="B354" t="n">
-        <v>80076</v>
+        <v>79595</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -41481,40 +41480,37 @@
         </is>
       </c>
       <c r="E354" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I354" t="inlineStr"/>
-      <c r="J354" t="inlineStr"/>
-      <c r="K354" t="inlineStr"/>
-      <c r="N354" t="inlineStr"/>
       <c r="P354" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q354" t="n">
-        <v>520364</v>
+        <v>520639</v>
       </c>
       <c r="R354" t="n">
-        <v>6934008</v>
+        <v>6933509</v>
       </c>
       <c r="S354" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T354" t="inlineStr">
         <is>
@@ -41552,7 +41548,6 @@
       <c r="AE354" t="b">
         <v>0</v>
       </c>
-      <c r="AF354" t="inlineStr"/>
       <c r="AG354" t="b">
         <v>0</v>
       </c>
@@ -41571,10 +41566,10 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>125661680</v>
+        <v>125670901</v>
       </c>
       <c r="B355" t="n">
-        <v>79591</v>
+        <v>91242</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -41582,37 +41577,37 @@
         </is>
       </c>
       <c r="E355" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I355" t="inlineStr"/>
       <c r="P355" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q355" t="n">
-        <v>520639</v>
+        <v>520257</v>
       </c>
       <c r="R355" t="n">
-        <v>6933509</v>
+        <v>6933643</v>
       </c>
       <c r="S355" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T355" t="inlineStr">
         <is>
@@ -41668,48 +41663,52 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>125670901</v>
+        <v>125671230</v>
       </c>
       <c r="B356" t="n">
-        <v>91238</v>
+        <v>98370</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E356" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I356" t="inlineStr"/>
+      <c r="J356" t="inlineStr"/>
+      <c r="K356" t="inlineStr"/>
+      <c r="L356" t="inlineStr"/>
+      <c r="N356" t="inlineStr"/>
       <c r="P356" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q356" t="n">
-        <v>520257</v>
+        <v>520549</v>
       </c>
       <c r="R356" t="n">
-        <v>6933643</v>
+        <v>6934058</v>
       </c>
       <c r="S356" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T356" t="inlineStr">
         <is>
@@ -41747,6 +41746,7 @@
       <c r="AE356" t="b">
         <v>0</v>
       </c>
+      <c r="AF356" t="inlineStr"/>
       <c r="AG356" t="b">
         <v>0</v>
       </c>
@@ -41768,7 +41768,7 @@
         <v>125659241</v>
       </c>
       <c r="B357" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>125670913</v>
       </c>
       <c r="B358" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -41959,38 +41959,37 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>125671157</v>
+        <v>125671278</v>
       </c>
       <c r="B359" t="n">
-        <v>98345</v>
+        <v>80080</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E359" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I359" t="inlineStr"/>
       <c r="J359" t="inlineStr"/>
       <c r="K359" t="inlineStr"/>
-      <c r="L359" t="inlineStr"/>
       <c r="N359" t="inlineStr"/>
       <c r="P359" t="inlineStr">
         <is>
@@ -41998,10 +41997,10 @@
         </is>
       </c>
       <c r="Q359" t="n">
-        <v>520540</v>
+        <v>520511</v>
       </c>
       <c r="R359" t="n">
-        <v>6934055</v>
+        <v>6934025</v>
       </c>
       <c r="S359" t="n">
         <v>10</v>
@@ -42061,10 +42060,10 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>125671278</v>
+        <v>125671098</v>
       </c>
       <c r="B360" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -42099,10 +42098,10 @@
         </is>
       </c>
       <c r="Q360" t="n">
-        <v>520511</v>
+        <v>520578</v>
       </c>
       <c r="R360" t="n">
-        <v>6934025</v>
+        <v>6934069</v>
       </c>
       <c r="S360" t="n">
         <v>10</v>
@@ -42162,10 +42161,10 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>125671098</v>
+        <v>125660786</v>
       </c>
       <c r="B361" t="n">
-        <v>80076</v>
+        <v>78735</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -42173,40 +42172,37 @@
         </is>
       </c>
       <c r="E361" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I361" t="inlineStr"/>
-      <c r="J361" t="inlineStr"/>
-      <c r="K361" t="inlineStr"/>
-      <c r="N361" t="inlineStr"/>
       <c r="P361" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q361" t="n">
-        <v>520578</v>
+        <v>520731</v>
       </c>
       <c r="R361" t="n">
-        <v>6934069</v>
+        <v>6933528</v>
       </c>
       <c r="S361" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T361" t="inlineStr">
         <is>
@@ -42244,7 +42240,6 @@
       <c r="AE361" t="b">
         <v>0</v>
       </c>
-      <c r="AF361" t="inlineStr"/>
       <c r="AG361" t="b">
         <v>0</v>
       </c>
@@ -42263,48 +42258,52 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>125660786</v>
+        <v>125671157</v>
       </c>
       <c r="B362" t="n">
-        <v>78731</v>
+        <v>98349</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E362" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I362" t="inlineStr"/>
+      <c r="J362" t="inlineStr"/>
+      <c r="K362" t="inlineStr"/>
+      <c r="L362" t="inlineStr"/>
+      <c r="N362" t="inlineStr"/>
       <c r="P362" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q362" t="n">
-        <v>520731</v>
+        <v>520540</v>
       </c>
       <c r="R362" t="n">
-        <v>6933528</v>
+        <v>6934055</v>
       </c>
       <c r="S362" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T362" t="inlineStr">
         <is>
@@ -42342,6 +42341,7 @@
       <c r="AE362" t="b">
         <v>0</v>
       </c>
+      <c r="AF362" t="inlineStr"/>
       <c r="AG362" t="b">
         <v>0</v>
       </c>
@@ -42363,7 +42363,7 @@
         <v>125670920</v>
       </c>
       <c r="B363" t="n">
-        <v>105371</v>
+        <v>105384</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -40182,10 +40182,10 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>125671469</v>
+        <v>125660155</v>
       </c>
       <c r="B341" t="n">
-        <v>80080</v>
+        <v>78736</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -40193,40 +40193,37 @@
         </is>
       </c>
       <c r="E341" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I341" t="inlineStr"/>
-      <c r="J341" t="inlineStr"/>
-      <c r="K341" t="inlineStr"/>
-      <c r="N341" t="inlineStr"/>
       <c r="P341" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>520296</v>
+        <v>520786</v>
       </c>
       <c r="R341" t="n">
-        <v>6933639</v>
+        <v>6933540</v>
       </c>
       <c r="S341" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T341" t="inlineStr">
         <is>
@@ -40264,7 +40261,6 @@
       <c r="AE341" t="b">
         <v>0</v>
       </c>
-      <c r="AF341" t="inlineStr"/>
       <c r="AG341" t="b">
         <v>0</v>
       </c>
@@ -40283,48 +40279,51 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>125659270</v>
+        <v>125671469</v>
       </c>
       <c r="B342" t="n">
-        <v>92532</v>
+        <v>80080</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E342" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I342" t="inlineStr"/>
+      <c r="J342" t="inlineStr"/>
+      <c r="K342" t="inlineStr"/>
+      <c r="N342" t="inlineStr"/>
       <c r="P342" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>520846</v>
+        <v>520296</v>
       </c>
       <c r="R342" t="n">
-        <v>6933515</v>
+        <v>6933639</v>
       </c>
       <c r="S342" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T342" t="inlineStr">
         <is>
@@ -40362,6 +40361,7 @@
       <c r="AE342" t="b">
         <v>0</v>
       </c>
+      <c r="AF342" t="inlineStr"/>
       <c r="AG342" t="b">
         <v>0</v>
       </c>
@@ -40380,32 +40380,32 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>125660155</v>
+        <v>125659270</v>
       </c>
       <c r="B343" t="n">
-        <v>78736</v>
+        <v>92532</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E343" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I343" t="inlineStr"/>
@@ -40415,10 +40415,10 @@
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>520786</v>
+        <v>520846</v>
       </c>
       <c r="R343" t="n">
-        <v>6933540</v>
+        <v>6933515</v>
       </c>
       <c r="S343" t="n">
         <v>20</v>
@@ -40574,10 +40574,10 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>125659251</v>
+        <v>125670905</v>
       </c>
       <c r="B345" t="n">
-        <v>78735</v>
+        <v>80081</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -40585,37 +40585,37 @@
         </is>
       </c>
       <c r="E345" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I345" t="inlineStr"/>
       <c r="P345" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q345" t="n">
-        <v>520823</v>
+        <v>520801</v>
       </c>
       <c r="R345" t="n">
-        <v>6933519</v>
+        <v>6933448</v>
       </c>
       <c r="S345" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T345" t="inlineStr">
         <is>
@@ -40671,48 +40671,48 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>125670910</v>
+        <v>125662204</v>
       </c>
       <c r="B346" t="n">
-        <v>80080</v>
+        <v>91403</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E346" t="n">
-        <v>6458</v>
+        <v>1503</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I346" t="inlineStr"/>
       <c r="P346" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q346" t="n">
-        <v>520830</v>
+        <v>520425</v>
       </c>
       <c r="R346" t="n">
-        <v>6933884</v>
+        <v>6933544</v>
       </c>
       <c r="S346" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T346" t="inlineStr">
         <is>
@@ -40768,10 +40768,10 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>125670905</v>
+        <v>125659251</v>
       </c>
       <c r="B347" t="n">
-        <v>80081</v>
+        <v>78735</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -40779,37 +40779,37 @@
         </is>
       </c>
       <c r="E347" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I347" t="inlineStr"/>
       <c r="P347" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q347" t="n">
-        <v>520801</v>
+        <v>520823</v>
       </c>
       <c r="R347" t="n">
-        <v>6933448</v>
+        <v>6933519</v>
       </c>
       <c r="S347" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T347" t="inlineStr">
         <is>
@@ -40865,48 +40865,48 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>125662204</v>
+        <v>125670910</v>
       </c>
       <c r="B348" t="n">
-        <v>91403</v>
+        <v>80080</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E348" t="n">
-        <v>1503</v>
+        <v>6458</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I348" t="inlineStr"/>
       <c r="P348" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q348" t="n">
-        <v>520425</v>
+        <v>520830</v>
       </c>
       <c r="R348" t="n">
-        <v>6933544</v>
+        <v>6933884</v>
       </c>
       <c r="S348" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T348" t="inlineStr">
         <is>
@@ -41267,37 +41267,38 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>125671498</v>
+        <v>125671230</v>
       </c>
       <c r="B352" t="n">
-        <v>80080</v>
+        <v>98370</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E352" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I352" t="inlineStr"/>
       <c r="J352" t="inlineStr"/>
       <c r="K352" t="inlineStr"/>
+      <c r="L352" t="inlineStr"/>
       <c r="N352" t="inlineStr"/>
       <c r="P352" t="inlineStr">
         <is>
@@ -41305,13 +41306,13 @@
         </is>
       </c>
       <c r="Q352" t="n">
-        <v>520385</v>
+        <v>520549</v>
       </c>
       <c r="R352" t="n">
-        <v>6933569</v>
+        <v>6934058</v>
       </c>
       <c r="S352" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T352" t="inlineStr">
         <is>
@@ -41368,10 +41369,10 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>125671434</v>
+        <v>125670901</v>
       </c>
       <c r="B353" t="n">
-        <v>80080</v>
+        <v>91242</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -41379,40 +41380,37 @@
         </is>
       </c>
       <c r="E353" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I353" t="inlineStr"/>
-      <c r="J353" t="inlineStr"/>
-      <c r="K353" t="inlineStr"/>
-      <c r="N353" t="inlineStr"/>
       <c r="P353" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberg, Mpd</t>
         </is>
       </c>
       <c r="Q353" t="n">
-        <v>520364</v>
+        <v>520257</v>
       </c>
       <c r="R353" t="n">
-        <v>6934008</v>
+        <v>6933643</v>
       </c>
       <c r="S353" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T353" t="inlineStr">
         <is>
@@ -41450,7 +41448,6 @@
       <c r="AE353" t="b">
         <v>0</v>
       </c>
-      <c r="AF353" t="inlineStr"/>
       <c r="AG353" t="b">
         <v>0</v>
       </c>
@@ -41469,10 +41466,10 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>125661680</v>
+        <v>125671498</v>
       </c>
       <c r="B354" t="n">
-        <v>79595</v>
+        <v>80080</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -41480,37 +41477,40 @@
         </is>
       </c>
       <c r="E354" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I354" t="inlineStr"/>
+      <c r="J354" t="inlineStr"/>
+      <c r="K354" t="inlineStr"/>
+      <c r="N354" t="inlineStr"/>
       <c r="P354" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q354" t="n">
-        <v>520639</v>
+        <v>520385</v>
       </c>
       <c r="R354" t="n">
-        <v>6933509</v>
+        <v>6933569</v>
       </c>
       <c r="S354" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T354" t="inlineStr">
         <is>
@@ -41548,6 +41548,7 @@
       <c r="AE354" t="b">
         <v>0</v>
       </c>
+      <c r="AF354" t="inlineStr"/>
       <c r="AG354" t="b">
         <v>0</v>
       </c>
@@ -41566,10 +41567,10 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>125670901</v>
+        <v>125671434</v>
       </c>
       <c r="B355" t="n">
-        <v>91242</v>
+        <v>80080</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -41577,37 +41578,40 @@
         </is>
       </c>
       <c r="E355" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I355" t="inlineStr"/>
+      <c r="J355" t="inlineStr"/>
+      <c r="K355" t="inlineStr"/>
+      <c r="N355" t="inlineStr"/>
       <c r="P355" t="inlineStr">
         <is>
-          <t>Grinsjöberg, Mpd</t>
+          <t>Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q355" t="n">
-        <v>520257</v>
+        <v>520364</v>
       </c>
       <c r="R355" t="n">
-        <v>6933643</v>
+        <v>6934008</v>
       </c>
       <c r="S355" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T355" t="inlineStr">
         <is>
@@ -41645,6 +41649,7 @@
       <c r="AE355" t="b">
         <v>0</v>
       </c>
+      <c r="AF355" t="inlineStr"/>
       <c r="AG355" t="b">
         <v>0</v>
       </c>
@@ -41663,52 +41668,48 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>125671230</v>
+        <v>125661680</v>
       </c>
       <c r="B356" t="n">
-        <v>98370</v>
+        <v>79595</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E356" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I356" t="inlineStr"/>
-      <c r="J356" t="inlineStr"/>
-      <c r="K356" t="inlineStr"/>
-      <c r="L356" t="inlineStr"/>
-      <c r="N356" t="inlineStr"/>
       <c r="P356" t="inlineStr">
         <is>
-          <t>Grinsjöberget, Mpd</t>
+          <t>Grinsjöberget, Grinsjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q356" t="n">
-        <v>520549</v>
+        <v>520639</v>
       </c>
       <c r="R356" t="n">
-        <v>6934058</v>
+        <v>6933509</v>
       </c>
       <c r="S356" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T356" t="inlineStr">
         <is>
@@ -41746,7 +41747,6 @@
       <c r="AE356" t="b">
         <v>0</v>
       </c>
-      <c r="AF356" t="inlineStr"/>
       <c r="AG356" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -39982,7 +39982,7 @@
         <v>125671021</v>
       </c>
       <c r="B339" t="n">
-        <v>57653</v>
+        <v>57658</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -39982,7 +39982,7 @@
         <v>125671021</v>
       </c>
       <c r="B339" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -39982,7 +39982,7 @@
         <v>125671021</v>
       </c>
       <c r="B339" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -39982,7 +39982,7 @@
         <v>125671021</v>
       </c>
       <c r="B339" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -39982,7 +39982,7 @@
         <v>125671021</v>
       </c>
       <c r="B339" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -39982,7 +39982,7 @@
         <v>125671021</v>
       </c>
       <c r="B339" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>

--- a/artfynd/A 64518-2023 artfynd.xlsx
+++ b/artfynd/A 64518-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY409"/>
+  <dimension ref="A1:AZ409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95469</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117615056</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117624125</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574154</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1180,6 +1205,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130780</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1296,6 +1326,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130781</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1402,6 +1437,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130782</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1499,6 +1539,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122277244</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1596,6 +1641,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125661442</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1702,6 +1752,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/196936</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1813,6 +1868,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/255000</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1910,6 +1970,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117624144</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2021,6 +2086,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/358642</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2132,6 +2202,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/358643</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2238,6 +2313,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/361514</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2344,6 +2424,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/361515</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2441,6 +2526,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117614921</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2538,6 +2628,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117624128</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2635,6 +2730,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117624129</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2732,6 +2832,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125670901</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2843,6 +2948,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/362656</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2954,6 +3064,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/339432</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3065,6 +3180,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/355738</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3176,6 +3296,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/355739</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3282,6 +3407,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/355740</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3379,6 +3509,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125662204</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3499,6 +3634,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/948407</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3605,6 +3745,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1082461</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3702,6 +3847,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117616097</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3813,6 +3963,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/597825</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3910,6 +4065,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117619504</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4007,6 +4167,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122277238</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4104,6 +4269,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125670905</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4224,6 +4394,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1073608</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4339,6 +4514,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1145038</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4455,6 +4635,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1145039</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4570,6 +4755,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1145040</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4685,6 +4875,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1145042</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4800,6 +4995,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1145043</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4915,6 +5115,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1145044</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5035,6 +5240,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1175427</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5155,6 +5365,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1175428</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5275,6 +5490,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1175432</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5391,6 +5611,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1175433</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5502,6 +5727,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1284599</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5612,6 +5842,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1284600</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5722,6 +5957,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1284601</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5832,6 +6072,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1284602</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5942,6 +6187,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1284603</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6072,6 +6322,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1284604</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6192,6 +6447,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1284605</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6312,6 +6572,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1284606</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6432,6 +6697,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1284607</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6552,6 +6822,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1284608</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6672,6 +6947,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1284609</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6792,6 +7072,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1284610</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6912,6 +7197,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1284611</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7032,6 +7322,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1284612</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7152,6 +7447,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1284613</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7272,6 +7572,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1284614</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7392,6 +7697,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1286252</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7512,6 +7822,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1286253</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7632,6 +7947,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1286254</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7747,6 +8067,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1286255</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7867,6 +8192,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1286256</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7987,6 +8317,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1286257</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8102,6 +8437,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1286260</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8217,6 +8557,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1286261</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8323,6 +8668,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1286262</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8443,6 +8793,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1286263</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8553,6 +8908,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1286264</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8668,6 +9028,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1286268</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8788,6 +9153,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1286269</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8898,6 +9268,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1286270</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8995,6 +9370,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125659270</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9092,6 +9472,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125661738</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9189,6 +9574,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125670924</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9309,6 +9699,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1391864</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9406,6 +9801,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117620923</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9504,6 +9904,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117624159</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9629,6 +10034,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1475607</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9735,6 +10145,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1557045</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9832,6 +10247,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117614361</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9934,6 +10354,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117614566</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10036,6 +10461,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117624132</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10133,6 +10563,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117624133</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10239,6 +10674,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1678501</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10350,6 +10790,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1745752</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10465,6 +10910,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1745753</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10571,6 +11021,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1842121</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10677,6 +11132,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1842122</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10783,6 +11243,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1842123</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10884,6 +11349,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1842124</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10995,6 +11465,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1842125</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11101,6 +11576,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1842126</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11207,6 +11687,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1842127</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11318,6 +11803,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1842128</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11429,6 +11919,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1842129</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11540,6 +12035,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1842130</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11651,6 +12151,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1842131</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11762,6 +12267,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1842132</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11873,6 +12383,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1842133</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11989,6 +12504,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1842134</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12095,6 +12615,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1842135</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12201,6 +12726,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1842136</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12307,6 +12837,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1842137</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12413,6 +12948,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1842138</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12519,6 +13059,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1842139</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12630,6 +13175,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1842140</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12741,6 +13291,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1842141</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12852,6 +13407,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1842142</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12958,6 +13518,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1842143</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13064,6 +13629,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1842144</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13170,6 +13740,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1842145</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13276,6 +13851,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1842146</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13387,6 +13967,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1842370</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13484,6 +14069,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117615181</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13581,6 +14171,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117616189</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13678,6 +14273,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117619065</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13775,6 +14375,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117619600</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13872,6 +14477,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117619628</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13969,6 +14579,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117619862</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14071,6 +14686,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117619968</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14168,6 +14788,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117624155</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14265,6 +14890,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117624156</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14362,6 +14992,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117624158</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14459,6 +15094,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120593206</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14556,6 +15196,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122277246</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14658,6 +15303,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574221</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14760,6 +15410,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574222</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14862,6 +15517,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574223</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14959,6 +15619,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574226</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15070,6 +15735,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2166846</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15186,6 +15856,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2166847</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15302,6 +15977,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1976278</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15418,6 +16098,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1976279</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15515,6 +16200,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117614268</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15612,6 +16302,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117615396</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15709,6 +16404,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117615933</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15806,6 +16506,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117617526</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15903,6 +16608,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117624146</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16000,6 +16710,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117624148</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16097,6 +16812,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125659251</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16194,6 +16914,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125660786</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16291,6 +17016,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574190</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16388,6 +17118,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574191</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16485,6 +17220,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574192</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16582,6 +17322,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574193</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16679,6 +17424,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117615776</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16776,6 +17526,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122277252</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16873,6 +17628,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125659241</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16970,6 +17730,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125660766</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17067,6 +17832,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125661680</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17178,6 +17948,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1893070</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -17279,6 +18054,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1893072</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -17385,6 +18165,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1893073</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -17505,6 +18290,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1893074</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17602,6 +18392,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125670906</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17713,6 +18508,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964542</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17829,6 +18629,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964543</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -17940,6 +18745,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964544</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -18051,6 +18861,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964545</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -18162,6 +18977,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964546</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -18282,6 +19102,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964547</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -18383,6 +19208,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964548</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -18489,6 +19319,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964549</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -18605,6 +19440,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964550</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -18711,6 +19551,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964552</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -18822,6 +19667,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964555</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -18928,6 +19778,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964556</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -19039,6 +19894,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964557</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -19154,6 +20014,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964558</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -19260,6 +20125,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964559</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -19375,6 +20245,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964560</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -19490,6 +20365,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964563</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -19596,6 +20476,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964564</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -19702,6 +20587,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964565</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -19813,6 +20703,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964566</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -19919,6 +20814,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964899</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -20030,6 +20930,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964900</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -20141,6 +21046,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964901</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -20252,6 +21162,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964902</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -20358,6 +21273,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964903</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -20469,6 +21389,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964904</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -20575,6 +21500,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964905</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -20681,6 +21611,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964906</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -20792,6 +21727,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964907</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -20898,6 +21838,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964908</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -21004,6 +21949,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964909</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -21115,6 +22065,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964910</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -21221,6 +22176,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964911</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -21318,6 +22278,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117614781</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -21415,6 +22380,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117615235</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -21512,6 +22482,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117615266</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -21609,6 +22584,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117615300</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -21706,6 +22686,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117615611</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -21803,6 +22788,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117616001</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -21900,6 +22890,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117616632</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -21997,6 +22992,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117616723</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -22094,6 +23094,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117617034</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -22191,6 +23196,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117617897</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -22288,6 +23298,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117618578</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -22385,6 +23400,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117618841</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -22482,6 +23502,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117618946</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -22579,6 +23604,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117618968</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -22676,6 +23706,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117619317</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -22773,6 +23808,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117619423</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -22870,6 +23910,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117619522</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -22967,6 +24012,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117619662</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -23064,6 +24114,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117619989</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -23161,6 +24216,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117620029</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -23263,6 +24323,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117624136</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -23360,6 +24425,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117624138</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -23457,6 +24527,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117624140</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -23554,6 +24629,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117624141</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -23651,6 +24731,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117624143</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -23748,6 +24833,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122277242</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -23845,6 +24935,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122277254</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -23947,6 +25042,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125662951</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -24044,6 +25144,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125663906</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -24146,6 +25251,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125670908</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -24248,6 +25358,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125670909</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -24345,6 +25460,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125670910</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -24442,6 +25562,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125670914</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -24539,6 +25664,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125670916</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -24640,6 +25770,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125671434</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -24741,6 +25876,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125671469</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -24842,6 +25982,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125671498</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -24944,6 +26089,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574169</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -25046,6 +26196,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574170</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -25143,6 +26298,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574173</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -25240,6 +26400,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574174</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -25337,6 +26502,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574175</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -25434,6 +26604,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574176</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -25531,6 +26706,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574177</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -25628,6 +26808,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574178</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -25725,6 +26910,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574179</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -25822,6 +27012,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574180</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -25919,6 +27114,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574181</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -26016,6 +27216,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574182</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -26127,6 +27332,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2011027</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -26238,6 +27448,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2063952</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -26344,6 +27559,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2063953</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -26455,6 +27675,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2063954</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -26552,6 +27777,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117619372</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -26658,6 +27888,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1936920</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -26755,6 +27990,11 @@
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117618861</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -26857,6 +28097,11 @@
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117615974</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -26954,6 +28199,11 @@
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117616157</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -27056,6 +28306,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117617145</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -27158,6 +28413,11 @@
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125662218</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -27264,6 +28524,11 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125663708</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -27361,6 +28626,11 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125670904</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -27463,6 +28733,11 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574157</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -27565,6 +28840,11 @@
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125661236</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -27671,6 +28951,11 @@
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122277223</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -27777,6 +29062,11 @@
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122277240</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -27883,6 +29173,11 @@
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122277249</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -27985,6 +29280,11 @@
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117614215</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -28087,6 +29387,11 @@
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117614799</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -28189,6 +29494,11 @@
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117615105</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -28291,6 +29601,11 @@
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117624131</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -28397,6 +29712,11 @@
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122277230</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -28494,6 +29814,11 @@
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117616751</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -28591,6 +29916,11 @@
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574187</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -28702,6 +30032,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3038079</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -28808,6 +30143,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3038080</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -28914,6 +30254,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3038081</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -29025,6 +30370,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3038082</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -29131,6 +30481,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3038083</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -29242,6 +30597,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3038088</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -29348,6 +30708,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3038089</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -29454,6 +30819,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3038090</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -29560,6 +30930,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3038091</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -29666,6 +31041,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3038092</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -29772,6 +31152,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3038093</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -29883,6 +31268,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3038094</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -29994,6 +31384,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3038095</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -30091,6 +31486,11 @@
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117615007</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -30188,6 +31588,11 @@
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117615486</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -30285,6 +31690,11 @@
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117616291</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -30382,6 +31792,11 @@
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117617202</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -30479,6 +31894,11 @@
         </is>
       </c>
       <c r="AY284" t="inlineStr"/>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117618638</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -30576,6 +31996,11 @@
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117624124</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -30673,6 +32098,11 @@
         </is>
       </c>
       <c r="AY286" t="inlineStr"/>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117624150</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -30770,6 +32200,11 @@
         </is>
       </c>
       <c r="AY287" t="inlineStr"/>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117624151</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -30867,6 +32302,11 @@
         </is>
       </c>
       <c r="AY288" t="inlineStr"/>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117624152</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -30964,6 +32404,11 @@
         </is>
       </c>
       <c r="AY289" t="inlineStr"/>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117624153</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -31061,6 +32506,11 @@
         </is>
       </c>
       <c r="AY290" t="inlineStr"/>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117624154</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -31162,6 +32612,11 @@
         </is>
       </c>
       <c r="AY291" t="inlineStr"/>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120593384</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -31259,6 +32714,11 @@
         </is>
       </c>
       <c r="AY292" t="inlineStr"/>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122277221</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -31356,6 +32816,11 @@
         </is>
       </c>
       <c r="AY293" t="inlineStr"/>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122277225</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -31453,6 +32918,11 @@
         </is>
       </c>
       <c r="AY294" t="inlineStr"/>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122277227</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -31550,6 +33020,11 @@
         </is>
       </c>
       <c r="AY295" t="inlineStr"/>
+      <c r="AZ295" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122277234</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -31647,6 +33122,11 @@
         </is>
       </c>
       <c r="AY296" t="inlineStr"/>
+      <c r="AZ296" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125661898</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -31744,6 +33224,11 @@
         </is>
       </c>
       <c r="AY297" t="inlineStr"/>
+      <c r="AZ297" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125670917</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -31841,6 +33326,11 @@
         </is>
       </c>
       <c r="AY298" t="inlineStr"/>
+      <c r="AZ298" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125670918</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -31938,6 +33428,11 @@
         </is>
       </c>
       <c r="AY299" t="inlineStr"/>
+      <c r="AZ299" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125670919</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -32040,6 +33535,11 @@
         </is>
       </c>
       <c r="AY300" t="inlineStr"/>
+      <c r="AZ300" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125671342</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -32137,6 +33637,11 @@
         </is>
       </c>
       <c r="AY301" t="inlineStr"/>
+      <c r="AZ301" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574194</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -32234,6 +33739,11 @@
         </is>
       </c>
       <c r="AY302" t="inlineStr"/>
+      <c r="AZ302" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574195</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -32331,6 +33841,11 @@
         </is>
       </c>
       <c r="AY303" t="inlineStr"/>
+      <c r="AZ303" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574196</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -32428,6 +33943,11 @@
         </is>
       </c>
       <c r="AY304" t="inlineStr"/>
+      <c r="AZ304" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574197</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -32525,6 +34045,11 @@
         </is>
       </c>
       <c r="AY305" t="inlineStr"/>
+      <c r="AZ305" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574198</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -32622,6 +34147,11 @@
         </is>
       </c>
       <c r="AY306" t="inlineStr"/>
+      <c r="AZ306" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574199</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -32719,6 +34249,11 @@
         </is>
       </c>
       <c r="AY307" t="inlineStr"/>
+      <c r="AZ307" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574200</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -32816,6 +34351,11 @@
         </is>
       </c>
       <c r="AY308" t="inlineStr"/>
+      <c r="AZ308" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574202</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -32913,6 +34453,11 @@
         </is>
       </c>
       <c r="AY309" t="inlineStr"/>
+      <c r="AZ309" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574203</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -33010,6 +34555,11 @@
         </is>
       </c>
       <c r="AY310" t="inlineStr"/>
+      <c r="AZ310" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574204</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -33107,6 +34657,11 @@
         </is>
       </c>
       <c r="AY311" t="inlineStr"/>
+      <c r="AZ311" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574205</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -33204,6 +34759,11 @@
         </is>
       </c>
       <c r="AY312" t="inlineStr"/>
+      <c r="AZ312" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574206</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -33301,6 +34861,11 @@
         </is>
       </c>
       <c r="AY313" t="inlineStr"/>
+      <c r="AZ313" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574207</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -33398,6 +34963,11 @@
         </is>
       </c>
       <c r="AY314" t="inlineStr"/>
+      <c r="AZ314" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574208</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -33495,6 +35065,11 @@
         </is>
       </c>
       <c r="AY315" t="inlineStr"/>
+      <c r="AZ315" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574209</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -33592,6 +35167,11 @@
         </is>
       </c>
       <c r="AY316" t="inlineStr"/>
+      <c r="AZ316" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574210</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -33689,6 +35269,11 @@
         </is>
       </c>
       <c r="AY317" t="inlineStr"/>
+      <c r="AZ317" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574211</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -33786,6 +35371,11 @@
         </is>
       </c>
       <c r="AY318" t="inlineStr"/>
+      <c r="AZ318" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574212</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -33883,6 +35473,11 @@
         </is>
       </c>
       <c r="AY319" t="inlineStr"/>
+      <c r="AZ319" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574214</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -33980,6 +35575,11 @@
         </is>
       </c>
       <c r="AY320" t="inlineStr"/>
+      <c r="AZ320" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117617321</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -34077,6 +35677,11 @@
         </is>
       </c>
       <c r="AY321" t="inlineStr"/>
+      <c r="AZ321" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117619202</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -34174,6 +35779,11 @@
         </is>
       </c>
       <c r="AY322" t="inlineStr"/>
+      <c r="AZ322" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125670920</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -34280,6 +35890,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ323" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4147774</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -34377,6 +35992,11 @@
         </is>
       </c>
       <c r="AY324" t="inlineStr"/>
+      <c r="AZ324" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117618235</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -34474,6 +36094,11 @@
         </is>
       </c>
       <c r="AY325" t="inlineStr"/>
+      <c r="AZ325" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120593379</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -34571,6 +36196,11 @@
         </is>
       </c>
       <c r="AY326" t="inlineStr"/>
+      <c r="AZ326" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117619582</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -34668,6 +36298,11 @@
         </is>
       </c>
       <c r="AY327" t="inlineStr"/>
+      <c r="AZ327" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574161</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -34765,6 +36400,11 @@
         </is>
       </c>
       <c r="AY328" t="inlineStr"/>
+      <c r="AZ328" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117619891</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -34862,6 +36502,11 @@
         </is>
       </c>
       <c r="AY329" t="inlineStr"/>
+      <c r="AZ329" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120593385</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -34959,6 +36604,11 @@
         </is>
       </c>
       <c r="AY330" t="inlineStr"/>
+      <c r="AZ330" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125660155</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -35056,6 +36706,11 @@
         </is>
       </c>
       <c r="AY331" t="inlineStr"/>
+      <c r="AZ331" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125670907</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -35153,6 +36808,11 @@
         </is>
       </c>
       <c r="AY332" t="inlineStr"/>
+      <c r="AZ332" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574168</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -35259,6 +36919,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ333" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6692620</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -35356,6 +37021,11 @@
         </is>
       </c>
       <c r="AY334" t="inlineStr"/>
+      <c r="AZ334" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117614676</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -35453,6 +37123,11 @@
         </is>
       </c>
       <c r="AY335" t="inlineStr"/>
+      <c r="AZ335" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574217</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -35550,6 +37225,11 @@
         </is>
       </c>
       <c r="AY336" t="inlineStr"/>
+      <c r="AZ336" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117620594</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -35656,6 +37336,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ337" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130783</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -35753,6 +37438,11 @@
         </is>
       </c>
       <c r="AY338" t="inlineStr"/>
+      <c r="AZ338" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117620347</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -35850,6 +37540,11 @@
         </is>
       </c>
       <c r="AY339" t="inlineStr"/>
+      <c r="AZ339" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117624135</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -35951,6 +37646,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ340" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/362530</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -36048,6 +37748,11 @@
         </is>
       </c>
       <c r="AY341" t="inlineStr"/>
+      <c r="AZ341" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117620395</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -36154,6 +37859,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ342" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/871838</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -36260,6 +37970,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ343" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/871839</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -36380,6 +38095,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ344" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1145045</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -36490,6 +38210,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ345" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1145046</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -36605,6 +38330,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ346" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1145047</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -36720,6 +38450,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ347" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1145048</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -36835,6 +38570,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ348" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1175434</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -36950,6 +38690,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ349" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1175435</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -37065,6 +38810,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ350" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1286265</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -37180,6 +38930,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ351" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1286266</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -37300,6 +39055,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ352" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1286267</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -37397,6 +39157,11 @@
         </is>
       </c>
       <c r="AY353" t="inlineStr"/>
+      <c r="AZ353" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125670921</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -37494,6 +39259,11 @@
         </is>
       </c>
       <c r="AY354" t="inlineStr"/>
+      <c r="AZ354" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125670922</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -37591,6 +39361,11 @@
         </is>
       </c>
       <c r="AY355" t="inlineStr"/>
+      <c r="AZ355" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125670923</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -37688,6 +39463,11 @@
         </is>
       </c>
       <c r="AY356" t="inlineStr"/>
+      <c r="AZ356" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574244</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -37794,6 +39574,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ357" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1842147</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -37900,6 +39685,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ358" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1842148</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -38002,6 +39792,11 @@
         </is>
       </c>
       <c r="AY359" t="inlineStr"/>
+      <c r="AZ359" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574220</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -38099,6 +39894,11 @@
         </is>
       </c>
       <c r="AY360" t="inlineStr"/>
+      <c r="AZ360" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117620214</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -38205,6 +40005,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ361" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964561</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -38320,6 +40125,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ362" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964562</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -38426,6 +40236,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ363" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964912</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -38532,6 +40347,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ364" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964913</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -38638,6 +40458,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ365" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964914</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -38744,6 +40569,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ366" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964915</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -38850,6 +40680,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ367" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964916</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -38966,6 +40801,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ368" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1965208</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -39072,6 +40912,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ369" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1965209</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -39192,6 +41037,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ370" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1965210</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -39298,6 +41148,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ371" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1965212</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -39404,6 +41259,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ372" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1965213</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -39519,6 +41379,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ373" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1965215</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -39625,6 +41490,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ374" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1965216</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -39745,6 +41615,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ375" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1965217</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -39856,6 +41731,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ376" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1965218</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -39962,6 +41842,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ377" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1965220</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -40068,6 +41953,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ378" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1965221</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -40165,6 +42055,11 @@
         </is>
       </c>
       <c r="AY379" t="inlineStr"/>
+      <c r="AZ379" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125670912</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -40262,6 +42157,11 @@
         </is>
       </c>
       <c r="AY380" t="inlineStr"/>
+      <c r="AZ380" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125670913</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -40363,6 +42263,11 @@
         </is>
       </c>
       <c r="AY381" t="inlineStr"/>
+      <c r="AZ381" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125671054</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -40464,6 +42369,11 @@
         </is>
       </c>
       <c r="AY382" t="inlineStr"/>
+      <c r="AZ382" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125671098</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -40565,6 +42475,11 @@
         </is>
       </c>
       <c r="AY383" t="inlineStr"/>
+      <c r="AZ383" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125671278</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -40662,6 +42577,11 @@
         </is>
       </c>
       <c r="AY384" t="inlineStr"/>
+      <c r="AZ384" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574171</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -40759,6 +42679,11 @@
         </is>
       </c>
       <c r="AY385" t="inlineStr"/>
+      <c r="AZ385" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574172</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -40865,6 +42790,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ386" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2063955</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -40971,6 +42901,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ387" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2063956</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -41077,6 +43012,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ388" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2014609</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -41181,6 +43121,11 @@
       <c r="AY389" t="inlineStr">
         <is>
           <t>Steget Före</t>
+        </is>
+      </c>
+      <c r="AZ389" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2014610</t>
         </is>
       </c>
     </row>
@@ -41289,6 +43234,11 @@
         </is>
       </c>
       <c r="AY390" t="inlineStr"/>
+      <c r="AZ390" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125671021</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -41391,6 +43341,11 @@
         </is>
       </c>
       <c r="AY391" t="inlineStr"/>
+      <c r="AZ391" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125670903</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -41492,6 +43447,11 @@
         </is>
       </c>
       <c r="AY392" t="inlineStr"/>
+      <c r="AZ392" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125671391</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -41594,6 +43554,11 @@
         </is>
       </c>
       <c r="AY393" t="inlineStr"/>
+      <c r="AZ393" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574158</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -41700,6 +43665,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ394" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3038096</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -41806,6 +43776,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ395" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3038097</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -41912,6 +43887,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ396" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3038098</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -42023,6 +44003,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ397" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3038099</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -42129,6 +44114,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ398" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3038100</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -42235,6 +44225,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ399" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3038101</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -42341,6 +44336,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ400" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3038709</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -42438,6 +44438,11 @@
         </is>
       </c>
       <c r="AY401" t="inlineStr"/>
+      <c r="AZ401" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117620495</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -42535,6 +44540,11 @@
         </is>
       </c>
       <c r="AY402" t="inlineStr"/>
+      <c r="AZ402" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117620535</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -42632,6 +44642,11 @@
         </is>
       </c>
       <c r="AY403" t="inlineStr"/>
+      <c r="AZ403" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117624149</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -42734,6 +44749,11 @@
         </is>
       </c>
       <c r="AY404" t="inlineStr"/>
+      <c r="AZ404" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125671157</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -42836,6 +44856,11 @@
         </is>
       </c>
       <c r="AY405" t="inlineStr"/>
+      <c r="AZ405" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125671307</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -42933,6 +44958,11 @@
         </is>
       </c>
       <c r="AY406" t="inlineStr"/>
+      <c r="AZ406" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117620580</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -43039,6 +45069,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ407" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4222806</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -43143,6 +45178,11 @@
       <c r="AY408" t="inlineStr">
         <is>
           <t>Steget Före</t>
+        </is>
+      </c>
+      <c r="AZ408" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4388624</t>
         </is>
       </c>
     </row>
@@ -43247,8 +45287,423 @@
         </is>
       </c>
       <c r="AY409" t="inlineStr"/>
+      <c r="AZ409" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125671230</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ301" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ302" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ303" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ304" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ305" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ306" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ307" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ308" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ309" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ310" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ311" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ312" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ313" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ314" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ315" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ316" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ317" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ318" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ319" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ320" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ321" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ322" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ323" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ324" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ325" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ326" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ327" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ328" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ329" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ330" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ331" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ332" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ333" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ334" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ335" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ336" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ337" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ338" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ339" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ340" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ341" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ342" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ343" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ344" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ345" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ346" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ347" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ348" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ349" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ350" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ351" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ352" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ353" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ354" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ355" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ356" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ357" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ358" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ359" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ360" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ361" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ362" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ363" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ364" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ365" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ366" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ367" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ368" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ369" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ370" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ371" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ372" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ373" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ374" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ375" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ376" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ377" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ378" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ379" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ380" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ381" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ382" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ383" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ384" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ385" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ386" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ387" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ388" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ389" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ390" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ391" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ392" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ393" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ394" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ395" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ396" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ397" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ398" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ399" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ400" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ401" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ402" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ403" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ404" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ405" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ406" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ407" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ408" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ409" r:id="rId408"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>